--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="1">
   <si>
     <t xml:space="preserve">✅</t>
   </si>
@@ -3910,9 +3910,12 @@
         <v>3214</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="n">
         <v>215</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E215" s="2" t="n">
         <f aca="false">A215 +1000</f>
@@ -3961,9 +3964,12 @@
         <v>3217</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="n">
         <v>218</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E218" s="2" t="n">
         <f aca="false">A218 +1000</f>
@@ -4318,9 +4324,12 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="n">
         <v>239</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E239" s="2" t="n">
         <f aca="false">A239 +1000</f>
@@ -4743,9 +4752,12 @@
         <v>3263</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="n">
         <v>264</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E264" s="2" t="n">
         <f aca="false">A264 +1000</f>
@@ -5270,9 +5282,12 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="n">
         <v>295</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E295" s="2" t="n">
         <f aca="false">A295 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="1">
   <si>
     <t xml:space="preserve">✅</t>
   </si>
@@ -124,7 +124,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5914,9 +5914,12 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="n">
         <v>332</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E332" s="2" t="n">
         <f aca="false">A332 +1000</f>
@@ -6169,9 +6172,12 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="n">
         <v>347</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E347" s="2" t="n">
         <f aca="false">A347 +1000</f>
@@ -6611,9 +6617,12 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="n">
         <v>373</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E373" s="2" t="n">
         <f aca="false">A373 +1000</f>
@@ -6696,9 +6705,12 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="n">
         <v>378</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E378" s="2" t="n">
         <f aca="false">A378 +1000</f>
@@ -7189,9 +7201,12 @@
         <v>3406</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="n">
         <v>407</v>
+      </c>
+      <c r="B407" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E407" s="2" t="n">
         <f aca="false">A407 +1000</f>
@@ -7410,9 +7425,12 @@
         <v>3419</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="n">
         <v>420</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E420" s="2" t="n">
         <f aca="false">A420 +1000</f>
@@ -7937,9 +7955,12 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="n">
         <v>451</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E451" s="2" t="n">
         <f aca="false">A451 +1000</f>
@@ -8430,9 +8451,12 @@
         <v>3479</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="n">
         <v>480</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E480" s="2" t="n">
         <f aca="false">A480 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="1">
   <si>
     <t xml:space="preserve">✅</t>
   </si>
@@ -37,7 +37,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -59,7 +58,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1037,7 +1035,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>46</v>
       </c>
@@ -1045,6 +1043,9 @@
         <f aca="false">A46 +1000</f>
         <v>1046</v>
       </c>
+      <c r="F46" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="I46" s="2" t="n">
         <f aca="false">E46 +1000</f>
         <v>2046</v>
@@ -1938,7 +1939,7 @@
         <v>3098</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
         <v>99</v>
       </c>
@@ -1950,6 +1951,9 @@
         <f aca="false">E99 +1000</f>
         <v>2099</v>
       </c>
+      <c r="J99" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M99" s="2" t="n">
         <f aca="false">I99 +1000</f>
         <v>3099</v>
@@ -4188,7 +4192,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="n">
         <v>231</v>
       </c>
@@ -4200,6 +4204,9 @@
         <f aca="false">E231 +1000</f>
         <v>2231</v>
       </c>
+      <c r="J231" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M231" s="2" t="n">
         <f aca="false">I231 +1000</f>
         <v>3231</v>
@@ -4771,6 +4778,9 @@
         <f aca="false">I264 +1000</f>
         <v>3264</v>
       </c>
+      <c r="N264" s="3" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="n">
@@ -5676,7 +5686,7 @@
         <v>3317</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="n">
         <v>318</v>
       </c>
@@ -5692,6 +5702,9 @@
         <f aca="false">I318 +1000</f>
         <v>3318</v>
       </c>
+      <c r="N318" s="3" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="n">
@@ -5968,7 +5981,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="n">
         <v>335</v>
       </c>
@@ -5980,6 +5993,9 @@
         <f aca="false">E335 +1000</f>
         <v>2335</v>
       </c>
+      <c r="J335" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M335" s="2" t="n">
         <f aca="false">I335 +1000</f>
         <v>3335</v>
@@ -6002,7 +6018,7 @@
         <v>3336</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="n">
         <v>337</v>
       </c>
@@ -6010,6 +6026,9 @@
         <f aca="false">A337 +1000</f>
         <v>1337</v>
       </c>
+      <c r="F337" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="I337" s="2" t="n">
         <f aca="false">E337 +1000</f>
         <v>2337</v>
@@ -6345,7 +6364,7 @@
         <v>3356</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="n">
         <v>357</v>
       </c>
@@ -6357,6 +6376,9 @@
         <f aca="false">E357 +1000</f>
         <v>2357</v>
       </c>
+      <c r="J357" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M357" s="2" t="n">
         <f aca="false">I357 +1000</f>
         <v>3357</v>
@@ -8179,7 +8201,7 @@
         <v>3463</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="n">
         <v>464</v>
       </c>
@@ -8187,6 +8209,9 @@
         <f aca="false">A464 +1000</f>
         <v>1464</v>
       </c>
+      <c r="F464" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="I464" s="2" t="n">
         <f aca="false">E464 +1000</f>
         <v>2464</v>
@@ -8794,7 +8819,7 @@
         <v>3499</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="n">
         <v>500</v>
       </c>
@@ -8806,6 +8831,9 @@
         <f aca="false">E500 +1000</f>
         <v>2500</v>
       </c>
+      <c r="J500" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M500" s="2" t="n">
         <f aca="false">I500 +1000</f>
         <v>3500</v>
@@ -8896,9 +8924,12 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="n">
         <v>506</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E506" s="2" t="n">
         <f aca="false">A506 +1000</f>
@@ -8913,7 +8944,7 @@
         <v>3506</v>
       </c>
     </row>
-    <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="n">
         <v>507</v>
       </c>
@@ -8929,6 +8960,9 @@
         <f aca="false">I507 +1000</f>
         <v>3507</v>
       </c>
+      <c r="N507" s="3" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="n">
@@ -9780,7 +9814,7 @@
         <v>3557</v>
       </c>
     </row>
-    <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="n">
         <v>558</v>
       </c>
@@ -9792,6 +9826,9 @@
         <f aca="false">E558 +1000</f>
         <v>2558</v>
       </c>
+      <c r="J558" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M558" s="2" t="n">
         <f aca="false">I558 +1000</f>
         <v>3558</v>
@@ -12245,9 +12282,12 @@
         <v>3702</v>
       </c>
     </row>
-    <row r="703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="n">
         <v>703</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E703" s="2" t="n">
         <f aca="false">A703 +1000</f>
@@ -16852,7 +16892,7 @@
         <v>3973</v>
       </c>
     </row>
-    <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="974" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="n">
         <v>974</v>
       </c>
@@ -16863,6 +16903,9 @@
       <c r="I974" s="2" t="n">
         <f aca="false">E974 +1000</f>
         <v>2974</v>
+      </c>
+      <c r="J974" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="M974" s="2" t="n">
         <f aca="false">I974 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="1">
   <si>
     <t xml:space="preserve">✅</t>
   </si>
@@ -37,6 +37,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -58,6 +59,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1046,6 +1048,9 @@
       <c r="F46" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="G46" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="I46" s="2" t="n">
         <f aca="false">E46 +1000</f>
         <v>2046</v>
@@ -1954,6 +1959,9 @@
       <c r="J99" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K99" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M99" s="2" t="n">
         <f aca="false">I99 +1000</f>
         <v>3099</v>
@@ -4207,6 +4215,9 @@
       <c r="J231" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K231" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M231" s="2" t="n">
         <f aca="false">I231 +1000</f>
         <v>3231</v>
@@ -4781,6 +4792,9 @@
       <c r="N264" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="O264" s="3" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="n">
@@ -5705,6 +5719,9 @@
       <c r="N318" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="O318" s="3" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="n">
@@ -5996,6 +6013,9 @@
       <c r="J335" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K335" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M335" s="2" t="n">
         <f aca="false">I335 +1000</f>
         <v>3335</v>
@@ -6029,6 +6049,9 @@
       <c r="F337" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="G337" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="I337" s="2" t="n">
         <f aca="false">E337 +1000</f>
         <v>2337</v>
@@ -6379,6 +6402,9 @@
       <c r="J357" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K357" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M357" s="2" t="n">
         <f aca="false">I357 +1000</f>
         <v>3357</v>
@@ -8212,6 +8238,9 @@
       <c r="F464" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="G464" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="I464" s="2" t="n">
         <f aca="false">E464 +1000</f>
         <v>2464</v>
@@ -8834,6 +8863,9 @@
       <c r="J500" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K500" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M500" s="2" t="n">
         <f aca="false">I500 +1000</f>
         <v>3500</v>
@@ -8931,6 +8963,9 @@
       <c r="B506" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="C506" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E506" s="2" t="n">
         <f aca="false">A506 +1000</f>
         <v>1506</v>
@@ -8963,6 +8998,9 @@
       <c r="N507" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="O507" s="3" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="n">
@@ -9829,6 +9867,9 @@
       <c r="J558" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="K558" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="M558" s="2" t="n">
         <f aca="false">I558 +1000</f>
         <v>3558</v>
@@ -12289,6 +12330,9 @@
       <c r="B703" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="C703" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E703" s="2" t="n">
         <f aca="false">A703 +1000</f>
         <v>1703</v>
@@ -16905,6 +16949,9 @@
         <v>2974</v>
       </c>
       <c r="J974" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K974" s="3" t="s">
         <v>0</v>
       </c>
       <c r="M974" s="2" t="n">

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="1001">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -3116,15 +3116,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3666,6 +3666,9 @@
       <c r="B23" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C23" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E23" s="2" t="n">
         <f aca="false">A23 +1000</f>
         <v>1022</v>
@@ -7134,9 +7137,7 @@
       <c r="A215" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B215" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B215" s="3"/>
       <c r="E215" s="2" t="n">
         <f aca="false">A215 +1000</f>
         <v>1214</v>
@@ -7158,6 +7159,9 @@
       <c r="B216" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C216" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E216" s="2" t="n">
         <f aca="false">A216 +1000</f>
         <v>1215</v>
@@ -7197,6 +7201,9 @@
       <c r="B218" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C218" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E218" s="2" t="n">
         <f aca="false">A218 +1000</f>
         <v>1217</v>
@@ -7584,6 +7591,9 @@
       <c r="B239" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C239" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E239" s="2" t="n">
         <f aca="false">A239 +1000</f>
         <v>1238</v>
@@ -8037,6 +8047,9 @@
       <c r="B264" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C264" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E264" s="2" t="n">
         <f aca="false">A264 +1000</f>
         <v>1263</v>
@@ -8601,9 +8614,7 @@
       <c r="A295" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B295" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
         <f aca="false">A295 +1000</f>
         <v>1294</v>
@@ -9279,6 +9290,9 @@
       <c r="B332" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C332" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E332" s="2" t="n">
         <f aca="false">A332 +1000</f>
         <v>1331</v>
@@ -9561,9 +9575,7 @@
       <c r="A347" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B347" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
         <f aca="false">A347 +1000</f>
         <v>1346</v>
@@ -10041,6 +10053,9 @@
       <c r="B373" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C373" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E373" s="2" t="n">
         <f aca="false">A373 +1000</f>
         <v>1372</v>
@@ -10134,6 +10149,9 @@
       <c r="B378" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C378" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E378" s="2" t="n">
         <f aca="false">A378 +1000</f>
         <v>1377</v>
@@ -10659,6 +10677,9 @@
       <c r="B407" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C407" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E407" s="2" t="n">
         <f aca="false">A407 +1000</f>
         <v>1406</v>
@@ -10894,6 +10915,9 @@
         <v>420</v>
       </c>
       <c r="B420" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C420" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E420" s="2" t="n">

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -11481,6 +11481,9 @@
       <c r="B451" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="C451" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E451" s="2" t="n">
         <f aca="false">A451 +1000</f>
         <v>1450</v>
@@ -12009,9 +12012,7 @@
       <c r="A480" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B480" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
         <f aca="false">A480 +1000</f>
         <v>1479</v>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="1004">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -718,6 +718,9 @@
     <t xml:space="preserve">0230</t>
   </si>
   <si>
+    <t xml:space="preserve">inOrder</t>
+  </si>
+  <si>
     <t xml:space="preserve">0231</t>
   </si>
   <si>
@@ -1891,6 +1894,9 @@
     <t xml:space="preserve">0621</t>
   </si>
   <si>
+    <t xml:space="preserve">Use Formula</t>
+  </si>
+  <si>
     <t xml:space="preserve">0622</t>
   </si>
   <si>
@@ -2564,6 +2570,9 @@
   </si>
   <si>
     <t xml:space="preserve">0846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map</t>
   </si>
   <si>
     <t xml:space="preserve">0847</t>
@@ -3687,6 +3696,12 @@
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="B24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E24" s="2" t="n">
         <f aca="false">A24 +1000</f>
         <v>1023</v>
@@ -7438,6 +7453,15 @@
       <c r="A231" s="1" t="s">
         <v>231</v>
       </c>
+      <c r="B231" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D231" s="0" t="s">
+        <v>232</v>
+      </c>
       <c r="E231" s="2" t="n">
         <f aca="false">A231 +1000</f>
         <v>1230</v>
@@ -7460,7 +7484,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">A232 +1000</f>
@@ -7478,7 +7502,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">A233 +1000</f>
@@ -7496,7 +7520,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">A234 +1000</f>
@@ -7514,7 +7538,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">A235 +1000</f>
@@ -7532,7 +7556,7 @@
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">A236 +1000</f>
@@ -7550,7 +7574,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">A237 +1000</f>
@@ -7568,7 +7592,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">A238 +1000</f>
@@ -7586,7 +7610,7 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>23</v>
@@ -7610,7 +7634,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">A240 +1000</f>
@@ -7628,7 +7652,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">A241 +1000</f>
@@ -7646,7 +7670,7 @@
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">A242 +1000</f>
@@ -7664,7 +7688,7 @@
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">A243 +1000</f>
@@ -7682,7 +7706,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">A244 +1000</f>
@@ -7700,7 +7724,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">A245 +1000</f>
@@ -7718,7 +7742,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E246" s="2" t="n">
         <f aca="false">A246 +1000</f>
@@ -7736,7 +7760,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E247" s="2" t="n">
         <f aca="false">A247 +1000</f>
@@ -7754,7 +7778,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E248" s="2" t="n">
         <f aca="false">A248 +1000</f>
@@ -7772,7 +7796,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E249" s="2" t="n">
         <f aca="false">A249 +1000</f>
@@ -7790,7 +7814,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E250" s="2" t="n">
         <f aca="false">A250 +1000</f>
@@ -7808,7 +7832,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E251" s="2" t="n">
         <f aca="false">A251 +1000</f>
@@ -7826,7 +7850,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E252" s="2" t="n">
         <f aca="false">A252 +1000</f>
@@ -7844,7 +7868,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E253" s="2" t="n">
         <f aca="false">A253 +1000</f>
@@ -7862,7 +7886,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E254" s="2" t="n">
         <f aca="false">A254 +1000</f>
@@ -7880,7 +7904,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E255" s="2" t="n">
         <f aca="false">A255 +1000</f>
@@ -7898,7 +7922,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E256" s="2" t="n">
         <f aca="false">A256 +1000</f>
@@ -7916,7 +7940,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E257" s="2" t="n">
         <f aca="false">A257 +1000</f>
@@ -7934,7 +7958,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E258" s="2" t="n">
         <f aca="false">A258 +1000</f>
@@ -7952,7 +7976,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E259" s="2" t="n">
         <f aca="false">A259 +1000</f>
@@ -7970,7 +7994,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E260" s="2" t="n">
         <f aca="false">A260 +1000</f>
@@ -7988,7 +8012,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E261" s="2" t="n">
         <f aca="false">A261 +1000</f>
@@ -8006,7 +8030,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E262" s="2" t="n">
         <f aca="false">A262 +1000</f>
@@ -8024,7 +8048,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E263" s="2" t="n">
         <f aca="false">A263 +1000</f>
@@ -8042,7 +8066,7 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>23</v>
@@ -8072,7 +8096,7 @@
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E265" s="2" t="n">
         <f aca="false">A265 +1000</f>
@@ -8090,7 +8114,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E266" s="2" t="n">
         <f aca="false">A266 +1000</f>
@@ -8108,7 +8132,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E267" s="2" t="n">
         <f aca="false">A267 +1000</f>
@@ -8126,7 +8150,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E268" s="2" t="n">
         <f aca="false">A268 +1000</f>
@@ -8144,7 +8168,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E269" s="2" t="n">
         <f aca="false">A269 +1000</f>
@@ -8162,7 +8186,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E270" s="2" t="n">
         <f aca="false">A270 +1000</f>
@@ -8180,7 +8204,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E271" s="2" t="n">
         <f aca="false">A271 +1000</f>
@@ -8198,7 +8222,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E272" s="2" t="n">
         <f aca="false">A272 +1000</f>
@@ -8216,7 +8240,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E273" s="2" t="n">
         <f aca="false">A273 +1000</f>
@@ -8234,7 +8258,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E274" s="2" t="n">
         <f aca="false">A274 +1000</f>
@@ -8252,7 +8276,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E275" s="2" t="n">
         <f aca="false">A275 +1000</f>
@@ -8270,7 +8294,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E276" s="2" t="n">
         <f aca="false">A276 +1000</f>
@@ -8288,7 +8312,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E277" s="2" t="n">
         <f aca="false">A277 +1000</f>
@@ -8306,7 +8330,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E278" s="2" t="n">
         <f aca="false">A278 +1000</f>
@@ -8324,7 +8348,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E279" s="2" t="n">
         <f aca="false">A279 +1000</f>
@@ -8342,7 +8366,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E280" s="2" t="n">
         <f aca="false">A280 +1000</f>
@@ -8360,7 +8384,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E281" s="2" t="n">
         <f aca="false">A281 +1000</f>
@@ -8378,7 +8402,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E282" s="2" t="n">
         <f aca="false">A282 +1000</f>
@@ -8396,7 +8420,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E283" s="2" t="n">
         <f aca="false">A283 +1000</f>
@@ -8414,7 +8438,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E284" s="2" t="n">
         <f aca="false">A284 +1000</f>
@@ -8432,7 +8456,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E285" s="2" t="n">
         <f aca="false">A285 +1000</f>
@@ -8450,7 +8474,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E286" s="2" t="n">
         <f aca="false">A286 +1000</f>
@@ -8468,7 +8492,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E287" s="2" t="n">
         <f aca="false">A287 +1000</f>
@@ -8486,7 +8510,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E288" s="2" t="n">
         <f aca="false">A288 +1000</f>
@@ -8504,7 +8528,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E289" s="2" t="n">
         <f aca="false">A289 +1000</f>
@@ -8522,7 +8546,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E290" s="2" t="n">
         <f aca="false">A290 +1000</f>
@@ -8540,7 +8564,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E291" s="2" t="n">
         <f aca="false">A291 +1000</f>
@@ -8558,7 +8582,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E292" s="2" t="n">
         <f aca="false">A292 +1000</f>
@@ -8576,7 +8600,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E293" s="2" t="n">
         <f aca="false">A293 +1000</f>
@@ -8594,7 +8618,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E294" s="2" t="n">
         <f aca="false">A294 +1000</f>
@@ -8612,7 +8636,7 @@
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
@@ -8631,7 +8655,13 @@
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E296" s="2" t="n">
         <f aca="false">A296 +1000</f>
@@ -8649,7 +8679,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E297" s="2" t="n">
         <f aca="false">A297 +1000</f>
@@ -8667,7 +8697,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E298" s="2" t="n">
         <f aca="false">A298 +1000</f>
@@ -8685,7 +8715,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E299" s="2" t="n">
         <f aca="false">A299 +1000</f>
@@ -8703,7 +8733,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E300" s="2" t="n">
         <f aca="false">A300 +1000</f>
@@ -8721,7 +8751,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E301" s="2" t="n">
         <f aca="false">A301 +1000</f>
@@ -8739,7 +8769,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E302" s="2" t="n">
         <f aca="false">A302 +1000</f>
@@ -8757,7 +8787,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E303" s="2" t="n">
         <f aca="false">A303 +1000</f>
@@ -8775,7 +8805,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E304" s="2" t="n">
         <f aca="false">A304 +1000</f>
@@ -8793,7 +8823,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E305" s="2" t="n">
         <f aca="false">A305 +1000</f>
@@ -8811,7 +8841,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E306" s="2" t="n">
         <f aca="false">A306 +1000</f>
@@ -8829,7 +8859,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E307" s="2" t="n">
         <f aca="false">A307 +1000</f>
@@ -8847,7 +8877,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E308" s="2" t="n">
         <f aca="false">A308 +1000</f>
@@ -8865,7 +8895,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E309" s="2" t="n">
         <f aca="false">A309 +1000</f>
@@ -8883,7 +8913,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E310" s="2" t="n">
         <f aca="false">A310 +1000</f>
@@ -8901,7 +8931,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E311" s="2" t="n">
         <f aca="false">A311 +1000</f>
@@ -8919,7 +8949,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E312" s="2" t="n">
         <f aca="false">A312 +1000</f>
@@ -8937,7 +8967,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E313" s="2" t="n">
         <f aca="false">A313 +1000</f>
@@ -8955,7 +8985,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E314" s="2" t="n">
         <f aca="false">A314 +1000</f>
@@ -8973,7 +9003,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E315" s="2" t="n">
         <f aca="false">A315 +1000</f>
@@ -8991,7 +9021,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E316" s="2" t="n">
         <f aca="false">A316 +1000</f>
@@ -9009,7 +9039,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E317" s="2" t="n">
         <f aca="false">A317 +1000</f>
@@ -9027,7 +9057,7 @@
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E318" s="2" t="n">
         <f aca="false">A318 +1000</f>
@@ -9051,7 +9081,7 @@
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E319" s="2" t="n">
         <f aca="false">A319 +1000</f>
@@ -9069,7 +9099,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E320" s="2" t="n">
         <f aca="false">A320 +1000</f>
@@ -9087,7 +9117,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E321" s="2" t="n">
         <f aca="false">A321 +1000</f>
@@ -9105,7 +9135,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E322" s="2" t="n">
         <f aca="false">A322 +1000</f>
@@ -9123,7 +9153,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E323" s="2" t="n">
         <f aca="false">A323 +1000</f>
@@ -9141,7 +9171,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E324" s="2" t="n">
         <f aca="false">A324 +1000</f>
@@ -9159,7 +9189,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E325" s="2" t="n">
         <f aca="false">A325 +1000</f>
@@ -9177,7 +9207,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E326" s="2" t="n">
         <f aca="false">A326 +1000</f>
@@ -9195,7 +9225,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E327" s="2" t="n">
         <f aca="false">A327 +1000</f>
@@ -9213,7 +9243,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E328" s="2" t="n">
         <f aca="false">A328 +1000</f>
@@ -9231,7 +9261,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E329" s="2" t="n">
         <f aca="false">A329 +1000</f>
@@ -9249,7 +9279,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E330" s="2" t="n">
         <f aca="false">A330 +1000</f>
@@ -9267,7 +9297,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E331" s="2" t="n">
         <f aca="false">A331 +1000</f>
@@ -9285,7 +9315,7 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>23</v>
@@ -9309,7 +9339,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E333" s="2" t="n">
         <f aca="false">A333 +1000</f>
@@ -9327,7 +9357,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E334" s="2" t="n">
         <f aca="false">A334 +1000</f>
@@ -9345,7 +9375,7 @@
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E335" s="2" t="n">
         <f aca="false">A335 +1000</f>
@@ -9369,7 +9399,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E336" s="2" t="n">
         <f aca="false">A336 +1000</f>
@@ -9387,7 +9417,7 @@
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E337" s="2" t="n">
         <f aca="false">A337 +1000</f>
@@ -9411,7 +9441,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E338" s="2" t="n">
         <f aca="false">A338 +1000</f>
@@ -9429,7 +9459,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E339" s="2" t="n">
         <f aca="false">A339 +1000</f>
@@ -9447,7 +9477,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E340" s="2" t="n">
         <f aca="false">A340 +1000</f>
@@ -9465,7 +9495,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E341" s="2" t="n">
         <f aca="false">A341 +1000</f>
@@ -9483,7 +9513,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E342" s="2" t="n">
         <f aca="false">A342 +1000</f>
@@ -9501,7 +9531,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E343" s="2" t="n">
         <f aca="false">A343 +1000</f>
@@ -9519,7 +9549,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E344" s="2" t="n">
         <f aca="false">A344 +1000</f>
@@ -9537,7 +9567,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E345" s="2" t="n">
         <f aca="false">A345 +1000</f>
@@ -9555,7 +9585,7 @@
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E346" s="2" t="n">
         <f aca="false">A346 +1000</f>
@@ -9573,7 +9603,7 @@
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
@@ -9592,7 +9622,13 @@
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E348" s="2" t="n">
         <f aca="false">A348 +1000</f>
@@ -9610,7 +9646,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E349" s="2" t="n">
         <f aca="false">A349 +1000</f>
@@ -9628,7 +9664,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E350" s="2" t="n">
         <f aca="false">A350 +1000</f>
@@ -9646,7 +9682,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E351" s="2" t="n">
         <f aca="false">A351 +1000</f>
@@ -9664,7 +9700,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E352" s="2" t="n">
         <f aca="false">A352 +1000</f>
@@ -9682,7 +9718,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E353" s="2" t="n">
         <f aca="false">A353 +1000</f>
@@ -9700,7 +9736,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E354" s="2" t="n">
         <f aca="false">A354 +1000</f>
@@ -9718,7 +9754,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E355" s="2" t="n">
         <f aca="false">A355 +1000</f>
@@ -9736,7 +9772,13 @@
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E356" s="2" t="n">
         <f aca="false">A356 +1000</f>
@@ -9754,7 +9796,7 @@
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E357" s="2" t="n">
         <f aca="false">A357 +1000</f>
@@ -9778,7 +9820,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E358" s="2" t="n">
         <f aca="false">A358 +1000</f>
@@ -9796,7 +9838,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E359" s="2" t="n">
         <f aca="false">A359 +1000</f>
@@ -9814,7 +9856,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E360" s="2" t="n">
         <f aca="false">A360 +1000</f>
@@ -9832,7 +9874,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E361" s="2" t="n">
         <f aca="false">A361 +1000</f>
@@ -9850,7 +9892,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E362" s="2" t="n">
         <f aca="false">A362 +1000</f>
@@ -9868,7 +9910,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E363" s="2" t="n">
         <f aca="false">A363 +1000</f>
@@ -9886,7 +9928,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E364" s="2" t="n">
         <f aca="false">A364 +1000</f>
@@ -9904,7 +9946,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E365" s="2" t="n">
         <f aca="false">A365 +1000</f>
@@ -9922,7 +9964,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E366" s="2" t="n">
         <f aca="false">A366 +1000</f>
@@ -9940,7 +9982,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E367" s="2" t="n">
         <f aca="false">A367 +1000</f>
@@ -9958,7 +10000,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E368" s="2" t="n">
         <f aca="false">A368 +1000</f>
@@ -9976,7 +10018,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E369" s="2" t="n">
         <f aca="false">A369 +1000</f>
@@ -9994,7 +10036,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E370" s="2" t="n">
         <f aca="false">A370 +1000</f>
@@ -10012,7 +10054,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E371" s="2" t="n">
         <f aca="false">A371 +1000</f>
@@ -10030,7 +10072,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E372" s="2" t="n">
         <f aca="false">A372 +1000</f>
@@ -10048,7 +10090,7 @@
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>23</v>
@@ -10072,7 +10114,7 @@
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E374" s="2" t="n">
         <f aca="false">A374 +1000</f>
@@ -10090,7 +10132,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E375" s="2" t="n">
         <f aca="false">A375 +1000</f>
@@ -10108,7 +10150,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E376" s="2" t="n">
         <f aca="false">A376 +1000</f>
@@ -10126,7 +10168,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E377" s="2" t="n">
         <f aca="false">A377 +1000</f>
@@ -10144,7 +10186,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>23</v>
@@ -10168,7 +10210,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E379" s="2" t="n">
         <f aca="false">A379 +1000</f>
@@ -10186,7 +10228,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E380" s="2" t="n">
         <f aca="false">A380 +1000</f>
@@ -10204,7 +10246,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E381" s="2" t="n">
         <f aca="false">A381 +1000</f>
@@ -10222,7 +10264,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E382" s="2" t="n">
         <f aca="false">A382 +1000</f>
@@ -10240,7 +10282,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E383" s="2" t="n">
         <f aca="false">A383 +1000</f>
@@ -10258,7 +10300,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E384" s="2" t="n">
         <f aca="false">A384 +1000</f>
@@ -10276,7 +10318,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E385" s="2" t="n">
         <f aca="false">A385 +1000</f>
@@ -10294,7 +10336,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E386" s="2" t="n">
         <f aca="false">A386 +1000</f>
@@ -10312,7 +10354,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E387" s="2" t="n">
         <f aca="false">A387 +1000</f>
@@ -10330,7 +10372,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E388" s="2" t="n">
         <f aca="false">A388 +1000</f>
@@ -10348,7 +10390,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E389" s="2" t="n">
         <f aca="false">A389 +1000</f>
@@ -10366,7 +10408,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E390" s="2" t="n">
         <f aca="false">A390 +1000</f>
@@ -10384,7 +10426,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E391" s="2" t="n">
         <f aca="false">A391 +1000</f>
@@ -10402,7 +10444,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E392" s="2" t="n">
         <f aca="false">A392 +1000</f>
@@ -10420,7 +10462,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E393" s="2" t="n">
         <f aca="false">A393 +1000</f>
@@ -10438,7 +10480,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E394" s="2" t="n">
         <f aca="false">A394 +1000</f>
@@ -10456,7 +10498,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E395" s="2" t="n">
         <f aca="false">A395 +1000</f>
@@ -10474,7 +10516,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E396" s="2" t="n">
         <f aca="false">A396 +1000</f>
@@ -10492,7 +10534,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E397" s="2" t="n">
         <f aca="false">A397 +1000</f>
@@ -10510,7 +10552,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E398" s="2" t="n">
         <f aca="false">A398 +1000</f>
@@ -10528,7 +10570,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E399" s="2" t="n">
         <f aca="false">A399 +1000</f>
@@ -10546,7 +10588,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E400" s="2" t="n">
         <f aca="false">A400 +1000</f>
@@ -10564,7 +10606,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E401" s="2" t="n">
         <f aca="false">A401 +1000</f>
@@ -10582,7 +10624,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E402" s="2" t="n">
         <f aca="false">A402 +1000</f>
@@ -10600,7 +10642,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E403" s="2" t="n">
         <f aca="false">A403 +1000</f>
@@ -10618,7 +10660,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E404" s="2" t="n">
         <f aca="false">A404 +1000</f>
@@ -10636,7 +10678,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E405" s="2" t="n">
         <f aca="false">A405 +1000</f>
@@ -10654,7 +10696,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E406" s="2" t="n">
         <f aca="false">A406 +1000</f>
@@ -10672,7 +10714,7 @@
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>23</v>
@@ -10696,7 +10738,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E408" s="2" t="n">
         <f aca="false">A408 +1000</f>
@@ -10714,7 +10756,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E409" s="2" t="n">
         <f aca="false">A409 +1000</f>
@@ -10732,7 +10774,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E410" s="2" t="n">
         <f aca="false">A410 +1000</f>
@@ -10750,7 +10792,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E411" s="2" t="n">
         <f aca="false">A411 +1000</f>
@@ -10768,7 +10810,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E412" s="2" t="n">
         <f aca="false">A412 +1000</f>
@@ -10786,7 +10828,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E413" s="2" t="n">
         <f aca="false">A413 +1000</f>
@@ -10804,7 +10846,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E414" s="2" t="n">
         <f aca="false">A414 +1000</f>
@@ -10822,7 +10864,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E415" s="2" t="n">
         <f aca="false">A415 +1000</f>
@@ -10840,7 +10882,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E416" s="2" t="n">
         <f aca="false">A416 +1000</f>
@@ -10858,7 +10900,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E417" s="2" t="n">
         <f aca="false">A417 +1000</f>
@@ -10876,7 +10918,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E418" s="2" t="n">
         <f aca="false">A418 +1000</f>
@@ -10894,7 +10936,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E419" s="2" t="n">
         <f aca="false">A419 +1000</f>
@@ -10912,7 +10954,7 @@
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>23</v>
@@ -10936,7 +10978,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E421" s="2" t="n">
         <f aca="false">A421 +1000</f>
@@ -10954,7 +10996,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
@@ -10972,7 +11014,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E423" s="2" t="n">
         <f aca="false">A423 +1000</f>
@@ -10990,7 +11032,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E424" s="2" t="n">
         <f aca="false">A424 +1000</f>
@@ -11008,7 +11050,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E425" s="2" t="n">
         <f aca="false">A425 +1000</f>
@@ -11026,7 +11068,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E426" s="2" t="n">
         <f aca="false">A426 +1000</f>
@@ -11044,7 +11086,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E427" s="2" t="n">
         <f aca="false">A427 +1000</f>
@@ -11062,7 +11104,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E428" s="2" t="n">
         <f aca="false">A428 +1000</f>
@@ -11080,7 +11122,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E429" s="2" t="n">
         <f aca="false">A429 +1000</f>
@@ -11098,7 +11140,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E430" s="2" t="n">
         <f aca="false">A430 +1000</f>
@@ -11116,7 +11158,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E431" s="2" t="n">
         <f aca="false">A431 +1000</f>
@@ -11134,7 +11176,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E432" s="2" t="n">
         <f aca="false">A432 +1000</f>
@@ -11152,7 +11194,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E433" s="2" t="n">
         <f aca="false">A433 +1000</f>
@@ -11170,7 +11212,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E434" s="2" t="n">
         <f aca="false">A434 +1000</f>
@@ -11188,7 +11230,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E435" s="2" t="n">
         <f aca="false">A435 +1000</f>
@@ -11206,7 +11248,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E436" s="2" t="n">
         <f aca="false">A436 +1000</f>
@@ -11224,7 +11266,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E437" s="2" t="n">
         <f aca="false">A437 +1000</f>
@@ -11242,7 +11284,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E438" s="2" t="n">
         <f aca="false">A438 +1000</f>
@@ -11260,7 +11302,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E439" s="2" t="n">
         <f aca="false">A439 +1000</f>
@@ -11278,7 +11320,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E440" s="2" t="n">
         <f aca="false">A440 +1000</f>
@@ -11296,7 +11338,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E441" s="2" t="n">
         <f aca="false">A441 +1000</f>
@@ -11314,7 +11356,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E442" s="2" t="n">
         <f aca="false">A442 +1000</f>
@@ -11332,7 +11374,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E443" s="2" t="n">
         <f aca="false">A443 +1000</f>
@@ -11350,7 +11392,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E444" s="2" t="n">
         <f aca="false">A444 +1000</f>
@@ -11368,7 +11410,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E445" s="2" t="n">
         <f aca="false">A445 +1000</f>
@@ -11386,7 +11428,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E446" s="2" t="n">
         <f aca="false">A446 +1000</f>
@@ -11404,7 +11446,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E447" s="2" t="n">
         <f aca="false">A447 +1000</f>
@@ -11422,7 +11464,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E448" s="2" t="n">
         <f aca="false">A448 +1000</f>
@@ -11440,7 +11482,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E449" s="2" t="n">
         <f aca="false">A449 +1000</f>
@@ -11458,7 +11500,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E450" s="2" t="n">
         <f aca="false">A450 +1000</f>
@@ -11476,7 +11518,7 @@
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>23</v>
@@ -11500,7 +11542,7 @@
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E452" s="2" t="n">
         <f aca="false">A452 +1000</f>
@@ -11518,7 +11560,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E453" s="2" t="n">
         <f aca="false">A453 +1000</f>
@@ -11536,7 +11578,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E454" s="2" t="n">
         <f aca="false">A454 +1000</f>
@@ -11554,7 +11596,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E455" s="2" t="n">
         <f aca="false">A455 +1000</f>
@@ -11572,7 +11614,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E456" s="2" t="n">
         <f aca="false">A456 +1000</f>
@@ -11590,7 +11632,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E457" s="2" t="n">
         <f aca="false">A457 +1000</f>
@@ -11608,7 +11650,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E458" s="2" t="n">
         <f aca="false">A458 +1000</f>
@@ -11626,7 +11668,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E459" s="2" t="n">
         <f aca="false">A459 +1000</f>
@@ -11644,7 +11686,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E460" s="2" t="n">
         <f aca="false">A460 +1000</f>
@@ -11662,7 +11704,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E461" s="2" t="n">
         <f aca="false">A461 +1000</f>
@@ -11680,7 +11722,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E462" s="2" t="n">
         <f aca="false">A462 +1000</f>
@@ -11698,7 +11740,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E463" s="2" t="n">
         <f aca="false">A463 +1000</f>
@@ -11716,7 +11758,7 @@
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E464" s="2" t="n">
         <f aca="false">A464 +1000</f>
@@ -11740,7 +11782,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E465" s="2" t="n">
         <f aca="false">A465 +1000</f>
@@ -11758,7 +11800,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E466" s="2" t="n">
         <f aca="false">A466 +1000</f>
@@ -11776,7 +11818,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E467" s="2" t="n">
         <f aca="false">A467 +1000</f>
@@ -11794,7 +11836,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E468" s="2" t="n">
         <f aca="false">A468 +1000</f>
@@ -11812,7 +11854,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E469" s="2" t="n">
         <f aca="false">A469 +1000</f>
@@ -11830,7 +11872,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E470" s="2" t="n">
         <f aca="false">A470 +1000</f>
@@ -11848,7 +11890,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E471" s="2" t="n">
         <f aca="false">A471 +1000</f>
@@ -11866,7 +11908,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E472" s="2" t="n">
         <f aca="false">A472 +1000</f>
@@ -11884,7 +11926,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E473" s="2" t="n">
         <f aca="false">A473 +1000</f>
@@ -11902,7 +11944,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E474" s="2" t="n">
         <f aca="false">A474 +1000</f>
@@ -11920,7 +11962,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E475" s="2" t="n">
         <f aca="false">A475 +1000</f>
@@ -11938,7 +11980,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E476" s="2" t="n">
         <f aca="false">A476 +1000</f>
@@ -11956,7 +11998,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E477" s="2" t="n">
         <f aca="false">A477 +1000</f>
@@ -11974,7 +12016,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E478" s="2" t="n">
         <f aca="false">A478 +1000</f>
@@ -11992,7 +12034,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E479" s="2" t="n">
         <f aca="false">A479 +1000</f>
@@ -12010,7 +12052,7 @@
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
@@ -12029,7 +12071,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E481" s="2" t="n">
         <f aca="false">A481 +1000</f>
@@ -12047,7 +12089,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E482" s="2" t="n">
         <f aca="false">A482 +1000</f>
@@ -12065,7 +12107,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E483" s="2" t="n">
         <f aca="false">A483 +1000</f>
@@ -12083,7 +12125,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E484" s="2" t="n">
         <f aca="false">A484 +1000</f>
@@ -12101,7 +12143,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E485" s="2" t="n">
         <f aca="false">A485 +1000</f>
@@ -12119,7 +12161,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E486" s="2" t="n">
         <f aca="false">A486 +1000</f>
@@ -12137,7 +12179,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E487" s="2" t="n">
         <f aca="false">A487 +1000</f>
@@ -12155,7 +12197,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E488" s="2" t="n">
         <f aca="false">A488 +1000</f>
@@ -12173,7 +12215,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E489" s="2" t="n">
         <f aca="false">A489 +1000</f>
@@ -12191,7 +12233,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E490" s="2" t="n">
         <f aca="false">A490 +1000</f>
@@ -12209,7 +12251,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E491" s="2" t="n">
         <f aca="false">A491 +1000</f>
@@ -12227,7 +12269,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E492" s="2" t="n">
         <f aca="false">A492 +1000</f>
@@ -12245,7 +12287,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E493" s="2" t="n">
         <f aca="false">A493 +1000</f>
@@ -12263,7 +12305,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E494" s="2" t="n">
         <f aca="false">A494 +1000</f>
@@ -12281,7 +12323,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E495" s="2" t="n">
         <f aca="false">A495 +1000</f>
@@ -12299,7 +12341,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E496" s="2" t="n">
         <f aca="false">A496 +1000</f>
@@ -12317,7 +12359,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E497" s="2" t="n">
         <f aca="false">A497 +1000</f>
@@ -12335,7 +12377,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E498" s="2" t="n">
         <f aca="false">A498 +1000</f>
@@ -12353,7 +12395,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E499" s="2" t="n">
         <f aca="false">A499 +1000</f>
@@ -12371,7 +12413,7 @@
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E500" s="2" t="n">
         <f aca="false">A500 +1000</f>
@@ -12395,7 +12437,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E501" s="2" t="n">
         <f aca="false">A501 +1000</f>
@@ -12413,7 +12455,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E502" s="2" t="n">
         <f aca="false">A502 +1000</f>
@@ -12431,7 +12473,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E503" s="2" t="n">
         <f aca="false">A503 +1000</f>
@@ -12449,7 +12491,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E504" s="2" t="n">
         <f aca="false">A504 +1000</f>
@@ -12467,7 +12509,7 @@
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E505" s="2" t="n">
         <f aca="false">A505 +1000</f>
@@ -12485,7 +12527,7 @@
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>23</v>
@@ -12509,7 +12551,7 @@
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E507" s="2" t="n">
         <f aca="false">A507 +1000</f>
@@ -12533,7 +12575,7 @@
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E508" s="2" t="n">
         <f aca="false">A508 +1000</f>
@@ -12551,7 +12593,7 @@
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E509" s="2" t="n">
         <f aca="false">A509 +1000</f>
@@ -12569,7 +12611,7 @@
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E510" s="2" t="n">
         <f aca="false">A510 +1000</f>
@@ -12587,7 +12629,7 @@
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E511" s="2" t="n">
         <f aca="false">A511 +1000</f>
@@ -12605,7 +12647,7 @@
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E512" s="2" t="n">
         <f aca="false">A512 +1000</f>
@@ -12623,7 +12665,7 @@
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E513" s="2" t="n">
         <f aca="false">A513 +1000</f>
@@ -12641,7 +12683,7 @@
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E514" s="2" t="n">
         <f aca="false">A514 +1000</f>
@@ -12659,7 +12701,7 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E515" s="2" t="n">
         <f aca="false">A515 +1000</f>
@@ -12677,7 +12719,7 @@
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E516" s="2" t="n">
         <f aca="false">A516 +1000</f>
@@ -12695,7 +12737,7 @@
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E517" s="2" t="n">
         <f aca="false">A517 +1000</f>
@@ -12713,7 +12755,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E518" s="2" t="n">
         <f aca="false">A518 +1000</f>
@@ -12731,7 +12773,7 @@
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E519" s="2" t="n">
         <f aca="false">A519 +1000</f>
@@ -12749,7 +12791,7 @@
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E520" s="2" t="n">
         <f aca="false">A520 +1000</f>
@@ -12767,7 +12809,7 @@
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E521" s="2" t="n">
         <f aca="false">A521 +1000</f>
@@ -12785,7 +12827,7 @@
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E522" s="2" t="n">
         <f aca="false">A522 +1000</f>
@@ -12803,7 +12845,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E523" s="2" t="n">
         <f aca="false">A523 +1000</f>
@@ -12821,7 +12863,7 @@
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E524" s="2" t="n">
         <f aca="false">A524 +1000</f>
@@ -12839,7 +12881,7 @@
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E525" s="2" t="n">
         <f aca="false">A525 +1000</f>
@@ -12857,7 +12899,7 @@
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E526" s="2" t="n">
         <f aca="false">A526 +1000</f>
@@ -12875,7 +12917,7 @@
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E527" s="2" t="n">
         <f aca="false">A527 +1000</f>
@@ -12893,7 +12935,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E528" s="2" t="n">
         <f aca="false">A528 +1000</f>
@@ -12911,7 +12953,7 @@
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E529" s="2" t="n">
         <f aca="false">A529 +1000</f>
@@ -12929,7 +12971,7 @@
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E530" s="2" t="n">
         <f aca="false">A530 +1000</f>
@@ -12947,7 +12989,7 @@
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E531" s="2" t="n">
         <f aca="false">A531 +1000</f>
@@ -12965,7 +13007,7 @@
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E532" s="2" t="n">
         <f aca="false">A532 +1000</f>
@@ -12983,7 +13025,7 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E533" s="2" t="n">
         <f aca="false">A533 +1000</f>
@@ -13001,7 +13043,7 @@
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E534" s="2" t="n">
         <f aca="false">A534 +1000</f>
@@ -13019,7 +13061,7 @@
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E535" s="2" t="n">
         <f aca="false">A535 +1000</f>
@@ -13037,7 +13079,7 @@
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E536" s="2" t="n">
         <f aca="false">A536 +1000</f>
@@ -13055,7 +13097,7 @@
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E537" s="2" t="n">
         <f aca="false">A537 +1000</f>
@@ -13073,7 +13115,7 @@
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E538" s="2" t="n">
         <f aca="false">A538 +1000</f>
@@ -13091,7 +13133,7 @@
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E539" s="2" t="n">
         <f aca="false">A539 +1000</f>
@@ -13109,7 +13151,7 @@
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E540" s="2" t="n">
         <f aca="false">A540 +1000</f>
@@ -13127,7 +13169,7 @@
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E541" s="2" t="n">
         <f aca="false">A541 +1000</f>
@@ -13145,7 +13187,7 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E542" s="2" t="n">
         <f aca="false">A542 +1000</f>
@@ -13163,7 +13205,7 @@
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E543" s="2" t="n">
         <f aca="false">A543 +1000</f>
@@ -13181,7 +13223,7 @@
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E544" s="2" t="n">
         <f aca="false">A544 +1000</f>
@@ -13199,7 +13241,7 @@
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E545" s="2" t="n">
         <f aca="false">A545 +1000</f>
@@ -13217,7 +13259,7 @@
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E546" s="2" t="n">
         <f aca="false">A546 +1000</f>
@@ -13235,7 +13277,7 @@
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E547" s="2" t="n">
         <f aca="false">A547 +1000</f>
@@ -13253,7 +13295,7 @@
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E548" s="2" t="n">
         <f aca="false">A548 +1000</f>
@@ -13271,7 +13313,7 @@
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E549" s="2" t="n">
         <f aca="false">A549 +1000</f>
@@ -13289,7 +13331,7 @@
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E550" s="2" t="n">
         <f aca="false">A550 +1000</f>
@@ -13307,7 +13349,7 @@
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E551" s="2" t="n">
         <f aca="false">A551 +1000</f>
@@ -13325,7 +13367,7 @@
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E552" s="2" t="n">
         <f aca="false">A552 +1000</f>
@@ -13343,7 +13385,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E553" s="2" t="n">
         <f aca="false">A553 +1000</f>
@@ -13361,7 +13403,7 @@
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E554" s="2" t="n">
         <f aca="false">A554 +1000</f>
@@ -13379,7 +13421,7 @@
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E555" s="2" t="n">
         <f aca="false">A555 +1000</f>
@@ -13397,7 +13439,7 @@
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E556" s="2" t="n">
         <f aca="false">A556 +1000</f>
@@ -13415,7 +13457,7 @@
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E557" s="2" t="n">
         <f aca="false">A557 +1000</f>
@@ -13433,7 +13475,7 @@
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E558" s="2" t="n">
         <f aca="false">A558 +1000</f>
@@ -13457,7 +13499,7 @@
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E559" s="2" t="n">
         <f aca="false">A559 +1000</f>
@@ -13475,7 +13517,7 @@
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E560" s="2" t="n">
         <f aca="false">A560 +1000</f>
@@ -13493,7 +13535,7 @@
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E561" s="2" t="n">
         <f aca="false">A561 +1000</f>
@@ -13511,7 +13553,7 @@
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E562" s="2" t="n">
         <f aca="false">A562 +1000</f>
@@ -13529,7 +13571,7 @@
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E563" s="2" t="n">
         <f aca="false">A563 +1000</f>
@@ -13547,7 +13589,7 @@
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E564" s="2" t="n">
         <f aca="false">A564 +1000</f>
@@ -13565,7 +13607,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E565" s="2" t="n">
         <f aca="false">A565 +1000</f>
@@ -13583,7 +13625,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E566" s="2" t="n">
         <f aca="false">A566 +1000</f>
@@ -13601,7 +13643,7 @@
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E567" s="2" t="n">
         <f aca="false">A567 +1000</f>
@@ -13619,7 +13661,7 @@
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E568" s="2" t="n">
         <f aca="false">A568 +1000</f>
@@ -13637,7 +13679,7 @@
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E569" s="2" t="n">
         <f aca="false">A569 +1000</f>
@@ -13655,7 +13697,7 @@
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E570" s="2" t="n">
         <f aca="false">A570 +1000</f>
@@ -13673,7 +13715,7 @@
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E571" s="2" t="n">
         <f aca="false">A571 +1000</f>
@@ -13691,7 +13733,7 @@
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E572" s="2" t="n">
         <f aca="false">A572 +1000</f>
@@ -13709,7 +13751,7 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E573" s="2" t="n">
         <f aca="false">A573 +1000</f>
@@ -13727,7 +13769,7 @@
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E574" s="2" t="n">
         <f aca="false">A574 +1000</f>
@@ -13745,7 +13787,7 @@
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E575" s="2" t="n">
         <f aca="false">A575 +1000</f>
@@ -13763,7 +13805,7 @@
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E576" s="2" t="n">
         <f aca="false">A576 +1000</f>
@@ -13781,7 +13823,7 @@
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E577" s="2" t="n">
         <f aca="false">A577 +1000</f>
@@ -13799,7 +13841,7 @@
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E578" s="2" t="n">
         <f aca="false">A578 +1000</f>
@@ -13817,7 +13859,7 @@
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E579" s="2" t="n">
         <f aca="false">A579 +1000</f>
@@ -13835,7 +13877,7 @@
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E580" s="2" t="n">
         <f aca="false">A580 +1000</f>
@@ -13853,7 +13895,7 @@
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E581" s="2" t="n">
         <f aca="false">A581 +1000</f>
@@ -13871,7 +13913,7 @@
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E582" s="2" t="n">
         <f aca="false">A582 +1000</f>
@@ -13889,7 +13931,7 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E583" s="2" t="n">
         <f aca="false">A583 +1000</f>
@@ -13907,7 +13949,7 @@
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E584" s="2" t="n">
         <f aca="false">A584 +1000</f>
@@ -13925,7 +13967,7 @@
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E585" s="2" t="n">
         <f aca="false">A585 +1000</f>
@@ -13943,7 +13985,7 @@
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E586" s="2" t="n">
         <f aca="false">A586 +1000</f>
@@ -13961,7 +14003,7 @@
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E587" s="2" t="n">
         <f aca="false">A587 +1000</f>
@@ -13979,7 +14021,7 @@
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E588" s="2" t="n">
         <f aca="false">A588 +1000</f>
@@ -13997,7 +14039,7 @@
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E589" s="2" t="n">
         <f aca="false">A589 +1000</f>
@@ -14015,7 +14057,7 @@
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E590" s="2" t="n">
         <f aca="false">A590 +1000</f>
@@ -14033,7 +14075,7 @@
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E591" s="2" t="n">
         <f aca="false">A591 +1000</f>
@@ -14051,7 +14093,7 @@
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E592" s="2" t="n">
         <f aca="false">A592 +1000</f>
@@ -14069,7 +14111,7 @@
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E593" s="2" t="n">
         <f aca="false">A593 +1000</f>
@@ -14087,7 +14129,7 @@
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E594" s="2" t="n">
         <f aca="false">A594 +1000</f>
@@ -14105,7 +14147,7 @@
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E595" s="2" t="n">
         <f aca="false">A595 +1000</f>
@@ -14123,7 +14165,7 @@
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E596" s="2" t="n">
         <f aca="false">A596 +1000</f>
@@ -14141,7 +14183,7 @@
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E597" s="2" t="n">
         <f aca="false">A597 +1000</f>
@@ -14159,7 +14201,7 @@
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E598" s="2" t="n">
         <f aca="false">A598 +1000</f>
@@ -14177,7 +14219,7 @@
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E599" s="2" t="n">
         <f aca="false">A599 +1000</f>
@@ -14195,7 +14237,7 @@
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E600" s="2" t="n">
         <f aca="false">A600 +1000</f>
@@ -14213,7 +14255,7 @@
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E601" s="2" t="n">
         <f aca="false">A601 +1000</f>
@@ -14231,7 +14273,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E602" s="2" t="n">
         <f aca="false">A602 +1000</f>
@@ -14249,7 +14291,7 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E603" s="2" t="n">
         <f aca="false">A603 +1000</f>
@@ -14267,7 +14309,7 @@
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E604" s="2" t="n">
         <f aca="false">A604 +1000</f>
@@ -14285,7 +14327,7 @@
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E605" s="2" t="n">
         <f aca="false">A605 +1000</f>
@@ -14303,7 +14345,7 @@
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E606" s="2" t="n">
         <f aca="false">A606 +1000</f>
@@ -14321,7 +14363,7 @@
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E607" s="2" t="n">
         <f aca="false">A607 +1000</f>
@@ -14339,7 +14381,7 @@
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E608" s="2" t="n">
         <f aca="false">A608 +1000</f>
@@ -14357,7 +14399,7 @@
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E609" s="2" t="n">
         <f aca="false">A609 +1000</f>
@@ -14375,7 +14417,7 @@
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E610" s="2" t="n">
         <f aca="false">A610 +1000</f>
@@ -14393,7 +14435,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E611" s="2" t="n">
         <f aca="false">A611 +1000</f>
@@ -14411,7 +14453,7 @@
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E612" s="2" t="n">
         <f aca="false">A612 +1000</f>
@@ -14429,7 +14471,7 @@
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E613" s="2" t="n">
         <f aca="false">A613 +1000</f>
@@ -14447,7 +14489,7 @@
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E614" s="2" t="n">
         <f aca="false">A614 +1000</f>
@@ -14465,7 +14507,7 @@
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E615" s="2" t="n">
         <f aca="false">A615 +1000</f>
@@ -14483,7 +14525,7 @@
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E616" s="2" t="n">
         <f aca="false">A616 +1000</f>
@@ -14501,7 +14543,7 @@
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E617" s="2" t="n">
         <f aca="false">A617 +1000</f>
@@ -14519,7 +14561,7 @@
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E618" s="2" t="n">
         <f aca="false">A618 +1000</f>
@@ -14537,7 +14579,7 @@
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E619" s="2" t="n">
         <f aca="false">A619 +1000</f>
@@ -14555,7 +14597,7 @@
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E620" s="2" t="n">
         <f aca="false">A620 +1000</f>
@@ -14573,7 +14615,7 @@
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E621" s="2" t="n">
         <f aca="false">A621 +1000</f>
@@ -14591,7 +14633,16 @@
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D622" s="2" t="s">
+        <v>624</v>
       </c>
       <c r="E622" s="2" t="n">
         <f aca="false">A622 +1000</f>
@@ -14609,7 +14660,7 @@
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E623" s="2" t="n">
         <f aca="false">A623 +1000</f>
@@ -14627,7 +14678,7 @@
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E624" s="2" t="n">
         <f aca="false">A624 +1000</f>
@@ -14645,7 +14696,7 @@
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E625" s="2" t="n">
         <f aca="false">A625 +1000</f>
@@ -14663,7 +14714,7 @@
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E626" s="2" t="n">
         <f aca="false">A626 +1000</f>
@@ -14681,7 +14732,7 @@
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E627" s="2" t="n">
         <f aca="false">A627 +1000</f>
@@ -14699,7 +14750,7 @@
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E628" s="2" t="n">
         <f aca="false">A628 +1000</f>
@@ -14717,7 +14768,7 @@
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E629" s="2" t="n">
         <f aca="false">A629 +1000</f>
@@ -14735,7 +14786,7 @@
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E630" s="2" t="n">
         <f aca="false">A630 +1000</f>
@@ -14753,7 +14804,7 @@
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E631" s="2" t="n">
         <f aca="false">A631 +1000</f>
@@ -14771,7 +14822,7 @@
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E632" s="2" t="n">
         <f aca="false">A632 +1000</f>
@@ -14789,7 +14840,7 @@
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E633" s="2" t="n">
         <f aca="false">A633 +1000</f>
@@ -14807,7 +14858,7 @@
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E634" s="2" t="n">
         <f aca="false">A634 +1000</f>
@@ -14825,7 +14876,7 @@
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E635" s="2" t="n">
         <f aca="false">A635 +1000</f>
@@ -14843,7 +14894,7 @@
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E636" s="2" t="n">
         <f aca="false">A636 +1000</f>
@@ -14861,7 +14912,7 @@
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E637" s="2" t="n">
         <f aca="false">A637 +1000</f>
@@ -14879,7 +14930,7 @@
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E638" s="2" t="n">
         <f aca="false">A638 +1000</f>
@@ -14897,7 +14948,7 @@
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E639" s="2" t="n">
         <f aca="false">A639 +1000</f>
@@ -14915,7 +14966,7 @@
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E640" s="2" t="n">
         <f aca="false">A640 +1000</f>
@@ -14933,7 +14984,7 @@
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E641" s="2" t="n">
         <f aca="false">A641 +1000</f>
@@ -14951,7 +15002,7 @@
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E642" s="2" t="n">
         <f aca="false">A642 +1000</f>
@@ -14969,7 +15020,7 @@
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E643" s="2" t="n">
         <f aca="false">A643 +1000</f>
@@ -14987,7 +15038,7 @@
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E644" s="2" t="n">
         <f aca="false">A644 +1000</f>
@@ -15005,7 +15056,7 @@
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E645" s="2" t="n">
         <f aca="false">A645 +1000</f>
@@ -15023,7 +15074,7 @@
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E646" s="2" t="n">
         <f aca="false">A646 +1000</f>
@@ -15041,7 +15092,7 @@
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E647" s="2" t="n">
         <f aca="false">A647 +1000</f>
@@ -15059,7 +15110,7 @@
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E648" s="2" t="n">
         <f aca="false">A648 +1000</f>
@@ -15077,7 +15128,7 @@
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E649" s="2" t="n">
         <f aca="false">A649 +1000</f>
@@ -15095,7 +15146,7 @@
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E650" s="2" t="n">
         <f aca="false">A650 +1000</f>
@@ -15113,7 +15164,7 @@
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E651" s="2" t="n">
         <f aca="false">A651 +1000</f>
@@ -15131,7 +15182,7 @@
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E652" s="2" t="n">
         <f aca="false">A652 +1000</f>
@@ -15149,7 +15200,7 @@
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E653" s="2" t="n">
         <f aca="false">A653 +1000</f>
@@ -15167,7 +15218,7 @@
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E654" s="2" t="n">
         <f aca="false">A654 +1000</f>
@@ -15185,7 +15236,7 @@
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E655" s="2" t="n">
         <f aca="false">A655 +1000</f>
@@ -15203,7 +15254,7 @@
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E656" s="2" t="n">
         <f aca="false">A656 +1000</f>
@@ -15221,7 +15272,7 @@
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E657" s="2" t="n">
         <f aca="false">A657 +1000</f>
@@ -15239,7 +15290,7 @@
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E658" s="2" t="n">
         <f aca="false">A658 +1000</f>
@@ -15257,7 +15308,7 @@
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E659" s="2" t="n">
         <f aca="false">A659 +1000</f>
@@ -15275,7 +15326,7 @@
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E660" s="2" t="n">
         <f aca="false">A660 +1000</f>
@@ -15293,7 +15344,7 @@
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E661" s="2" t="n">
         <f aca="false">A661 +1000</f>
@@ -15311,7 +15362,7 @@
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E662" s="2" t="n">
         <f aca="false">A662 +1000</f>
@@ -15329,7 +15380,7 @@
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E663" s="2" t="n">
         <f aca="false">A663 +1000</f>
@@ -15347,7 +15398,7 @@
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E664" s="2" t="n">
         <f aca="false">A664 +1000</f>
@@ -15365,7 +15416,7 @@
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E665" s="2" t="n">
         <f aca="false">A665 +1000</f>
@@ -15383,7 +15434,7 @@
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E666" s="2" t="n">
         <f aca="false">A666 +1000</f>
@@ -15401,7 +15452,7 @@
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E667" s="2" t="n">
         <f aca="false">A667 +1000</f>
@@ -15419,7 +15470,7 @@
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E668" s="2" t="n">
         <f aca="false">A668 +1000</f>
@@ -15437,7 +15488,7 @@
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E669" s="2" t="n">
         <f aca="false">A669 +1000</f>
@@ -15455,7 +15506,7 @@
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E670" s="2" t="n">
         <f aca="false">A670 +1000</f>
@@ -15473,7 +15524,7 @@
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E671" s="2" t="n">
         <f aca="false">A671 +1000</f>
@@ -15491,7 +15542,7 @@
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E672" s="2" t="n">
         <f aca="false">A672 +1000</f>
@@ -15509,7 +15560,7 @@
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E673" s="2" t="n">
         <f aca="false">A673 +1000</f>
@@ -15527,7 +15578,7 @@
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E674" s="2" t="n">
         <f aca="false">A674 +1000</f>
@@ -15545,7 +15596,7 @@
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E675" s="2" t="n">
         <f aca="false">A675 +1000</f>
@@ -15563,7 +15614,7 @@
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E676" s="2" t="n">
         <f aca="false">A676 +1000</f>
@@ -15581,7 +15632,7 @@
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E677" s="2" t="n">
         <f aca="false">A677 +1000</f>
@@ -15599,7 +15650,7 @@
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E678" s="2" t="n">
         <f aca="false">A678 +1000</f>
@@ -15617,7 +15668,7 @@
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E679" s="2" t="n">
         <f aca="false">A679 +1000</f>
@@ -15635,7 +15686,7 @@
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E680" s="2" t="n">
         <f aca="false">A680 +1000</f>
@@ -15653,7 +15704,7 @@
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E681" s="2" t="n">
         <f aca="false">A681 +1000</f>
@@ -15671,7 +15722,7 @@
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E682" s="2" t="n">
         <f aca="false">A682 +1000</f>
@@ -15689,7 +15740,7 @@
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E683" s="2" t="n">
         <f aca="false">A683 +1000</f>
@@ -15707,7 +15758,7 @@
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E684" s="2" t="n">
         <f aca="false">A684 +1000</f>
@@ -15725,7 +15776,7 @@
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E685" s="2" t="n">
         <f aca="false">A685 +1000</f>
@@ -15743,7 +15794,7 @@
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E686" s="2" t="n">
         <f aca="false">A686 +1000</f>
@@ -15761,7 +15812,7 @@
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E687" s="2" t="n">
         <f aca="false">A687 +1000</f>
@@ -15779,7 +15830,7 @@
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E688" s="2" t="n">
         <f aca="false">A688 +1000</f>
@@ -15797,7 +15848,7 @@
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E689" s="2" t="n">
         <f aca="false">A689 +1000</f>
@@ -15815,7 +15866,7 @@
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E690" s="2" t="n">
         <f aca="false">A690 +1000</f>
@@ -15833,7 +15884,7 @@
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E691" s="2" t="n">
         <f aca="false">A691 +1000</f>
@@ -15851,7 +15902,7 @@
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E692" s="2" t="n">
         <f aca="false">A692 +1000</f>
@@ -15869,7 +15920,7 @@
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E693" s="2" t="n">
         <f aca="false">A693 +1000</f>
@@ -15887,7 +15938,7 @@
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E694" s="2" t="n">
         <f aca="false">A694 +1000</f>
@@ -15905,7 +15956,7 @@
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E695" s="2" t="n">
         <f aca="false">A695 +1000</f>
@@ -15923,7 +15974,7 @@
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E696" s="2" t="n">
         <f aca="false">A696 +1000</f>
@@ -15941,7 +15992,7 @@
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E697" s="2" t="n">
         <f aca="false">A697 +1000</f>
@@ -15959,7 +16010,7 @@
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E698" s="2" t="n">
         <f aca="false">A698 +1000</f>
@@ -15977,7 +16028,7 @@
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E699" s="2" t="n">
         <f aca="false">A699 +1000</f>
@@ -15995,7 +16046,7 @@
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E700" s="2" t="n">
         <f aca="false">A700 +1000</f>
@@ -16013,7 +16064,13 @@
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
+      </c>
+      <c r="B701" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E701" s="2" t="n">
         <f aca="false">A701 +1000</f>
@@ -16031,7 +16088,13 @@
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E702" s="2" t="n">
         <f aca="false">A702 +1000</f>
@@ -16049,7 +16112,7 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>23</v>
@@ -16073,7 +16136,13 @@
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="E704" s="2" t="n">
         <f aca="false">A704 +1000</f>
@@ -16091,7 +16160,7 @@
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="E705" s="2" t="n">
         <f aca="false">A705 +1000</f>
@@ -16109,7 +16178,7 @@
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E706" s="2" t="n">
         <f aca="false">A706 +1000</f>
@@ -16127,7 +16196,7 @@
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E707" s="2" t="n">
         <f aca="false">A707 +1000</f>
@@ -16145,7 +16214,7 @@
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
@@ -16163,7 +16232,7 @@
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E709" s="2" t="n">
         <f aca="false">A709 +1000</f>
@@ -16181,7 +16250,7 @@
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E710" s="2" t="n">
         <f aca="false">A710 +1000</f>
@@ -16199,7 +16268,7 @@
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E711" s="2" t="n">
         <f aca="false">A711 +1000</f>
@@ -16217,7 +16286,7 @@
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E712" s="2" t="n">
         <f aca="false">A712 +1000</f>
@@ -16235,7 +16304,7 @@
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E713" s="2" t="n">
         <f aca="false">A713 +1000</f>
@@ -16253,7 +16322,7 @@
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E714" s="2" t="n">
         <f aca="false">A714 +1000</f>
@@ -16271,7 +16340,7 @@
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E715" s="2" t="n">
         <f aca="false">A715 +1000</f>
@@ -16289,7 +16358,7 @@
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E716" s="2" t="n">
         <f aca="false">A716 +1000</f>
@@ -16307,7 +16376,7 @@
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E717" s="2" t="n">
         <f aca="false">A717 +1000</f>
@@ -16325,7 +16394,7 @@
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E718" s="2" t="n">
         <f aca="false">A718 +1000</f>
@@ -16343,7 +16412,7 @@
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E719" s="2" t="n">
         <f aca="false">A719 +1000</f>
@@ -16361,7 +16430,7 @@
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E720" s="2" t="n">
         <f aca="false">A720 +1000</f>
@@ -16379,7 +16448,7 @@
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E721" s="2" t="n">
         <f aca="false">A721 +1000</f>
@@ -16397,7 +16466,7 @@
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E722" s="2" t="n">
         <f aca="false">A722 +1000</f>
@@ -16415,7 +16484,7 @@
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E723" s="2" t="n">
         <f aca="false">A723 +1000</f>
@@ -16433,7 +16502,7 @@
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E724" s="2" t="n">
         <f aca="false">A724 +1000</f>
@@ -16451,7 +16520,7 @@
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E725" s="2" t="n">
         <f aca="false">A725 +1000</f>
@@ -16469,7 +16538,7 @@
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E726" s="2" t="n">
         <f aca="false">A726 +1000</f>
@@ -16487,7 +16556,7 @@
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E727" s="2" t="n">
         <f aca="false">A727 +1000</f>
@@ -16505,7 +16574,7 @@
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E728" s="2" t="n">
         <f aca="false">A728 +1000</f>
@@ -16523,7 +16592,7 @@
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E729" s="2" t="n">
         <f aca="false">A729 +1000</f>
@@ -16541,7 +16610,7 @@
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E730" s="2" t="n">
         <f aca="false">A730 +1000</f>
@@ -16559,7 +16628,7 @@
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E731" s="2" t="n">
         <f aca="false">A731 +1000</f>
@@ -16577,7 +16646,7 @@
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E732" s="2" t="n">
         <f aca="false">A732 +1000</f>
@@ -16595,7 +16664,7 @@
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E733" s="2" t="n">
         <f aca="false">A733 +1000</f>
@@ -16613,7 +16682,7 @@
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E734" s="2" t="n">
         <f aca="false">A734 +1000</f>
@@ -16631,7 +16700,7 @@
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E735" s="2" t="n">
         <f aca="false">A735 +1000</f>
@@ -16649,7 +16718,7 @@
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E736" s="2" t="n">
         <f aca="false">A736 +1000</f>
@@ -16667,7 +16736,7 @@
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E737" s="2" t="n">
         <f aca="false">A737 +1000</f>
@@ -16685,7 +16754,7 @@
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E738" s="2" t="n">
         <f aca="false">A738 +1000</f>
@@ -16703,7 +16772,7 @@
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E739" s="2" t="n">
         <f aca="false">A739 +1000</f>
@@ -16721,7 +16790,7 @@
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E740" s="2" t="n">
         <f aca="false">A740 +1000</f>
@@ -16739,7 +16808,7 @@
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E741" s="2" t="n">
         <f aca="false">A741 +1000</f>
@@ -16757,7 +16826,7 @@
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E742" s="2" t="n">
         <f aca="false">A742 +1000</f>
@@ -16775,7 +16844,7 @@
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="E743" s="2" t="n">
         <f aca="false">A743 +1000</f>
@@ -16793,7 +16862,7 @@
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E744" s="2" t="n">
         <f aca="false">A744 +1000</f>
@@ -16811,7 +16880,7 @@
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E745" s="2" t="n">
         <f aca="false">A745 +1000</f>
@@ -16829,7 +16898,7 @@
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E746" s="2" t="n">
         <f aca="false">A746 +1000</f>
@@ -16847,7 +16916,7 @@
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E747" s="2" t="n">
         <f aca="false">A747 +1000</f>
@@ -16865,7 +16934,7 @@
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E748" s="2" t="n">
         <f aca="false">A748 +1000</f>
@@ -16883,7 +16952,7 @@
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E749" s="2" t="n">
         <f aca="false">A749 +1000</f>
@@ -16901,7 +16970,7 @@
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E750" s="2" t="n">
         <f aca="false">A750 +1000</f>
@@ -16919,7 +16988,7 @@
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="E751" s="2" t="n">
         <f aca="false">A751 +1000</f>
@@ -16937,7 +17006,7 @@
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E752" s="2" t="n">
         <f aca="false">A752 +1000</f>
@@ -16955,7 +17024,7 @@
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E753" s="2" t="n">
         <f aca="false">A753 +1000</f>
@@ -16973,7 +17042,7 @@
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E754" s="2" t="n">
         <f aca="false">A754 +1000</f>
@@ -16991,7 +17060,7 @@
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E755" s="2" t="n">
         <f aca="false">A755 +1000</f>
@@ -17009,7 +17078,7 @@
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E756" s="2" t="n">
         <f aca="false">A756 +1000</f>
@@ -17027,7 +17096,7 @@
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E757" s="2" t="n">
         <f aca="false">A757 +1000</f>
@@ -17045,7 +17114,7 @@
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E758" s="2" t="n">
         <f aca="false">A758 +1000</f>
@@ -17063,7 +17132,7 @@
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E759" s="2" t="n">
         <f aca="false">A759 +1000</f>
@@ -17081,7 +17150,7 @@
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E760" s="2" t="n">
         <f aca="false">A760 +1000</f>
@@ -17099,7 +17168,7 @@
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E761" s="2" t="n">
         <f aca="false">A761 +1000</f>
@@ -17117,7 +17186,7 @@
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E762" s="2" t="n">
         <f aca="false">A762 +1000</f>
@@ -17135,7 +17204,7 @@
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E763" s="2" t="n">
         <f aca="false">A763 +1000</f>
@@ -17153,7 +17222,7 @@
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E764" s="2" t="n">
         <f aca="false">A764 +1000</f>
@@ -17171,7 +17240,7 @@
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E765" s="2" t="n">
         <f aca="false">A765 +1000</f>
@@ -17189,7 +17258,7 @@
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E766" s="2" t="n">
         <f aca="false">A766 +1000</f>
@@ -17207,7 +17276,7 @@
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E767" s="2" t="n">
         <f aca="false">A767 +1000</f>
@@ -17225,7 +17294,7 @@
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E768" s="2" t="n">
         <f aca="false">A768 +1000</f>
@@ -17243,7 +17312,7 @@
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E769" s="2" t="n">
         <f aca="false">A769 +1000</f>
@@ -17261,7 +17330,7 @@
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E770" s="2" t="n">
         <f aca="false">A770 +1000</f>
@@ -17279,7 +17348,7 @@
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E771" s="2" t="n">
         <f aca="false">A771 +1000</f>
@@ -17297,7 +17366,7 @@
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E772" s="2" t="n">
         <f aca="false">A772 +1000</f>
@@ -17315,7 +17384,7 @@
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E773" s="2" t="n">
         <f aca="false">A773 +1000</f>
@@ -17333,7 +17402,7 @@
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="E774" s="2" t="n">
         <f aca="false">A774 +1000</f>
@@ -17351,7 +17420,7 @@
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E775" s="2" t="n">
         <f aca="false">A775 +1000</f>
@@ -17369,7 +17438,7 @@
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E776" s="2" t="n">
         <f aca="false">A776 +1000</f>
@@ -17387,7 +17456,7 @@
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E777" s="2" t="n">
         <f aca="false">A777 +1000</f>
@@ -17405,7 +17474,7 @@
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E778" s="2" t="n">
         <f aca="false">A778 +1000</f>
@@ -17423,7 +17492,7 @@
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E779" s="2" t="n">
         <f aca="false">A779 +1000</f>
@@ -17441,7 +17510,7 @@
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="E780" s="2" t="n">
         <f aca="false">A780 +1000</f>
@@ -17459,7 +17528,7 @@
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E781" s="2" t="n">
         <f aca="false">A781 +1000</f>
@@ -17477,7 +17546,7 @@
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E782" s="2" t="n">
         <f aca="false">A782 +1000</f>
@@ -17495,7 +17564,7 @@
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="E783" s="2" t="n">
         <f aca="false">A783 +1000</f>
@@ -17513,7 +17582,7 @@
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E784" s="2" t="n">
         <f aca="false">A784 +1000</f>
@@ -17531,7 +17600,7 @@
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E785" s="2" t="n">
         <f aca="false">A785 +1000</f>
@@ -17549,7 +17618,7 @@
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="E786" s="2" t="n">
         <f aca="false">A786 +1000</f>
@@ -17567,7 +17636,7 @@
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="E787" s="2" t="n">
         <f aca="false">A787 +1000</f>
@@ -17585,7 +17654,7 @@
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E788" s="2" t="n">
         <f aca="false">A788 +1000</f>
@@ -17603,7 +17672,7 @@
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E789" s="2" t="n">
         <f aca="false">A789 +1000</f>
@@ -17621,7 +17690,7 @@
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E790" s="2" t="n">
         <f aca="false">A790 +1000</f>
@@ -17639,7 +17708,7 @@
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="E791" s="2" t="n">
         <f aca="false">A791 +1000</f>
@@ -17657,7 +17726,7 @@
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="E792" s="2" t="n">
         <f aca="false">A792 +1000</f>
@@ -17675,7 +17744,7 @@
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E793" s="2" t="n">
         <f aca="false">A793 +1000</f>
@@ -17693,7 +17762,7 @@
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="E794" s="2" t="n">
         <f aca="false">A794 +1000</f>
@@ -17711,7 +17780,7 @@
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E795" s="2" t="n">
         <f aca="false">A795 +1000</f>
@@ -17729,7 +17798,7 @@
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="E796" s="2" t="n">
         <f aca="false">A796 +1000</f>
@@ -17747,7 +17816,7 @@
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E797" s="2" t="n">
         <f aca="false">A797 +1000</f>
@@ -17765,7 +17834,7 @@
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="E798" s="2" t="n">
         <f aca="false">A798 +1000</f>
@@ -17783,7 +17852,7 @@
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="E799" s="2" t="n">
         <f aca="false">A799 +1000</f>
@@ -17801,7 +17870,7 @@
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E800" s="2" t="n">
         <f aca="false">A800 +1000</f>
@@ -17819,7 +17888,7 @@
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E801" s="2" t="n">
         <f aca="false">A801 +1000</f>
@@ -17837,7 +17906,7 @@
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E802" s="2" t="n">
         <f aca="false">A802 +1000</f>
@@ -17855,7 +17924,7 @@
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E803" s="2" t="n">
         <f aca="false">A803 +1000</f>
@@ -17873,7 +17942,7 @@
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E804" s="2" t="n">
         <f aca="false">A804 +1000</f>
@@ -17891,7 +17960,7 @@
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="E805" s="2" t="n">
         <f aca="false">A805 +1000</f>
@@ -17909,7 +17978,7 @@
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="E806" s="2" t="n">
         <f aca="false">A806 +1000</f>
@@ -17927,7 +17996,7 @@
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="E807" s="2" t="n">
         <f aca="false">A807 +1000</f>
@@ -17945,7 +18014,7 @@
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="E808" s="2" t="n">
         <f aca="false">A808 +1000</f>
@@ -17963,7 +18032,7 @@
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E809" s="2" t="n">
         <f aca="false">A809 +1000</f>
@@ -17981,7 +18050,7 @@
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="E810" s="2" t="n">
         <f aca="false">A810 +1000</f>
@@ -17999,7 +18068,7 @@
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="E811" s="2" t="n">
         <f aca="false">A811 +1000</f>
@@ -18017,7 +18086,7 @@
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E812" s="2" t="n">
         <f aca="false">A812 +1000</f>
@@ -18035,7 +18104,7 @@
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E813" s="2" t="n">
         <f aca="false">A813 +1000</f>
@@ -18053,7 +18122,7 @@
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E814" s="2" t="n">
         <f aca="false">A814 +1000</f>
@@ -18071,7 +18140,7 @@
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="E815" s="2" t="n">
         <f aca="false">A815 +1000</f>
@@ -18089,7 +18158,7 @@
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="E816" s="2" t="n">
         <f aca="false">A816 +1000</f>
@@ -18107,7 +18176,7 @@
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="E817" s="2" t="n">
         <f aca="false">A817 +1000</f>
@@ -18125,7 +18194,7 @@
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E818" s="2" t="n">
         <f aca="false">A818 +1000</f>
@@ -18143,7 +18212,7 @@
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E819" s="2" t="n">
         <f aca="false">A819 +1000</f>
@@ -18161,7 +18230,7 @@
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E820" s="2" t="n">
         <f aca="false">A820 +1000</f>
@@ -18179,7 +18248,7 @@
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="E821" s="2" t="n">
         <f aca="false">A821 +1000</f>
@@ -18197,7 +18266,7 @@
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E822" s="2" t="n">
         <f aca="false">A822 +1000</f>
@@ -18215,7 +18284,7 @@
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="E823" s="2" t="n">
         <f aca="false">A823 +1000</f>
@@ -18233,7 +18302,7 @@
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="E824" s="2" t="n">
         <f aca="false">A824 +1000</f>
@@ -18251,7 +18320,7 @@
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E825" s="2" t="n">
         <f aca="false">A825 +1000</f>
@@ -18269,7 +18338,7 @@
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="E826" s="2" t="n">
         <f aca="false">A826 +1000</f>
@@ -18287,7 +18356,7 @@
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E827" s="2" t="n">
         <f aca="false">A827 +1000</f>
@@ -18305,7 +18374,7 @@
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E828" s="2" t="n">
         <f aca="false">A828 +1000</f>
@@ -18323,7 +18392,7 @@
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E829" s="2" t="n">
         <f aca="false">A829 +1000</f>
@@ -18341,7 +18410,7 @@
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E830" s="2" t="n">
         <f aca="false">A830 +1000</f>
@@ -18359,7 +18428,7 @@
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E831" s="2" t="n">
         <f aca="false">A831 +1000</f>
@@ -18377,7 +18446,7 @@
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E832" s="2" t="n">
         <f aca="false">A832 +1000</f>
@@ -18395,7 +18464,7 @@
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="E833" s="2" t="n">
         <f aca="false">A833 +1000</f>
@@ -18413,7 +18482,7 @@
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E834" s="2" t="n">
         <f aca="false">A834 +1000</f>
@@ -18431,7 +18500,7 @@
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E835" s="2" t="n">
         <f aca="false">A835 +1000</f>
@@ -18449,7 +18518,7 @@
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E836" s="2" t="n">
         <f aca="false">A836 +1000</f>
@@ -18467,7 +18536,7 @@
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E837" s="2" t="n">
         <f aca="false">A837 +1000</f>
@@ -18485,7 +18554,7 @@
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E838" s="2" t="n">
         <f aca="false">A838 +1000</f>
@@ -18503,7 +18572,7 @@
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="E839" s="2" t="n">
         <f aca="false">A839 +1000</f>
@@ -18521,7 +18590,7 @@
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E840" s="2" t="n">
         <f aca="false">A840 +1000</f>
@@ -18539,7 +18608,7 @@
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E841" s="2" t="n">
         <f aca="false">A841 +1000</f>
@@ -18557,7 +18626,7 @@
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E842" s="2" t="n">
         <f aca="false">A842 +1000</f>
@@ -18575,7 +18644,7 @@
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E843" s="2" t="n">
         <f aca="false">A843 +1000</f>
@@ -18593,7 +18662,7 @@
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E844" s="2" t="n">
         <f aca="false">A844 +1000</f>
@@ -18611,7 +18680,7 @@
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="E845" s="2" t="n">
         <f aca="false">A845 +1000</f>
@@ -18629,7 +18698,7 @@
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="E846" s="2" t="n">
         <f aca="false">A846 +1000</f>
@@ -18647,7 +18716,16 @@
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
+      </c>
+      <c r="B847" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C847" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D847" s="2" t="s">
+        <v>850</v>
       </c>
       <c r="E847" s="2" t="n">
         <f aca="false">A847 +1000</f>
@@ -18665,7 +18743,7 @@
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E848" s="2" t="n">
         <f aca="false">A848 +1000</f>
@@ -18683,7 +18761,7 @@
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="E849" s="2" t="n">
         <f aca="false">A849 +1000</f>
@@ -18701,7 +18779,7 @@
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E850" s="2" t="n">
         <f aca="false">A850 +1000</f>
@@ -18719,7 +18797,7 @@
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E851" s="2" t="n">
         <f aca="false">A851 +1000</f>
@@ -18737,7 +18815,7 @@
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E852" s="2" t="n">
         <f aca="false">A852 +1000</f>
@@ -18755,7 +18833,7 @@
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E853" s="2" t="n">
         <f aca="false">A853 +1000</f>
@@ -18773,7 +18851,7 @@
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E854" s="2" t="n">
         <f aca="false">A854 +1000</f>
@@ -18791,7 +18869,7 @@
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E855" s="2" t="n">
         <f aca="false">A855 +1000</f>
@@ -18809,7 +18887,7 @@
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="E856" s="2" t="n">
         <f aca="false">A856 +1000</f>
@@ -18827,7 +18905,7 @@
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E857" s="2" t="n">
         <f aca="false">A857 +1000</f>
@@ -18845,7 +18923,7 @@
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="E858" s="2" t="n">
         <f aca="false">A858 +1000</f>
@@ -18863,7 +18941,7 @@
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E859" s="2" t="n">
         <f aca="false">A859 +1000</f>
@@ -18881,7 +18959,7 @@
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="E860" s="2" t="n">
         <f aca="false">A860 +1000</f>
@@ -18899,7 +18977,7 @@
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E861" s="2" t="n">
         <f aca="false">A861 +1000</f>
@@ -18917,7 +18995,7 @@
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="E862" s="2" t="n">
         <f aca="false">A862 +1000</f>
@@ -18935,7 +19013,7 @@
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E863" s="2" t="n">
         <f aca="false">A863 +1000</f>
@@ -18953,7 +19031,7 @@
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="E864" s="2" t="n">
         <f aca="false">A864 +1000</f>
@@ -18971,7 +19049,7 @@
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="E865" s="2" t="n">
         <f aca="false">A865 +1000</f>
@@ -18989,7 +19067,7 @@
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E866" s="2" t="n">
         <f aca="false">A866 +1000</f>
@@ -19007,7 +19085,7 @@
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E867" s="2" t="n">
         <f aca="false">A867 +1000</f>
@@ -19025,7 +19103,7 @@
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E868" s="2" t="n">
         <f aca="false">A868 +1000</f>
@@ -19043,7 +19121,7 @@
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E869" s="2" t="n">
         <f aca="false">A869 +1000</f>
@@ -19061,7 +19139,7 @@
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="E870" s="2" t="n">
         <f aca="false">A870 +1000</f>
@@ -19079,7 +19157,7 @@
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E871" s="2" t="n">
         <f aca="false">A871 +1000</f>
@@ -19097,7 +19175,7 @@
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="E872" s="2" t="n">
         <f aca="false">A872 +1000</f>
@@ -19115,7 +19193,7 @@
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E873" s="2" t="n">
         <f aca="false">A873 +1000</f>
@@ -19133,7 +19211,7 @@
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E874" s="2" t="n">
         <f aca="false">A874 +1000</f>
@@ -19151,7 +19229,7 @@
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="E875" s="2" t="n">
         <f aca="false">A875 +1000</f>
@@ -19169,7 +19247,7 @@
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E876" s="2" t="n">
         <f aca="false">A876 +1000</f>
@@ -19187,7 +19265,7 @@
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E877" s="2" t="n">
         <f aca="false">A877 +1000</f>
@@ -19205,7 +19283,7 @@
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E878" s="2" t="n">
         <f aca="false">A878 +1000</f>
@@ -19223,7 +19301,7 @@
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E879" s="2" t="n">
         <f aca="false">A879 +1000</f>
@@ -19241,7 +19319,7 @@
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E880" s="2" t="n">
         <f aca="false">A880 +1000</f>
@@ -19259,7 +19337,7 @@
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E881" s="2" t="n">
         <f aca="false">A881 +1000</f>
@@ -19277,7 +19355,7 @@
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E882" s="2" t="n">
         <f aca="false">A882 +1000</f>
@@ -19295,7 +19373,7 @@
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E883" s="2" t="n">
         <f aca="false">A883 +1000</f>
@@ -19313,7 +19391,7 @@
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E884" s="2" t="n">
         <f aca="false">A884 +1000</f>
@@ -19331,7 +19409,7 @@
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E885" s="2" t="n">
         <f aca="false">A885 +1000</f>
@@ -19349,7 +19427,7 @@
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E886" s="2" t="n">
         <f aca="false">A886 +1000</f>
@@ -19367,7 +19445,7 @@
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E887" s="2" t="n">
         <f aca="false">A887 +1000</f>
@@ -19385,7 +19463,7 @@
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E888" s="2" t="n">
         <f aca="false">A888 +1000</f>
@@ -19403,7 +19481,7 @@
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="E889" s="2" t="n">
         <f aca="false">A889 +1000</f>
@@ -19421,7 +19499,7 @@
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E890" s="2" t="n">
         <f aca="false">A890 +1000</f>
@@ -19439,7 +19517,7 @@
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E891" s="2" t="n">
         <f aca="false">A891 +1000</f>
@@ -19457,7 +19535,7 @@
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E892" s="2" t="n">
         <f aca="false">A892 +1000</f>
@@ -19475,7 +19553,7 @@
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E893" s="2" t="n">
         <f aca="false">A893 +1000</f>
@@ -19493,7 +19571,7 @@
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E894" s="2" t="n">
         <f aca="false">A894 +1000</f>
@@ -19511,7 +19589,7 @@
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="E895" s="2" t="n">
         <f aca="false">A895 +1000</f>
@@ -19529,7 +19607,7 @@
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E896" s="2" t="n">
         <f aca="false">A896 +1000</f>
@@ -19547,7 +19625,7 @@
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E897" s="2" t="n">
         <f aca="false">A897 +1000</f>
@@ -19565,7 +19643,7 @@
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E898" s="2" t="n">
         <f aca="false">A898 +1000</f>
@@ -19583,7 +19661,7 @@
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E899" s="2" t="n">
         <f aca="false">A899 +1000</f>
@@ -19601,7 +19679,7 @@
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E900" s="2" t="n">
         <f aca="false">A900 +1000</f>
@@ -19619,7 +19697,7 @@
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E901" s="2" t="n">
         <f aca="false">A901 +1000</f>
@@ -19637,7 +19715,7 @@
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E902" s="2" t="n">
         <f aca="false">A902 +1000</f>
@@ -19655,7 +19733,7 @@
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E903" s="2" t="n">
         <f aca="false">A903 +1000</f>
@@ -19673,7 +19751,7 @@
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E904" s="2" t="n">
         <f aca="false">A904 +1000</f>
@@ -19691,7 +19769,7 @@
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E905" s="2" t="n">
         <f aca="false">A905 +1000</f>
@@ -19709,7 +19787,7 @@
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E906" s="2" t="n">
         <f aca="false">A906 +1000</f>
@@ -19727,7 +19805,7 @@
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E907" s="2" t="n">
         <f aca="false">A907 +1000</f>
@@ -19745,7 +19823,7 @@
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E908" s="2" t="n">
         <f aca="false">A908 +1000</f>
@@ -19763,7 +19841,7 @@
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E909" s="2" t="n">
         <f aca="false">A909 +1000</f>
@@ -19781,7 +19859,7 @@
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E910" s="2" t="n">
         <f aca="false">A910 +1000</f>
@@ -19799,7 +19877,7 @@
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E911" s="2" t="n">
         <f aca="false">A911 +1000</f>
@@ -19817,7 +19895,7 @@
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E912" s="2" t="n">
         <f aca="false">A912 +1000</f>
@@ -19835,7 +19913,7 @@
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E913" s="2" t="n">
         <f aca="false">A913 +1000</f>
@@ -19853,7 +19931,7 @@
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E914" s="2" t="n">
         <f aca="false">A914 +1000</f>
@@ -19871,7 +19949,7 @@
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="1" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="E915" s="2" t="n">
         <f aca="false">A915 +1000</f>
@@ -19889,7 +19967,7 @@
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="E916" s="2" t="n">
         <f aca="false">A916 +1000</f>
@@ -19907,7 +19985,7 @@
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E917" s="2" t="n">
         <f aca="false">A917 +1000</f>
@@ -19925,7 +20003,7 @@
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E918" s="2" t="n">
         <f aca="false">A918 +1000</f>
@@ -19943,7 +20021,7 @@
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E919" s="2" t="n">
         <f aca="false">A919 +1000</f>
@@ -19961,7 +20039,7 @@
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="1" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E920" s="2" t="n">
         <f aca="false">A920 +1000</f>
@@ -19979,7 +20057,7 @@
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="1" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E921" s="2" t="n">
         <f aca="false">A921 +1000</f>
@@ -19997,7 +20075,7 @@
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E922" s="2" t="n">
         <f aca="false">A922 +1000</f>
@@ -20015,7 +20093,7 @@
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="1" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="E923" s="2" t="n">
         <f aca="false">A923 +1000</f>
@@ -20033,7 +20111,7 @@
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E924" s="2" t="n">
         <f aca="false">A924 +1000</f>
@@ -20051,7 +20129,7 @@
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E925" s="2" t="n">
         <f aca="false">A925 +1000</f>
@@ -20069,7 +20147,7 @@
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E926" s="2" t="n">
         <f aca="false">A926 +1000</f>
@@ -20087,7 +20165,7 @@
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E927" s="2" t="n">
         <f aca="false">A927 +1000</f>
@@ -20105,7 +20183,7 @@
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="1" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E928" s="2" t="n">
         <f aca="false">A928 +1000</f>
@@ -20123,7 +20201,7 @@
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E929" s="2" t="n">
         <f aca="false">A929 +1000</f>
@@ -20141,7 +20219,7 @@
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="1" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E930" s="2" t="n">
         <f aca="false">A930 +1000</f>
@@ -20159,7 +20237,7 @@
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="E931" s="2" t="n">
         <f aca="false">A931 +1000</f>
@@ -20177,7 +20255,7 @@
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E932" s="2" t="n">
         <f aca="false">A932 +1000</f>
@@ -20195,7 +20273,7 @@
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="E933" s="2" t="n">
         <f aca="false">A933 +1000</f>
@@ -20213,7 +20291,7 @@
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="1" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E934" s="2" t="n">
         <f aca="false">A934 +1000</f>
@@ -20231,7 +20309,7 @@
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E935" s="2" t="n">
         <f aca="false">A935 +1000</f>
@@ -20249,7 +20327,7 @@
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E936" s="2" t="n">
         <f aca="false">A936 +1000</f>
@@ -20267,7 +20345,7 @@
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="E937" s="2" t="n">
         <f aca="false">A937 +1000</f>
@@ -20285,7 +20363,7 @@
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="1" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E938" s="2" t="n">
         <f aca="false">A938 +1000</f>
@@ -20303,7 +20381,7 @@
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="1" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="E939" s="2" t="n">
         <f aca="false">A939 +1000</f>
@@ -20321,7 +20399,7 @@
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="1" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E940" s="2" t="n">
         <f aca="false">A940 +1000</f>
@@ -20339,7 +20417,7 @@
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E941" s="2" t="n">
         <f aca="false">A941 +1000</f>
@@ -20357,7 +20435,7 @@
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="1" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E942" s="2" t="n">
         <f aca="false">A942 +1000</f>
@@ -20375,7 +20453,7 @@
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="1" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E943" s="2" t="n">
         <f aca="false">A943 +1000</f>
@@ -20393,7 +20471,7 @@
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="1" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E944" s="2" t="n">
         <f aca="false">A944 +1000</f>
@@ -20411,7 +20489,7 @@
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="E945" s="2" t="n">
         <f aca="false">A945 +1000</f>
@@ -20429,7 +20507,7 @@
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E946" s="2" t="n">
         <f aca="false">A946 +1000</f>
@@ -20447,7 +20525,7 @@
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E947" s="2" t="n">
         <f aca="false">A947 +1000</f>
@@ -20465,7 +20543,7 @@
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E948" s="2" t="n">
         <f aca="false">A948 +1000</f>
@@ -20483,7 +20561,7 @@
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="E949" s="2" t="n">
         <f aca="false">A949 +1000</f>
@@ -20501,7 +20579,7 @@
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E950" s="2" t="n">
         <f aca="false">A950 +1000</f>
@@ -20519,7 +20597,7 @@
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="E951" s="2" t="n">
         <f aca="false">A951 +1000</f>
@@ -20537,7 +20615,7 @@
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E952" s="2" t="n">
         <f aca="false">A952 +1000</f>
@@ -20555,7 +20633,7 @@
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E953" s="2" t="n">
         <f aca="false">A953 +1000</f>
@@ -20573,7 +20651,7 @@
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="E954" s="2" t="n">
         <f aca="false">A954 +1000</f>
@@ -20591,7 +20669,7 @@
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="E955" s="2" t="n">
         <f aca="false">A955 +1000</f>
@@ -20609,7 +20687,7 @@
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E956" s="2" t="n">
         <f aca="false">A956 +1000</f>
@@ -20627,7 +20705,7 @@
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="E957" s="2" t="n">
         <f aca="false">A957 +1000</f>
@@ -20645,7 +20723,7 @@
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="E958" s="2" t="n">
         <f aca="false">A958 +1000</f>
@@ -20663,7 +20741,7 @@
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E959" s="2" t="n">
         <f aca="false">A959 +1000</f>
@@ -20681,7 +20759,7 @@
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E960" s="2" t="n">
         <f aca="false">A960 +1000</f>
@@ -20699,7 +20777,7 @@
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="E961" s="2" t="n">
         <f aca="false">A961 +1000</f>
@@ -20717,7 +20795,7 @@
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="E962" s="2" t="n">
         <f aca="false">A962 +1000</f>
@@ -20735,7 +20813,7 @@
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E963" s="2" t="n">
         <f aca="false">A963 +1000</f>
@@ -20753,7 +20831,7 @@
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="1" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="E964" s="2" t="n">
         <f aca="false">A964 +1000</f>
@@ -20771,7 +20849,7 @@
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E965" s="2" t="n">
         <f aca="false">A965 +1000</f>
@@ -20789,7 +20867,7 @@
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E966" s="2" t="n">
         <f aca="false">A966 +1000</f>
@@ -20807,7 +20885,7 @@
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="1" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="E967" s="2" t="n">
         <f aca="false">A967 +1000</f>
@@ -20825,7 +20903,7 @@
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="1" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E968" s="2" t="n">
         <f aca="false">A968 +1000</f>
@@ -20843,7 +20921,7 @@
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E969" s="2" t="n">
         <f aca="false">A969 +1000</f>
@@ -20861,7 +20939,7 @@
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E970" s="2" t="n">
         <f aca="false">A970 +1000</f>
@@ -20879,7 +20957,7 @@
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E971" s="2" t="n">
         <f aca="false">A971 +1000</f>
@@ -20897,7 +20975,7 @@
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E972" s="2" t="n">
         <f aca="false">A972 +1000</f>
@@ -20915,7 +20993,7 @@
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="1" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E973" s="2" t="n">
         <f aca="false">A973 +1000</f>
@@ -20933,7 +21011,7 @@
     </row>
     <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="E974" s="2" t="n">
         <f aca="false">A974 +1000</f>
@@ -20957,7 +21035,7 @@
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="1" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="E975" s="2" t="n">
         <f aca="false">A975 +1000</f>
@@ -20975,7 +21053,7 @@
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="1" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E976" s="2" t="n">
         <f aca="false">A976 +1000</f>
@@ -20993,7 +21071,7 @@
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="1" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="E977" s="2" t="n">
         <f aca="false">A977 +1000</f>
@@ -21011,7 +21089,7 @@
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="1" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="E978" s="2" t="n">
         <f aca="false">A978 +1000</f>
@@ -21029,7 +21107,7 @@
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="1" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E979" s="2" t="n">
         <f aca="false">A979 +1000</f>
@@ -21047,7 +21125,7 @@
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="1" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E980" s="2" t="n">
         <f aca="false">A980 +1000</f>
@@ -21065,7 +21143,7 @@
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E981" s="2" t="n">
         <f aca="false">A981 +1000</f>
@@ -21083,7 +21161,7 @@
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E982" s="2" t="n">
         <f aca="false">A982 +1000</f>
@@ -21101,7 +21179,7 @@
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="E983" s="2" t="n">
         <f aca="false">A983 +1000</f>
@@ -21119,7 +21197,7 @@
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="E984" s="2" t="n">
         <f aca="false">A984 +1000</f>
@@ -21137,7 +21215,7 @@
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E985" s="2" t="n">
         <f aca="false">A985 +1000</f>
@@ -21155,7 +21233,7 @@
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="1" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="E986" s="2" t="n">
         <f aca="false">A986 +1000</f>
@@ -21173,7 +21251,7 @@
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="E987" s="2" t="n">
         <f aca="false">A987 +1000</f>
@@ -21191,7 +21269,7 @@
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="1" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E988" s="2" t="n">
         <f aca="false">A988 +1000</f>
@@ -21209,7 +21287,7 @@
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="E989" s="2" t="n">
         <f aca="false">A989 +1000</f>
@@ -21227,7 +21305,7 @@
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="E990" s="2" t="n">
         <f aca="false">A990 +1000</f>
@@ -21245,7 +21323,7 @@
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E991" s="2" t="n">
         <f aca="false">A991 +1000</f>
@@ -21263,7 +21341,7 @@
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E992" s="2" t="n">
         <f aca="false">A992 +1000</f>
@@ -21281,7 +21359,7 @@
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E993" s="2" t="n">
         <f aca="false">A993 +1000</f>
@@ -21299,7 +21377,7 @@
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="1" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E994" s="2" t="n">
         <f aca="false">A994 +1000</f>
@@ -21317,7 +21395,7 @@
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="E995" s="2" t="n">
         <f aca="false">A995 +1000</f>
@@ -21335,7 +21413,7 @@
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="E996" s="2" t="n">
         <f aca="false">A996 +1000</f>
@@ -21353,7 +21431,7 @@
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E997" s="2" t="n">
         <f aca="false">A997 +1000</f>
@@ -21371,7 +21449,7 @@
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="1" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E998" s="2" t="n">
         <f aca="false">A998 +1000</f>
@@ -21389,7 +21467,7 @@
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="E999" s="2" t="n">
         <f aca="false">A999 +1000</f>
@@ -21407,7 +21485,7 @@
     </row>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="1" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E1000" s="2" t="n">
         <f aca="false">A1000 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="1007">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -49,6 +49,12 @@
     <t xml:space="preserve">0008</t>
   </si>
   <si>
+    <t xml:space="preserve">✅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use in &amp; pre </t>
+  </si>
+  <si>
     <t xml:space="preserve">0009</t>
   </si>
   <si>
@@ -91,9 +97,6 @@
     <t xml:space="preserve">0022</t>
   </si>
   <si>
-    <t xml:space="preserve">✅</t>
-  </si>
-  <si>
     <t xml:space="preserve">0023</t>
   </si>
   <si>
@@ -322,6 +325,9 @@
     <t xml:space="preserve">0098</t>
   </si>
   <si>
+    <t xml:space="preserve">use Helper Function</t>
+  </si>
+  <si>
     <t xml:space="preserve">0099</t>
   </si>
   <si>
@@ -734,6 +740,9 @@
   </si>
   <si>
     <t xml:space="preserve">0235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;,&gt;  OR &lt;,&lt;</t>
   </si>
   <si>
     <t xml:space="preserve">0236</t>
@@ -3424,6 +3433,15 @@
         <f aca="false">A9 +1000</f>
         <v>1008</v>
       </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>10</v>
+      </c>
       <c r="I9" s="2" t="n">
         <f aca="false">E9 +1000</f>
         <v>2008</v>
@@ -3436,7 +3454,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">A10 +1000</f>
@@ -3454,7 +3472,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">A11 +1000</f>
@@ -3472,7 +3490,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">A12 +1000</f>
@@ -3490,7 +3508,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">A13 +1000</f>
@@ -3508,7 +3526,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">A14 +1000</f>
@@ -3526,7 +3544,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
         <f aca="false">A15 +1000</f>
@@ -3544,7 +3562,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E16" s="2" t="n">
         <f aca="false">A16 +1000</f>
@@ -3562,7 +3580,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E17" s="2" t="n">
         <f aca="false">A17 +1000</f>
@@ -3580,7 +3598,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2" t="n">
         <f aca="false">A18 +1000</f>
@@ -3598,7 +3616,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2" t="n">
         <f aca="false">A19 +1000</f>
@@ -3616,7 +3634,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2" t="n">
         <f aca="false">A20 +1000</f>
@@ -3634,7 +3652,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E21" s="2" t="n">
         <f aca="false">A21 +1000</f>
@@ -3652,7 +3670,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E22" s="2" t="n">
         <f aca="false">A22 +1000</f>
@@ -3670,13 +3688,13 @@
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="n">
         <f aca="false">A23 +1000</f>
@@ -3694,13 +3712,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="n">
         <f aca="false">A24 +1000</f>
@@ -3718,7 +3736,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="2" t="n">
         <f aca="false">A25 +1000</f>
@@ -3736,7 +3754,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="2" t="n">
         <f aca="false">A26 +1000</f>
@@ -3754,7 +3772,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="n">
         <f aca="false">A27 +1000</f>
@@ -3772,7 +3790,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E28" s="2" t="n">
         <f aca="false">A28 +1000</f>
@@ -3790,7 +3808,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E29" s="2" t="n">
         <f aca="false">A29 +1000</f>
@@ -3808,7 +3826,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">A30 +1000</f>
@@ -3826,7 +3844,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">A31 +1000</f>
@@ -3844,7 +3862,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">A32 +1000</f>
@@ -3862,7 +3880,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">A33 +1000</f>
@@ -3880,7 +3898,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2" t="n">
         <f aca="false">A34 +1000</f>
@@ -3898,7 +3916,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35" s="2" t="n">
         <f aca="false">A35 +1000</f>
@@ -3916,7 +3934,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E36" s="2" t="n">
         <f aca="false">A36 +1000</f>
@@ -3934,7 +3952,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E37" s="2" t="n">
         <f aca="false">A37 +1000</f>
@@ -3952,7 +3970,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2" t="n">
         <f aca="false">A38 +1000</f>
@@ -3970,7 +3988,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E39" s="2" t="n">
         <f aca="false">A39 +1000</f>
@@ -3988,7 +4006,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2" t="n">
         <f aca="false">A40 +1000</f>
@@ -4006,7 +4024,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E41" s="2" t="n">
         <f aca="false">A41 +1000</f>
@@ -4024,7 +4042,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E42" s="2" t="n">
         <f aca="false">A42 +1000</f>
@@ -4042,7 +4060,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E43" s="2" t="n">
         <f aca="false">A43 +1000</f>
@@ -4060,7 +4078,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E44" s="2" t="n">
         <f aca="false">A44 +1000</f>
@@ -4078,7 +4096,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E45" s="2" t="n">
         <f aca="false">A45 +1000</f>
@@ -4096,17 +4114,17 @@
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E46" s="2" t="n">
         <f aca="false">A46 +1000</f>
         <v>1045</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I46" s="2" t="n">
         <f aca="false">E46 +1000</f>
@@ -4120,7 +4138,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E47" s="2" t="n">
         <f aca="false">A47 +1000</f>
@@ -4138,7 +4156,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E48" s="2" t="n">
         <f aca="false">A48 +1000</f>
@@ -4156,7 +4174,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E49" s="2" t="n">
         <f aca="false">A49 +1000</f>
@@ -4174,7 +4192,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E50" s="2" t="n">
         <f aca="false">A50 +1000</f>
@@ -4192,7 +4210,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E51" s="2" t="n">
         <f aca="false">A51 +1000</f>
@@ -4210,7 +4228,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E52" s="2" t="n">
         <f aca="false">A52 +1000</f>
@@ -4228,7 +4246,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E53" s="2" t="n">
         <f aca="false">A53 +1000</f>
@@ -4246,7 +4264,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E54" s="2" t="n">
         <f aca="false">A54 +1000</f>
@@ -4264,7 +4282,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E55" s="2" t="n">
         <f aca="false">A55 +1000</f>
@@ -4282,7 +4300,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E56" s="2" t="n">
         <f aca="false">A56 +1000</f>
@@ -4300,7 +4318,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E57" s="2" t="n">
         <f aca="false">A57 +1000</f>
@@ -4318,7 +4336,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E58" s="2" t="n">
         <f aca="false">A58 +1000</f>
@@ -4336,7 +4354,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E59" s="2" t="n">
         <f aca="false">A59 +1000</f>
@@ -4354,7 +4372,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E60" s="2" t="n">
         <f aca="false">A60 +1000</f>
@@ -4372,7 +4390,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E61" s="2" t="n">
         <f aca="false">A61 +1000</f>
@@ -4390,7 +4408,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E62" s="2" t="n">
         <f aca="false">A62 +1000</f>
@@ -4408,7 +4426,7 @@
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E63" s="2" t="n">
         <f aca="false">A63 +1000</f>
@@ -4426,7 +4444,7 @@
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E64" s="2" t="n">
         <f aca="false">A64 +1000</f>
@@ -4444,7 +4462,7 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E65" s="2" t="n">
         <f aca="false">A65 +1000</f>
@@ -4462,7 +4480,7 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E66" s="2" t="n">
         <f aca="false">A66 +1000</f>
@@ -4480,7 +4498,7 @@
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E67" s="2" t="n">
         <f aca="false">A67 +1000</f>
@@ -4498,7 +4516,7 @@
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E68" s="2" t="n">
         <f aca="false">A68 +1000</f>
@@ -4516,7 +4534,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E69" s="2" t="n">
         <f aca="false">A69 +1000</f>
@@ -4534,7 +4552,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E70" s="2" t="n">
         <f aca="false">A70 +1000</f>
@@ -4552,7 +4570,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E71" s="2" t="n">
         <f aca="false">A71 +1000</f>
@@ -4570,7 +4588,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E72" s="2" t="n">
         <f aca="false">A72 +1000</f>
@@ -4588,7 +4606,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E73" s="2" t="n">
         <f aca="false">A73 +1000</f>
@@ -4606,7 +4624,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E74" s="2" t="n">
         <f aca="false">A74 +1000</f>
@@ -4624,7 +4642,7 @@
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E75" s="2" t="n">
         <f aca="false">A75 +1000</f>
@@ -4642,7 +4660,7 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2" t="n">
         <f aca="false">A76 +1000</f>
@@ -4660,7 +4678,7 @@
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E77" s="2" t="n">
         <f aca="false">A77 +1000</f>
@@ -4678,7 +4696,7 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E78" s="2" t="n">
         <f aca="false">A78 +1000</f>
@@ -4696,7 +4714,7 @@
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E79" s="2" t="n">
         <f aca="false">A79 +1000</f>
@@ -4714,7 +4732,7 @@
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E80" s="2" t="n">
         <f aca="false">A80 +1000</f>
@@ -4732,7 +4750,7 @@
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2" t="n">
         <f aca="false">A81 +1000</f>
@@ -4750,7 +4768,7 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E82" s="2" t="n">
         <f aca="false">A82 +1000</f>
@@ -4768,7 +4786,7 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E83" s="2" t="n">
         <f aca="false">A83 +1000</f>
@@ -4786,7 +4804,7 @@
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E84" s="2" t="n">
         <f aca="false">A84 +1000</f>
@@ -4804,7 +4822,7 @@
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E85" s="2" t="n">
         <f aca="false">A85 +1000</f>
@@ -4822,7 +4840,7 @@
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E86" s="2" t="n">
         <f aca="false">A86 +1000</f>
@@ -4840,7 +4858,7 @@
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E87" s="2" t="n">
         <f aca="false">A87 +1000</f>
@@ -4858,7 +4876,7 @@
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E88" s="2" t="n">
         <f aca="false">A88 +1000</f>
@@ -4876,7 +4894,7 @@
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E89" s="2" t="n">
         <f aca="false">A89 +1000</f>
@@ -4894,7 +4912,7 @@
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E90" s="2" t="n">
         <f aca="false">A90 +1000</f>
@@ -4912,7 +4930,7 @@
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E91" s="2" t="n">
         <f aca="false">A91 +1000</f>
@@ -4930,7 +4948,7 @@
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E92" s="2" t="n">
         <f aca="false">A92 +1000</f>
@@ -4948,7 +4966,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E93" s="2" t="n">
         <f aca="false">A93 +1000</f>
@@ -4966,7 +4984,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E94" s="2" t="n">
         <f aca="false">A94 +1000</f>
@@ -4984,7 +5002,7 @@
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E95" s="2" t="n">
         <f aca="false">A95 +1000</f>
@@ -5002,7 +5020,7 @@
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E96" s="2" t="n">
         <f aca="false">A96 +1000</f>
@@ -5020,7 +5038,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E97" s="2" t="n">
         <f aca="false">A97 +1000</f>
@@ -5038,7 +5056,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E98" s="2" t="n">
         <f aca="false">A98 +1000</f>
@@ -5056,7 +5074,16 @@
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="0" t="s">
+        <v>101</v>
       </c>
       <c r="E99" s="2" t="n">
         <f aca="false">A99 +1000</f>
@@ -5067,10 +5094,10 @@
         <v>2098</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M99" s="2" t="n">
         <f aca="false">I99 +1000</f>
@@ -5080,7 +5107,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E100" s="2" t="n">
         <f aca="false">A100 +1000</f>
@@ -5098,7 +5125,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E101" s="2" t="n">
         <f aca="false">A101 +1000</f>
@@ -5116,7 +5143,7 @@
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E102" s="2" t="n">
         <f aca="false">A102 +1000</f>
@@ -5134,7 +5161,7 @@
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E103" s="2" t="n">
         <f aca="false">A103 +1000</f>
@@ -5152,7 +5179,7 @@
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E104" s="2" t="n">
         <f aca="false">A104 +1000</f>
@@ -5170,7 +5197,7 @@
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E105" s="2" t="n">
         <f aca="false">A105 +1000</f>
@@ -5188,7 +5215,7 @@
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E106" s="2" t="n">
         <f aca="false">A106 +1000</f>
@@ -5206,7 +5233,7 @@
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E107" s="2" t="n">
         <f aca="false">A107 +1000</f>
@@ -5224,7 +5251,7 @@
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E108" s="2" t="n">
         <f aca="false">A108 +1000</f>
@@ -5242,7 +5269,7 @@
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E109" s="2" t="n">
         <f aca="false">A109 +1000</f>
@@ -5260,7 +5287,7 @@
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E110" s="2" t="n">
         <f aca="false">A110 +1000</f>
@@ -5278,7 +5305,7 @@
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E111" s="2" t="n">
         <f aca="false">A111 +1000</f>
@@ -5296,7 +5323,7 @@
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E112" s="2" t="n">
         <f aca="false">A112 +1000</f>
@@ -5314,7 +5341,7 @@
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E113" s="2" t="n">
         <f aca="false">A113 +1000</f>
@@ -5332,7 +5359,7 @@
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E114" s="2" t="n">
         <f aca="false">A114 +1000</f>
@@ -5350,7 +5377,7 @@
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E115" s="2" t="n">
         <f aca="false">A115 +1000</f>
@@ -5368,7 +5395,7 @@
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E116" s="2" t="n">
         <f aca="false">A116 +1000</f>
@@ -5386,7 +5413,7 @@
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E117" s="2" t="n">
         <f aca="false">A117 +1000</f>
@@ -5404,7 +5431,7 @@
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E118" s="2" t="n">
         <f aca="false">A118 +1000</f>
@@ -5422,7 +5449,7 @@
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E119" s="2" t="n">
         <f aca="false">A119 +1000</f>
@@ -5440,7 +5467,7 @@
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E120" s="2" t="n">
         <f aca="false">A120 +1000</f>
@@ -5458,7 +5485,7 @@
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E121" s="2" t="n">
         <f aca="false">A121 +1000</f>
@@ -5476,7 +5503,7 @@
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E122" s="2" t="n">
         <f aca="false">A122 +1000</f>
@@ -5494,7 +5521,7 @@
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E123" s="2" t="n">
         <f aca="false">A123 +1000</f>
@@ -5512,7 +5539,7 @@
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E124" s="2" t="n">
         <f aca="false">A124 +1000</f>
@@ -5530,7 +5557,7 @@
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E125" s="2" t="n">
         <f aca="false">A125 +1000</f>
@@ -5548,7 +5575,7 @@
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E126" s="2" t="n">
         <f aca="false">A126 +1000</f>
@@ -5566,7 +5593,7 @@
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E127" s="2" t="n">
         <f aca="false">A127 +1000</f>
@@ -5584,7 +5611,7 @@
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E128" s="2" t="n">
         <f aca="false">A128 +1000</f>
@@ -5602,7 +5629,7 @@
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E129" s="2" t="n">
         <f aca="false">A129 +1000</f>
@@ -5620,7 +5647,7 @@
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E130" s="2" t="n">
         <f aca="false">A130 +1000</f>
@@ -5638,7 +5665,7 @@
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E131" s="2" t="n">
         <f aca="false">A131 +1000</f>
@@ -5656,7 +5683,7 @@
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E132" s="2" t="n">
         <f aca="false">A132 +1000</f>
@@ -5674,7 +5701,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E133" s="2" t="n">
         <f aca="false">A133 +1000</f>
@@ -5692,7 +5719,7 @@
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E134" s="2" t="n">
         <f aca="false">A134 +1000</f>
@@ -5710,7 +5737,7 @@
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E135" s="2" t="n">
         <f aca="false">A135 +1000</f>
@@ -5728,7 +5755,7 @@
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E136" s="2" t="n">
         <f aca="false">A136 +1000</f>
@@ -5746,7 +5773,7 @@
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E137" s="2" t="n">
         <f aca="false">A137 +1000</f>
@@ -5764,7 +5791,7 @@
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E138" s="2" t="n">
         <f aca="false">A138 +1000</f>
@@ -5782,7 +5809,7 @@
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E139" s="2" t="n">
         <f aca="false">A139 +1000</f>
@@ -5800,7 +5827,7 @@
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E140" s="2" t="n">
         <f aca="false">A140 +1000</f>
@@ -5818,7 +5845,7 @@
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E141" s="2" t="n">
         <f aca="false">A141 +1000</f>
@@ -5836,7 +5863,7 @@
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E142" s="2" t="n">
         <f aca="false">A142 +1000</f>
@@ -5854,7 +5881,7 @@
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E143" s="2" t="n">
         <f aca="false">A143 +1000</f>
@@ -5872,7 +5899,7 @@
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E144" s="2" t="n">
         <f aca="false">A144 +1000</f>
@@ -5890,7 +5917,7 @@
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E145" s="2" t="n">
         <f aca="false">A145 +1000</f>
@@ -5908,7 +5935,7 @@
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E146" s="2" t="n">
         <f aca="false">A146 +1000</f>
@@ -5926,7 +5953,7 @@
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E147" s="2" t="n">
         <f aca="false">A147 +1000</f>
@@ -5944,7 +5971,7 @@
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E148" s="2" t="n">
         <f aca="false">A148 +1000</f>
@@ -5962,7 +5989,7 @@
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E149" s="2" t="n">
         <f aca="false">A149 +1000</f>
@@ -5980,7 +6007,7 @@
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E150" s="2" t="n">
         <f aca="false">A150 +1000</f>
@@ -5998,7 +6025,7 @@
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E151" s="2" t="n">
         <f aca="false">A151 +1000</f>
@@ -6016,7 +6043,7 @@
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E152" s="2" t="n">
         <f aca="false">A152 +1000</f>
@@ -6034,7 +6061,7 @@
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E153" s="2" t="n">
         <f aca="false">A153 +1000</f>
@@ -6052,7 +6079,7 @@
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E154" s="2" t="n">
         <f aca="false">A154 +1000</f>
@@ -6070,7 +6097,7 @@
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E155" s="2" t="n">
         <f aca="false">A155 +1000</f>
@@ -6088,7 +6115,7 @@
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E156" s="2" t="n">
         <f aca="false">A156 +1000</f>
@@ -6106,7 +6133,7 @@
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E157" s="2" t="n">
         <f aca="false">A157 +1000</f>
@@ -6124,7 +6151,7 @@
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E158" s="2" t="n">
         <f aca="false">A158 +1000</f>
@@ -6142,7 +6169,7 @@
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E159" s="2" t="n">
         <f aca="false">A159 +1000</f>
@@ -6160,7 +6187,7 @@
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E160" s="2" t="n">
         <f aca="false">A160 +1000</f>
@@ -6178,7 +6205,7 @@
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E161" s="2" t="n">
         <f aca="false">A161 +1000</f>
@@ -6196,7 +6223,7 @@
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E162" s="2" t="n">
         <f aca="false">A162 +1000</f>
@@ -6214,7 +6241,7 @@
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E163" s="2" t="n">
         <f aca="false">A163 +1000</f>
@@ -6232,7 +6259,7 @@
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E164" s="2" t="n">
         <f aca="false">A164 +1000</f>
@@ -6250,7 +6277,7 @@
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E165" s="2" t="n">
         <f aca="false">A165 +1000</f>
@@ -6268,7 +6295,7 @@
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E166" s="2" t="n">
         <f aca="false">A166 +1000</f>
@@ -6286,7 +6313,7 @@
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E167" s="2" t="n">
         <f aca="false">A167 +1000</f>
@@ -6304,7 +6331,7 @@
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E168" s="2" t="n">
         <f aca="false">A168 +1000</f>
@@ -6322,7 +6349,7 @@
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E169" s="2" t="n">
         <f aca="false">A169 +1000</f>
@@ -6340,7 +6367,7 @@
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E170" s="2" t="n">
         <f aca="false">A170 +1000</f>
@@ -6358,7 +6385,7 @@
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E171" s="2" t="n">
         <f aca="false">A171 +1000</f>
@@ -6376,7 +6403,7 @@
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E172" s="2" t="n">
         <f aca="false">A172 +1000</f>
@@ -6394,7 +6421,7 @@
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E173" s="2" t="n">
         <f aca="false">A173 +1000</f>
@@ -6412,7 +6439,7 @@
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E174" s="2" t="n">
         <f aca="false">A174 +1000</f>
@@ -6430,7 +6457,7 @@
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E175" s="2" t="n">
         <f aca="false">A175 +1000</f>
@@ -6448,7 +6475,7 @@
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E176" s="2" t="n">
         <f aca="false">A176 +1000</f>
@@ -6466,7 +6493,7 @@
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E177" s="2" t="n">
         <f aca="false">A177 +1000</f>
@@ -6484,7 +6511,7 @@
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E178" s="2" t="n">
         <f aca="false">A178 +1000</f>
@@ -6502,7 +6529,7 @@
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E179" s="2" t="n">
         <f aca="false">A179 +1000</f>
@@ -6520,7 +6547,7 @@
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E180" s="2" t="n">
         <f aca="false">A180 +1000</f>
@@ -6538,7 +6565,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E181" s="2" t="n">
         <f aca="false">A181 +1000</f>
@@ -6556,7 +6583,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E182" s="2" t="n">
         <f aca="false">A182 +1000</f>
@@ -6574,7 +6601,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E183" s="2" t="n">
         <f aca="false">A183 +1000</f>
@@ -6592,7 +6619,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E184" s="2" t="n">
         <f aca="false">A184 +1000</f>
@@ -6610,7 +6637,7 @@
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E185" s="2" t="n">
         <f aca="false">A185 +1000</f>
@@ -6628,7 +6655,7 @@
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E186" s="2" t="n">
         <f aca="false">A186 +1000</f>
@@ -6646,7 +6673,7 @@
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E187" s="2" t="n">
         <f aca="false">A187 +1000</f>
@@ -6664,7 +6691,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E188" s="2" t="n">
         <f aca="false">A188 +1000</f>
@@ -6682,7 +6709,7 @@
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E189" s="2" t="n">
         <f aca="false">A189 +1000</f>
@@ -6700,7 +6727,7 @@
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E190" s="2" t="n">
         <f aca="false">A190 +1000</f>
@@ -6718,7 +6745,7 @@
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E191" s="2" t="n">
         <f aca="false">A191 +1000</f>
@@ -6736,7 +6763,7 @@
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E192" s="2" t="n">
         <f aca="false">A192 +1000</f>
@@ -6754,7 +6781,7 @@
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E193" s="2" t="n">
         <f aca="false">A193 +1000</f>
@@ -6772,7 +6799,7 @@
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E194" s="2" t="n">
         <f aca="false">A194 +1000</f>
@@ -6790,7 +6817,7 @@
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E195" s="2" t="n">
         <f aca="false">A195 +1000</f>
@@ -6808,7 +6835,7 @@
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E196" s="2" t="n">
         <f aca="false">A196 +1000</f>
@@ -6826,7 +6853,7 @@
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E197" s="2" t="n">
         <f aca="false">A197 +1000</f>
@@ -6844,7 +6871,7 @@
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E198" s="2" t="n">
         <f aca="false">A198 +1000</f>
@@ -6862,7 +6889,7 @@
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E199" s="2" t="n">
         <f aca="false">A199 +1000</f>
@@ -6880,7 +6907,7 @@
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E200" s="2" t="n">
         <f aca="false">A200 +1000</f>
@@ -6898,7 +6925,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E201" s="2" t="n">
         <f aca="false">A201 +1000</f>
@@ -6916,7 +6943,7 @@
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E202" s="2" t="n">
         <f aca="false">A202 +1000</f>
@@ -6934,7 +6961,7 @@
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E203" s="2" t="n">
         <f aca="false">A203 +1000</f>
@@ -6952,7 +6979,7 @@
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E204" s="2" t="n">
         <f aca="false">A204 +1000</f>
@@ -6970,7 +6997,7 @@
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E205" s="2" t="n">
         <f aca="false">A205 +1000</f>
@@ -6988,7 +7015,7 @@
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E206" s="2" t="n">
         <f aca="false">A206 +1000</f>
@@ -7006,7 +7033,7 @@
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E207" s="2" t="n">
         <f aca="false">A207 +1000</f>
@@ -7024,7 +7051,7 @@
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E208" s="2" t="n">
         <f aca="false">A208 +1000</f>
@@ -7042,7 +7069,7 @@
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E209" s="2" t="n">
         <f aca="false">A209 +1000</f>
@@ -7060,7 +7087,7 @@
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E210" s="2" t="n">
         <f aca="false">A210 +1000</f>
@@ -7078,7 +7105,7 @@
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E211" s="2" t="n">
         <f aca="false">A211 +1000</f>
@@ -7096,7 +7123,7 @@
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E212" s="2" t="n">
         <f aca="false">A212 +1000</f>
@@ -7114,7 +7141,7 @@
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E213" s="2" t="n">
         <f aca="false">A213 +1000</f>
@@ -7132,7 +7159,7 @@
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E214" s="2" t="n">
         <f aca="false">A214 +1000</f>
@@ -7150,7 +7177,7 @@
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B215" s="3"/>
       <c r="E215" s="2" t="n">
@@ -7169,13 +7196,13 @@
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E216" s="2" t="n">
         <f aca="false">A216 +1000</f>
@@ -7193,7 +7220,7 @@
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E217" s="2" t="n">
         <f aca="false">A217 +1000</f>
@@ -7211,13 +7238,13 @@
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E218" s="2" t="n">
         <f aca="false">A218 +1000</f>
@@ -7235,7 +7262,7 @@
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E219" s="2" t="n">
         <f aca="false">A219 +1000</f>
@@ -7253,7 +7280,7 @@
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E220" s="2" t="n">
         <f aca="false">A220 +1000</f>
@@ -7271,7 +7298,7 @@
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E221" s="2" t="n">
         <f aca="false">A221 +1000</f>
@@ -7289,7 +7316,7 @@
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E222" s="2" t="n">
         <f aca="false">A222 +1000</f>
@@ -7307,7 +7334,7 @@
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E223" s="2" t="n">
         <f aca="false">A223 +1000</f>
@@ -7325,7 +7352,7 @@
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E224" s="2" t="n">
         <f aca="false">A224 +1000</f>
@@ -7343,7 +7370,7 @@
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E225" s="2" t="n">
         <f aca="false">A225 +1000</f>
@@ -7361,7 +7388,7 @@
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E226" s="2" t="n">
         <f aca="false">A226 +1000</f>
@@ -7379,7 +7406,7 @@
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E227" s="2" t="n">
         <f aca="false">A227 +1000</f>
@@ -7397,7 +7424,7 @@
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E228" s="2" t="n">
         <f aca="false">A228 +1000</f>
@@ -7415,7 +7442,7 @@
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E229" s="2" t="n">
         <f aca="false">A229 +1000</f>
@@ -7433,7 +7460,7 @@
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E230" s="2" t="n">
         <f aca="false">A230 +1000</f>
@@ -7451,16 +7478,16 @@
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D231" s="0" t="s">
-        <v>232</v>
+        <v>9</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="E231" s="2" t="n">
         <f aca="false">A231 +1000</f>
@@ -7471,10 +7498,10 @@
         <v>2230</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M231" s="2" t="n">
         <f aca="false">I231 +1000</f>
@@ -7484,7 +7511,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">A232 +1000</f>
@@ -7502,7 +7529,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">A233 +1000</f>
@@ -7520,7 +7547,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">A234 +1000</f>
@@ -7538,7 +7565,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">A235 +1000</f>
@@ -7556,7 +7583,16 @@
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D236" s="0" t="s">
+        <v>240</v>
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">A236 +1000</f>
@@ -7574,7 +7610,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">A237 +1000</f>
@@ -7592,7 +7628,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">A238 +1000</f>
@@ -7610,13 +7646,13 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E239" s="2" t="n">
         <f aca="false">A239 +1000</f>
@@ -7634,7 +7670,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">A240 +1000</f>
@@ -7652,7 +7688,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">A241 +1000</f>
@@ -7670,7 +7706,7 @@
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">A242 +1000</f>
@@ -7688,7 +7724,7 @@
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">A243 +1000</f>
@@ -7706,7 +7742,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">A244 +1000</f>
@@ -7724,7 +7760,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">A245 +1000</f>
@@ -7742,7 +7778,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E246" s="2" t="n">
         <f aca="false">A246 +1000</f>
@@ -7760,7 +7796,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E247" s="2" t="n">
         <f aca="false">A247 +1000</f>
@@ -7778,7 +7814,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E248" s="2" t="n">
         <f aca="false">A248 +1000</f>
@@ -7796,7 +7832,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E249" s="2" t="n">
         <f aca="false">A249 +1000</f>
@@ -7814,7 +7850,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E250" s="2" t="n">
         <f aca="false">A250 +1000</f>
@@ -7832,7 +7868,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E251" s="2" t="n">
         <f aca="false">A251 +1000</f>
@@ -7850,7 +7886,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E252" s="2" t="n">
         <f aca="false">A252 +1000</f>
@@ -7868,7 +7904,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E253" s="2" t="n">
         <f aca="false">A253 +1000</f>
@@ -7886,7 +7922,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E254" s="2" t="n">
         <f aca="false">A254 +1000</f>
@@ -7904,7 +7940,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E255" s="2" t="n">
         <f aca="false">A255 +1000</f>
@@ -7922,7 +7958,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E256" s="2" t="n">
         <f aca="false">A256 +1000</f>
@@ -7940,7 +7976,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E257" s="2" t="n">
         <f aca="false">A257 +1000</f>
@@ -7958,7 +7994,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E258" s="2" t="n">
         <f aca="false">A258 +1000</f>
@@ -7976,7 +8012,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E259" s="2" t="n">
         <f aca="false">A259 +1000</f>
@@ -7994,7 +8030,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E260" s="2" t="n">
         <f aca="false">A260 +1000</f>
@@ -8012,7 +8048,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E261" s="2" t="n">
         <f aca="false">A261 +1000</f>
@@ -8030,7 +8066,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E262" s="2" t="n">
         <f aca="false">A262 +1000</f>
@@ -8048,7 +8084,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E263" s="2" t="n">
         <f aca="false">A263 +1000</f>
@@ -8066,13 +8102,13 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E264" s="2" t="n">
         <f aca="false">A264 +1000</f>
@@ -8087,16 +8123,16 @@
         <v>3263</v>
       </c>
       <c r="N264" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O264" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q264" s="2"/>
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E265" s="2" t="n">
         <f aca="false">A265 +1000</f>
@@ -8114,7 +8150,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E266" s="2" t="n">
         <f aca="false">A266 +1000</f>
@@ -8132,7 +8168,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E267" s="2" t="n">
         <f aca="false">A267 +1000</f>
@@ -8150,7 +8186,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E268" s="2" t="n">
         <f aca="false">A268 +1000</f>
@@ -8168,7 +8204,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E269" s="2" t="n">
         <f aca="false">A269 +1000</f>
@@ -8186,7 +8222,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E270" s="2" t="n">
         <f aca="false">A270 +1000</f>
@@ -8204,7 +8240,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E271" s="2" t="n">
         <f aca="false">A271 +1000</f>
@@ -8222,7 +8258,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E272" s="2" t="n">
         <f aca="false">A272 +1000</f>
@@ -8240,7 +8276,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E273" s="2" t="n">
         <f aca="false">A273 +1000</f>
@@ -8258,7 +8294,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E274" s="2" t="n">
         <f aca="false">A274 +1000</f>
@@ -8276,7 +8312,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E275" s="2" t="n">
         <f aca="false">A275 +1000</f>
@@ -8294,7 +8330,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E276" s="2" t="n">
         <f aca="false">A276 +1000</f>
@@ -8312,7 +8348,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E277" s="2" t="n">
         <f aca="false">A277 +1000</f>
@@ -8330,7 +8366,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E278" s="2" t="n">
         <f aca="false">A278 +1000</f>
@@ -8348,7 +8384,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E279" s="2" t="n">
         <f aca="false">A279 +1000</f>
@@ -8366,7 +8402,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E280" s="2" t="n">
         <f aca="false">A280 +1000</f>
@@ -8384,7 +8420,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E281" s="2" t="n">
         <f aca="false">A281 +1000</f>
@@ -8402,7 +8438,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E282" s="2" t="n">
         <f aca="false">A282 +1000</f>
@@ -8420,7 +8456,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E283" s="2" t="n">
         <f aca="false">A283 +1000</f>
@@ -8438,7 +8474,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E284" s="2" t="n">
         <f aca="false">A284 +1000</f>
@@ -8456,7 +8492,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E285" s="2" t="n">
         <f aca="false">A285 +1000</f>
@@ -8474,7 +8510,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E286" s="2" t="n">
         <f aca="false">A286 +1000</f>
@@ -8492,7 +8528,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E287" s="2" t="n">
         <f aca="false">A287 +1000</f>
@@ -8510,7 +8546,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E288" s="2" t="n">
         <f aca="false">A288 +1000</f>
@@ -8528,7 +8564,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E289" s="2" t="n">
         <f aca="false">A289 +1000</f>
@@ -8546,7 +8582,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E290" s="2" t="n">
         <f aca="false">A290 +1000</f>
@@ -8564,7 +8600,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E291" s="2" t="n">
         <f aca="false">A291 +1000</f>
@@ -8582,7 +8618,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E292" s="2" t="n">
         <f aca="false">A292 +1000</f>
@@ -8600,7 +8636,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E293" s="2" t="n">
         <f aca="false">A293 +1000</f>
@@ -8618,7 +8654,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E294" s="2" t="n">
         <f aca="false">A294 +1000</f>
@@ -8636,7 +8672,7 @@
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
@@ -8655,13 +8691,13 @@
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E296" s="2" t="n">
         <f aca="false">A296 +1000</f>
@@ -8679,7 +8715,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E297" s="2" t="n">
         <f aca="false">A297 +1000</f>
@@ -8697,7 +8733,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E298" s="2" t="n">
         <f aca="false">A298 +1000</f>
@@ -8715,7 +8751,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E299" s="2" t="n">
         <f aca="false">A299 +1000</f>
@@ -8733,7 +8769,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E300" s="2" t="n">
         <f aca="false">A300 +1000</f>
@@ -8751,7 +8787,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E301" s="2" t="n">
         <f aca="false">A301 +1000</f>
@@ -8769,7 +8805,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E302" s="2" t="n">
         <f aca="false">A302 +1000</f>
@@ -8787,7 +8823,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E303" s="2" t="n">
         <f aca="false">A303 +1000</f>
@@ -8805,7 +8841,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E304" s="2" t="n">
         <f aca="false">A304 +1000</f>
@@ -8823,7 +8859,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E305" s="2" t="n">
         <f aca="false">A305 +1000</f>
@@ -8841,7 +8877,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E306" s="2" t="n">
         <f aca="false">A306 +1000</f>
@@ -8859,7 +8895,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E307" s="2" t="n">
         <f aca="false">A307 +1000</f>
@@ -8877,7 +8913,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E308" s="2" t="n">
         <f aca="false">A308 +1000</f>
@@ -8895,7 +8931,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E309" s="2" t="n">
         <f aca="false">A309 +1000</f>
@@ -8913,7 +8949,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E310" s="2" t="n">
         <f aca="false">A310 +1000</f>
@@ -8931,7 +8967,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E311" s="2" t="n">
         <f aca="false">A311 +1000</f>
@@ -8949,7 +8985,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E312" s="2" t="n">
         <f aca="false">A312 +1000</f>
@@ -8967,7 +9003,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E313" s="2" t="n">
         <f aca="false">A313 +1000</f>
@@ -8985,7 +9021,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E314" s="2" t="n">
         <f aca="false">A314 +1000</f>
@@ -9003,7 +9039,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E315" s="2" t="n">
         <f aca="false">A315 +1000</f>
@@ -9021,7 +9057,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E316" s="2" t="n">
         <f aca="false">A316 +1000</f>
@@ -9039,7 +9075,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E317" s="2" t="n">
         <f aca="false">A317 +1000</f>
@@ -9057,7 +9093,7 @@
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E318" s="2" t="n">
         <f aca="false">A318 +1000</f>
@@ -9072,16 +9108,16 @@
         <v>3317</v>
       </c>
       <c r="N318" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q318" s="2"/>
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E319" s="2" t="n">
         <f aca="false">A319 +1000</f>
@@ -9099,7 +9135,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E320" s="2" t="n">
         <f aca="false">A320 +1000</f>
@@ -9117,7 +9153,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E321" s="2" t="n">
         <f aca="false">A321 +1000</f>
@@ -9135,7 +9171,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E322" s="2" t="n">
         <f aca="false">A322 +1000</f>
@@ -9153,7 +9189,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E323" s="2" t="n">
         <f aca="false">A323 +1000</f>
@@ -9171,7 +9207,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E324" s="2" t="n">
         <f aca="false">A324 +1000</f>
@@ -9189,7 +9225,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E325" s="2" t="n">
         <f aca="false">A325 +1000</f>
@@ -9207,7 +9243,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E326" s="2" t="n">
         <f aca="false">A326 +1000</f>
@@ -9225,7 +9261,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E327" s="2" t="n">
         <f aca="false">A327 +1000</f>
@@ -9243,7 +9279,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E328" s="2" t="n">
         <f aca="false">A328 +1000</f>
@@ -9261,7 +9297,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E329" s="2" t="n">
         <f aca="false">A329 +1000</f>
@@ -9279,7 +9315,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E330" s="2" t="n">
         <f aca="false">A330 +1000</f>
@@ -9297,7 +9333,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E331" s="2" t="n">
         <f aca="false">A331 +1000</f>
@@ -9315,13 +9351,13 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E332" s="2" t="n">
         <f aca="false">A332 +1000</f>
@@ -9339,7 +9375,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E333" s="2" t="n">
         <f aca="false">A333 +1000</f>
@@ -9357,7 +9393,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E334" s="2" t="n">
         <f aca="false">A334 +1000</f>
@@ -9375,7 +9411,7 @@
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E335" s="2" t="n">
         <f aca="false">A335 +1000</f>
@@ -9386,10 +9422,10 @@
         <v>2334</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K335" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M335" s="2" t="n">
         <f aca="false">I335 +1000</f>
@@ -9399,7 +9435,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E336" s="2" t="n">
         <f aca="false">A336 +1000</f>
@@ -9417,17 +9453,17 @@
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E337" s="2" t="n">
         <f aca="false">A337 +1000</f>
         <v>1336</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I337" s="2" t="n">
         <f aca="false">E337 +1000</f>
@@ -9441,7 +9477,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E338" s="2" t="n">
         <f aca="false">A338 +1000</f>
@@ -9459,7 +9495,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E339" s="2" t="n">
         <f aca="false">A339 +1000</f>
@@ -9477,7 +9513,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E340" s="2" t="n">
         <f aca="false">A340 +1000</f>
@@ -9495,7 +9531,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E341" s="2" t="n">
         <f aca="false">A341 +1000</f>
@@ -9513,7 +9549,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E342" s="2" t="n">
         <f aca="false">A342 +1000</f>
@@ -9531,7 +9567,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E343" s="2" t="n">
         <f aca="false">A343 +1000</f>
@@ -9549,7 +9585,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E344" s="2" t="n">
         <f aca="false">A344 +1000</f>
@@ -9567,7 +9603,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E345" s="2" t="n">
         <f aca="false">A345 +1000</f>
@@ -9585,7 +9621,7 @@
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E346" s="2" t="n">
         <f aca="false">A346 +1000</f>
@@ -9603,7 +9639,7 @@
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
@@ -9622,13 +9658,13 @@
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E348" s="2" t="n">
         <f aca="false">A348 +1000</f>
@@ -9646,7 +9682,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E349" s="2" t="n">
         <f aca="false">A349 +1000</f>
@@ -9664,7 +9700,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E350" s="2" t="n">
         <f aca="false">A350 +1000</f>
@@ -9682,7 +9718,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E351" s="2" t="n">
         <f aca="false">A351 +1000</f>
@@ -9700,7 +9736,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E352" s="2" t="n">
         <f aca="false">A352 +1000</f>
@@ -9718,7 +9754,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E353" s="2" t="n">
         <f aca="false">A353 +1000</f>
@@ -9736,7 +9772,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E354" s="2" t="n">
         <f aca="false">A354 +1000</f>
@@ -9754,7 +9790,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E355" s="2" t="n">
         <f aca="false">A355 +1000</f>
@@ -9772,13 +9808,13 @@
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E356" s="2" t="n">
         <f aca="false">A356 +1000</f>
@@ -9796,7 +9832,7 @@
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E357" s="2" t="n">
         <f aca="false">A357 +1000</f>
@@ -9807,10 +9843,10 @@
         <v>2356</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K357" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M357" s="2" t="n">
         <f aca="false">I357 +1000</f>
@@ -9820,7 +9856,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E358" s="2" t="n">
         <f aca="false">A358 +1000</f>
@@ -9838,7 +9874,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E359" s="2" t="n">
         <f aca="false">A359 +1000</f>
@@ -9856,7 +9892,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E360" s="2" t="n">
         <f aca="false">A360 +1000</f>
@@ -9874,7 +9910,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E361" s="2" t="n">
         <f aca="false">A361 +1000</f>
@@ -9892,7 +9928,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E362" s="2" t="n">
         <f aca="false">A362 +1000</f>
@@ -9910,7 +9946,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E363" s="2" t="n">
         <f aca="false">A363 +1000</f>
@@ -9928,7 +9964,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E364" s="2" t="n">
         <f aca="false">A364 +1000</f>
@@ -9946,7 +9982,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E365" s="2" t="n">
         <f aca="false">A365 +1000</f>
@@ -9964,7 +10000,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E366" s="2" t="n">
         <f aca="false">A366 +1000</f>
@@ -9982,7 +10018,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E367" s="2" t="n">
         <f aca="false">A367 +1000</f>
@@ -10000,7 +10036,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E368" s="2" t="n">
         <f aca="false">A368 +1000</f>
@@ -10018,7 +10054,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E369" s="2" t="n">
         <f aca="false">A369 +1000</f>
@@ -10036,7 +10072,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E370" s="2" t="n">
         <f aca="false">A370 +1000</f>
@@ -10054,7 +10090,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E371" s="2" t="n">
         <f aca="false">A371 +1000</f>
@@ -10072,7 +10108,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E372" s="2" t="n">
         <f aca="false">A372 +1000</f>
@@ -10090,13 +10126,13 @@
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E373" s="2" t="n">
         <f aca="false">A373 +1000</f>
@@ -10114,7 +10150,7 @@
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E374" s="2" t="n">
         <f aca="false">A374 +1000</f>
@@ -10132,7 +10168,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E375" s="2" t="n">
         <f aca="false">A375 +1000</f>
@@ -10150,7 +10186,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E376" s="2" t="n">
         <f aca="false">A376 +1000</f>
@@ -10168,7 +10204,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E377" s="2" t="n">
         <f aca="false">A377 +1000</f>
@@ -10186,13 +10222,13 @@
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E378" s="2" t="n">
         <f aca="false">A378 +1000</f>
@@ -10210,7 +10246,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E379" s="2" t="n">
         <f aca="false">A379 +1000</f>
@@ -10228,7 +10264,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E380" s="2" t="n">
         <f aca="false">A380 +1000</f>
@@ -10246,7 +10282,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E381" s="2" t="n">
         <f aca="false">A381 +1000</f>
@@ -10264,7 +10300,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E382" s="2" t="n">
         <f aca="false">A382 +1000</f>
@@ -10282,7 +10318,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E383" s="2" t="n">
         <f aca="false">A383 +1000</f>
@@ -10300,7 +10336,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E384" s="2" t="n">
         <f aca="false">A384 +1000</f>
@@ -10318,7 +10354,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E385" s="2" t="n">
         <f aca="false">A385 +1000</f>
@@ -10336,7 +10372,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E386" s="2" t="n">
         <f aca="false">A386 +1000</f>
@@ -10354,7 +10390,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E387" s="2" t="n">
         <f aca="false">A387 +1000</f>
@@ -10372,7 +10408,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E388" s="2" t="n">
         <f aca="false">A388 +1000</f>
@@ -10390,7 +10426,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E389" s="2" t="n">
         <f aca="false">A389 +1000</f>
@@ -10408,7 +10444,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E390" s="2" t="n">
         <f aca="false">A390 +1000</f>
@@ -10426,7 +10462,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E391" s="2" t="n">
         <f aca="false">A391 +1000</f>
@@ -10444,7 +10480,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E392" s="2" t="n">
         <f aca="false">A392 +1000</f>
@@ -10462,7 +10498,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E393" s="2" t="n">
         <f aca="false">A393 +1000</f>
@@ -10480,7 +10516,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E394" s="2" t="n">
         <f aca="false">A394 +1000</f>
@@ -10498,7 +10534,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E395" s="2" t="n">
         <f aca="false">A395 +1000</f>
@@ -10516,7 +10552,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E396" s="2" t="n">
         <f aca="false">A396 +1000</f>
@@ -10534,7 +10570,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E397" s="2" t="n">
         <f aca="false">A397 +1000</f>
@@ -10552,7 +10588,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E398" s="2" t="n">
         <f aca="false">A398 +1000</f>
@@ -10570,7 +10606,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E399" s="2" t="n">
         <f aca="false">A399 +1000</f>
@@ -10588,7 +10624,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E400" s="2" t="n">
         <f aca="false">A400 +1000</f>
@@ -10606,7 +10642,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E401" s="2" t="n">
         <f aca="false">A401 +1000</f>
@@ -10624,7 +10660,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E402" s="2" t="n">
         <f aca="false">A402 +1000</f>
@@ -10642,7 +10678,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E403" s="2" t="n">
         <f aca="false">A403 +1000</f>
@@ -10660,7 +10696,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E404" s="2" t="n">
         <f aca="false">A404 +1000</f>
@@ -10678,7 +10714,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E405" s="2" t="n">
         <f aca="false">A405 +1000</f>
@@ -10696,7 +10732,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E406" s="2" t="n">
         <f aca="false">A406 +1000</f>
@@ -10714,13 +10750,13 @@
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E407" s="2" t="n">
         <f aca="false">A407 +1000</f>
@@ -10738,7 +10774,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E408" s="2" t="n">
         <f aca="false">A408 +1000</f>
@@ -10756,7 +10792,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E409" s="2" t="n">
         <f aca="false">A409 +1000</f>
@@ -10774,7 +10810,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E410" s="2" t="n">
         <f aca="false">A410 +1000</f>
@@ -10792,7 +10828,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E411" s="2" t="n">
         <f aca="false">A411 +1000</f>
@@ -10810,7 +10846,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E412" s="2" t="n">
         <f aca="false">A412 +1000</f>
@@ -10828,7 +10864,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E413" s="2" t="n">
         <f aca="false">A413 +1000</f>
@@ -10846,7 +10882,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E414" s="2" t="n">
         <f aca="false">A414 +1000</f>
@@ -10864,7 +10900,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E415" s="2" t="n">
         <f aca="false">A415 +1000</f>
@@ -10882,7 +10918,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E416" s="2" t="n">
         <f aca="false">A416 +1000</f>
@@ -10900,7 +10936,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E417" s="2" t="n">
         <f aca="false">A417 +1000</f>
@@ -10918,7 +10954,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E418" s="2" t="n">
         <f aca="false">A418 +1000</f>
@@ -10936,7 +10972,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E419" s="2" t="n">
         <f aca="false">A419 +1000</f>
@@ -10954,13 +10990,13 @@
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E420" s="2" t="n">
         <f aca="false">A420 +1000</f>
@@ -10978,7 +11014,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E421" s="2" t="n">
         <f aca="false">A421 +1000</f>
@@ -10996,7 +11032,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
@@ -11014,7 +11050,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E423" s="2" t="n">
         <f aca="false">A423 +1000</f>
@@ -11032,7 +11068,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E424" s="2" t="n">
         <f aca="false">A424 +1000</f>
@@ -11050,7 +11086,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E425" s="2" t="n">
         <f aca="false">A425 +1000</f>
@@ -11068,7 +11104,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E426" s="2" t="n">
         <f aca="false">A426 +1000</f>
@@ -11086,7 +11122,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E427" s="2" t="n">
         <f aca="false">A427 +1000</f>
@@ -11104,7 +11140,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E428" s="2" t="n">
         <f aca="false">A428 +1000</f>
@@ -11122,7 +11158,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E429" s="2" t="n">
         <f aca="false">A429 +1000</f>
@@ -11140,7 +11176,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E430" s="2" t="n">
         <f aca="false">A430 +1000</f>
@@ -11158,7 +11194,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E431" s="2" t="n">
         <f aca="false">A431 +1000</f>
@@ -11176,7 +11212,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E432" s="2" t="n">
         <f aca="false">A432 +1000</f>
@@ -11194,7 +11230,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E433" s="2" t="n">
         <f aca="false">A433 +1000</f>
@@ -11212,7 +11248,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E434" s="2" t="n">
         <f aca="false">A434 +1000</f>
@@ -11230,7 +11266,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E435" s="2" t="n">
         <f aca="false">A435 +1000</f>
@@ -11248,7 +11284,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E436" s="2" t="n">
         <f aca="false">A436 +1000</f>
@@ -11266,7 +11302,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E437" s="2" t="n">
         <f aca="false">A437 +1000</f>
@@ -11284,7 +11320,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E438" s="2" t="n">
         <f aca="false">A438 +1000</f>
@@ -11302,7 +11338,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E439" s="2" t="n">
         <f aca="false">A439 +1000</f>
@@ -11320,7 +11356,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E440" s="2" t="n">
         <f aca="false">A440 +1000</f>
@@ -11338,7 +11374,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E441" s="2" t="n">
         <f aca="false">A441 +1000</f>
@@ -11356,7 +11392,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E442" s="2" t="n">
         <f aca="false">A442 +1000</f>
@@ -11374,7 +11410,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E443" s="2" t="n">
         <f aca="false">A443 +1000</f>
@@ -11392,7 +11428,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E444" s="2" t="n">
         <f aca="false">A444 +1000</f>
@@ -11410,7 +11446,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E445" s="2" t="n">
         <f aca="false">A445 +1000</f>
@@ -11428,7 +11464,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E446" s="2" t="n">
         <f aca="false">A446 +1000</f>
@@ -11446,7 +11482,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E447" s="2" t="n">
         <f aca="false">A447 +1000</f>
@@ -11464,7 +11500,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E448" s="2" t="n">
         <f aca="false">A448 +1000</f>
@@ -11482,7 +11518,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E449" s="2" t="n">
         <f aca="false">A449 +1000</f>
@@ -11500,7 +11536,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E450" s="2" t="n">
         <f aca="false">A450 +1000</f>
@@ -11518,13 +11554,13 @@
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E451" s="2" t="n">
         <f aca="false">A451 +1000</f>
@@ -11542,7 +11578,7 @@
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E452" s="2" t="n">
         <f aca="false">A452 +1000</f>
@@ -11560,7 +11596,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E453" s="2" t="n">
         <f aca="false">A453 +1000</f>
@@ -11578,7 +11614,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E454" s="2" t="n">
         <f aca="false">A454 +1000</f>
@@ -11596,7 +11632,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E455" s="2" t="n">
         <f aca="false">A455 +1000</f>
@@ -11614,7 +11650,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E456" s="2" t="n">
         <f aca="false">A456 +1000</f>
@@ -11632,7 +11668,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E457" s="2" t="n">
         <f aca="false">A457 +1000</f>
@@ -11650,7 +11686,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E458" s="2" t="n">
         <f aca="false">A458 +1000</f>
@@ -11668,7 +11704,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E459" s="2" t="n">
         <f aca="false">A459 +1000</f>
@@ -11686,7 +11722,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E460" s="2" t="n">
         <f aca="false">A460 +1000</f>
@@ -11704,7 +11740,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E461" s="2" t="n">
         <f aca="false">A461 +1000</f>
@@ -11722,7 +11758,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E462" s="2" t="n">
         <f aca="false">A462 +1000</f>
@@ -11740,7 +11776,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E463" s="2" t="n">
         <f aca="false">A463 +1000</f>
@@ -11758,17 +11794,17 @@
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E464" s="2" t="n">
         <f aca="false">A464 +1000</f>
         <v>1463</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G464" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I464" s="2" t="n">
         <f aca="false">E464 +1000</f>
@@ -11782,7 +11818,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E465" s="2" t="n">
         <f aca="false">A465 +1000</f>
@@ -11800,7 +11836,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E466" s="2" t="n">
         <f aca="false">A466 +1000</f>
@@ -11818,7 +11854,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E467" s="2" t="n">
         <f aca="false">A467 +1000</f>
@@ -11836,7 +11872,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E468" s="2" t="n">
         <f aca="false">A468 +1000</f>
@@ -11854,7 +11890,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E469" s="2" t="n">
         <f aca="false">A469 +1000</f>
@@ -11872,7 +11908,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E470" s="2" t="n">
         <f aca="false">A470 +1000</f>
@@ -11890,7 +11926,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E471" s="2" t="n">
         <f aca="false">A471 +1000</f>
@@ -11908,7 +11944,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E472" s="2" t="n">
         <f aca="false">A472 +1000</f>
@@ -11926,7 +11962,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E473" s="2" t="n">
         <f aca="false">A473 +1000</f>
@@ -11944,7 +11980,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E474" s="2" t="n">
         <f aca="false">A474 +1000</f>
@@ -11962,7 +11998,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E475" s="2" t="n">
         <f aca="false">A475 +1000</f>
@@ -11980,7 +12016,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E476" s="2" t="n">
         <f aca="false">A476 +1000</f>
@@ -11998,7 +12034,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E477" s="2" t="n">
         <f aca="false">A477 +1000</f>
@@ -12016,7 +12052,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E478" s="2" t="n">
         <f aca="false">A478 +1000</f>
@@ -12034,7 +12070,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E479" s="2" t="n">
         <f aca="false">A479 +1000</f>
@@ -12052,7 +12088,7 @@
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
@@ -12071,7 +12107,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E481" s="2" t="n">
         <f aca="false">A481 +1000</f>
@@ -12089,7 +12125,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E482" s="2" t="n">
         <f aca="false">A482 +1000</f>
@@ -12107,7 +12143,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E483" s="2" t="n">
         <f aca="false">A483 +1000</f>
@@ -12125,7 +12161,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E484" s="2" t="n">
         <f aca="false">A484 +1000</f>
@@ -12143,7 +12179,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E485" s="2" t="n">
         <f aca="false">A485 +1000</f>
@@ -12161,7 +12197,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E486" s="2" t="n">
         <f aca="false">A486 +1000</f>
@@ -12179,7 +12215,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E487" s="2" t="n">
         <f aca="false">A487 +1000</f>
@@ -12197,7 +12233,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E488" s="2" t="n">
         <f aca="false">A488 +1000</f>
@@ -12215,7 +12251,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E489" s="2" t="n">
         <f aca="false">A489 +1000</f>
@@ -12233,7 +12269,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E490" s="2" t="n">
         <f aca="false">A490 +1000</f>
@@ -12251,7 +12287,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E491" s="2" t="n">
         <f aca="false">A491 +1000</f>
@@ -12269,7 +12305,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E492" s="2" t="n">
         <f aca="false">A492 +1000</f>
@@ -12287,7 +12323,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E493" s="2" t="n">
         <f aca="false">A493 +1000</f>
@@ -12305,7 +12341,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E494" s="2" t="n">
         <f aca="false">A494 +1000</f>
@@ -12323,7 +12359,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E495" s="2" t="n">
         <f aca="false">A495 +1000</f>
@@ -12341,7 +12377,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E496" s="2" t="n">
         <f aca="false">A496 +1000</f>
@@ -12359,7 +12395,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E497" s="2" t="n">
         <f aca="false">A497 +1000</f>
@@ -12377,7 +12413,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E498" s="2" t="n">
         <f aca="false">A498 +1000</f>
@@ -12395,7 +12431,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E499" s="2" t="n">
         <f aca="false">A499 +1000</f>
@@ -12413,7 +12449,7 @@
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E500" s="2" t="n">
         <f aca="false">A500 +1000</f>
@@ -12424,10 +12460,10 @@
         <v>2499</v>
       </c>
       <c r="J500" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K500" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M500" s="2" t="n">
         <f aca="false">I500 +1000</f>
@@ -12437,7 +12473,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E501" s="2" t="n">
         <f aca="false">A501 +1000</f>
@@ -12455,7 +12491,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E502" s="2" t="n">
         <f aca="false">A502 +1000</f>
@@ -12473,7 +12509,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E503" s="2" t="n">
         <f aca="false">A503 +1000</f>
@@ -12491,7 +12527,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E504" s="2" t="n">
         <f aca="false">A504 +1000</f>
@@ -12509,7 +12545,7 @@
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E505" s="2" t="n">
         <f aca="false">A505 +1000</f>
@@ -12527,13 +12563,13 @@
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E506" s="2" t="n">
         <f aca="false">A506 +1000</f>
@@ -12551,7 +12587,7 @@
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E507" s="2" t="n">
         <f aca="false">A507 +1000</f>
@@ -12566,16 +12602,16 @@
         <v>3506</v>
       </c>
       <c r="N507" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O507" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q507" s="2"/>
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E508" s="2" t="n">
         <f aca="false">A508 +1000</f>
@@ -12593,7 +12629,7 @@
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E509" s="2" t="n">
         <f aca="false">A509 +1000</f>
@@ -12611,7 +12647,7 @@
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E510" s="2" t="n">
         <f aca="false">A510 +1000</f>
@@ -12629,7 +12665,7 @@
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E511" s="2" t="n">
         <f aca="false">A511 +1000</f>
@@ -12647,7 +12683,7 @@
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E512" s="2" t="n">
         <f aca="false">A512 +1000</f>
@@ -12665,7 +12701,7 @@
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E513" s="2" t="n">
         <f aca="false">A513 +1000</f>
@@ -12683,7 +12719,7 @@
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E514" s="2" t="n">
         <f aca="false">A514 +1000</f>
@@ -12701,7 +12737,7 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E515" s="2" t="n">
         <f aca="false">A515 +1000</f>
@@ -12719,7 +12755,7 @@
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E516" s="2" t="n">
         <f aca="false">A516 +1000</f>
@@ -12737,7 +12773,7 @@
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E517" s="2" t="n">
         <f aca="false">A517 +1000</f>
@@ -12755,7 +12791,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E518" s="2" t="n">
         <f aca="false">A518 +1000</f>
@@ -12773,7 +12809,7 @@
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E519" s="2" t="n">
         <f aca="false">A519 +1000</f>
@@ -12791,7 +12827,7 @@
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E520" s="2" t="n">
         <f aca="false">A520 +1000</f>
@@ -12809,7 +12845,7 @@
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E521" s="2" t="n">
         <f aca="false">A521 +1000</f>
@@ -12827,7 +12863,7 @@
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E522" s="2" t="n">
         <f aca="false">A522 +1000</f>
@@ -12845,7 +12881,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E523" s="2" t="n">
         <f aca="false">A523 +1000</f>
@@ -12863,7 +12899,7 @@
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E524" s="2" t="n">
         <f aca="false">A524 +1000</f>
@@ -12881,7 +12917,7 @@
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E525" s="2" t="n">
         <f aca="false">A525 +1000</f>
@@ -12899,7 +12935,7 @@
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E526" s="2" t="n">
         <f aca="false">A526 +1000</f>
@@ -12917,7 +12953,7 @@
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E527" s="2" t="n">
         <f aca="false">A527 +1000</f>
@@ -12935,7 +12971,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E528" s="2" t="n">
         <f aca="false">A528 +1000</f>
@@ -12953,7 +12989,7 @@
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E529" s="2" t="n">
         <f aca="false">A529 +1000</f>
@@ -12971,7 +13007,7 @@
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E530" s="2" t="n">
         <f aca="false">A530 +1000</f>
@@ -12989,7 +13025,7 @@
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E531" s="2" t="n">
         <f aca="false">A531 +1000</f>
@@ -13007,7 +13043,7 @@
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E532" s="2" t="n">
         <f aca="false">A532 +1000</f>
@@ -13025,7 +13061,7 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E533" s="2" t="n">
         <f aca="false">A533 +1000</f>
@@ -13043,7 +13079,7 @@
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E534" s="2" t="n">
         <f aca="false">A534 +1000</f>
@@ -13061,7 +13097,7 @@
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E535" s="2" t="n">
         <f aca="false">A535 +1000</f>
@@ -13079,7 +13115,7 @@
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E536" s="2" t="n">
         <f aca="false">A536 +1000</f>
@@ -13097,7 +13133,7 @@
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E537" s="2" t="n">
         <f aca="false">A537 +1000</f>
@@ -13115,7 +13151,7 @@
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E538" s="2" t="n">
         <f aca="false">A538 +1000</f>
@@ -13133,7 +13169,7 @@
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E539" s="2" t="n">
         <f aca="false">A539 +1000</f>
@@ -13151,7 +13187,7 @@
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E540" s="2" t="n">
         <f aca="false">A540 +1000</f>
@@ -13169,7 +13205,7 @@
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E541" s="2" t="n">
         <f aca="false">A541 +1000</f>
@@ -13187,7 +13223,7 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E542" s="2" t="n">
         <f aca="false">A542 +1000</f>
@@ -13205,7 +13241,7 @@
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E543" s="2" t="n">
         <f aca="false">A543 +1000</f>
@@ -13223,7 +13259,7 @@
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E544" s="2" t="n">
         <f aca="false">A544 +1000</f>
@@ -13241,7 +13277,7 @@
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E545" s="2" t="n">
         <f aca="false">A545 +1000</f>
@@ -13259,7 +13295,7 @@
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E546" s="2" t="n">
         <f aca="false">A546 +1000</f>
@@ -13277,7 +13313,7 @@
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E547" s="2" t="n">
         <f aca="false">A547 +1000</f>
@@ -13295,7 +13331,7 @@
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E548" s="2" t="n">
         <f aca="false">A548 +1000</f>
@@ -13313,7 +13349,7 @@
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E549" s="2" t="n">
         <f aca="false">A549 +1000</f>
@@ -13331,7 +13367,7 @@
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E550" s="2" t="n">
         <f aca="false">A550 +1000</f>
@@ -13349,7 +13385,7 @@
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E551" s="2" t="n">
         <f aca="false">A551 +1000</f>
@@ -13367,7 +13403,7 @@
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E552" s="2" t="n">
         <f aca="false">A552 +1000</f>
@@ -13385,7 +13421,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E553" s="2" t="n">
         <f aca="false">A553 +1000</f>
@@ -13403,7 +13439,7 @@
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E554" s="2" t="n">
         <f aca="false">A554 +1000</f>
@@ -13421,7 +13457,7 @@
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E555" s="2" t="n">
         <f aca="false">A555 +1000</f>
@@ -13439,7 +13475,7 @@
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E556" s="2" t="n">
         <f aca="false">A556 +1000</f>
@@ -13457,7 +13493,7 @@
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E557" s="2" t="n">
         <f aca="false">A557 +1000</f>
@@ -13475,7 +13511,7 @@
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E558" s="2" t="n">
         <f aca="false">A558 +1000</f>
@@ -13486,10 +13522,10 @@
         <v>2557</v>
       </c>
       <c r="J558" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K558" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M558" s="2" t="n">
         <f aca="false">I558 +1000</f>
@@ -13499,7 +13535,7 @@
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E559" s="2" t="n">
         <f aca="false">A559 +1000</f>
@@ -13517,7 +13553,7 @@
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E560" s="2" t="n">
         <f aca="false">A560 +1000</f>
@@ -13535,7 +13571,7 @@
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E561" s="2" t="n">
         <f aca="false">A561 +1000</f>
@@ -13553,7 +13589,7 @@
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E562" s="2" t="n">
         <f aca="false">A562 +1000</f>
@@ -13571,7 +13607,7 @@
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E563" s="2" t="n">
         <f aca="false">A563 +1000</f>
@@ -13589,7 +13625,7 @@
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E564" s="2" t="n">
         <f aca="false">A564 +1000</f>
@@ -13607,7 +13643,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E565" s="2" t="n">
         <f aca="false">A565 +1000</f>
@@ -13625,7 +13661,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E566" s="2" t="n">
         <f aca="false">A566 +1000</f>
@@ -13643,7 +13679,7 @@
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E567" s="2" t="n">
         <f aca="false">A567 +1000</f>
@@ -13661,7 +13697,7 @@
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E568" s="2" t="n">
         <f aca="false">A568 +1000</f>
@@ -13679,7 +13715,7 @@
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E569" s="2" t="n">
         <f aca="false">A569 +1000</f>
@@ -13697,7 +13733,7 @@
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E570" s="2" t="n">
         <f aca="false">A570 +1000</f>
@@ -13715,7 +13751,7 @@
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E571" s="2" t="n">
         <f aca="false">A571 +1000</f>
@@ -13733,7 +13769,7 @@
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E572" s="2" t="n">
         <f aca="false">A572 +1000</f>
@@ -13751,7 +13787,7 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E573" s="2" t="n">
         <f aca="false">A573 +1000</f>
@@ -13769,7 +13805,7 @@
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E574" s="2" t="n">
         <f aca="false">A574 +1000</f>
@@ -13787,7 +13823,7 @@
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E575" s="2" t="n">
         <f aca="false">A575 +1000</f>
@@ -13805,7 +13841,7 @@
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E576" s="2" t="n">
         <f aca="false">A576 +1000</f>
@@ -13823,7 +13859,7 @@
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E577" s="2" t="n">
         <f aca="false">A577 +1000</f>
@@ -13841,7 +13877,7 @@
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E578" s="2" t="n">
         <f aca="false">A578 +1000</f>
@@ -13859,7 +13895,7 @@
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E579" s="2" t="n">
         <f aca="false">A579 +1000</f>
@@ -13877,7 +13913,7 @@
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E580" s="2" t="n">
         <f aca="false">A580 +1000</f>
@@ -13895,7 +13931,7 @@
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E581" s="2" t="n">
         <f aca="false">A581 +1000</f>
@@ -13913,7 +13949,7 @@
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E582" s="2" t="n">
         <f aca="false">A582 +1000</f>
@@ -13931,7 +13967,7 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E583" s="2" t="n">
         <f aca="false">A583 +1000</f>
@@ -13949,7 +13985,7 @@
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E584" s="2" t="n">
         <f aca="false">A584 +1000</f>
@@ -13967,7 +14003,7 @@
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E585" s="2" t="n">
         <f aca="false">A585 +1000</f>
@@ -13985,7 +14021,7 @@
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E586" s="2" t="n">
         <f aca="false">A586 +1000</f>
@@ -14003,7 +14039,7 @@
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E587" s="2" t="n">
         <f aca="false">A587 +1000</f>
@@ -14021,7 +14057,7 @@
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E588" s="2" t="n">
         <f aca="false">A588 +1000</f>
@@ -14039,7 +14075,7 @@
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E589" s="2" t="n">
         <f aca="false">A589 +1000</f>
@@ -14057,7 +14093,7 @@
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E590" s="2" t="n">
         <f aca="false">A590 +1000</f>
@@ -14075,7 +14111,7 @@
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E591" s="2" t="n">
         <f aca="false">A591 +1000</f>
@@ -14093,7 +14129,7 @@
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E592" s="2" t="n">
         <f aca="false">A592 +1000</f>
@@ -14111,7 +14147,7 @@
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E593" s="2" t="n">
         <f aca="false">A593 +1000</f>
@@ -14129,7 +14165,7 @@
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E594" s="2" t="n">
         <f aca="false">A594 +1000</f>
@@ -14147,7 +14183,7 @@
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E595" s="2" t="n">
         <f aca="false">A595 +1000</f>
@@ -14165,7 +14201,7 @@
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E596" s="2" t="n">
         <f aca="false">A596 +1000</f>
@@ -14183,7 +14219,7 @@
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E597" s="2" t="n">
         <f aca="false">A597 +1000</f>
@@ -14201,7 +14237,7 @@
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E598" s="2" t="n">
         <f aca="false">A598 +1000</f>
@@ -14219,7 +14255,7 @@
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E599" s="2" t="n">
         <f aca="false">A599 +1000</f>
@@ -14237,7 +14273,7 @@
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E600" s="2" t="n">
         <f aca="false">A600 +1000</f>
@@ -14255,7 +14291,7 @@
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E601" s="2" t="n">
         <f aca="false">A601 +1000</f>
@@ -14273,7 +14309,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E602" s="2" t="n">
         <f aca="false">A602 +1000</f>
@@ -14291,7 +14327,7 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E603" s="2" t="n">
         <f aca="false">A603 +1000</f>
@@ -14309,7 +14345,7 @@
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E604" s="2" t="n">
         <f aca="false">A604 +1000</f>
@@ -14327,7 +14363,7 @@
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E605" s="2" t="n">
         <f aca="false">A605 +1000</f>
@@ -14345,7 +14381,7 @@
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E606" s="2" t="n">
         <f aca="false">A606 +1000</f>
@@ -14363,7 +14399,7 @@
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E607" s="2" t="n">
         <f aca="false">A607 +1000</f>
@@ -14381,7 +14417,7 @@
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E608" s="2" t="n">
         <f aca="false">A608 +1000</f>
@@ -14399,7 +14435,7 @@
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E609" s="2" t="n">
         <f aca="false">A609 +1000</f>
@@ -14417,7 +14453,7 @@
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E610" s="2" t="n">
         <f aca="false">A610 +1000</f>
@@ -14435,7 +14471,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E611" s="2" t="n">
         <f aca="false">A611 +1000</f>
@@ -14453,7 +14489,7 @@
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E612" s="2" t="n">
         <f aca="false">A612 +1000</f>
@@ -14471,7 +14507,7 @@
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="E613" s="2" t="n">
         <f aca="false">A613 +1000</f>
@@ -14489,7 +14525,7 @@
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E614" s="2" t="n">
         <f aca="false">A614 +1000</f>
@@ -14507,7 +14543,7 @@
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E615" s="2" t="n">
         <f aca="false">A615 +1000</f>
@@ -14525,7 +14561,7 @@
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E616" s="2" t="n">
         <f aca="false">A616 +1000</f>
@@ -14543,7 +14579,7 @@
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E617" s="2" t="n">
         <f aca="false">A617 +1000</f>
@@ -14561,7 +14597,7 @@
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E618" s="2" t="n">
         <f aca="false">A618 +1000</f>
@@ -14579,7 +14615,7 @@
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E619" s="2" t="n">
         <f aca="false">A619 +1000</f>
@@ -14597,7 +14633,7 @@
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E620" s="2" t="n">
         <f aca="false">A620 +1000</f>
@@ -14615,7 +14651,7 @@
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E621" s="2" t="n">
         <f aca="false">A621 +1000</f>
@@ -14633,16 +14669,16 @@
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C622" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E622" s="2" t="n">
         <f aca="false">A622 +1000</f>
@@ -14660,7 +14696,7 @@
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E623" s="2" t="n">
         <f aca="false">A623 +1000</f>
@@ -14678,7 +14714,7 @@
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E624" s="2" t="n">
         <f aca="false">A624 +1000</f>
@@ -14696,7 +14732,7 @@
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E625" s="2" t="n">
         <f aca="false">A625 +1000</f>
@@ -14714,7 +14750,7 @@
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E626" s="2" t="n">
         <f aca="false">A626 +1000</f>
@@ -14732,7 +14768,7 @@
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E627" s="2" t="n">
         <f aca="false">A627 +1000</f>
@@ -14750,7 +14786,7 @@
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E628" s="2" t="n">
         <f aca="false">A628 +1000</f>
@@ -14768,7 +14804,7 @@
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E629" s="2" t="n">
         <f aca="false">A629 +1000</f>
@@ -14786,7 +14822,7 @@
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E630" s="2" t="n">
         <f aca="false">A630 +1000</f>
@@ -14804,7 +14840,7 @@
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E631" s="2" t="n">
         <f aca="false">A631 +1000</f>
@@ -14822,7 +14858,7 @@
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E632" s="2" t="n">
         <f aca="false">A632 +1000</f>
@@ -14840,7 +14876,7 @@
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E633" s="2" t="n">
         <f aca="false">A633 +1000</f>
@@ -14858,7 +14894,7 @@
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E634" s="2" t="n">
         <f aca="false">A634 +1000</f>
@@ -14876,7 +14912,7 @@
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E635" s="2" t="n">
         <f aca="false">A635 +1000</f>
@@ -14894,7 +14930,7 @@
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E636" s="2" t="n">
         <f aca="false">A636 +1000</f>
@@ -14912,7 +14948,7 @@
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E637" s="2" t="n">
         <f aca="false">A637 +1000</f>
@@ -14930,7 +14966,7 @@
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E638" s="2" t="n">
         <f aca="false">A638 +1000</f>
@@ -14948,7 +14984,7 @@
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E639" s="2" t="n">
         <f aca="false">A639 +1000</f>
@@ -14966,7 +15002,7 @@
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E640" s="2" t="n">
         <f aca="false">A640 +1000</f>
@@ -14984,7 +15020,7 @@
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E641" s="2" t="n">
         <f aca="false">A641 +1000</f>
@@ -15002,7 +15038,7 @@
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E642" s="2" t="n">
         <f aca="false">A642 +1000</f>
@@ -15020,7 +15056,7 @@
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E643" s="2" t="n">
         <f aca="false">A643 +1000</f>
@@ -15038,7 +15074,7 @@
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E644" s="2" t="n">
         <f aca="false">A644 +1000</f>
@@ -15056,7 +15092,7 @@
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E645" s="2" t="n">
         <f aca="false">A645 +1000</f>
@@ -15074,7 +15110,7 @@
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E646" s="2" t="n">
         <f aca="false">A646 +1000</f>
@@ -15092,7 +15128,7 @@
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E647" s="2" t="n">
         <f aca="false">A647 +1000</f>
@@ -15110,7 +15146,7 @@
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E648" s="2" t="n">
         <f aca="false">A648 +1000</f>
@@ -15128,7 +15164,7 @@
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E649" s="2" t="n">
         <f aca="false">A649 +1000</f>
@@ -15146,7 +15182,7 @@
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E650" s="2" t="n">
         <f aca="false">A650 +1000</f>
@@ -15164,7 +15200,7 @@
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E651" s="2" t="n">
         <f aca="false">A651 +1000</f>
@@ -15182,7 +15218,7 @@
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E652" s="2" t="n">
         <f aca="false">A652 +1000</f>
@@ -15200,7 +15236,7 @@
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E653" s="2" t="n">
         <f aca="false">A653 +1000</f>
@@ -15218,7 +15254,7 @@
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E654" s="2" t="n">
         <f aca="false">A654 +1000</f>
@@ -15236,7 +15272,7 @@
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E655" s="2" t="n">
         <f aca="false">A655 +1000</f>
@@ -15254,7 +15290,7 @@
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E656" s="2" t="n">
         <f aca="false">A656 +1000</f>
@@ -15272,7 +15308,7 @@
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E657" s="2" t="n">
         <f aca="false">A657 +1000</f>
@@ -15290,7 +15326,7 @@
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E658" s="2" t="n">
         <f aca="false">A658 +1000</f>
@@ -15308,7 +15344,7 @@
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E659" s="2" t="n">
         <f aca="false">A659 +1000</f>
@@ -15326,7 +15362,7 @@
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E660" s="2" t="n">
         <f aca="false">A660 +1000</f>
@@ -15344,7 +15380,7 @@
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E661" s="2" t="n">
         <f aca="false">A661 +1000</f>
@@ -15362,7 +15398,7 @@
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E662" s="2" t="n">
         <f aca="false">A662 +1000</f>
@@ -15380,7 +15416,7 @@
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E663" s="2" t="n">
         <f aca="false">A663 +1000</f>
@@ -15398,7 +15434,7 @@
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E664" s="2" t="n">
         <f aca="false">A664 +1000</f>
@@ -15416,7 +15452,7 @@
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E665" s="2" t="n">
         <f aca="false">A665 +1000</f>
@@ -15434,7 +15470,7 @@
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E666" s="2" t="n">
         <f aca="false">A666 +1000</f>
@@ -15452,7 +15488,7 @@
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E667" s="2" t="n">
         <f aca="false">A667 +1000</f>
@@ -15470,7 +15506,7 @@
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E668" s="2" t="n">
         <f aca="false">A668 +1000</f>
@@ -15488,7 +15524,7 @@
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E669" s="2" t="n">
         <f aca="false">A669 +1000</f>
@@ -15506,7 +15542,7 @@
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E670" s="2" t="n">
         <f aca="false">A670 +1000</f>
@@ -15524,7 +15560,7 @@
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E671" s="2" t="n">
         <f aca="false">A671 +1000</f>
@@ -15542,7 +15578,7 @@
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E672" s="2" t="n">
         <f aca="false">A672 +1000</f>
@@ -15560,7 +15596,7 @@
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E673" s="2" t="n">
         <f aca="false">A673 +1000</f>
@@ -15578,7 +15614,7 @@
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E674" s="2" t="n">
         <f aca="false">A674 +1000</f>
@@ -15596,7 +15632,7 @@
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E675" s="2" t="n">
         <f aca="false">A675 +1000</f>
@@ -15614,7 +15650,7 @@
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E676" s="2" t="n">
         <f aca="false">A676 +1000</f>
@@ -15632,7 +15668,7 @@
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E677" s="2" t="n">
         <f aca="false">A677 +1000</f>
@@ -15650,7 +15686,7 @@
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E678" s="2" t="n">
         <f aca="false">A678 +1000</f>
@@ -15668,7 +15704,7 @@
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E679" s="2" t="n">
         <f aca="false">A679 +1000</f>
@@ -15686,7 +15722,7 @@
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E680" s="2" t="n">
         <f aca="false">A680 +1000</f>
@@ -15704,7 +15740,7 @@
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E681" s="2" t="n">
         <f aca="false">A681 +1000</f>
@@ -15722,7 +15758,7 @@
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E682" s="2" t="n">
         <f aca="false">A682 +1000</f>
@@ -15740,7 +15776,7 @@
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E683" s="2" t="n">
         <f aca="false">A683 +1000</f>
@@ -15758,7 +15794,7 @@
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E684" s="2" t="n">
         <f aca="false">A684 +1000</f>
@@ -15776,7 +15812,7 @@
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E685" s="2" t="n">
         <f aca="false">A685 +1000</f>
@@ -15794,7 +15830,7 @@
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E686" s="2" t="n">
         <f aca="false">A686 +1000</f>
@@ -15812,7 +15848,7 @@
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E687" s="2" t="n">
         <f aca="false">A687 +1000</f>
@@ -15830,7 +15866,7 @@
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E688" s="2" t="n">
         <f aca="false">A688 +1000</f>
@@ -15848,7 +15884,7 @@
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E689" s="2" t="n">
         <f aca="false">A689 +1000</f>
@@ -15866,7 +15902,7 @@
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E690" s="2" t="n">
         <f aca="false">A690 +1000</f>
@@ -15884,7 +15920,7 @@
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E691" s="2" t="n">
         <f aca="false">A691 +1000</f>
@@ -15902,7 +15938,7 @@
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E692" s="2" t="n">
         <f aca="false">A692 +1000</f>
@@ -15920,7 +15956,7 @@
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E693" s="2" t="n">
         <f aca="false">A693 +1000</f>
@@ -15938,7 +15974,7 @@
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E694" s="2" t="n">
         <f aca="false">A694 +1000</f>
@@ -15956,7 +15992,7 @@
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E695" s="2" t="n">
         <f aca="false">A695 +1000</f>
@@ -15974,7 +16010,7 @@
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="E696" s="2" t="n">
         <f aca="false">A696 +1000</f>
@@ -15992,7 +16028,7 @@
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E697" s="2" t="n">
         <f aca="false">A697 +1000</f>
@@ -16010,7 +16046,7 @@
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E698" s="2" t="n">
         <f aca="false">A698 +1000</f>
@@ -16028,7 +16064,7 @@
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="E699" s="2" t="n">
         <f aca="false">A699 +1000</f>
@@ -16046,7 +16082,7 @@
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E700" s="2" t="n">
         <f aca="false">A700 +1000</f>
@@ -16064,13 +16100,13 @@
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B701" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C701" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E701" s="2" t="n">
         <f aca="false">A701 +1000</f>
@@ -16088,13 +16124,13 @@
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B702" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C702" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E702" s="2" t="n">
         <f aca="false">A702 +1000</f>
@@ -16112,13 +16148,13 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C703" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E703" s="2" t="n">
         <f aca="false">A703 +1000</f>
@@ -16136,13 +16172,13 @@
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B704" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C704" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E704" s="2" t="n">
         <f aca="false">A704 +1000</f>
@@ -16160,7 +16196,7 @@
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E705" s="2" t="n">
         <f aca="false">A705 +1000</f>
@@ -16178,7 +16214,7 @@
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E706" s="2" t="n">
         <f aca="false">A706 +1000</f>
@@ -16196,7 +16232,7 @@
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E707" s="2" t="n">
         <f aca="false">A707 +1000</f>
@@ -16214,7 +16250,7 @@
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
@@ -16232,7 +16268,7 @@
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E709" s="2" t="n">
         <f aca="false">A709 +1000</f>
@@ -16250,7 +16286,7 @@
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E710" s="2" t="n">
         <f aca="false">A710 +1000</f>
@@ -16268,7 +16304,7 @@
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E711" s="2" t="n">
         <f aca="false">A711 +1000</f>
@@ -16286,7 +16322,7 @@
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E712" s="2" t="n">
         <f aca="false">A712 +1000</f>
@@ -16304,7 +16340,7 @@
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E713" s="2" t="n">
         <f aca="false">A713 +1000</f>
@@ -16322,7 +16358,7 @@
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E714" s="2" t="n">
         <f aca="false">A714 +1000</f>
@@ -16340,7 +16376,7 @@
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E715" s="2" t="n">
         <f aca="false">A715 +1000</f>
@@ -16358,7 +16394,7 @@
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E716" s="2" t="n">
         <f aca="false">A716 +1000</f>
@@ -16376,7 +16412,7 @@
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E717" s="2" t="n">
         <f aca="false">A717 +1000</f>
@@ -16394,7 +16430,7 @@
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E718" s="2" t="n">
         <f aca="false">A718 +1000</f>
@@ -16412,7 +16448,7 @@
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E719" s="2" t="n">
         <f aca="false">A719 +1000</f>
@@ -16430,7 +16466,7 @@
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E720" s="2" t="n">
         <f aca="false">A720 +1000</f>
@@ -16448,7 +16484,7 @@
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E721" s="2" t="n">
         <f aca="false">A721 +1000</f>
@@ -16466,7 +16502,7 @@
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E722" s="2" t="n">
         <f aca="false">A722 +1000</f>
@@ -16484,7 +16520,7 @@
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E723" s="2" t="n">
         <f aca="false">A723 +1000</f>
@@ -16502,7 +16538,7 @@
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E724" s="2" t="n">
         <f aca="false">A724 +1000</f>
@@ -16520,7 +16556,7 @@
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E725" s="2" t="n">
         <f aca="false">A725 +1000</f>
@@ -16538,7 +16574,7 @@
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="E726" s="2" t="n">
         <f aca="false">A726 +1000</f>
@@ -16556,7 +16592,7 @@
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E727" s="2" t="n">
         <f aca="false">A727 +1000</f>
@@ -16574,7 +16610,7 @@
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E728" s="2" t="n">
         <f aca="false">A728 +1000</f>
@@ -16592,7 +16628,7 @@
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E729" s="2" t="n">
         <f aca="false">A729 +1000</f>
@@ -16610,7 +16646,7 @@
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E730" s="2" t="n">
         <f aca="false">A730 +1000</f>
@@ -16628,7 +16664,7 @@
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E731" s="2" t="n">
         <f aca="false">A731 +1000</f>
@@ -16646,7 +16682,7 @@
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="E732" s="2" t="n">
         <f aca="false">A732 +1000</f>
@@ -16664,7 +16700,7 @@
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E733" s="2" t="n">
         <f aca="false">A733 +1000</f>
@@ -16682,7 +16718,7 @@
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E734" s="2" t="n">
         <f aca="false">A734 +1000</f>
@@ -16700,7 +16736,7 @@
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="E735" s="2" t="n">
         <f aca="false">A735 +1000</f>
@@ -16718,7 +16754,7 @@
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E736" s="2" t="n">
         <f aca="false">A736 +1000</f>
@@ -16736,7 +16772,7 @@
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E737" s="2" t="n">
         <f aca="false">A737 +1000</f>
@@ -16754,7 +16790,7 @@
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="E738" s="2" t="n">
         <f aca="false">A738 +1000</f>
@@ -16772,7 +16808,7 @@
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E739" s="2" t="n">
         <f aca="false">A739 +1000</f>
@@ -16790,7 +16826,7 @@
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E740" s="2" t="n">
         <f aca="false">A740 +1000</f>
@@ -16808,7 +16844,7 @@
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="E741" s="2" t="n">
         <f aca="false">A741 +1000</f>
@@ -16826,7 +16862,7 @@
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="E742" s="2" t="n">
         <f aca="false">A742 +1000</f>
@@ -16844,7 +16880,7 @@
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E743" s="2" t="n">
         <f aca="false">A743 +1000</f>
@@ -16862,7 +16898,7 @@
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E744" s="2" t="n">
         <f aca="false">A744 +1000</f>
@@ -16880,7 +16916,7 @@
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E745" s="2" t="n">
         <f aca="false">A745 +1000</f>
@@ -16898,7 +16934,7 @@
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E746" s="2" t="n">
         <f aca="false">A746 +1000</f>
@@ -16916,7 +16952,7 @@
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="E747" s="2" t="n">
         <f aca="false">A747 +1000</f>
@@ -16934,7 +16970,7 @@
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E748" s="2" t="n">
         <f aca="false">A748 +1000</f>
@@ -16952,7 +16988,7 @@
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E749" s="2" t="n">
         <f aca="false">A749 +1000</f>
@@ -16970,7 +17006,7 @@
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="E750" s="2" t="n">
         <f aca="false">A750 +1000</f>
@@ -16988,7 +17024,7 @@
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="E751" s="2" t="n">
         <f aca="false">A751 +1000</f>
@@ -17006,7 +17042,7 @@
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E752" s="2" t="n">
         <f aca="false">A752 +1000</f>
@@ -17024,7 +17060,7 @@
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E753" s="2" t="n">
         <f aca="false">A753 +1000</f>
@@ -17042,7 +17078,7 @@
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="E754" s="2" t="n">
         <f aca="false">A754 +1000</f>
@@ -17060,7 +17096,7 @@
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E755" s="2" t="n">
         <f aca="false">A755 +1000</f>
@@ -17078,7 +17114,7 @@
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E756" s="2" t="n">
         <f aca="false">A756 +1000</f>
@@ -17096,7 +17132,7 @@
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="E757" s="2" t="n">
         <f aca="false">A757 +1000</f>
@@ -17114,7 +17150,7 @@
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="E758" s="2" t="n">
         <f aca="false">A758 +1000</f>
@@ -17132,7 +17168,7 @@
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="E759" s="2" t="n">
         <f aca="false">A759 +1000</f>
@@ -17150,7 +17186,7 @@
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E760" s="2" t="n">
         <f aca="false">A760 +1000</f>
@@ -17168,7 +17204,7 @@
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E761" s="2" t="n">
         <f aca="false">A761 +1000</f>
@@ -17186,7 +17222,7 @@
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="E762" s="2" t="n">
         <f aca="false">A762 +1000</f>
@@ -17204,7 +17240,7 @@
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="E763" s="2" t="n">
         <f aca="false">A763 +1000</f>
@@ -17222,7 +17258,7 @@
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E764" s="2" t="n">
         <f aca="false">A764 +1000</f>
@@ -17240,7 +17276,7 @@
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E765" s="2" t="n">
         <f aca="false">A765 +1000</f>
@@ -17258,7 +17294,7 @@
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E766" s="2" t="n">
         <f aca="false">A766 +1000</f>
@@ -17276,7 +17312,7 @@
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="E767" s="2" t="n">
         <f aca="false">A767 +1000</f>
@@ -17294,7 +17330,7 @@
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E768" s="2" t="n">
         <f aca="false">A768 +1000</f>
@@ -17312,7 +17348,7 @@
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E769" s="2" t="n">
         <f aca="false">A769 +1000</f>
@@ -17330,7 +17366,7 @@
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="E770" s="2" t="n">
         <f aca="false">A770 +1000</f>
@@ -17348,7 +17384,7 @@
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E771" s="2" t="n">
         <f aca="false">A771 +1000</f>
@@ -17366,7 +17402,7 @@
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E772" s="2" t="n">
         <f aca="false">A772 +1000</f>
@@ -17384,7 +17420,7 @@
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E773" s="2" t="n">
         <f aca="false">A773 +1000</f>
@@ -17402,7 +17438,7 @@
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="E774" s="2" t="n">
         <f aca="false">A774 +1000</f>
@@ -17420,7 +17456,7 @@
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="E775" s="2" t="n">
         <f aca="false">A775 +1000</f>
@@ -17438,7 +17474,7 @@
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E776" s="2" t="n">
         <f aca="false">A776 +1000</f>
@@ -17456,7 +17492,7 @@
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E777" s="2" t="n">
         <f aca="false">A777 +1000</f>
@@ -17474,7 +17510,7 @@
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="E778" s="2" t="n">
         <f aca="false">A778 +1000</f>
@@ -17492,7 +17528,7 @@
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E779" s="2" t="n">
         <f aca="false">A779 +1000</f>
@@ -17510,7 +17546,7 @@
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E780" s="2" t="n">
         <f aca="false">A780 +1000</f>
@@ -17528,7 +17564,7 @@
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="E781" s="2" t="n">
         <f aca="false">A781 +1000</f>
@@ -17546,7 +17582,7 @@
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="E782" s="2" t="n">
         <f aca="false">A782 +1000</f>
@@ -17564,7 +17600,7 @@
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="E783" s="2" t="n">
         <f aca="false">A783 +1000</f>
@@ -17582,7 +17618,7 @@
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="E784" s="2" t="n">
         <f aca="false">A784 +1000</f>
@@ -17600,7 +17636,7 @@
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E785" s="2" t="n">
         <f aca="false">A785 +1000</f>
@@ -17618,7 +17654,7 @@
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E786" s="2" t="n">
         <f aca="false">A786 +1000</f>
@@ -17636,7 +17672,7 @@
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="E787" s="2" t="n">
         <f aca="false">A787 +1000</f>
@@ -17654,7 +17690,7 @@
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E788" s="2" t="n">
         <f aca="false">A788 +1000</f>
@@ -17672,7 +17708,7 @@
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E789" s="2" t="n">
         <f aca="false">A789 +1000</f>
@@ -17690,7 +17726,7 @@
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E790" s="2" t="n">
         <f aca="false">A790 +1000</f>
@@ -17708,7 +17744,7 @@
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="E791" s="2" t="n">
         <f aca="false">A791 +1000</f>
@@ -17726,7 +17762,7 @@
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E792" s="2" t="n">
         <f aca="false">A792 +1000</f>
@@ -17744,7 +17780,7 @@
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E793" s="2" t="n">
         <f aca="false">A793 +1000</f>
@@ -17762,7 +17798,7 @@
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E794" s="2" t="n">
         <f aca="false">A794 +1000</f>
@@ -17780,7 +17816,7 @@
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="E795" s="2" t="n">
         <f aca="false">A795 +1000</f>
@@ -17798,7 +17834,7 @@
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E796" s="2" t="n">
         <f aca="false">A796 +1000</f>
@@ -17816,7 +17852,7 @@
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E797" s="2" t="n">
         <f aca="false">A797 +1000</f>
@@ -17834,7 +17870,7 @@
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="E798" s="2" t="n">
         <f aca="false">A798 +1000</f>
@@ -17852,7 +17888,7 @@
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E799" s="2" t="n">
         <f aca="false">A799 +1000</f>
@@ -17870,7 +17906,7 @@
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E800" s="2" t="n">
         <f aca="false">A800 +1000</f>
@@ -17888,7 +17924,7 @@
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="E801" s="2" t="n">
         <f aca="false">A801 +1000</f>
@@ -17906,7 +17942,7 @@
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E802" s="2" t="n">
         <f aca="false">A802 +1000</f>
@@ -17924,7 +17960,7 @@
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="E803" s="2" t="n">
         <f aca="false">A803 +1000</f>
@@ -17942,7 +17978,7 @@
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E804" s="2" t="n">
         <f aca="false">A804 +1000</f>
@@ -17960,7 +17996,7 @@
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E805" s="2" t="n">
         <f aca="false">A805 +1000</f>
@@ -17978,7 +18014,7 @@
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="E806" s="2" t="n">
         <f aca="false">A806 +1000</f>
@@ -17996,7 +18032,7 @@
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E807" s="2" t="n">
         <f aca="false">A807 +1000</f>
@@ -18014,7 +18050,7 @@
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E808" s="2" t="n">
         <f aca="false">A808 +1000</f>
@@ -18032,7 +18068,7 @@
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E809" s="2" t="n">
         <f aca="false">A809 +1000</f>
@@ -18050,7 +18086,7 @@
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E810" s="2" t="n">
         <f aca="false">A810 +1000</f>
@@ -18068,7 +18104,7 @@
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="E811" s="2" t="n">
         <f aca="false">A811 +1000</f>
@@ -18086,7 +18122,7 @@
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E812" s="2" t="n">
         <f aca="false">A812 +1000</f>
@@ -18104,7 +18140,7 @@
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E813" s="2" t="n">
         <f aca="false">A813 +1000</f>
@@ -18122,7 +18158,7 @@
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="E814" s="2" t="n">
         <f aca="false">A814 +1000</f>
@@ -18140,7 +18176,7 @@
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E815" s="2" t="n">
         <f aca="false">A815 +1000</f>
@@ -18158,7 +18194,7 @@
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E816" s="2" t="n">
         <f aca="false">A816 +1000</f>
@@ -18176,7 +18212,7 @@
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E817" s="2" t="n">
         <f aca="false">A817 +1000</f>
@@ -18194,7 +18230,7 @@
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E818" s="2" t="n">
         <f aca="false">A818 +1000</f>
@@ -18212,7 +18248,7 @@
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E819" s="2" t="n">
         <f aca="false">A819 +1000</f>
@@ -18230,7 +18266,7 @@
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E820" s="2" t="n">
         <f aca="false">A820 +1000</f>
@@ -18248,7 +18284,7 @@
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E821" s="2" t="n">
         <f aca="false">A821 +1000</f>
@@ -18266,7 +18302,7 @@
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="E822" s="2" t="n">
         <f aca="false">A822 +1000</f>
@@ -18284,7 +18320,7 @@
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E823" s="2" t="n">
         <f aca="false">A823 +1000</f>
@@ -18302,7 +18338,7 @@
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E824" s="2" t="n">
         <f aca="false">A824 +1000</f>
@@ -18320,7 +18356,7 @@
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E825" s="2" t="n">
         <f aca="false">A825 +1000</f>
@@ -18338,7 +18374,7 @@
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E826" s="2" t="n">
         <f aca="false">A826 +1000</f>
@@ -18356,7 +18392,7 @@
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E827" s="2" t="n">
         <f aca="false">A827 +1000</f>
@@ -18374,7 +18410,7 @@
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E828" s="2" t="n">
         <f aca="false">A828 +1000</f>
@@ -18392,7 +18428,7 @@
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E829" s="2" t="n">
         <f aca="false">A829 +1000</f>
@@ -18410,7 +18446,7 @@
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E830" s="2" t="n">
         <f aca="false">A830 +1000</f>
@@ -18428,7 +18464,7 @@
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E831" s="2" t="n">
         <f aca="false">A831 +1000</f>
@@ -18446,7 +18482,7 @@
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E832" s="2" t="n">
         <f aca="false">A832 +1000</f>
@@ -18464,7 +18500,7 @@
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E833" s="2" t="n">
         <f aca="false">A833 +1000</f>
@@ -18482,7 +18518,7 @@
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="E834" s="2" t="n">
         <f aca="false">A834 +1000</f>
@@ -18500,7 +18536,7 @@
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E835" s="2" t="n">
         <f aca="false">A835 +1000</f>
@@ -18518,7 +18554,7 @@
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E836" s="2" t="n">
         <f aca="false">A836 +1000</f>
@@ -18536,7 +18572,7 @@
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E837" s="2" t="n">
         <f aca="false">A837 +1000</f>
@@ -18554,7 +18590,7 @@
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="E838" s="2" t="n">
         <f aca="false">A838 +1000</f>
@@ -18572,7 +18608,7 @@
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E839" s="2" t="n">
         <f aca="false">A839 +1000</f>
@@ -18590,7 +18626,7 @@
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E840" s="2" t="n">
         <f aca="false">A840 +1000</f>
@@ -18608,7 +18644,7 @@
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="E841" s="2" t="n">
         <f aca="false">A841 +1000</f>
@@ -18626,7 +18662,7 @@
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="E842" s="2" t="n">
         <f aca="false">A842 +1000</f>
@@ -18644,7 +18680,7 @@
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E843" s="2" t="n">
         <f aca="false">A843 +1000</f>
@@ -18662,7 +18698,7 @@
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E844" s="2" t="n">
         <f aca="false">A844 +1000</f>
@@ -18680,7 +18716,7 @@
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E845" s="2" t="n">
         <f aca="false">A845 +1000</f>
@@ -18698,7 +18734,7 @@
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E846" s="2" t="n">
         <f aca="false">A846 +1000</f>
@@ -18716,16 +18752,16 @@
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B847" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C847" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E847" s="2" t="n">
         <f aca="false">A847 +1000</f>
@@ -18743,7 +18779,7 @@
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E848" s="2" t="n">
         <f aca="false">A848 +1000</f>
@@ -18761,7 +18797,7 @@
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E849" s="2" t="n">
         <f aca="false">A849 +1000</f>
@@ -18779,7 +18815,7 @@
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="E850" s="2" t="n">
         <f aca="false">A850 +1000</f>
@@ -18797,7 +18833,7 @@
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E851" s="2" t="n">
         <f aca="false">A851 +1000</f>
@@ -18815,7 +18851,7 @@
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E852" s="2" t="n">
         <f aca="false">A852 +1000</f>
@@ -18833,7 +18869,7 @@
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="E853" s="2" t="n">
         <f aca="false">A853 +1000</f>
@@ -18851,7 +18887,7 @@
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E854" s="2" t="n">
         <f aca="false">A854 +1000</f>
@@ -18869,7 +18905,7 @@
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="E855" s="2" t="n">
         <f aca="false">A855 +1000</f>
@@ -18887,7 +18923,7 @@
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E856" s="2" t="n">
         <f aca="false">A856 +1000</f>
@@ -18905,7 +18941,7 @@
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="E857" s="2" t="n">
         <f aca="false">A857 +1000</f>
@@ -18923,7 +18959,7 @@
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E858" s="2" t="n">
         <f aca="false">A858 +1000</f>
@@ -18941,7 +18977,7 @@
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="E859" s="2" t="n">
         <f aca="false">A859 +1000</f>
@@ -18959,7 +18995,7 @@
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E860" s="2" t="n">
         <f aca="false">A860 +1000</f>
@@ -18977,7 +19013,7 @@
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="E861" s="2" t="n">
         <f aca="false">A861 +1000</f>
@@ -18995,7 +19031,7 @@
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="E862" s="2" t="n">
         <f aca="false">A862 +1000</f>
@@ -19013,7 +19049,7 @@
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E863" s="2" t="n">
         <f aca="false">A863 +1000</f>
@@ -19031,7 +19067,7 @@
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E864" s="2" t="n">
         <f aca="false">A864 +1000</f>
@@ -19049,7 +19085,7 @@
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E865" s="2" t="n">
         <f aca="false">A865 +1000</f>
@@ -19067,7 +19103,7 @@
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E866" s="2" t="n">
         <f aca="false">A866 +1000</f>
@@ -19085,7 +19121,7 @@
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="E867" s="2" t="n">
         <f aca="false">A867 +1000</f>
@@ -19103,7 +19139,7 @@
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E868" s="2" t="n">
         <f aca="false">A868 +1000</f>
@@ -19121,7 +19157,7 @@
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="E869" s="2" t="n">
         <f aca="false">A869 +1000</f>
@@ -19139,7 +19175,7 @@
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E870" s="2" t="n">
         <f aca="false">A870 +1000</f>
@@ -19157,7 +19193,7 @@
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E871" s="2" t="n">
         <f aca="false">A871 +1000</f>
@@ -19175,7 +19211,7 @@
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="E872" s="2" t="n">
         <f aca="false">A872 +1000</f>
@@ -19193,7 +19229,7 @@
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E873" s="2" t="n">
         <f aca="false">A873 +1000</f>
@@ -19211,7 +19247,7 @@
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E874" s="2" t="n">
         <f aca="false">A874 +1000</f>
@@ -19229,7 +19265,7 @@
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E875" s="2" t="n">
         <f aca="false">A875 +1000</f>
@@ -19247,7 +19283,7 @@
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E876" s="2" t="n">
         <f aca="false">A876 +1000</f>
@@ -19265,7 +19301,7 @@
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E877" s="2" t="n">
         <f aca="false">A877 +1000</f>
@@ -19283,7 +19319,7 @@
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E878" s="2" t="n">
         <f aca="false">A878 +1000</f>
@@ -19301,7 +19337,7 @@
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E879" s="2" t="n">
         <f aca="false">A879 +1000</f>
@@ -19319,7 +19355,7 @@
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E880" s="2" t="n">
         <f aca="false">A880 +1000</f>
@@ -19337,7 +19373,7 @@
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E881" s="2" t="n">
         <f aca="false">A881 +1000</f>
@@ -19355,7 +19391,7 @@
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E882" s="2" t="n">
         <f aca="false">A882 +1000</f>
@@ -19373,7 +19409,7 @@
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E883" s="2" t="n">
         <f aca="false">A883 +1000</f>
@@ -19391,7 +19427,7 @@
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E884" s="2" t="n">
         <f aca="false">A884 +1000</f>
@@ -19409,7 +19445,7 @@
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E885" s="2" t="n">
         <f aca="false">A885 +1000</f>
@@ -19427,7 +19463,7 @@
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="E886" s="2" t="n">
         <f aca="false">A886 +1000</f>
@@ -19445,7 +19481,7 @@
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E887" s="2" t="n">
         <f aca="false">A887 +1000</f>
@@ -19463,7 +19499,7 @@
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E888" s="2" t="n">
         <f aca="false">A888 +1000</f>
@@ -19481,7 +19517,7 @@
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E889" s="2" t="n">
         <f aca="false">A889 +1000</f>
@@ -19499,7 +19535,7 @@
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E890" s="2" t="n">
         <f aca="false">A890 +1000</f>
@@ -19517,7 +19553,7 @@
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E891" s="2" t="n">
         <f aca="false">A891 +1000</f>
@@ -19535,7 +19571,7 @@
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="E892" s="2" t="n">
         <f aca="false">A892 +1000</f>
@@ -19553,7 +19589,7 @@
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E893" s="2" t="n">
         <f aca="false">A893 +1000</f>
@@ -19571,7 +19607,7 @@
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E894" s="2" t="n">
         <f aca="false">A894 +1000</f>
@@ -19589,7 +19625,7 @@
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E895" s="2" t="n">
         <f aca="false">A895 +1000</f>
@@ -19607,7 +19643,7 @@
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E896" s="2" t="n">
         <f aca="false">A896 +1000</f>
@@ -19625,7 +19661,7 @@
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E897" s="2" t="n">
         <f aca="false">A897 +1000</f>
@@ -19643,7 +19679,7 @@
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E898" s="2" t="n">
         <f aca="false">A898 +1000</f>
@@ -19661,7 +19697,7 @@
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E899" s="2" t="n">
         <f aca="false">A899 +1000</f>
@@ -19679,7 +19715,7 @@
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E900" s="2" t="n">
         <f aca="false">A900 +1000</f>
@@ -19697,7 +19733,7 @@
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E901" s="2" t="n">
         <f aca="false">A901 +1000</f>
@@ -19715,7 +19751,7 @@
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E902" s="2" t="n">
         <f aca="false">A902 +1000</f>
@@ -19733,7 +19769,7 @@
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E903" s="2" t="n">
         <f aca="false">A903 +1000</f>
@@ -19751,7 +19787,7 @@
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E904" s="2" t="n">
         <f aca="false">A904 +1000</f>
@@ -19769,7 +19805,7 @@
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E905" s="2" t="n">
         <f aca="false">A905 +1000</f>
@@ -19787,7 +19823,7 @@
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E906" s="2" t="n">
         <f aca="false">A906 +1000</f>
@@ -19805,7 +19841,7 @@
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E907" s="2" t="n">
         <f aca="false">A907 +1000</f>
@@ -19823,7 +19859,7 @@
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E908" s="2" t="n">
         <f aca="false">A908 +1000</f>
@@ -19841,7 +19877,7 @@
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E909" s="2" t="n">
         <f aca="false">A909 +1000</f>
@@ -19859,7 +19895,7 @@
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E910" s="2" t="n">
         <f aca="false">A910 +1000</f>
@@ -19877,7 +19913,7 @@
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E911" s="2" t="n">
         <f aca="false">A911 +1000</f>
@@ -19895,7 +19931,7 @@
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="E912" s="2" t="n">
         <f aca="false">A912 +1000</f>
@@ -19913,7 +19949,7 @@
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="E913" s="2" t="n">
         <f aca="false">A913 +1000</f>
@@ -19931,7 +19967,7 @@
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E914" s="2" t="n">
         <f aca="false">A914 +1000</f>
@@ -19949,7 +19985,7 @@
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="1" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E915" s="2" t="n">
         <f aca="false">A915 +1000</f>
@@ -19967,7 +20003,7 @@
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="1" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E916" s="2" t="n">
         <f aca="false">A916 +1000</f>
@@ -19985,7 +20021,7 @@
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E917" s="2" t="n">
         <f aca="false">A917 +1000</f>
@@ -20003,7 +20039,7 @@
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E918" s="2" t="n">
         <f aca="false">A918 +1000</f>
@@ -20021,7 +20057,7 @@
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E919" s="2" t="n">
         <f aca="false">A919 +1000</f>
@@ -20039,7 +20075,7 @@
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="1" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="E920" s="2" t="n">
         <f aca="false">A920 +1000</f>
@@ -20057,7 +20093,7 @@
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="1" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E921" s="2" t="n">
         <f aca="false">A921 +1000</f>
@@ -20075,7 +20111,7 @@
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="1" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E922" s="2" t="n">
         <f aca="false">A922 +1000</f>
@@ -20093,7 +20129,7 @@
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E923" s="2" t="n">
         <f aca="false">A923 +1000</f>
@@ -20111,7 +20147,7 @@
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E924" s="2" t="n">
         <f aca="false">A924 +1000</f>
@@ -20129,7 +20165,7 @@
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E925" s="2" t="n">
         <f aca="false">A925 +1000</f>
@@ -20147,7 +20183,7 @@
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E926" s="2" t="n">
         <f aca="false">A926 +1000</f>
@@ -20165,7 +20201,7 @@
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E927" s="2" t="n">
         <f aca="false">A927 +1000</f>
@@ -20183,7 +20219,7 @@
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="1" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="E928" s="2" t="n">
         <f aca="false">A928 +1000</f>
@@ -20201,7 +20237,7 @@
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="1" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E929" s="2" t="n">
         <f aca="false">A929 +1000</f>
@@ -20219,7 +20255,7 @@
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="1" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="E930" s="2" t="n">
         <f aca="false">A930 +1000</f>
@@ -20237,7 +20273,7 @@
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E931" s="2" t="n">
         <f aca="false">A931 +1000</f>
@@ -20255,7 +20291,7 @@
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E932" s="2" t="n">
         <f aca="false">A932 +1000</f>
@@ -20273,7 +20309,7 @@
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E933" s="2" t="n">
         <f aca="false">A933 +1000</f>
@@ -20291,7 +20327,7 @@
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="1" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="E934" s="2" t="n">
         <f aca="false">A934 +1000</f>
@@ -20309,7 +20345,7 @@
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E935" s="2" t="n">
         <f aca="false">A935 +1000</f>
@@ -20327,7 +20363,7 @@
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="E936" s="2" t="n">
         <f aca="false">A936 +1000</f>
@@ -20345,7 +20381,7 @@
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E937" s="2" t="n">
         <f aca="false">A937 +1000</f>
@@ -20363,7 +20399,7 @@
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="1" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E938" s="2" t="n">
         <f aca="false">A938 +1000</f>
@@ -20381,7 +20417,7 @@
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="1" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E939" s="2" t="n">
         <f aca="false">A939 +1000</f>
@@ -20399,7 +20435,7 @@
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="1" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E940" s="2" t="n">
         <f aca="false">A940 +1000</f>
@@ -20417,7 +20453,7 @@
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E941" s="2" t="n">
         <f aca="false">A941 +1000</f>
@@ -20435,7 +20471,7 @@
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="1" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="E942" s="2" t="n">
         <f aca="false">A942 +1000</f>
@@ -20453,7 +20489,7 @@
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E943" s="2" t="n">
         <f aca="false">A943 +1000</f>
@@ -20471,7 +20507,7 @@
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="1" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E944" s="2" t="n">
         <f aca="false">A944 +1000</f>
@@ -20489,7 +20525,7 @@
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E945" s="2" t="n">
         <f aca="false">A945 +1000</f>
@@ -20507,7 +20543,7 @@
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="E946" s="2" t="n">
         <f aca="false">A946 +1000</f>
@@ -20525,7 +20561,7 @@
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E947" s="2" t="n">
         <f aca="false">A947 +1000</f>
@@ -20543,7 +20579,7 @@
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="E948" s="2" t="n">
         <f aca="false">A948 +1000</f>
@@ -20561,7 +20597,7 @@
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E949" s="2" t="n">
         <f aca="false">A949 +1000</f>
@@ -20579,7 +20615,7 @@
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E950" s="2" t="n">
         <f aca="false">A950 +1000</f>
@@ -20597,7 +20633,7 @@
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="E951" s="2" t="n">
         <f aca="false">A951 +1000</f>
@@ -20615,7 +20651,7 @@
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="E952" s="2" t="n">
         <f aca="false">A952 +1000</f>
@@ -20633,7 +20669,7 @@
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E953" s="2" t="n">
         <f aca="false">A953 +1000</f>
@@ -20651,7 +20687,7 @@
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="E954" s="2" t="n">
         <f aca="false">A954 +1000</f>
@@ -20669,7 +20705,7 @@
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="E955" s="2" t="n">
         <f aca="false">A955 +1000</f>
@@ -20687,7 +20723,7 @@
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E956" s="2" t="n">
         <f aca="false">A956 +1000</f>
@@ -20705,7 +20741,7 @@
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E957" s="2" t="n">
         <f aca="false">A957 +1000</f>
@@ -20723,7 +20759,7 @@
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="E958" s="2" t="n">
         <f aca="false">A958 +1000</f>
@@ -20741,7 +20777,7 @@
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="E959" s="2" t="n">
         <f aca="false">A959 +1000</f>
@@ -20759,7 +20795,7 @@
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E960" s="2" t="n">
         <f aca="false">A960 +1000</f>
@@ -20777,7 +20813,7 @@
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="E961" s="2" t="n">
         <f aca="false">A961 +1000</f>
@@ -20795,7 +20831,7 @@
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E962" s="2" t="n">
         <f aca="false">A962 +1000</f>
@@ -20813,7 +20849,7 @@
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E963" s="2" t="n">
         <f aca="false">A963 +1000</f>
@@ -20831,7 +20867,7 @@
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="1" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="E964" s="2" t="n">
         <f aca="false">A964 +1000</f>
@@ -20849,7 +20885,7 @@
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E965" s="2" t="n">
         <f aca="false">A965 +1000</f>
@@ -20867,7 +20903,7 @@
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E966" s="2" t="n">
         <f aca="false">A966 +1000</f>
@@ -20885,7 +20921,7 @@
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="1" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E967" s="2" t="n">
         <f aca="false">A967 +1000</f>
@@ -20903,7 +20939,7 @@
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="1" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E968" s="2" t="n">
         <f aca="false">A968 +1000</f>
@@ -20921,7 +20957,7 @@
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E969" s="2" t="n">
         <f aca="false">A969 +1000</f>
@@ -20939,7 +20975,7 @@
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E970" s="2" t="n">
         <f aca="false">A970 +1000</f>
@@ -20957,7 +20993,7 @@
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="E971" s="2" t="n">
         <f aca="false">A971 +1000</f>
@@ -20975,7 +21011,7 @@
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="E972" s="2" t="n">
         <f aca="false">A972 +1000</f>
@@ -20993,7 +21029,7 @@
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="1" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E973" s="2" t="n">
         <f aca="false">A973 +1000</f>
@@ -21011,7 +21047,7 @@
     </row>
     <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="E974" s="2" t="n">
         <f aca="false">A974 +1000</f>
@@ -21022,10 +21058,10 @@
         <v>2973</v>
       </c>
       <c r="J974" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K974" s="3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="M974" s="2" t="n">
         <f aca="false">I974 +1000</f>
@@ -21035,7 +21071,7 @@
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="1" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="E975" s="2" t="n">
         <f aca="false">A975 +1000</f>
@@ -21053,7 +21089,7 @@
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="1" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E976" s="2" t="n">
         <f aca="false">A976 +1000</f>
@@ -21071,7 +21107,7 @@
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="1" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E977" s="2" t="n">
         <f aca="false">A977 +1000</f>
@@ -21089,7 +21125,7 @@
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E978" s="2" t="n">
         <f aca="false">A978 +1000</f>
@@ -21107,7 +21143,7 @@
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E979" s="2" t="n">
         <f aca="false">A979 +1000</f>
@@ -21125,7 +21161,7 @@
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="E980" s="2" t="n">
         <f aca="false">A980 +1000</f>
@@ -21143,7 +21179,7 @@
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="E981" s="2" t="n">
         <f aca="false">A981 +1000</f>
@@ -21161,7 +21197,7 @@
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E982" s="2" t="n">
         <f aca="false">A982 +1000</f>
@@ -21179,7 +21215,7 @@
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="1" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="E983" s="2" t="n">
         <f aca="false">A983 +1000</f>
@@ -21197,7 +21233,7 @@
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="E984" s="2" t="n">
         <f aca="false">A984 +1000</f>
@@ -21215,7 +21251,7 @@
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="1" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E985" s="2" t="n">
         <f aca="false">A985 +1000</f>
@@ -21233,7 +21269,7 @@
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="E986" s="2" t="n">
         <f aca="false">A986 +1000</f>
@@ -21251,7 +21287,7 @@
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="E987" s="2" t="n">
         <f aca="false">A987 +1000</f>
@@ -21269,7 +21305,7 @@
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E988" s="2" t="n">
         <f aca="false">A988 +1000</f>
@@ -21287,7 +21323,7 @@
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E989" s="2" t="n">
         <f aca="false">A989 +1000</f>
@@ -21305,7 +21341,7 @@
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E990" s="2" t="n">
         <f aca="false">A990 +1000</f>
@@ -21323,7 +21359,7 @@
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="1" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E991" s="2" t="n">
         <f aca="false">A991 +1000</f>
@@ -21341,7 +21377,7 @@
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="E992" s="2" t="n">
         <f aca="false">A992 +1000</f>
@@ -21359,7 +21395,7 @@
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="E993" s="2" t="n">
         <f aca="false">A993 +1000</f>
@@ -21377,7 +21413,7 @@
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="1" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E994" s="2" t="n">
         <f aca="false">A994 +1000</f>
@@ -21395,7 +21431,7 @@
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E995" s="2" t="n">
         <f aca="false">A995 +1000</f>
@@ -21413,7 +21449,7 @@
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="E996" s="2" t="n">
         <f aca="false">A996 +1000</f>
@@ -21431,7 +21467,7 @@
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E997" s="2" t="n">
         <f aca="false">A997 +1000</f>
@@ -21449,7 +21485,7 @@
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="E998" s="2" t="n">
         <f aca="false">A998 +1000</f>
@@ -21467,7 +21503,7 @@
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="1" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E999" s="2" t="n">
         <f aca="false">A999 +1000</f>
@@ -21485,7 +21521,7 @@
     </row>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="1" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E1000" s="2" t="n">
         <f aca="false">A1000 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1008">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -551,6 +551,9 @@
   </si>
   <si>
     <t xml:space="preserve">0173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pushAll→push left</t>
   </si>
   <si>
     <t xml:space="preserve">0174</t>
@@ -3273,6 +3276,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3439,7 +3443,7 @@
       <c r="G9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I9" s="2" t="n">
@@ -5082,7 +5086,7 @@
       <c r="C99" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D99" s="0" t="s">
+      <c r="D99" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E99" s="2" t="n">
@@ -6441,6 +6445,15 @@
       <c r="A174" s="1" t="s">
         <v>176</v>
       </c>
+      <c r="B174" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="0" t="s">
+        <v>177</v>
+      </c>
       <c r="E174" s="2" t="n">
         <f aca="false">A174 +1000</f>
         <v>1173</v>
@@ -6457,7 +6470,7 @@
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E175" s="2" t="n">
         <f aca="false">A175 +1000</f>
@@ -6475,7 +6488,7 @@
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E176" s="2" t="n">
         <f aca="false">A176 +1000</f>
@@ -6493,7 +6506,7 @@
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E177" s="2" t="n">
         <f aca="false">A177 +1000</f>
@@ -6511,7 +6524,7 @@
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E178" s="2" t="n">
         <f aca="false">A178 +1000</f>
@@ -6529,7 +6542,7 @@
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E179" s="2" t="n">
         <f aca="false">A179 +1000</f>
@@ -6547,7 +6560,7 @@
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E180" s="2" t="n">
         <f aca="false">A180 +1000</f>
@@ -6565,7 +6578,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E181" s="2" t="n">
         <f aca="false">A181 +1000</f>
@@ -6583,7 +6596,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E182" s="2" t="n">
         <f aca="false">A182 +1000</f>
@@ -6601,7 +6614,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E183" s="2" t="n">
         <f aca="false">A183 +1000</f>
@@ -6619,7 +6632,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E184" s="2" t="n">
         <f aca="false">A184 +1000</f>
@@ -6637,7 +6650,7 @@
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E185" s="2" t="n">
         <f aca="false">A185 +1000</f>
@@ -6655,7 +6668,7 @@
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E186" s="2" t="n">
         <f aca="false">A186 +1000</f>
@@ -6673,7 +6686,7 @@
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E187" s="2" t="n">
         <f aca="false">A187 +1000</f>
@@ -6691,7 +6704,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E188" s="2" t="n">
         <f aca="false">A188 +1000</f>
@@ -6709,7 +6722,7 @@
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E189" s="2" t="n">
         <f aca="false">A189 +1000</f>
@@ -6727,7 +6740,7 @@
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E190" s="2" t="n">
         <f aca="false">A190 +1000</f>
@@ -6745,7 +6758,7 @@
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E191" s="2" t="n">
         <f aca="false">A191 +1000</f>
@@ -6763,7 +6776,7 @@
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E192" s="2" t="n">
         <f aca="false">A192 +1000</f>
@@ -6781,7 +6794,7 @@
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E193" s="2" t="n">
         <f aca="false">A193 +1000</f>
@@ -6799,7 +6812,7 @@
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E194" s="2" t="n">
         <f aca="false">A194 +1000</f>
@@ -6817,7 +6830,7 @@
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E195" s="2" t="n">
         <f aca="false">A195 +1000</f>
@@ -6835,7 +6848,7 @@
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E196" s="2" t="n">
         <f aca="false">A196 +1000</f>
@@ -6853,7 +6866,7 @@
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E197" s="2" t="n">
         <f aca="false">A197 +1000</f>
@@ -6871,7 +6884,7 @@
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E198" s="2" t="n">
         <f aca="false">A198 +1000</f>
@@ -6889,7 +6902,7 @@
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E199" s="2" t="n">
         <f aca="false">A199 +1000</f>
@@ -6907,7 +6920,7 @@
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E200" s="2" t="n">
         <f aca="false">A200 +1000</f>
@@ -6925,7 +6938,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E201" s="2" t="n">
         <f aca="false">A201 +1000</f>
@@ -6943,7 +6956,7 @@
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E202" s="2" t="n">
         <f aca="false">A202 +1000</f>
@@ -6961,7 +6974,7 @@
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E203" s="2" t="n">
         <f aca="false">A203 +1000</f>
@@ -6979,7 +6992,7 @@
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E204" s="2" t="n">
         <f aca="false">A204 +1000</f>
@@ -6997,7 +7010,7 @@
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E205" s="2" t="n">
         <f aca="false">A205 +1000</f>
@@ -7015,7 +7028,7 @@
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E206" s="2" t="n">
         <f aca="false">A206 +1000</f>
@@ -7033,7 +7046,7 @@
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E207" s="2" t="n">
         <f aca="false">A207 +1000</f>
@@ -7051,7 +7064,7 @@
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E208" s="2" t="n">
         <f aca="false">A208 +1000</f>
@@ -7069,7 +7082,7 @@
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E209" s="2" t="n">
         <f aca="false">A209 +1000</f>
@@ -7087,7 +7100,7 @@
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E210" s="2" t="n">
         <f aca="false">A210 +1000</f>
@@ -7105,7 +7118,7 @@
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E211" s="2" t="n">
         <f aca="false">A211 +1000</f>
@@ -7123,7 +7136,7 @@
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E212" s="2" t="n">
         <f aca="false">A212 +1000</f>
@@ -7141,7 +7154,7 @@
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E213" s="2" t="n">
         <f aca="false">A213 +1000</f>
@@ -7159,7 +7172,7 @@
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E214" s="2" t="n">
         <f aca="false">A214 +1000</f>
@@ -7177,7 +7190,7 @@
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B215" s="3"/>
       <c r="E215" s="2" t="n">
@@ -7196,7 +7209,7 @@
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>9</v>
@@ -7220,7 +7233,7 @@
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E217" s="2" t="n">
         <f aca="false">A217 +1000</f>
@@ -7238,7 +7251,7 @@
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>9</v>
@@ -7262,7 +7275,7 @@
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E219" s="2" t="n">
         <f aca="false">A219 +1000</f>
@@ -7280,7 +7293,7 @@
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E220" s="2" t="n">
         <f aca="false">A220 +1000</f>
@@ -7298,7 +7311,7 @@
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E221" s="2" t="n">
         <f aca="false">A221 +1000</f>
@@ -7316,7 +7329,7 @@
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E222" s="2" t="n">
         <f aca="false">A222 +1000</f>
@@ -7334,7 +7347,7 @@
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E223" s="2" t="n">
         <f aca="false">A223 +1000</f>
@@ -7352,7 +7365,7 @@
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E224" s="2" t="n">
         <f aca="false">A224 +1000</f>
@@ -7370,7 +7383,7 @@
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E225" s="2" t="n">
         <f aca="false">A225 +1000</f>
@@ -7388,7 +7401,7 @@
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E226" s="2" t="n">
         <f aca="false">A226 +1000</f>
@@ -7406,7 +7419,7 @@
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E227" s="2" t="n">
         <f aca="false">A227 +1000</f>
@@ -7424,7 +7437,7 @@
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E228" s="2" t="n">
         <f aca="false">A228 +1000</f>
@@ -7442,7 +7455,7 @@
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E229" s="2" t="n">
         <f aca="false">A229 +1000</f>
@@ -7460,7 +7473,7 @@
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E230" s="2" t="n">
         <f aca="false">A230 +1000</f>
@@ -7478,7 +7491,7 @@
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>9</v>
@@ -7487,7 +7500,7 @@
         <v>9</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E231" s="2" t="n">
         <f aca="false">A231 +1000</f>
@@ -7511,7 +7524,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">A232 +1000</f>
@@ -7529,7 +7542,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">A233 +1000</f>
@@ -7547,7 +7560,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">A234 +1000</f>
@@ -7565,7 +7578,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">A235 +1000</f>
@@ -7583,7 +7596,7 @@
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>9</v>
@@ -7591,8 +7604,8 @@
       <c r="C236" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D236" s="0" t="s">
-        <v>240</v>
+      <c r="D236" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">A236 +1000</f>
@@ -7610,7 +7623,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">A237 +1000</f>
@@ -7628,7 +7641,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">A238 +1000</f>
@@ -7646,7 +7659,7 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>9</v>
@@ -7670,7 +7683,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">A240 +1000</f>
@@ -7688,7 +7701,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">A241 +1000</f>
@@ -7706,7 +7719,7 @@
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">A242 +1000</f>
@@ -7724,7 +7737,7 @@
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">A243 +1000</f>
@@ -7742,7 +7755,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">A244 +1000</f>
@@ -7760,7 +7773,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">A245 +1000</f>
@@ -7778,7 +7791,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E246" s="2" t="n">
         <f aca="false">A246 +1000</f>
@@ -7796,7 +7809,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E247" s="2" t="n">
         <f aca="false">A247 +1000</f>
@@ -7814,7 +7827,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E248" s="2" t="n">
         <f aca="false">A248 +1000</f>
@@ -7832,7 +7845,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E249" s="2" t="n">
         <f aca="false">A249 +1000</f>
@@ -7850,7 +7863,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E250" s="2" t="n">
         <f aca="false">A250 +1000</f>
@@ -7868,7 +7881,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E251" s="2" t="n">
         <f aca="false">A251 +1000</f>
@@ -7886,7 +7899,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E252" s="2" t="n">
         <f aca="false">A252 +1000</f>
@@ -7904,7 +7917,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E253" s="2" t="n">
         <f aca="false">A253 +1000</f>
@@ -7922,7 +7935,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E254" s="2" t="n">
         <f aca="false">A254 +1000</f>
@@ -7940,7 +7953,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E255" s="2" t="n">
         <f aca="false">A255 +1000</f>
@@ -7958,7 +7971,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E256" s="2" t="n">
         <f aca="false">A256 +1000</f>
@@ -7976,7 +7989,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E257" s="2" t="n">
         <f aca="false">A257 +1000</f>
@@ -7994,7 +8007,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E258" s="2" t="n">
         <f aca="false">A258 +1000</f>
@@ -8012,7 +8025,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E259" s="2" t="n">
         <f aca="false">A259 +1000</f>
@@ -8030,7 +8043,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E260" s="2" t="n">
         <f aca="false">A260 +1000</f>
@@ -8048,7 +8061,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E261" s="2" t="n">
         <f aca="false">A261 +1000</f>
@@ -8066,7 +8079,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E262" s="2" t="n">
         <f aca="false">A262 +1000</f>
@@ -8084,7 +8097,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E263" s="2" t="n">
         <f aca="false">A263 +1000</f>
@@ -8102,7 +8115,7 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>9</v>
@@ -8132,7 +8145,7 @@
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E265" s="2" t="n">
         <f aca="false">A265 +1000</f>
@@ -8150,7 +8163,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E266" s="2" t="n">
         <f aca="false">A266 +1000</f>
@@ -8168,7 +8181,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E267" s="2" t="n">
         <f aca="false">A267 +1000</f>
@@ -8186,7 +8199,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E268" s="2" t="n">
         <f aca="false">A268 +1000</f>
@@ -8204,7 +8217,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E269" s="2" t="n">
         <f aca="false">A269 +1000</f>
@@ -8222,7 +8235,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E270" s="2" t="n">
         <f aca="false">A270 +1000</f>
@@ -8240,7 +8253,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E271" s="2" t="n">
         <f aca="false">A271 +1000</f>
@@ -8258,7 +8271,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E272" s="2" t="n">
         <f aca="false">A272 +1000</f>
@@ -8276,7 +8289,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E273" s="2" t="n">
         <f aca="false">A273 +1000</f>
@@ -8294,7 +8307,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E274" s="2" t="n">
         <f aca="false">A274 +1000</f>
@@ -8312,7 +8325,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E275" s="2" t="n">
         <f aca="false">A275 +1000</f>
@@ -8330,7 +8343,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E276" s="2" t="n">
         <f aca="false">A276 +1000</f>
@@ -8348,7 +8361,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E277" s="2" t="n">
         <f aca="false">A277 +1000</f>
@@ -8366,7 +8379,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E278" s="2" t="n">
         <f aca="false">A278 +1000</f>
@@ -8384,7 +8397,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E279" s="2" t="n">
         <f aca="false">A279 +1000</f>
@@ -8402,7 +8415,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E280" s="2" t="n">
         <f aca="false">A280 +1000</f>
@@ -8420,7 +8433,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E281" s="2" t="n">
         <f aca="false">A281 +1000</f>
@@ -8438,7 +8451,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E282" s="2" t="n">
         <f aca="false">A282 +1000</f>
@@ -8456,7 +8469,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E283" s="2" t="n">
         <f aca="false">A283 +1000</f>
@@ -8474,7 +8487,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E284" s="2" t="n">
         <f aca="false">A284 +1000</f>
@@ -8492,7 +8505,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E285" s="2" t="n">
         <f aca="false">A285 +1000</f>
@@ -8510,7 +8523,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E286" s="2" t="n">
         <f aca="false">A286 +1000</f>
@@ -8528,7 +8541,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E287" s="2" t="n">
         <f aca="false">A287 +1000</f>
@@ -8546,7 +8559,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E288" s="2" t="n">
         <f aca="false">A288 +1000</f>
@@ -8564,7 +8577,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E289" s="2" t="n">
         <f aca="false">A289 +1000</f>
@@ -8582,7 +8595,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E290" s="2" t="n">
         <f aca="false">A290 +1000</f>
@@ -8600,7 +8613,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E291" s="2" t="n">
         <f aca="false">A291 +1000</f>
@@ -8618,7 +8631,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E292" s="2" t="n">
         <f aca="false">A292 +1000</f>
@@ -8636,7 +8649,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E293" s="2" t="n">
         <f aca="false">A293 +1000</f>
@@ -8654,7 +8667,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E294" s="2" t="n">
         <f aca="false">A294 +1000</f>
@@ -8672,7 +8685,7 @@
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
@@ -8691,7 +8704,7 @@
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>9</v>
@@ -8715,7 +8728,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E297" s="2" t="n">
         <f aca="false">A297 +1000</f>
@@ -8733,7 +8746,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E298" s="2" t="n">
         <f aca="false">A298 +1000</f>
@@ -8751,7 +8764,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E299" s="2" t="n">
         <f aca="false">A299 +1000</f>
@@ -8769,7 +8782,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E300" s="2" t="n">
         <f aca="false">A300 +1000</f>
@@ -8787,7 +8800,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E301" s="2" t="n">
         <f aca="false">A301 +1000</f>
@@ -8805,7 +8818,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E302" s="2" t="n">
         <f aca="false">A302 +1000</f>
@@ -8823,7 +8836,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E303" s="2" t="n">
         <f aca="false">A303 +1000</f>
@@ -8841,7 +8854,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E304" s="2" t="n">
         <f aca="false">A304 +1000</f>
@@ -8859,7 +8872,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E305" s="2" t="n">
         <f aca="false">A305 +1000</f>
@@ -8877,7 +8890,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E306" s="2" t="n">
         <f aca="false">A306 +1000</f>
@@ -8895,7 +8908,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E307" s="2" t="n">
         <f aca="false">A307 +1000</f>
@@ -8913,7 +8926,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E308" s="2" t="n">
         <f aca="false">A308 +1000</f>
@@ -8931,7 +8944,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E309" s="2" t="n">
         <f aca="false">A309 +1000</f>
@@ -8949,7 +8962,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E310" s="2" t="n">
         <f aca="false">A310 +1000</f>
@@ -8967,7 +8980,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E311" s="2" t="n">
         <f aca="false">A311 +1000</f>
@@ -8985,7 +8998,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E312" s="2" t="n">
         <f aca="false">A312 +1000</f>
@@ -9003,7 +9016,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E313" s="2" t="n">
         <f aca="false">A313 +1000</f>
@@ -9021,7 +9034,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E314" s="2" t="n">
         <f aca="false">A314 +1000</f>
@@ -9039,7 +9052,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E315" s="2" t="n">
         <f aca="false">A315 +1000</f>
@@ -9057,7 +9070,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E316" s="2" t="n">
         <f aca="false">A316 +1000</f>
@@ -9075,7 +9088,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E317" s="2" t="n">
         <f aca="false">A317 +1000</f>
@@ -9093,7 +9106,7 @@
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E318" s="2" t="n">
         <f aca="false">A318 +1000</f>
@@ -9117,7 +9130,7 @@
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E319" s="2" t="n">
         <f aca="false">A319 +1000</f>
@@ -9135,7 +9148,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E320" s="2" t="n">
         <f aca="false">A320 +1000</f>
@@ -9153,7 +9166,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E321" s="2" t="n">
         <f aca="false">A321 +1000</f>
@@ -9171,7 +9184,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E322" s="2" t="n">
         <f aca="false">A322 +1000</f>
@@ -9189,7 +9202,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E323" s="2" t="n">
         <f aca="false">A323 +1000</f>
@@ -9207,7 +9220,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E324" s="2" t="n">
         <f aca="false">A324 +1000</f>
@@ -9225,7 +9238,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E325" s="2" t="n">
         <f aca="false">A325 +1000</f>
@@ -9243,7 +9256,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E326" s="2" t="n">
         <f aca="false">A326 +1000</f>
@@ -9261,7 +9274,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E327" s="2" t="n">
         <f aca="false">A327 +1000</f>
@@ -9279,7 +9292,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E328" s="2" t="n">
         <f aca="false">A328 +1000</f>
@@ -9297,7 +9310,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E329" s="2" t="n">
         <f aca="false">A329 +1000</f>
@@ -9315,7 +9328,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E330" s="2" t="n">
         <f aca="false">A330 +1000</f>
@@ -9333,7 +9346,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E331" s="2" t="n">
         <f aca="false">A331 +1000</f>
@@ -9351,7 +9364,7 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>9</v>
@@ -9375,7 +9388,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E333" s="2" t="n">
         <f aca="false">A333 +1000</f>
@@ -9393,7 +9406,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E334" s="2" t="n">
         <f aca="false">A334 +1000</f>
@@ -9411,7 +9424,7 @@
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E335" s="2" t="n">
         <f aca="false">A335 +1000</f>
@@ -9435,7 +9448,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E336" s="2" t="n">
         <f aca="false">A336 +1000</f>
@@ -9453,7 +9466,7 @@
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E337" s="2" t="n">
         <f aca="false">A337 +1000</f>
@@ -9477,7 +9490,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E338" s="2" t="n">
         <f aca="false">A338 +1000</f>
@@ -9495,7 +9508,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E339" s="2" t="n">
         <f aca="false">A339 +1000</f>
@@ -9513,7 +9526,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E340" s="2" t="n">
         <f aca="false">A340 +1000</f>
@@ -9531,7 +9544,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E341" s="2" t="n">
         <f aca="false">A341 +1000</f>
@@ -9549,7 +9562,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E342" s="2" t="n">
         <f aca="false">A342 +1000</f>
@@ -9567,7 +9580,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E343" s="2" t="n">
         <f aca="false">A343 +1000</f>
@@ -9585,7 +9598,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E344" s="2" t="n">
         <f aca="false">A344 +1000</f>
@@ -9603,7 +9616,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E345" s="2" t="n">
         <f aca="false">A345 +1000</f>
@@ -9621,7 +9634,7 @@
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E346" s="2" t="n">
         <f aca="false">A346 +1000</f>
@@ -9639,7 +9652,7 @@
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
@@ -9658,7 +9671,7 @@
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>9</v>
@@ -9682,7 +9695,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E349" s="2" t="n">
         <f aca="false">A349 +1000</f>
@@ -9700,7 +9713,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E350" s="2" t="n">
         <f aca="false">A350 +1000</f>
@@ -9718,7 +9731,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E351" s="2" t="n">
         <f aca="false">A351 +1000</f>
@@ -9736,7 +9749,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E352" s="2" t="n">
         <f aca="false">A352 +1000</f>
@@ -9754,7 +9767,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E353" s="2" t="n">
         <f aca="false">A353 +1000</f>
@@ -9772,7 +9785,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E354" s="2" t="n">
         <f aca="false">A354 +1000</f>
@@ -9790,7 +9803,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E355" s="2" t="n">
         <f aca="false">A355 +1000</f>
@@ -9808,7 +9821,7 @@
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>9</v>
@@ -9832,7 +9845,7 @@
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E357" s="2" t="n">
         <f aca="false">A357 +1000</f>
@@ -9856,7 +9869,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E358" s="2" t="n">
         <f aca="false">A358 +1000</f>
@@ -9874,7 +9887,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E359" s="2" t="n">
         <f aca="false">A359 +1000</f>
@@ -9892,7 +9905,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E360" s="2" t="n">
         <f aca="false">A360 +1000</f>
@@ -9910,7 +9923,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E361" s="2" t="n">
         <f aca="false">A361 +1000</f>
@@ -9928,7 +9941,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E362" s="2" t="n">
         <f aca="false">A362 +1000</f>
@@ -9946,7 +9959,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E363" s="2" t="n">
         <f aca="false">A363 +1000</f>
@@ -9964,7 +9977,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E364" s="2" t="n">
         <f aca="false">A364 +1000</f>
@@ -9982,7 +9995,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E365" s="2" t="n">
         <f aca="false">A365 +1000</f>
@@ -10000,7 +10013,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E366" s="2" t="n">
         <f aca="false">A366 +1000</f>
@@ -10018,7 +10031,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E367" s="2" t="n">
         <f aca="false">A367 +1000</f>
@@ -10036,7 +10049,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E368" s="2" t="n">
         <f aca="false">A368 +1000</f>
@@ -10054,7 +10067,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E369" s="2" t="n">
         <f aca="false">A369 +1000</f>
@@ -10072,7 +10085,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E370" s="2" t="n">
         <f aca="false">A370 +1000</f>
@@ -10090,7 +10103,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E371" s="2" t="n">
         <f aca="false">A371 +1000</f>
@@ -10108,7 +10121,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E372" s="2" t="n">
         <f aca="false">A372 +1000</f>
@@ -10126,7 +10139,7 @@
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>9</v>
@@ -10150,7 +10163,7 @@
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E374" s="2" t="n">
         <f aca="false">A374 +1000</f>
@@ -10168,7 +10181,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E375" s="2" t="n">
         <f aca="false">A375 +1000</f>
@@ -10186,7 +10199,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E376" s="2" t="n">
         <f aca="false">A376 +1000</f>
@@ -10204,7 +10217,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E377" s="2" t="n">
         <f aca="false">A377 +1000</f>
@@ -10222,7 +10235,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>9</v>
@@ -10246,7 +10259,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E379" s="2" t="n">
         <f aca="false">A379 +1000</f>
@@ -10264,7 +10277,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E380" s="2" t="n">
         <f aca="false">A380 +1000</f>
@@ -10282,7 +10295,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E381" s="2" t="n">
         <f aca="false">A381 +1000</f>
@@ -10300,7 +10313,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E382" s="2" t="n">
         <f aca="false">A382 +1000</f>
@@ -10318,7 +10331,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E383" s="2" t="n">
         <f aca="false">A383 +1000</f>
@@ -10336,7 +10349,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E384" s="2" t="n">
         <f aca="false">A384 +1000</f>
@@ -10354,7 +10367,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E385" s="2" t="n">
         <f aca="false">A385 +1000</f>
@@ -10372,7 +10385,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E386" s="2" t="n">
         <f aca="false">A386 +1000</f>
@@ -10390,7 +10403,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E387" s="2" t="n">
         <f aca="false">A387 +1000</f>
@@ -10408,7 +10421,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E388" s="2" t="n">
         <f aca="false">A388 +1000</f>
@@ -10426,7 +10439,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E389" s="2" t="n">
         <f aca="false">A389 +1000</f>
@@ -10444,7 +10457,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E390" s="2" t="n">
         <f aca="false">A390 +1000</f>
@@ -10462,7 +10475,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E391" s="2" t="n">
         <f aca="false">A391 +1000</f>
@@ -10480,7 +10493,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E392" s="2" t="n">
         <f aca="false">A392 +1000</f>
@@ -10498,7 +10511,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E393" s="2" t="n">
         <f aca="false">A393 +1000</f>
@@ -10516,7 +10529,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E394" s="2" t="n">
         <f aca="false">A394 +1000</f>
@@ -10534,7 +10547,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E395" s="2" t="n">
         <f aca="false">A395 +1000</f>
@@ -10552,7 +10565,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E396" s="2" t="n">
         <f aca="false">A396 +1000</f>
@@ -10570,7 +10583,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E397" s="2" t="n">
         <f aca="false">A397 +1000</f>
@@ -10588,7 +10601,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E398" s="2" t="n">
         <f aca="false">A398 +1000</f>
@@ -10606,7 +10619,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E399" s="2" t="n">
         <f aca="false">A399 +1000</f>
@@ -10624,7 +10637,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E400" s="2" t="n">
         <f aca="false">A400 +1000</f>
@@ -10642,7 +10655,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E401" s="2" t="n">
         <f aca="false">A401 +1000</f>
@@ -10660,7 +10673,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E402" s="2" t="n">
         <f aca="false">A402 +1000</f>
@@ -10678,7 +10691,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E403" s="2" t="n">
         <f aca="false">A403 +1000</f>
@@ -10696,7 +10709,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E404" s="2" t="n">
         <f aca="false">A404 +1000</f>
@@ -10714,7 +10727,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E405" s="2" t="n">
         <f aca="false">A405 +1000</f>
@@ -10732,7 +10745,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E406" s="2" t="n">
         <f aca="false">A406 +1000</f>
@@ -10750,7 +10763,7 @@
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>9</v>
@@ -10774,7 +10787,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E408" s="2" t="n">
         <f aca="false">A408 +1000</f>
@@ -10792,7 +10805,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E409" s="2" t="n">
         <f aca="false">A409 +1000</f>
@@ -10810,7 +10823,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E410" s="2" t="n">
         <f aca="false">A410 +1000</f>
@@ -10828,7 +10841,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E411" s="2" t="n">
         <f aca="false">A411 +1000</f>
@@ -10846,7 +10859,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E412" s="2" t="n">
         <f aca="false">A412 +1000</f>
@@ -10864,7 +10877,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E413" s="2" t="n">
         <f aca="false">A413 +1000</f>
@@ -10882,7 +10895,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E414" s="2" t="n">
         <f aca="false">A414 +1000</f>
@@ -10900,7 +10913,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E415" s="2" t="n">
         <f aca="false">A415 +1000</f>
@@ -10918,7 +10931,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E416" s="2" t="n">
         <f aca="false">A416 +1000</f>
@@ -10936,7 +10949,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E417" s="2" t="n">
         <f aca="false">A417 +1000</f>
@@ -10954,7 +10967,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E418" s="2" t="n">
         <f aca="false">A418 +1000</f>
@@ -10972,7 +10985,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E419" s="2" t="n">
         <f aca="false">A419 +1000</f>
@@ -10990,7 +11003,7 @@
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>9</v>
@@ -11014,7 +11027,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E421" s="2" t="n">
         <f aca="false">A421 +1000</f>
@@ -11032,7 +11045,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
@@ -11050,7 +11063,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E423" s="2" t="n">
         <f aca="false">A423 +1000</f>
@@ -11068,7 +11081,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E424" s="2" t="n">
         <f aca="false">A424 +1000</f>
@@ -11086,7 +11099,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E425" s="2" t="n">
         <f aca="false">A425 +1000</f>
@@ -11104,7 +11117,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E426" s="2" t="n">
         <f aca="false">A426 +1000</f>
@@ -11122,7 +11135,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E427" s="2" t="n">
         <f aca="false">A427 +1000</f>
@@ -11140,7 +11153,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E428" s="2" t="n">
         <f aca="false">A428 +1000</f>
@@ -11158,7 +11171,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E429" s="2" t="n">
         <f aca="false">A429 +1000</f>
@@ -11176,7 +11189,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E430" s="2" t="n">
         <f aca="false">A430 +1000</f>
@@ -11194,7 +11207,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E431" s="2" t="n">
         <f aca="false">A431 +1000</f>
@@ -11212,7 +11225,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E432" s="2" t="n">
         <f aca="false">A432 +1000</f>
@@ -11230,7 +11243,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E433" s="2" t="n">
         <f aca="false">A433 +1000</f>
@@ -11248,7 +11261,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E434" s="2" t="n">
         <f aca="false">A434 +1000</f>
@@ -11266,7 +11279,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E435" s="2" t="n">
         <f aca="false">A435 +1000</f>
@@ -11284,7 +11297,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E436" s="2" t="n">
         <f aca="false">A436 +1000</f>
@@ -11302,7 +11315,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E437" s="2" t="n">
         <f aca="false">A437 +1000</f>
@@ -11320,7 +11333,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E438" s="2" t="n">
         <f aca="false">A438 +1000</f>
@@ -11338,7 +11351,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E439" s="2" t="n">
         <f aca="false">A439 +1000</f>
@@ -11356,7 +11369,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E440" s="2" t="n">
         <f aca="false">A440 +1000</f>
@@ -11374,7 +11387,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E441" s="2" t="n">
         <f aca="false">A441 +1000</f>
@@ -11392,7 +11405,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E442" s="2" t="n">
         <f aca="false">A442 +1000</f>
@@ -11410,7 +11423,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E443" s="2" t="n">
         <f aca="false">A443 +1000</f>
@@ -11428,7 +11441,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E444" s="2" t="n">
         <f aca="false">A444 +1000</f>
@@ -11446,7 +11459,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E445" s="2" t="n">
         <f aca="false">A445 +1000</f>
@@ -11464,7 +11477,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E446" s="2" t="n">
         <f aca="false">A446 +1000</f>
@@ -11482,7 +11495,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E447" s="2" t="n">
         <f aca="false">A447 +1000</f>
@@ -11500,7 +11513,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E448" s="2" t="n">
         <f aca="false">A448 +1000</f>
@@ -11518,7 +11531,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E449" s="2" t="n">
         <f aca="false">A449 +1000</f>
@@ -11536,7 +11549,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E450" s="2" t="n">
         <f aca="false">A450 +1000</f>
@@ -11554,7 +11567,7 @@
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>9</v>
@@ -11578,7 +11591,7 @@
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E452" s="2" t="n">
         <f aca="false">A452 +1000</f>
@@ -11596,7 +11609,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E453" s="2" t="n">
         <f aca="false">A453 +1000</f>
@@ -11614,7 +11627,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E454" s="2" t="n">
         <f aca="false">A454 +1000</f>
@@ -11632,7 +11645,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E455" s="2" t="n">
         <f aca="false">A455 +1000</f>
@@ -11650,7 +11663,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E456" s="2" t="n">
         <f aca="false">A456 +1000</f>
@@ -11668,7 +11681,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E457" s="2" t="n">
         <f aca="false">A457 +1000</f>
@@ -11686,7 +11699,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E458" s="2" t="n">
         <f aca="false">A458 +1000</f>
@@ -11704,7 +11717,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E459" s="2" t="n">
         <f aca="false">A459 +1000</f>
@@ -11722,7 +11735,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E460" s="2" t="n">
         <f aca="false">A460 +1000</f>
@@ -11740,7 +11753,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E461" s="2" t="n">
         <f aca="false">A461 +1000</f>
@@ -11758,7 +11771,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E462" s="2" t="n">
         <f aca="false">A462 +1000</f>
@@ -11776,7 +11789,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E463" s="2" t="n">
         <f aca="false">A463 +1000</f>
@@ -11794,7 +11807,7 @@
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E464" s="2" t="n">
         <f aca="false">A464 +1000</f>
@@ -11818,7 +11831,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E465" s="2" t="n">
         <f aca="false">A465 +1000</f>
@@ -11836,7 +11849,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E466" s="2" t="n">
         <f aca="false">A466 +1000</f>
@@ -11854,7 +11867,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E467" s="2" t="n">
         <f aca="false">A467 +1000</f>
@@ -11872,7 +11885,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E468" s="2" t="n">
         <f aca="false">A468 +1000</f>
@@ -11890,7 +11903,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E469" s="2" t="n">
         <f aca="false">A469 +1000</f>
@@ -11908,7 +11921,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E470" s="2" t="n">
         <f aca="false">A470 +1000</f>
@@ -11926,7 +11939,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E471" s="2" t="n">
         <f aca="false">A471 +1000</f>
@@ -11944,7 +11957,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E472" s="2" t="n">
         <f aca="false">A472 +1000</f>
@@ -11962,7 +11975,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E473" s="2" t="n">
         <f aca="false">A473 +1000</f>
@@ -11980,7 +11993,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E474" s="2" t="n">
         <f aca="false">A474 +1000</f>
@@ -11998,7 +12011,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E475" s="2" t="n">
         <f aca="false">A475 +1000</f>
@@ -12016,7 +12029,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E476" s="2" t="n">
         <f aca="false">A476 +1000</f>
@@ -12034,7 +12047,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E477" s="2" t="n">
         <f aca="false">A477 +1000</f>
@@ -12052,7 +12065,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E478" s="2" t="n">
         <f aca="false">A478 +1000</f>
@@ -12070,7 +12083,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E479" s="2" t="n">
         <f aca="false">A479 +1000</f>
@@ -12088,7 +12101,7 @@
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
@@ -12107,7 +12120,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E481" s="2" t="n">
         <f aca="false">A481 +1000</f>
@@ -12125,7 +12138,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E482" s="2" t="n">
         <f aca="false">A482 +1000</f>
@@ -12143,7 +12156,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E483" s="2" t="n">
         <f aca="false">A483 +1000</f>
@@ -12161,7 +12174,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E484" s="2" t="n">
         <f aca="false">A484 +1000</f>
@@ -12179,7 +12192,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E485" s="2" t="n">
         <f aca="false">A485 +1000</f>
@@ -12197,7 +12210,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E486" s="2" t="n">
         <f aca="false">A486 +1000</f>
@@ -12215,7 +12228,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E487" s="2" t="n">
         <f aca="false">A487 +1000</f>
@@ -12233,7 +12246,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E488" s="2" t="n">
         <f aca="false">A488 +1000</f>
@@ -12251,7 +12264,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E489" s="2" t="n">
         <f aca="false">A489 +1000</f>
@@ -12269,7 +12282,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E490" s="2" t="n">
         <f aca="false">A490 +1000</f>
@@ -12287,7 +12300,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E491" s="2" t="n">
         <f aca="false">A491 +1000</f>
@@ -12305,7 +12318,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E492" s="2" t="n">
         <f aca="false">A492 +1000</f>
@@ -12323,7 +12336,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E493" s="2" t="n">
         <f aca="false">A493 +1000</f>
@@ -12341,7 +12354,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E494" s="2" t="n">
         <f aca="false">A494 +1000</f>
@@ -12359,7 +12372,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E495" s="2" t="n">
         <f aca="false">A495 +1000</f>
@@ -12377,7 +12390,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E496" s="2" t="n">
         <f aca="false">A496 +1000</f>
@@ -12395,7 +12408,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E497" s="2" t="n">
         <f aca="false">A497 +1000</f>
@@ -12413,7 +12426,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E498" s="2" t="n">
         <f aca="false">A498 +1000</f>
@@ -12431,7 +12444,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E499" s="2" t="n">
         <f aca="false">A499 +1000</f>
@@ -12449,7 +12462,7 @@
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E500" s="2" t="n">
         <f aca="false">A500 +1000</f>
@@ -12473,7 +12486,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E501" s="2" t="n">
         <f aca="false">A501 +1000</f>
@@ -12491,7 +12504,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E502" s="2" t="n">
         <f aca="false">A502 +1000</f>
@@ -12509,7 +12522,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E503" s="2" t="n">
         <f aca="false">A503 +1000</f>
@@ -12527,7 +12540,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E504" s="2" t="n">
         <f aca="false">A504 +1000</f>
@@ -12545,7 +12558,7 @@
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E505" s="2" t="n">
         <f aca="false">A505 +1000</f>
@@ -12563,7 +12576,7 @@
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>9</v>
@@ -12587,7 +12600,7 @@
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E507" s="2" t="n">
         <f aca="false">A507 +1000</f>
@@ -12611,7 +12624,7 @@
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E508" s="2" t="n">
         <f aca="false">A508 +1000</f>
@@ -12629,7 +12642,7 @@
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E509" s="2" t="n">
         <f aca="false">A509 +1000</f>
@@ -12647,7 +12660,7 @@
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E510" s="2" t="n">
         <f aca="false">A510 +1000</f>
@@ -12665,7 +12678,7 @@
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E511" s="2" t="n">
         <f aca="false">A511 +1000</f>
@@ -12683,7 +12696,7 @@
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E512" s="2" t="n">
         <f aca="false">A512 +1000</f>
@@ -12701,7 +12714,7 @@
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E513" s="2" t="n">
         <f aca="false">A513 +1000</f>
@@ -12719,7 +12732,7 @@
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E514" s="2" t="n">
         <f aca="false">A514 +1000</f>
@@ -12737,7 +12750,7 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E515" s="2" t="n">
         <f aca="false">A515 +1000</f>
@@ -12755,7 +12768,7 @@
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E516" s="2" t="n">
         <f aca="false">A516 +1000</f>
@@ -12773,7 +12786,7 @@
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E517" s="2" t="n">
         <f aca="false">A517 +1000</f>
@@ -12791,7 +12804,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E518" s="2" t="n">
         <f aca="false">A518 +1000</f>
@@ -12809,7 +12822,7 @@
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E519" s="2" t="n">
         <f aca="false">A519 +1000</f>
@@ -12827,7 +12840,7 @@
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E520" s="2" t="n">
         <f aca="false">A520 +1000</f>
@@ -12845,7 +12858,7 @@
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E521" s="2" t="n">
         <f aca="false">A521 +1000</f>
@@ -12863,7 +12876,7 @@
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E522" s="2" t="n">
         <f aca="false">A522 +1000</f>
@@ -12881,7 +12894,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E523" s="2" t="n">
         <f aca="false">A523 +1000</f>
@@ -12899,7 +12912,7 @@
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E524" s="2" t="n">
         <f aca="false">A524 +1000</f>
@@ -12917,7 +12930,7 @@
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E525" s="2" t="n">
         <f aca="false">A525 +1000</f>
@@ -12935,7 +12948,7 @@
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E526" s="2" t="n">
         <f aca="false">A526 +1000</f>
@@ -12953,7 +12966,7 @@
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E527" s="2" t="n">
         <f aca="false">A527 +1000</f>
@@ -12971,7 +12984,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E528" s="2" t="n">
         <f aca="false">A528 +1000</f>
@@ -12989,7 +13002,7 @@
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E529" s="2" t="n">
         <f aca="false">A529 +1000</f>
@@ -13007,7 +13020,7 @@
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E530" s="2" t="n">
         <f aca="false">A530 +1000</f>
@@ -13025,7 +13038,7 @@
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E531" s="2" t="n">
         <f aca="false">A531 +1000</f>
@@ -13043,7 +13056,7 @@
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E532" s="2" t="n">
         <f aca="false">A532 +1000</f>
@@ -13061,7 +13074,7 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E533" s="2" t="n">
         <f aca="false">A533 +1000</f>
@@ -13079,7 +13092,7 @@
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E534" s="2" t="n">
         <f aca="false">A534 +1000</f>
@@ -13097,7 +13110,7 @@
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E535" s="2" t="n">
         <f aca="false">A535 +1000</f>
@@ -13115,7 +13128,7 @@
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E536" s="2" t="n">
         <f aca="false">A536 +1000</f>
@@ -13133,7 +13146,7 @@
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E537" s="2" t="n">
         <f aca="false">A537 +1000</f>
@@ -13151,7 +13164,7 @@
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E538" s="2" t="n">
         <f aca="false">A538 +1000</f>
@@ -13169,7 +13182,7 @@
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E539" s="2" t="n">
         <f aca="false">A539 +1000</f>
@@ -13187,7 +13200,7 @@
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E540" s="2" t="n">
         <f aca="false">A540 +1000</f>
@@ -13205,7 +13218,7 @@
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E541" s="2" t="n">
         <f aca="false">A541 +1000</f>
@@ -13223,7 +13236,7 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E542" s="2" t="n">
         <f aca="false">A542 +1000</f>
@@ -13241,7 +13254,7 @@
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E543" s="2" t="n">
         <f aca="false">A543 +1000</f>
@@ -13259,7 +13272,7 @@
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E544" s="2" t="n">
         <f aca="false">A544 +1000</f>
@@ -13277,7 +13290,7 @@
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E545" s="2" t="n">
         <f aca="false">A545 +1000</f>
@@ -13295,7 +13308,7 @@
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E546" s="2" t="n">
         <f aca="false">A546 +1000</f>
@@ -13313,7 +13326,7 @@
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E547" s="2" t="n">
         <f aca="false">A547 +1000</f>
@@ -13331,7 +13344,7 @@
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E548" s="2" t="n">
         <f aca="false">A548 +1000</f>
@@ -13349,7 +13362,7 @@
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E549" s="2" t="n">
         <f aca="false">A549 +1000</f>
@@ -13367,7 +13380,7 @@
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E550" s="2" t="n">
         <f aca="false">A550 +1000</f>
@@ -13385,7 +13398,7 @@
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E551" s="2" t="n">
         <f aca="false">A551 +1000</f>
@@ -13403,7 +13416,7 @@
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E552" s="2" t="n">
         <f aca="false">A552 +1000</f>
@@ -13421,7 +13434,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E553" s="2" t="n">
         <f aca="false">A553 +1000</f>
@@ -13439,7 +13452,7 @@
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E554" s="2" t="n">
         <f aca="false">A554 +1000</f>
@@ -13457,7 +13470,7 @@
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E555" s="2" t="n">
         <f aca="false">A555 +1000</f>
@@ -13475,7 +13488,7 @@
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E556" s="2" t="n">
         <f aca="false">A556 +1000</f>
@@ -13493,7 +13506,7 @@
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E557" s="2" t="n">
         <f aca="false">A557 +1000</f>
@@ -13511,7 +13524,7 @@
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E558" s="2" t="n">
         <f aca="false">A558 +1000</f>
@@ -13535,7 +13548,7 @@
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E559" s="2" t="n">
         <f aca="false">A559 +1000</f>
@@ -13553,7 +13566,7 @@
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E560" s="2" t="n">
         <f aca="false">A560 +1000</f>
@@ -13571,7 +13584,7 @@
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E561" s="2" t="n">
         <f aca="false">A561 +1000</f>
@@ -13589,7 +13602,7 @@
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E562" s="2" t="n">
         <f aca="false">A562 +1000</f>
@@ -13607,7 +13620,7 @@
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E563" s="2" t="n">
         <f aca="false">A563 +1000</f>
@@ -13625,7 +13638,7 @@
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E564" s="2" t="n">
         <f aca="false">A564 +1000</f>
@@ -13643,7 +13656,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E565" s="2" t="n">
         <f aca="false">A565 +1000</f>
@@ -13661,7 +13674,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E566" s="2" t="n">
         <f aca="false">A566 +1000</f>
@@ -13679,7 +13692,7 @@
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E567" s="2" t="n">
         <f aca="false">A567 +1000</f>
@@ -13697,7 +13710,7 @@
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E568" s="2" t="n">
         <f aca="false">A568 +1000</f>
@@ -13715,7 +13728,7 @@
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E569" s="2" t="n">
         <f aca="false">A569 +1000</f>
@@ -13733,7 +13746,7 @@
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E570" s="2" t="n">
         <f aca="false">A570 +1000</f>
@@ -13751,7 +13764,7 @@
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E571" s="2" t="n">
         <f aca="false">A571 +1000</f>
@@ -13769,7 +13782,7 @@
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E572" s="2" t="n">
         <f aca="false">A572 +1000</f>
@@ -13787,7 +13800,7 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E573" s="2" t="n">
         <f aca="false">A573 +1000</f>
@@ -13805,7 +13818,7 @@
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E574" s="2" t="n">
         <f aca="false">A574 +1000</f>
@@ -13823,7 +13836,7 @@
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E575" s="2" t="n">
         <f aca="false">A575 +1000</f>
@@ -13841,7 +13854,7 @@
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E576" s="2" t="n">
         <f aca="false">A576 +1000</f>
@@ -13859,7 +13872,7 @@
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E577" s="2" t="n">
         <f aca="false">A577 +1000</f>
@@ -13877,7 +13890,7 @@
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E578" s="2" t="n">
         <f aca="false">A578 +1000</f>
@@ -13895,7 +13908,7 @@
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E579" s="2" t="n">
         <f aca="false">A579 +1000</f>
@@ -13913,7 +13926,7 @@
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E580" s="2" t="n">
         <f aca="false">A580 +1000</f>
@@ -13931,7 +13944,7 @@
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E581" s="2" t="n">
         <f aca="false">A581 +1000</f>
@@ -13949,7 +13962,7 @@
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E582" s="2" t="n">
         <f aca="false">A582 +1000</f>
@@ -13967,7 +13980,7 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E583" s="2" t="n">
         <f aca="false">A583 +1000</f>
@@ -13985,7 +13998,7 @@
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E584" s="2" t="n">
         <f aca="false">A584 +1000</f>
@@ -14003,7 +14016,7 @@
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E585" s="2" t="n">
         <f aca="false">A585 +1000</f>
@@ -14021,7 +14034,7 @@
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E586" s="2" t="n">
         <f aca="false">A586 +1000</f>
@@ -14039,7 +14052,7 @@
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E587" s="2" t="n">
         <f aca="false">A587 +1000</f>
@@ -14057,7 +14070,7 @@
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E588" s="2" t="n">
         <f aca="false">A588 +1000</f>
@@ -14075,7 +14088,7 @@
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E589" s="2" t="n">
         <f aca="false">A589 +1000</f>
@@ -14093,7 +14106,7 @@
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E590" s="2" t="n">
         <f aca="false">A590 +1000</f>
@@ -14111,7 +14124,7 @@
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E591" s="2" t="n">
         <f aca="false">A591 +1000</f>
@@ -14129,7 +14142,7 @@
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E592" s="2" t="n">
         <f aca="false">A592 +1000</f>
@@ -14147,7 +14160,7 @@
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E593" s="2" t="n">
         <f aca="false">A593 +1000</f>
@@ -14165,7 +14178,7 @@
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E594" s="2" t="n">
         <f aca="false">A594 +1000</f>
@@ -14183,7 +14196,7 @@
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E595" s="2" t="n">
         <f aca="false">A595 +1000</f>
@@ -14201,7 +14214,7 @@
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E596" s="2" t="n">
         <f aca="false">A596 +1000</f>
@@ -14219,7 +14232,7 @@
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E597" s="2" t="n">
         <f aca="false">A597 +1000</f>
@@ -14237,7 +14250,7 @@
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E598" s="2" t="n">
         <f aca="false">A598 +1000</f>
@@ -14255,7 +14268,7 @@
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E599" s="2" t="n">
         <f aca="false">A599 +1000</f>
@@ -14273,7 +14286,7 @@
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E600" s="2" t="n">
         <f aca="false">A600 +1000</f>
@@ -14291,7 +14304,7 @@
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E601" s="2" t="n">
         <f aca="false">A601 +1000</f>
@@ -14309,7 +14322,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E602" s="2" t="n">
         <f aca="false">A602 +1000</f>
@@ -14327,7 +14340,7 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E603" s="2" t="n">
         <f aca="false">A603 +1000</f>
@@ -14345,7 +14358,7 @@
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E604" s="2" t="n">
         <f aca="false">A604 +1000</f>
@@ -14363,7 +14376,7 @@
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E605" s="2" t="n">
         <f aca="false">A605 +1000</f>
@@ -14381,7 +14394,7 @@
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E606" s="2" t="n">
         <f aca="false">A606 +1000</f>
@@ -14399,7 +14412,7 @@
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E607" s="2" t="n">
         <f aca="false">A607 +1000</f>
@@ -14417,7 +14430,7 @@
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E608" s="2" t="n">
         <f aca="false">A608 +1000</f>
@@ -14435,7 +14448,7 @@
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E609" s="2" t="n">
         <f aca="false">A609 +1000</f>
@@ -14453,7 +14466,7 @@
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E610" s="2" t="n">
         <f aca="false">A610 +1000</f>
@@ -14471,7 +14484,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E611" s="2" t="n">
         <f aca="false">A611 +1000</f>
@@ -14489,7 +14502,7 @@
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E612" s="2" t="n">
         <f aca="false">A612 +1000</f>
@@ -14507,7 +14520,7 @@
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E613" s="2" t="n">
         <f aca="false">A613 +1000</f>
@@ -14525,7 +14538,7 @@
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E614" s="2" t="n">
         <f aca="false">A614 +1000</f>
@@ -14543,7 +14556,7 @@
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E615" s="2" t="n">
         <f aca="false">A615 +1000</f>
@@ -14561,7 +14574,7 @@
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E616" s="2" t="n">
         <f aca="false">A616 +1000</f>
@@ -14579,7 +14592,7 @@
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E617" s="2" t="n">
         <f aca="false">A617 +1000</f>
@@ -14597,7 +14610,7 @@
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E618" s="2" t="n">
         <f aca="false">A618 +1000</f>
@@ -14615,7 +14628,7 @@
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E619" s="2" t="n">
         <f aca="false">A619 +1000</f>
@@ -14633,7 +14646,7 @@
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E620" s="2" t="n">
         <f aca="false">A620 +1000</f>
@@ -14651,7 +14664,7 @@
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E621" s="2" t="n">
         <f aca="false">A621 +1000</f>
@@ -14669,7 +14682,7 @@
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>9</v>
@@ -14678,7 +14691,7 @@
         <v>9</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E622" s="2" t="n">
         <f aca="false">A622 +1000</f>
@@ -14696,7 +14709,7 @@
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E623" s="2" t="n">
         <f aca="false">A623 +1000</f>
@@ -14714,7 +14727,7 @@
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E624" s="2" t="n">
         <f aca="false">A624 +1000</f>
@@ -14732,7 +14745,7 @@
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E625" s="2" t="n">
         <f aca="false">A625 +1000</f>
@@ -14750,7 +14763,7 @@
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E626" s="2" t="n">
         <f aca="false">A626 +1000</f>
@@ -14768,7 +14781,7 @@
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E627" s="2" t="n">
         <f aca="false">A627 +1000</f>
@@ -14786,7 +14799,7 @@
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E628" s="2" t="n">
         <f aca="false">A628 +1000</f>
@@ -14804,7 +14817,7 @@
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E629" s="2" t="n">
         <f aca="false">A629 +1000</f>
@@ -14822,7 +14835,7 @@
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E630" s="2" t="n">
         <f aca="false">A630 +1000</f>
@@ -14840,7 +14853,7 @@
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E631" s="2" t="n">
         <f aca="false">A631 +1000</f>
@@ -14858,7 +14871,7 @@
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E632" s="2" t="n">
         <f aca="false">A632 +1000</f>
@@ -14876,7 +14889,7 @@
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E633" s="2" t="n">
         <f aca="false">A633 +1000</f>
@@ -14894,7 +14907,7 @@
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E634" s="2" t="n">
         <f aca="false">A634 +1000</f>
@@ -14912,7 +14925,7 @@
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E635" s="2" t="n">
         <f aca="false">A635 +1000</f>
@@ -14930,7 +14943,7 @@
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E636" s="2" t="n">
         <f aca="false">A636 +1000</f>
@@ -14948,7 +14961,7 @@
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E637" s="2" t="n">
         <f aca="false">A637 +1000</f>
@@ -14966,7 +14979,7 @@
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E638" s="2" t="n">
         <f aca="false">A638 +1000</f>
@@ -14984,7 +14997,7 @@
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E639" s="2" t="n">
         <f aca="false">A639 +1000</f>
@@ -15002,7 +15015,7 @@
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E640" s="2" t="n">
         <f aca="false">A640 +1000</f>
@@ -15020,7 +15033,7 @@
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E641" s="2" t="n">
         <f aca="false">A641 +1000</f>
@@ -15038,7 +15051,7 @@
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E642" s="2" t="n">
         <f aca="false">A642 +1000</f>
@@ -15056,7 +15069,7 @@
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E643" s="2" t="n">
         <f aca="false">A643 +1000</f>
@@ -15074,7 +15087,7 @@
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E644" s="2" t="n">
         <f aca="false">A644 +1000</f>
@@ -15092,7 +15105,7 @@
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E645" s="2" t="n">
         <f aca="false">A645 +1000</f>
@@ -15110,7 +15123,7 @@
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E646" s="2" t="n">
         <f aca="false">A646 +1000</f>
@@ -15128,7 +15141,7 @@
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E647" s="2" t="n">
         <f aca="false">A647 +1000</f>
@@ -15146,7 +15159,7 @@
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E648" s="2" t="n">
         <f aca="false">A648 +1000</f>
@@ -15164,7 +15177,7 @@
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E649" s="2" t="n">
         <f aca="false">A649 +1000</f>
@@ -15182,7 +15195,7 @@
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E650" s="2" t="n">
         <f aca="false">A650 +1000</f>
@@ -15200,7 +15213,7 @@
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E651" s="2" t="n">
         <f aca="false">A651 +1000</f>
@@ -15218,7 +15231,7 @@
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E652" s="2" t="n">
         <f aca="false">A652 +1000</f>
@@ -15236,7 +15249,7 @@
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E653" s="2" t="n">
         <f aca="false">A653 +1000</f>
@@ -15254,7 +15267,13 @@
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="E654" s="2" t="n">
         <f aca="false">A654 +1000</f>
@@ -15272,7 +15291,7 @@
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E655" s="2" t="n">
         <f aca="false">A655 +1000</f>
@@ -15290,7 +15309,7 @@
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E656" s="2" t="n">
         <f aca="false">A656 +1000</f>
@@ -15308,7 +15327,7 @@
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E657" s="2" t="n">
         <f aca="false">A657 +1000</f>
@@ -15326,7 +15345,7 @@
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E658" s="2" t="n">
         <f aca="false">A658 +1000</f>
@@ -15344,7 +15363,7 @@
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E659" s="2" t="n">
         <f aca="false">A659 +1000</f>
@@ -15362,7 +15381,7 @@
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E660" s="2" t="n">
         <f aca="false">A660 +1000</f>
@@ -15380,7 +15399,7 @@
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E661" s="2" t="n">
         <f aca="false">A661 +1000</f>
@@ -15398,7 +15417,7 @@
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E662" s="2" t="n">
         <f aca="false">A662 +1000</f>
@@ -15416,7 +15435,7 @@
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E663" s="2" t="n">
         <f aca="false">A663 +1000</f>
@@ -15434,7 +15453,7 @@
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E664" s="2" t="n">
         <f aca="false">A664 +1000</f>
@@ -15452,7 +15471,7 @@
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E665" s="2" t="n">
         <f aca="false">A665 +1000</f>
@@ -15470,7 +15489,7 @@
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E666" s="2" t="n">
         <f aca="false">A666 +1000</f>
@@ -15488,7 +15507,7 @@
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E667" s="2" t="n">
         <f aca="false">A667 +1000</f>
@@ -15506,7 +15525,7 @@
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E668" s="2" t="n">
         <f aca="false">A668 +1000</f>
@@ -15524,7 +15543,7 @@
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E669" s="2" t="n">
         <f aca="false">A669 +1000</f>
@@ -15542,7 +15561,7 @@
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E670" s="2" t="n">
         <f aca="false">A670 +1000</f>
@@ -15560,7 +15579,7 @@
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E671" s="2" t="n">
         <f aca="false">A671 +1000</f>
@@ -15578,7 +15597,7 @@
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E672" s="2" t="n">
         <f aca="false">A672 +1000</f>
@@ -15596,7 +15615,7 @@
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E673" s="2" t="n">
         <f aca="false">A673 +1000</f>
@@ -15614,7 +15633,7 @@
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E674" s="2" t="n">
         <f aca="false">A674 +1000</f>
@@ -15632,7 +15651,7 @@
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E675" s="2" t="n">
         <f aca="false">A675 +1000</f>
@@ -15650,7 +15669,7 @@
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E676" s="2" t="n">
         <f aca="false">A676 +1000</f>
@@ -15668,7 +15687,7 @@
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E677" s="2" t="n">
         <f aca="false">A677 +1000</f>
@@ -15686,7 +15705,7 @@
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E678" s="2" t="n">
         <f aca="false">A678 +1000</f>
@@ -15704,7 +15723,7 @@
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E679" s="2" t="n">
         <f aca="false">A679 +1000</f>
@@ -15722,7 +15741,7 @@
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E680" s="2" t="n">
         <f aca="false">A680 +1000</f>
@@ -15740,7 +15759,7 @@
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E681" s="2" t="n">
         <f aca="false">A681 +1000</f>
@@ -15758,7 +15777,7 @@
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E682" s="2" t="n">
         <f aca="false">A682 +1000</f>
@@ -15776,7 +15795,7 @@
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E683" s="2" t="n">
         <f aca="false">A683 +1000</f>
@@ -15794,7 +15813,7 @@
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E684" s="2" t="n">
         <f aca="false">A684 +1000</f>
@@ -15812,7 +15831,7 @@
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E685" s="2" t="n">
         <f aca="false">A685 +1000</f>
@@ -15830,7 +15849,7 @@
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E686" s="2" t="n">
         <f aca="false">A686 +1000</f>
@@ -15848,7 +15867,7 @@
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E687" s="2" t="n">
         <f aca="false">A687 +1000</f>
@@ -15866,7 +15885,7 @@
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E688" s="2" t="n">
         <f aca="false">A688 +1000</f>
@@ -15884,7 +15903,7 @@
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E689" s="2" t="n">
         <f aca="false">A689 +1000</f>
@@ -15902,7 +15921,7 @@
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E690" s="2" t="n">
         <f aca="false">A690 +1000</f>
@@ -15920,7 +15939,7 @@
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E691" s="2" t="n">
         <f aca="false">A691 +1000</f>
@@ -15938,7 +15957,7 @@
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E692" s="2" t="n">
         <f aca="false">A692 +1000</f>
@@ -15956,7 +15975,7 @@
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E693" s="2" t="n">
         <f aca="false">A693 +1000</f>
@@ -15974,7 +15993,7 @@
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E694" s="2" t="n">
         <f aca="false">A694 +1000</f>
@@ -15992,7 +16011,7 @@
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E695" s="2" t="n">
         <f aca="false">A695 +1000</f>
@@ -16010,7 +16029,7 @@
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E696" s="2" t="n">
         <f aca="false">A696 +1000</f>
@@ -16028,7 +16047,7 @@
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E697" s="2" t="n">
         <f aca="false">A697 +1000</f>
@@ -16046,7 +16065,7 @@
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E698" s="2" t="n">
         <f aca="false">A698 +1000</f>
@@ -16064,7 +16083,7 @@
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E699" s="2" t="n">
         <f aca="false">A699 +1000</f>
@@ -16082,7 +16101,7 @@
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E700" s="2" t="n">
         <f aca="false">A700 +1000</f>
@@ -16100,7 +16119,7 @@
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>9</v>
@@ -16124,7 +16143,7 @@
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>9</v>
@@ -16148,7 +16167,7 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>9</v>
@@ -16172,7 +16191,7 @@
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>9</v>
@@ -16196,7 +16215,7 @@
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E705" s="2" t="n">
         <f aca="false">A705 +1000</f>
@@ -16214,7 +16233,7 @@
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E706" s="2" t="n">
         <f aca="false">A706 +1000</f>
@@ -16232,7 +16251,7 @@
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E707" s="2" t="n">
         <f aca="false">A707 +1000</f>
@@ -16250,7 +16269,7 @@
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
@@ -16268,7 +16287,7 @@
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E709" s="2" t="n">
         <f aca="false">A709 +1000</f>
@@ -16286,7 +16305,7 @@
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E710" s="2" t="n">
         <f aca="false">A710 +1000</f>
@@ -16304,7 +16323,7 @@
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E711" s="2" t="n">
         <f aca="false">A711 +1000</f>
@@ -16322,7 +16341,7 @@
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E712" s="2" t="n">
         <f aca="false">A712 +1000</f>
@@ -16340,7 +16359,7 @@
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E713" s="2" t="n">
         <f aca="false">A713 +1000</f>
@@ -16358,7 +16377,7 @@
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E714" s="2" t="n">
         <f aca="false">A714 +1000</f>
@@ -16376,7 +16395,7 @@
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E715" s="2" t="n">
         <f aca="false">A715 +1000</f>
@@ -16394,7 +16413,7 @@
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E716" s="2" t="n">
         <f aca="false">A716 +1000</f>
@@ -16412,7 +16431,7 @@
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E717" s="2" t="n">
         <f aca="false">A717 +1000</f>
@@ -16430,7 +16449,7 @@
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E718" s="2" t="n">
         <f aca="false">A718 +1000</f>
@@ -16448,7 +16467,7 @@
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E719" s="2" t="n">
         <f aca="false">A719 +1000</f>
@@ -16466,7 +16485,7 @@
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E720" s="2" t="n">
         <f aca="false">A720 +1000</f>
@@ -16484,7 +16503,7 @@
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E721" s="2" t="n">
         <f aca="false">A721 +1000</f>
@@ -16502,7 +16521,7 @@
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E722" s="2" t="n">
         <f aca="false">A722 +1000</f>
@@ -16520,7 +16539,7 @@
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E723" s="2" t="n">
         <f aca="false">A723 +1000</f>
@@ -16538,7 +16557,7 @@
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E724" s="2" t="n">
         <f aca="false">A724 +1000</f>
@@ -16556,7 +16575,7 @@
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E725" s="2" t="n">
         <f aca="false">A725 +1000</f>
@@ -16574,7 +16593,7 @@
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E726" s="2" t="n">
         <f aca="false">A726 +1000</f>
@@ -16592,7 +16611,7 @@
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E727" s="2" t="n">
         <f aca="false">A727 +1000</f>
@@ -16610,7 +16629,7 @@
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E728" s="2" t="n">
         <f aca="false">A728 +1000</f>
@@ -16628,7 +16647,7 @@
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E729" s="2" t="n">
         <f aca="false">A729 +1000</f>
@@ -16646,7 +16665,7 @@
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E730" s="2" t="n">
         <f aca="false">A730 +1000</f>
@@ -16664,7 +16683,7 @@
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E731" s="2" t="n">
         <f aca="false">A731 +1000</f>
@@ -16682,7 +16701,7 @@
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E732" s="2" t="n">
         <f aca="false">A732 +1000</f>
@@ -16700,7 +16719,7 @@
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E733" s="2" t="n">
         <f aca="false">A733 +1000</f>
@@ -16718,7 +16737,7 @@
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E734" s="2" t="n">
         <f aca="false">A734 +1000</f>
@@ -16736,7 +16755,7 @@
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E735" s="2" t="n">
         <f aca="false">A735 +1000</f>
@@ -16754,7 +16773,7 @@
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E736" s="2" t="n">
         <f aca="false">A736 +1000</f>
@@ -16772,7 +16791,7 @@
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E737" s="2" t="n">
         <f aca="false">A737 +1000</f>
@@ -16790,7 +16809,7 @@
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E738" s="2" t="n">
         <f aca="false">A738 +1000</f>
@@ -16808,7 +16827,7 @@
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E739" s="2" t="n">
         <f aca="false">A739 +1000</f>
@@ -16826,7 +16845,7 @@
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E740" s="2" t="n">
         <f aca="false">A740 +1000</f>
@@ -16844,7 +16863,7 @@
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E741" s="2" t="n">
         <f aca="false">A741 +1000</f>
@@ -16862,7 +16881,7 @@
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E742" s="2" t="n">
         <f aca="false">A742 +1000</f>
@@ -16880,7 +16899,7 @@
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E743" s="2" t="n">
         <f aca="false">A743 +1000</f>
@@ -16898,7 +16917,7 @@
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E744" s="2" t="n">
         <f aca="false">A744 +1000</f>
@@ -16916,7 +16935,7 @@
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E745" s="2" t="n">
         <f aca="false">A745 +1000</f>
@@ -16934,7 +16953,7 @@
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E746" s="2" t="n">
         <f aca="false">A746 +1000</f>
@@ -16952,7 +16971,7 @@
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E747" s="2" t="n">
         <f aca="false">A747 +1000</f>
@@ -16970,7 +16989,7 @@
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E748" s="2" t="n">
         <f aca="false">A748 +1000</f>
@@ -16988,7 +17007,7 @@
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E749" s="2" t="n">
         <f aca="false">A749 +1000</f>
@@ -17006,7 +17025,7 @@
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E750" s="2" t="n">
         <f aca="false">A750 +1000</f>
@@ -17024,7 +17043,7 @@
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E751" s="2" t="n">
         <f aca="false">A751 +1000</f>
@@ -17042,7 +17061,7 @@
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E752" s="2" t="n">
         <f aca="false">A752 +1000</f>
@@ -17060,7 +17079,7 @@
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E753" s="2" t="n">
         <f aca="false">A753 +1000</f>
@@ -17078,7 +17097,7 @@
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E754" s="2" t="n">
         <f aca="false">A754 +1000</f>
@@ -17096,7 +17115,7 @@
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E755" s="2" t="n">
         <f aca="false">A755 +1000</f>
@@ -17114,7 +17133,7 @@
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E756" s="2" t="n">
         <f aca="false">A756 +1000</f>
@@ -17132,7 +17151,7 @@
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E757" s="2" t="n">
         <f aca="false">A757 +1000</f>
@@ -17150,7 +17169,7 @@
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E758" s="2" t="n">
         <f aca="false">A758 +1000</f>
@@ -17168,7 +17187,7 @@
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E759" s="2" t="n">
         <f aca="false">A759 +1000</f>
@@ -17186,7 +17205,7 @@
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E760" s="2" t="n">
         <f aca="false">A760 +1000</f>
@@ -17204,7 +17223,7 @@
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E761" s="2" t="n">
         <f aca="false">A761 +1000</f>
@@ -17222,7 +17241,7 @@
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E762" s="2" t="n">
         <f aca="false">A762 +1000</f>
@@ -17240,7 +17259,7 @@
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E763" s="2" t="n">
         <f aca="false">A763 +1000</f>
@@ -17258,7 +17277,7 @@
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E764" s="2" t="n">
         <f aca="false">A764 +1000</f>
@@ -17276,7 +17295,7 @@
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E765" s="2" t="n">
         <f aca="false">A765 +1000</f>
@@ -17294,7 +17313,7 @@
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E766" s="2" t="n">
         <f aca="false">A766 +1000</f>
@@ -17312,7 +17331,7 @@
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E767" s="2" t="n">
         <f aca="false">A767 +1000</f>
@@ -17330,7 +17349,7 @@
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E768" s="2" t="n">
         <f aca="false">A768 +1000</f>
@@ -17348,7 +17367,7 @@
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E769" s="2" t="n">
         <f aca="false">A769 +1000</f>
@@ -17366,7 +17385,7 @@
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E770" s="2" t="n">
         <f aca="false">A770 +1000</f>
@@ -17384,7 +17403,7 @@
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E771" s="2" t="n">
         <f aca="false">A771 +1000</f>
@@ -17402,7 +17421,7 @@
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E772" s="2" t="n">
         <f aca="false">A772 +1000</f>
@@ -17420,7 +17439,7 @@
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E773" s="2" t="n">
         <f aca="false">A773 +1000</f>
@@ -17438,7 +17457,7 @@
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E774" s="2" t="n">
         <f aca="false">A774 +1000</f>
@@ -17456,7 +17475,7 @@
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E775" s="2" t="n">
         <f aca="false">A775 +1000</f>
@@ -17474,7 +17493,7 @@
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E776" s="2" t="n">
         <f aca="false">A776 +1000</f>
@@ -17492,7 +17511,7 @@
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E777" s="2" t="n">
         <f aca="false">A777 +1000</f>
@@ -17510,7 +17529,7 @@
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E778" s="2" t="n">
         <f aca="false">A778 +1000</f>
@@ -17528,7 +17547,7 @@
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E779" s="2" t="n">
         <f aca="false">A779 +1000</f>
@@ -17546,7 +17565,7 @@
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E780" s="2" t="n">
         <f aca="false">A780 +1000</f>
@@ -17564,7 +17583,7 @@
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E781" s="2" t="n">
         <f aca="false">A781 +1000</f>
@@ -17582,7 +17601,7 @@
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E782" s="2" t="n">
         <f aca="false">A782 +1000</f>
@@ -17600,7 +17619,7 @@
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E783" s="2" t="n">
         <f aca="false">A783 +1000</f>
@@ -17618,7 +17637,7 @@
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E784" s="2" t="n">
         <f aca="false">A784 +1000</f>
@@ -17636,7 +17655,7 @@
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E785" s="2" t="n">
         <f aca="false">A785 +1000</f>
@@ -17654,7 +17673,7 @@
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E786" s="2" t="n">
         <f aca="false">A786 +1000</f>
@@ -17672,7 +17691,7 @@
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E787" s="2" t="n">
         <f aca="false">A787 +1000</f>
@@ -17690,7 +17709,7 @@
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E788" s="2" t="n">
         <f aca="false">A788 +1000</f>
@@ -17708,7 +17727,7 @@
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E789" s="2" t="n">
         <f aca="false">A789 +1000</f>
@@ -17726,7 +17745,7 @@
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E790" s="2" t="n">
         <f aca="false">A790 +1000</f>
@@ -17744,7 +17763,7 @@
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E791" s="2" t="n">
         <f aca="false">A791 +1000</f>
@@ -17762,7 +17781,7 @@
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E792" s="2" t="n">
         <f aca="false">A792 +1000</f>
@@ -17780,7 +17799,7 @@
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E793" s="2" t="n">
         <f aca="false">A793 +1000</f>
@@ -17798,7 +17817,7 @@
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E794" s="2" t="n">
         <f aca="false">A794 +1000</f>
@@ -17816,7 +17835,7 @@
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E795" s="2" t="n">
         <f aca="false">A795 +1000</f>
@@ -17834,7 +17853,7 @@
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E796" s="2" t="n">
         <f aca="false">A796 +1000</f>
@@ -17852,7 +17871,7 @@
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E797" s="2" t="n">
         <f aca="false">A797 +1000</f>
@@ -17870,7 +17889,7 @@
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E798" s="2" t="n">
         <f aca="false">A798 +1000</f>
@@ -17888,7 +17907,7 @@
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E799" s="2" t="n">
         <f aca="false">A799 +1000</f>
@@ -17906,7 +17925,7 @@
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E800" s="2" t="n">
         <f aca="false">A800 +1000</f>
@@ -17924,7 +17943,7 @@
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E801" s="2" t="n">
         <f aca="false">A801 +1000</f>
@@ -17942,7 +17961,7 @@
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E802" s="2" t="n">
         <f aca="false">A802 +1000</f>
@@ -17960,7 +17979,7 @@
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E803" s="2" t="n">
         <f aca="false">A803 +1000</f>
@@ -17978,7 +17997,7 @@
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E804" s="2" t="n">
         <f aca="false">A804 +1000</f>
@@ -17996,7 +18015,7 @@
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E805" s="2" t="n">
         <f aca="false">A805 +1000</f>
@@ -18014,7 +18033,7 @@
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E806" s="2" t="n">
         <f aca="false">A806 +1000</f>
@@ -18032,7 +18051,7 @@
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E807" s="2" t="n">
         <f aca="false">A807 +1000</f>
@@ -18050,7 +18069,7 @@
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E808" s="2" t="n">
         <f aca="false">A808 +1000</f>
@@ -18068,7 +18087,7 @@
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E809" s="2" t="n">
         <f aca="false">A809 +1000</f>
@@ -18086,7 +18105,7 @@
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E810" s="2" t="n">
         <f aca="false">A810 +1000</f>
@@ -18104,7 +18123,7 @@
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E811" s="2" t="n">
         <f aca="false">A811 +1000</f>
@@ -18122,7 +18141,7 @@
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E812" s="2" t="n">
         <f aca="false">A812 +1000</f>
@@ -18140,7 +18159,7 @@
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E813" s="2" t="n">
         <f aca="false">A813 +1000</f>
@@ -18158,7 +18177,7 @@
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E814" s="2" t="n">
         <f aca="false">A814 +1000</f>
@@ -18176,7 +18195,7 @@
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E815" s="2" t="n">
         <f aca="false">A815 +1000</f>
@@ -18194,7 +18213,7 @@
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E816" s="2" t="n">
         <f aca="false">A816 +1000</f>
@@ -18212,7 +18231,7 @@
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E817" s="2" t="n">
         <f aca="false">A817 +1000</f>
@@ -18230,7 +18249,7 @@
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E818" s="2" t="n">
         <f aca="false">A818 +1000</f>
@@ -18248,7 +18267,7 @@
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E819" s="2" t="n">
         <f aca="false">A819 +1000</f>
@@ -18266,7 +18285,7 @@
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E820" s="2" t="n">
         <f aca="false">A820 +1000</f>
@@ -18284,7 +18303,7 @@
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E821" s="2" t="n">
         <f aca="false">A821 +1000</f>
@@ -18302,7 +18321,7 @@
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E822" s="2" t="n">
         <f aca="false">A822 +1000</f>
@@ -18320,7 +18339,7 @@
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E823" s="2" t="n">
         <f aca="false">A823 +1000</f>
@@ -18338,7 +18357,7 @@
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E824" s="2" t="n">
         <f aca="false">A824 +1000</f>
@@ -18356,7 +18375,7 @@
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E825" s="2" t="n">
         <f aca="false">A825 +1000</f>
@@ -18374,7 +18393,7 @@
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E826" s="2" t="n">
         <f aca="false">A826 +1000</f>
@@ -18392,7 +18411,7 @@
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E827" s="2" t="n">
         <f aca="false">A827 +1000</f>
@@ -18410,7 +18429,7 @@
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E828" s="2" t="n">
         <f aca="false">A828 +1000</f>
@@ -18428,7 +18447,7 @@
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E829" s="2" t="n">
         <f aca="false">A829 +1000</f>
@@ -18446,7 +18465,7 @@
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E830" s="2" t="n">
         <f aca="false">A830 +1000</f>
@@ -18464,7 +18483,7 @@
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E831" s="2" t="n">
         <f aca="false">A831 +1000</f>
@@ -18482,7 +18501,7 @@
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E832" s="2" t="n">
         <f aca="false">A832 +1000</f>
@@ -18500,7 +18519,7 @@
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E833" s="2" t="n">
         <f aca="false">A833 +1000</f>
@@ -18518,7 +18537,7 @@
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E834" s="2" t="n">
         <f aca="false">A834 +1000</f>
@@ -18536,7 +18555,7 @@
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E835" s="2" t="n">
         <f aca="false">A835 +1000</f>
@@ -18554,7 +18573,7 @@
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E836" s="2" t="n">
         <f aca="false">A836 +1000</f>
@@ -18572,7 +18591,7 @@
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E837" s="2" t="n">
         <f aca="false">A837 +1000</f>
@@ -18590,7 +18609,7 @@
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E838" s="2" t="n">
         <f aca="false">A838 +1000</f>
@@ -18608,7 +18627,7 @@
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E839" s="2" t="n">
         <f aca="false">A839 +1000</f>
@@ -18626,7 +18645,7 @@
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E840" s="2" t="n">
         <f aca="false">A840 +1000</f>
@@ -18644,7 +18663,7 @@
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E841" s="2" t="n">
         <f aca="false">A841 +1000</f>
@@ -18662,7 +18681,7 @@
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E842" s="2" t="n">
         <f aca="false">A842 +1000</f>
@@ -18680,7 +18699,7 @@
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E843" s="2" t="n">
         <f aca="false">A843 +1000</f>
@@ -18698,7 +18717,7 @@
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E844" s="2" t="n">
         <f aca="false">A844 +1000</f>
@@ -18716,7 +18735,7 @@
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E845" s="2" t="n">
         <f aca="false">A845 +1000</f>
@@ -18734,7 +18753,7 @@
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E846" s="2" t="n">
         <f aca="false">A846 +1000</f>
@@ -18752,7 +18771,7 @@
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B847" s="3" t="s">
         <v>9</v>
@@ -18761,7 +18780,7 @@
         <v>9</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E847" s="2" t="n">
         <f aca="false">A847 +1000</f>
@@ -18779,7 +18798,7 @@
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E848" s="2" t="n">
         <f aca="false">A848 +1000</f>
@@ -18797,7 +18816,7 @@
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E849" s="2" t="n">
         <f aca="false">A849 +1000</f>
@@ -18815,7 +18834,7 @@
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E850" s="2" t="n">
         <f aca="false">A850 +1000</f>
@@ -18833,7 +18852,7 @@
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E851" s="2" t="n">
         <f aca="false">A851 +1000</f>
@@ -18851,7 +18870,7 @@
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E852" s="2" t="n">
         <f aca="false">A852 +1000</f>
@@ -18869,7 +18888,7 @@
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E853" s="2" t="n">
         <f aca="false">A853 +1000</f>
@@ -18887,7 +18906,7 @@
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E854" s="2" t="n">
         <f aca="false">A854 +1000</f>
@@ -18905,7 +18924,7 @@
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E855" s="2" t="n">
         <f aca="false">A855 +1000</f>
@@ -18923,7 +18942,7 @@
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E856" s="2" t="n">
         <f aca="false">A856 +1000</f>
@@ -18941,7 +18960,7 @@
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E857" s="2" t="n">
         <f aca="false">A857 +1000</f>
@@ -18959,7 +18978,7 @@
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E858" s="2" t="n">
         <f aca="false">A858 +1000</f>
@@ -18977,7 +18996,7 @@
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E859" s="2" t="n">
         <f aca="false">A859 +1000</f>
@@ -18995,7 +19014,7 @@
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E860" s="2" t="n">
         <f aca="false">A860 +1000</f>
@@ -19013,7 +19032,7 @@
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E861" s="2" t="n">
         <f aca="false">A861 +1000</f>
@@ -19031,7 +19050,7 @@
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E862" s="2" t="n">
         <f aca="false">A862 +1000</f>
@@ -19049,7 +19068,7 @@
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E863" s="2" t="n">
         <f aca="false">A863 +1000</f>
@@ -19067,7 +19086,7 @@
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E864" s="2" t="n">
         <f aca="false">A864 +1000</f>
@@ -19085,7 +19104,7 @@
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E865" s="2" t="n">
         <f aca="false">A865 +1000</f>
@@ -19103,7 +19122,7 @@
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E866" s="2" t="n">
         <f aca="false">A866 +1000</f>
@@ -19121,7 +19140,7 @@
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E867" s="2" t="n">
         <f aca="false">A867 +1000</f>
@@ -19139,7 +19158,7 @@
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E868" s="2" t="n">
         <f aca="false">A868 +1000</f>
@@ -19157,7 +19176,7 @@
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E869" s="2" t="n">
         <f aca="false">A869 +1000</f>
@@ -19175,7 +19194,7 @@
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E870" s="2" t="n">
         <f aca="false">A870 +1000</f>
@@ -19193,7 +19212,7 @@
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E871" s="2" t="n">
         <f aca="false">A871 +1000</f>
@@ -19211,7 +19230,7 @@
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E872" s="2" t="n">
         <f aca="false">A872 +1000</f>
@@ -19229,7 +19248,7 @@
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E873" s="2" t="n">
         <f aca="false">A873 +1000</f>
@@ -19247,7 +19266,7 @@
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E874" s="2" t="n">
         <f aca="false">A874 +1000</f>
@@ -19265,7 +19284,7 @@
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E875" s="2" t="n">
         <f aca="false">A875 +1000</f>
@@ -19283,7 +19302,7 @@
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E876" s="2" t="n">
         <f aca="false">A876 +1000</f>
@@ -19301,7 +19320,7 @@
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E877" s="2" t="n">
         <f aca="false">A877 +1000</f>
@@ -19319,7 +19338,7 @@
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E878" s="2" t="n">
         <f aca="false">A878 +1000</f>
@@ -19337,7 +19356,7 @@
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E879" s="2" t="n">
         <f aca="false">A879 +1000</f>
@@ -19355,7 +19374,7 @@
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E880" s="2" t="n">
         <f aca="false">A880 +1000</f>
@@ -19373,7 +19392,7 @@
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E881" s="2" t="n">
         <f aca="false">A881 +1000</f>
@@ -19391,7 +19410,7 @@
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E882" s="2" t="n">
         <f aca="false">A882 +1000</f>
@@ -19409,7 +19428,7 @@
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E883" s="2" t="n">
         <f aca="false">A883 +1000</f>
@@ -19427,7 +19446,7 @@
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E884" s="2" t="n">
         <f aca="false">A884 +1000</f>
@@ -19445,7 +19464,7 @@
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E885" s="2" t="n">
         <f aca="false">A885 +1000</f>
@@ -19463,7 +19482,7 @@
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E886" s="2" t="n">
         <f aca="false">A886 +1000</f>
@@ -19481,7 +19500,7 @@
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E887" s="2" t="n">
         <f aca="false">A887 +1000</f>
@@ -19499,7 +19518,7 @@
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E888" s="2" t="n">
         <f aca="false">A888 +1000</f>
@@ -19517,7 +19536,7 @@
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E889" s="2" t="n">
         <f aca="false">A889 +1000</f>
@@ -19535,7 +19554,7 @@
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E890" s="2" t="n">
         <f aca="false">A890 +1000</f>
@@ -19553,7 +19572,7 @@
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E891" s="2" t="n">
         <f aca="false">A891 +1000</f>
@@ -19571,7 +19590,7 @@
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E892" s="2" t="n">
         <f aca="false">A892 +1000</f>
@@ -19589,7 +19608,7 @@
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E893" s="2" t="n">
         <f aca="false">A893 +1000</f>
@@ -19607,7 +19626,7 @@
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E894" s="2" t="n">
         <f aca="false">A894 +1000</f>
@@ -19625,7 +19644,7 @@
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E895" s="2" t="n">
         <f aca="false">A895 +1000</f>
@@ -19643,7 +19662,7 @@
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E896" s="2" t="n">
         <f aca="false">A896 +1000</f>
@@ -19661,7 +19680,7 @@
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E897" s="2" t="n">
         <f aca="false">A897 +1000</f>
@@ -19679,7 +19698,7 @@
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E898" s="2" t="n">
         <f aca="false">A898 +1000</f>
@@ -19697,7 +19716,7 @@
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E899" s="2" t="n">
         <f aca="false">A899 +1000</f>
@@ -19715,7 +19734,7 @@
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E900" s="2" t="n">
         <f aca="false">A900 +1000</f>
@@ -19733,7 +19752,7 @@
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E901" s="2" t="n">
         <f aca="false">A901 +1000</f>
@@ -19751,7 +19770,7 @@
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E902" s="2" t="n">
         <f aca="false">A902 +1000</f>
@@ -19769,7 +19788,7 @@
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E903" s="2" t="n">
         <f aca="false">A903 +1000</f>
@@ -19787,7 +19806,7 @@
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E904" s="2" t="n">
         <f aca="false">A904 +1000</f>
@@ -19805,7 +19824,7 @@
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E905" s="2" t="n">
         <f aca="false">A905 +1000</f>
@@ -19823,7 +19842,7 @@
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E906" s="2" t="n">
         <f aca="false">A906 +1000</f>
@@ -19841,7 +19860,7 @@
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E907" s="2" t="n">
         <f aca="false">A907 +1000</f>
@@ -19859,7 +19878,7 @@
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E908" s="2" t="n">
         <f aca="false">A908 +1000</f>
@@ -19877,7 +19896,7 @@
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E909" s="2" t="n">
         <f aca="false">A909 +1000</f>
@@ -19895,7 +19914,7 @@
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E910" s="2" t="n">
         <f aca="false">A910 +1000</f>
@@ -19913,7 +19932,7 @@
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E911" s="2" t="n">
         <f aca="false">A911 +1000</f>
@@ -19931,7 +19950,7 @@
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E912" s="2" t="n">
         <f aca="false">A912 +1000</f>
@@ -19949,7 +19968,7 @@
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E913" s="2" t="n">
         <f aca="false">A913 +1000</f>
@@ -19967,7 +19986,7 @@
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E914" s="2" t="n">
         <f aca="false">A914 +1000</f>
@@ -19985,7 +20004,7 @@
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E915" s="2" t="n">
         <f aca="false">A915 +1000</f>
@@ -20003,7 +20022,7 @@
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E916" s="2" t="n">
         <f aca="false">A916 +1000</f>
@@ -20021,7 +20040,7 @@
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E917" s="2" t="n">
         <f aca="false">A917 +1000</f>
@@ -20039,7 +20058,7 @@
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E918" s="2" t="n">
         <f aca="false">A918 +1000</f>
@@ -20057,7 +20076,7 @@
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E919" s="2" t="n">
         <f aca="false">A919 +1000</f>
@@ -20075,7 +20094,7 @@
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E920" s="2" t="n">
         <f aca="false">A920 +1000</f>
@@ -20093,7 +20112,7 @@
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E921" s="2" t="n">
         <f aca="false">A921 +1000</f>
@@ -20111,7 +20130,7 @@
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E922" s="2" t="n">
         <f aca="false">A922 +1000</f>
@@ -20129,7 +20148,7 @@
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E923" s="2" t="n">
         <f aca="false">A923 +1000</f>
@@ -20147,7 +20166,7 @@
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E924" s="2" t="n">
         <f aca="false">A924 +1000</f>
@@ -20165,7 +20184,7 @@
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E925" s="2" t="n">
         <f aca="false">A925 +1000</f>
@@ -20183,7 +20202,7 @@
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E926" s="2" t="n">
         <f aca="false">A926 +1000</f>
@@ -20201,7 +20220,7 @@
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E927" s="2" t="n">
         <f aca="false">A927 +1000</f>
@@ -20219,7 +20238,7 @@
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E928" s="2" t="n">
         <f aca="false">A928 +1000</f>
@@ -20237,7 +20256,7 @@
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E929" s="2" t="n">
         <f aca="false">A929 +1000</f>
@@ -20255,7 +20274,7 @@
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E930" s="2" t="n">
         <f aca="false">A930 +1000</f>
@@ -20273,7 +20292,7 @@
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E931" s="2" t="n">
         <f aca="false">A931 +1000</f>
@@ -20291,7 +20310,7 @@
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E932" s="2" t="n">
         <f aca="false">A932 +1000</f>
@@ -20309,7 +20328,7 @@
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E933" s="2" t="n">
         <f aca="false">A933 +1000</f>
@@ -20327,7 +20346,7 @@
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="E934" s="2" t="n">
         <f aca="false">A934 +1000</f>
@@ -20345,7 +20364,7 @@
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E935" s="2" t="n">
         <f aca="false">A935 +1000</f>
@@ -20363,7 +20382,7 @@
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E936" s="2" t="n">
         <f aca="false">A936 +1000</f>
@@ -20381,7 +20400,7 @@
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E937" s="2" t="n">
         <f aca="false">A937 +1000</f>
@@ -20399,7 +20418,7 @@
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E938" s="2" t="n">
         <f aca="false">A938 +1000</f>
@@ -20417,7 +20436,7 @@
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E939" s="2" t="n">
         <f aca="false">A939 +1000</f>
@@ -20435,7 +20454,7 @@
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E940" s="2" t="n">
         <f aca="false">A940 +1000</f>
@@ -20453,7 +20472,7 @@
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E941" s="2" t="n">
         <f aca="false">A941 +1000</f>
@@ -20471,7 +20490,7 @@
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E942" s="2" t="n">
         <f aca="false">A942 +1000</f>
@@ -20489,7 +20508,7 @@
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E943" s="2" t="n">
         <f aca="false">A943 +1000</f>
@@ -20507,7 +20526,7 @@
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="E944" s="2" t="n">
         <f aca="false">A944 +1000</f>
@@ -20525,7 +20544,7 @@
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E945" s="2" t="n">
         <f aca="false">A945 +1000</f>
@@ -20543,7 +20562,7 @@
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="E946" s="2" t="n">
         <f aca="false">A946 +1000</f>
@@ -20561,7 +20580,7 @@
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E947" s="2" t="n">
         <f aca="false">A947 +1000</f>
@@ -20579,7 +20598,7 @@
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E948" s="2" t="n">
         <f aca="false">A948 +1000</f>
@@ -20597,7 +20616,7 @@
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E949" s="2" t="n">
         <f aca="false">A949 +1000</f>
@@ -20615,7 +20634,7 @@
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E950" s="2" t="n">
         <f aca="false">A950 +1000</f>
@@ -20633,7 +20652,7 @@
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E951" s="2" t="n">
         <f aca="false">A951 +1000</f>
@@ -20651,7 +20670,7 @@
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E952" s="2" t="n">
         <f aca="false">A952 +1000</f>
@@ -20669,7 +20688,7 @@
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E953" s="2" t="n">
         <f aca="false">A953 +1000</f>
@@ -20687,7 +20706,7 @@
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E954" s="2" t="n">
         <f aca="false">A954 +1000</f>
@@ -20705,7 +20724,7 @@
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="E955" s="2" t="n">
         <f aca="false">A955 +1000</f>
@@ -20723,7 +20742,7 @@
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E956" s="2" t="n">
         <f aca="false">A956 +1000</f>
@@ -20741,7 +20760,7 @@
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E957" s="2" t="n">
         <f aca="false">A957 +1000</f>
@@ -20759,7 +20778,7 @@
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E958" s="2" t="n">
         <f aca="false">A958 +1000</f>
@@ -20777,7 +20796,7 @@
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E959" s="2" t="n">
         <f aca="false">A959 +1000</f>
@@ -20795,7 +20814,7 @@
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E960" s="2" t="n">
         <f aca="false">A960 +1000</f>
@@ -20813,7 +20832,7 @@
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E961" s="2" t="n">
         <f aca="false">A961 +1000</f>
@@ -20831,7 +20850,7 @@
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E962" s="2" t="n">
         <f aca="false">A962 +1000</f>
@@ -20849,7 +20868,7 @@
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E963" s="2" t="n">
         <f aca="false">A963 +1000</f>
@@ -20867,7 +20886,7 @@
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E964" s="2" t="n">
         <f aca="false">A964 +1000</f>
@@ -20885,7 +20904,7 @@
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E965" s="2" t="n">
         <f aca="false">A965 +1000</f>
@@ -20903,7 +20922,7 @@
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E966" s="2" t="n">
         <f aca="false">A966 +1000</f>
@@ -20921,7 +20940,7 @@
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E967" s="2" t="n">
         <f aca="false">A967 +1000</f>
@@ -20939,7 +20958,7 @@
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E968" s="2" t="n">
         <f aca="false">A968 +1000</f>
@@ -20957,7 +20976,7 @@
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E969" s="2" t="n">
         <f aca="false">A969 +1000</f>
@@ -20975,7 +20994,7 @@
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E970" s="2" t="n">
         <f aca="false">A970 +1000</f>
@@ -20993,7 +21012,7 @@
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E971" s="2" t="n">
         <f aca="false">A971 +1000</f>
@@ -21011,7 +21030,7 @@
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E972" s="2" t="n">
         <f aca="false">A972 +1000</f>
@@ -21029,7 +21048,7 @@
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E973" s="2" t="n">
         <f aca="false">A973 +1000</f>
@@ -21047,7 +21066,7 @@
     </row>
     <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E974" s="2" t="n">
         <f aca="false">A974 +1000</f>
@@ -21071,7 +21090,7 @@
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E975" s="2" t="n">
         <f aca="false">A975 +1000</f>
@@ -21089,7 +21108,7 @@
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E976" s="2" t="n">
         <f aca="false">A976 +1000</f>
@@ -21107,7 +21126,7 @@
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E977" s="2" t="n">
         <f aca="false">A977 +1000</f>
@@ -21125,7 +21144,7 @@
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="E978" s="2" t="n">
         <f aca="false">A978 +1000</f>
@@ -21143,7 +21162,7 @@
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E979" s="2" t="n">
         <f aca="false">A979 +1000</f>
@@ -21161,7 +21180,7 @@
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E980" s="2" t="n">
         <f aca="false">A980 +1000</f>
@@ -21179,7 +21198,7 @@
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E981" s="2" t="n">
         <f aca="false">A981 +1000</f>
@@ -21197,7 +21216,7 @@
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E982" s="2" t="n">
         <f aca="false">A982 +1000</f>
@@ -21215,7 +21234,7 @@
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E983" s="2" t="n">
         <f aca="false">A983 +1000</f>
@@ -21233,7 +21252,7 @@
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E984" s="2" t="n">
         <f aca="false">A984 +1000</f>
@@ -21251,7 +21270,7 @@
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E985" s="2" t="n">
         <f aca="false">A985 +1000</f>
@@ -21269,7 +21288,7 @@
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E986" s="2" t="n">
         <f aca="false">A986 +1000</f>
@@ -21287,7 +21306,7 @@
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E987" s="2" t="n">
         <f aca="false">A987 +1000</f>
@@ -21305,7 +21324,7 @@
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E988" s="2" t="n">
         <f aca="false">A988 +1000</f>
@@ -21323,7 +21342,7 @@
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E989" s="2" t="n">
         <f aca="false">A989 +1000</f>
@@ -21341,7 +21360,7 @@
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E990" s="2" t="n">
         <f aca="false">A990 +1000</f>
@@ -21359,7 +21378,7 @@
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E991" s="2" t="n">
         <f aca="false">A991 +1000</f>
@@ -21377,7 +21396,7 @@
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="E992" s="2" t="n">
         <f aca="false">A992 +1000</f>
@@ -21395,7 +21414,7 @@
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E993" s="2" t="n">
         <f aca="false">A993 +1000</f>
@@ -21413,7 +21432,7 @@
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E994" s="2" t="n">
         <f aca="false">A994 +1000</f>
@@ -21431,7 +21450,7 @@
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E995" s="2" t="n">
         <f aca="false">A995 +1000</f>
@@ -21449,7 +21468,7 @@
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E996" s="2" t="n">
         <f aca="false">A996 +1000</f>
@@ -21467,7 +21486,7 @@
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E997" s="2" t="n">
         <f aca="false">A997 +1000</f>
@@ -21485,7 +21504,7 @@
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E998" s="2" t="n">
         <f aca="false">A998 +1000</f>
@@ -21503,7 +21522,7 @@
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E999" s="2" t="n">
         <f aca="false">A999 +1000</f>
@@ -21521,7 +21540,7 @@
     </row>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E1000" s="2" t="n">
         <f aca="false">A1000 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="1011">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -331,6 +331,9 @@
     <t xml:space="preserve">0099</t>
   </si>
   <si>
+    <t xml:space="preserve">use InOrder</t>
+  </si>
+  <si>
     <t xml:space="preserve">0100</t>
   </si>
   <si>
@@ -1162,6 +1165,9 @@
     <t xml:space="preserve">0373</t>
   </si>
   <si>
+    <t xml:space="preserve">dfs</t>
+  </si>
+  <si>
     <t xml:space="preserve">0374</t>
   </si>
   <si>
@@ -2003,6 +2009,9 @@
   </si>
   <si>
     <t xml:space="preserve">0653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSTIterator</t>
   </si>
   <si>
     <t xml:space="preserve">0654</t>
@@ -3276,7 +3285,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="17.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5113,6 +5122,15 @@
       <c r="A100" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="B100" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="E100" s="2" t="n">
         <f aca="false">A100 +1000</f>
         <v>1099</v>
@@ -5129,7 +5147,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E101" s="2" t="n">
         <f aca="false">A101 +1000</f>
@@ -5147,7 +5165,7 @@
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E102" s="2" t="n">
         <f aca="false">A102 +1000</f>
@@ -5165,7 +5183,7 @@
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E103" s="2" t="n">
         <f aca="false">A103 +1000</f>
@@ -5183,7 +5201,7 @@
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E104" s="2" t="n">
         <f aca="false">A104 +1000</f>
@@ -5201,7 +5219,7 @@
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E105" s="2" t="n">
         <f aca="false">A105 +1000</f>
@@ -5219,7 +5237,7 @@
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E106" s="2" t="n">
         <f aca="false">A106 +1000</f>
@@ -5237,7 +5255,7 @@
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E107" s="2" t="n">
         <f aca="false">A107 +1000</f>
@@ -5255,7 +5273,7 @@
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E108" s="2" t="n">
         <f aca="false">A108 +1000</f>
@@ -5273,7 +5291,7 @@
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E109" s="2" t="n">
         <f aca="false">A109 +1000</f>
@@ -5291,7 +5309,7 @@
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E110" s="2" t="n">
         <f aca="false">A110 +1000</f>
@@ -5309,7 +5327,7 @@
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E111" s="2" t="n">
         <f aca="false">A111 +1000</f>
@@ -5327,7 +5345,7 @@
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E112" s="2" t="n">
         <f aca="false">A112 +1000</f>
@@ -5345,7 +5363,7 @@
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E113" s="2" t="n">
         <f aca="false">A113 +1000</f>
@@ -5363,7 +5381,7 @@
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E114" s="2" t="n">
         <f aca="false">A114 +1000</f>
@@ -5381,7 +5399,7 @@
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E115" s="2" t="n">
         <f aca="false">A115 +1000</f>
@@ -5399,7 +5417,7 @@
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E116" s="2" t="n">
         <f aca="false">A116 +1000</f>
@@ -5417,7 +5435,7 @@
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E117" s="2" t="n">
         <f aca="false">A117 +1000</f>
@@ -5435,7 +5453,7 @@
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E118" s="2" t="n">
         <f aca="false">A118 +1000</f>
@@ -5453,7 +5471,7 @@
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E119" s="2" t="n">
         <f aca="false">A119 +1000</f>
@@ -5471,7 +5489,7 @@
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E120" s="2" t="n">
         <f aca="false">A120 +1000</f>
@@ -5489,7 +5507,7 @@
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E121" s="2" t="n">
         <f aca="false">A121 +1000</f>
@@ -5507,7 +5525,7 @@
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E122" s="2" t="n">
         <f aca="false">A122 +1000</f>
@@ -5525,7 +5543,7 @@
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E123" s="2" t="n">
         <f aca="false">A123 +1000</f>
@@ -5543,7 +5561,7 @@
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E124" s="2" t="n">
         <f aca="false">A124 +1000</f>
@@ -5561,7 +5579,7 @@
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E125" s="2" t="n">
         <f aca="false">A125 +1000</f>
@@ -5579,7 +5597,7 @@
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E126" s="2" t="n">
         <f aca="false">A126 +1000</f>
@@ -5597,7 +5615,7 @@
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E127" s="2" t="n">
         <f aca="false">A127 +1000</f>
@@ -5615,7 +5633,7 @@
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E128" s="2" t="n">
         <f aca="false">A128 +1000</f>
@@ -5633,7 +5651,7 @@
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E129" s="2" t="n">
         <f aca="false">A129 +1000</f>
@@ -5651,7 +5669,7 @@
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E130" s="2" t="n">
         <f aca="false">A130 +1000</f>
@@ -5669,7 +5687,7 @@
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E131" s="2" t="n">
         <f aca="false">A131 +1000</f>
@@ -5687,7 +5705,7 @@
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E132" s="2" t="n">
         <f aca="false">A132 +1000</f>
@@ -5705,7 +5723,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E133" s="2" t="n">
         <f aca="false">A133 +1000</f>
@@ -5723,7 +5741,7 @@
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E134" s="2" t="n">
         <f aca="false">A134 +1000</f>
@@ -5741,7 +5759,7 @@
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E135" s="2" t="n">
         <f aca="false">A135 +1000</f>
@@ -5759,7 +5777,7 @@
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E136" s="2" t="n">
         <f aca="false">A136 +1000</f>
@@ -5777,7 +5795,7 @@
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E137" s="2" t="n">
         <f aca="false">A137 +1000</f>
@@ -5795,7 +5813,7 @@
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E138" s="2" t="n">
         <f aca="false">A138 +1000</f>
@@ -5813,7 +5831,7 @@
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E139" s="2" t="n">
         <f aca="false">A139 +1000</f>
@@ -5831,7 +5849,7 @@
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E140" s="2" t="n">
         <f aca="false">A140 +1000</f>
@@ -5849,7 +5867,7 @@
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E141" s="2" t="n">
         <f aca="false">A141 +1000</f>
@@ -5867,7 +5885,7 @@
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E142" s="2" t="n">
         <f aca="false">A142 +1000</f>
@@ -5885,7 +5903,7 @@
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E143" s="2" t="n">
         <f aca="false">A143 +1000</f>
@@ -5903,7 +5921,7 @@
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E144" s="2" t="n">
         <f aca="false">A144 +1000</f>
@@ -5921,7 +5939,7 @@
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E145" s="2" t="n">
         <f aca="false">A145 +1000</f>
@@ -5939,7 +5957,7 @@
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E146" s="2" t="n">
         <f aca="false">A146 +1000</f>
@@ -5957,7 +5975,7 @@
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E147" s="2" t="n">
         <f aca="false">A147 +1000</f>
@@ -5975,7 +5993,7 @@
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E148" s="2" t="n">
         <f aca="false">A148 +1000</f>
@@ -5993,7 +6011,7 @@
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E149" s="2" t="n">
         <f aca="false">A149 +1000</f>
@@ -6011,7 +6029,7 @@
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E150" s="2" t="n">
         <f aca="false">A150 +1000</f>
@@ -6029,7 +6047,7 @@
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E151" s="2" t="n">
         <f aca="false">A151 +1000</f>
@@ -6047,7 +6065,7 @@
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E152" s="2" t="n">
         <f aca="false">A152 +1000</f>
@@ -6065,7 +6083,7 @@
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E153" s="2" t="n">
         <f aca="false">A153 +1000</f>
@@ -6083,7 +6101,7 @@
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E154" s="2" t="n">
         <f aca="false">A154 +1000</f>
@@ -6101,7 +6119,7 @@
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E155" s="2" t="n">
         <f aca="false">A155 +1000</f>
@@ -6119,7 +6137,7 @@
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E156" s="2" t="n">
         <f aca="false">A156 +1000</f>
@@ -6137,7 +6155,7 @@
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E157" s="2" t="n">
         <f aca="false">A157 +1000</f>
@@ -6155,7 +6173,7 @@
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E158" s="2" t="n">
         <f aca="false">A158 +1000</f>
@@ -6173,7 +6191,7 @@
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E159" s="2" t="n">
         <f aca="false">A159 +1000</f>
@@ -6191,7 +6209,7 @@
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E160" s="2" t="n">
         <f aca="false">A160 +1000</f>
@@ -6209,7 +6227,7 @@
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E161" s="2" t="n">
         <f aca="false">A161 +1000</f>
@@ -6227,7 +6245,7 @@
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E162" s="2" t="n">
         <f aca="false">A162 +1000</f>
@@ -6245,7 +6263,7 @@
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E163" s="2" t="n">
         <f aca="false">A163 +1000</f>
@@ -6263,7 +6281,7 @@
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E164" s="2" t="n">
         <f aca="false">A164 +1000</f>
@@ -6281,7 +6299,7 @@
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E165" s="2" t="n">
         <f aca="false">A165 +1000</f>
@@ -6299,7 +6317,7 @@
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E166" s="2" t="n">
         <f aca="false">A166 +1000</f>
@@ -6317,7 +6335,7 @@
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E167" s="2" t="n">
         <f aca="false">A167 +1000</f>
@@ -6335,7 +6353,7 @@
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E168" s="2" t="n">
         <f aca="false">A168 +1000</f>
@@ -6353,7 +6371,7 @@
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E169" s="2" t="n">
         <f aca="false">A169 +1000</f>
@@ -6371,7 +6389,7 @@
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E170" s="2" t="n">
         <f aca="false">A170 +1000</f>
@@ -6389,7 +6407,7 @@
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E171" s="2" t="n">
         <f aca="false">A171 +1000</f>
@@ -6407,7 +6425,7 @@
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E172" s="2" t="n">
         <f aca="false">A172 +1000</f>
@@ -6425,7 +6443,7 @@
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E173" s="2" t="n">
         <f aca="false">A173 +1000</f>
@@ -6443,7 +6461,7 @@
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>9</v>
@@ -6451,8 +6469,8 @@
       <c r="C174" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D174" s="0" t="s">
-        <v>177</v>
+      <c r="D174" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="E174" s="2" t="n">
         <f aca="false">A174 +1000</f>
@@ -6470,7 +6488,7 @@
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E175" s="2" t="n">
         <f aca="false">A175 +1000</f>
@@ -6488,7 +6506,7 @@
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E176" s="2" t="n">
         <f aca="false">A176 +1000</f>
@@ -6506,7 +6524,7 @@
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E177" s="2" t="n">
         <f aca="false">A177 +1000</f>
@@ -6524,7 +6542,7 @@
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E178" s="2" t="n">
         <f aca="false">A178 +1000</f>
@@ -6542,7 +6560,7 @@
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E179" s="2" t="n">
         <f aca="false">A179 +1000</f>
@@ -6560,7 +6578,7 @@
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E180" s="2" t="n">
         <f aca="false">A180 +1000</f>
@@ -6578,7 +6596,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E181" s="2" t="n">
         <f aca="false">A181 +1000</f>
@@ -6596,7 +6614,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E182" s="2" t="n">
         <f aca="false">A182 +1000</f>
@@ -6614,7 +6632,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E183" s="2" t="n">
         <f aca="false">A183 +1000</f>
@@ -6632,7 +6650,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E184" s="2" t="n">
         <f aca="false">A184 +1000</f>
@@ -6650,7 +6668,7 @@
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E185" s="2" t="n">
         <f aca="false">A185 +1000</f>
@@ -6668,7 +6686,7 @@
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E186" s="2" t="n">
         <f aca="false">A186 +1000</f>
@@ -6686,7 +6704,7 @@
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E187" s="2" t="n">
         <f aca="false">A187 +1000</f>
@@ -6704,7 +6722,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E188" s="2" t="n">
         <f aca="false">A188 +1000</f>
@@ -6722,7 +6740,7 @@
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E189" s="2" t="n">
         <f aca="false">A189 +1000</f>
@@ -6740,7 +6758,7 @@
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E190" s="2" t="n">
         <f aca="false">A190 +1000</f>
@@ -6758,7 +6776,7 @@
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E191" s="2" t="n">
         <f aca="false">A191 +1000</f>
@@ -6776,7 +6794,7 @@
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E192" s="2" t="n">
         <f aca="false">A192 +1000</f>
@@ -6794,7 +6812,7 @@
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E193" s="2" t="n">
         <f aca="false">A193 +1000</f>
@@ -6812,7 +6830,7 @@
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E194" s="2" t="n">
         <f aca="false">A194 +1000</f>
@@ -6830,7 +6848,7 @@
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E195" s="2" t="n">
         <f aca="false">A195 +1000</f>
@@ -6848,7 +6866,7 @@
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E196" s="2" t="n">
         <f aca="false">A196 +1000</f>
@@ -6866,7 +6884,7 @@
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E197" s="2" t="n">
         <f aca="false">A197 +1000</f>
@@ -6884,7 +6902,7 @@
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E198" s="2" t="n">
         <f aca="false">A198 +1000</f>
@@ -6902,7 +6920,7 @@
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E199" s="2" t="n">
         <f aca="false">A199 +1000</f>
@@ -6920,7 +6938,7 @@
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E200" s="2" t="n">
         <f aca="false">A200 +1000</f>
@@ -6938,7 +6956,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E201" s="2" t="n">
         <f aca="false">A201 +1000</f>
@@ -6956,7 +6974,7 @@
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E202" s="2" t="n">
         <f aca="false">A202 +1000</f>
@@ -6974,7 +6992,7 @@
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E203" s="2" t="n">
         <f aca="false">A203 +1000</f>
@@ -6992,7 +7010,7 @@
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E204" s="2" t="n">
         <f aca="false">A204 +1000</f>
@@ -7010,7 +7028,7 @@
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E205" s="2" t="n">
         <f aca="false">A205 +1000</f>
@@ -7028,7 +7046,7 @@
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E206" s="2" t="n">
         <f aca="false">A206 +1000</f>
@@ -7046,7 +7064,7 @@
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E207" s="2" t="n">
         <f aca="false">A207 +1000</f>
@@ -7064,7 +7082,7 @@
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E208" s="2" t="n">
         <f aca="false">A208 +1000</f>
@@ -7082,7 +7100,7 @@
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E209" s="2" t="n">
         <f aca="false">A209 +1000</f>
@@ -7100,7 +7118,7 @@
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E210" s="2" t="n">
         <f aca="false">A210 +1000</f>
@@ -7118,7 +7136,7 @@
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E211" s="2" t="n">
         <f aca="false">A211 +1000</f>
@@ -7136,7 +7154,7 @@
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E212" s="2" t="n">
         <f aca="false">A212 +1000</f>
@@ -7154,7 +7172,7 @@
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E213" s="2" t="n">
         <f aca="false">A213 +1000</f>
@@ -7172,7 +7190,7 @@
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E214" s="2" t="n">
         <f aca="false">A214 +1000</f>
@@ -7190,7 +7208,7 @@
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B215" s="3"/>
       <c r="E215" s="2" t="n">
@@ -7209,7 +7227,7 @@
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>9</v>
@@ -7233,7 +7251,7 @@
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E217" s="2" t="n">
         <f aca="false">A217 +1000</f>
@@ -7251,7 +7269,7 @@
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>9</v>
@@ -7275,7 +7293,7 @@
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E219" s="2" t="n">
         <f aca="false">A219 +1000</f>
@@ -7293,7 +7311,7 @@
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E220" s="2" t="n">
         <f aca="false">A220 +1000</f>
@@ -7311,7 +7329,7 @@
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E221" s="2" t="n">
         <f aca="false">A221 +1000</f>
@@ -7329,7 +7347,7 @@
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E222" s="2" t="n">
         <f aca="false">A222 +1000</f>
@@ -7347,7 +7365,7 @@
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E223" s="2" t="n">
         <f aca="false">A223 +1000</f>
@@ -7365,7 +7383,7 @@
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E224" s="2" t="n">
         <f aca="false">A224 +1000</f>
@@ -7383,7 +7401,7 @@
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E225" s="2" t="n">
         <f aca="false">A225 +1000</f>
@@ -7401,7 +7419,7 @@
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E226" s="2" t="n">
         <f aca="false">A226 +1000</f>
@@ -7419,7 +7437,7 @@
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E227" s="2" t="n">
         <f aca="false">A227 +1000</f>
@@ -7437,7 +7455,7 @@
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E228" s="2" t="n">
         <f aca="false">A228 +1000</f>
@@ -7455,7 +7473,7 @@
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E229" s="2" t="n">
         <f aca="false">A229 +1000</f>
@@ -7473,7 +7491,7 @@
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E230" s="2" t="n">
         <f aca="false">A230 +1000</f>
@@ -7491,7 +7509,7 @@
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>9</v>
@@ -7500,7 +7518,7 @@
         <v>9</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E231" s="2" t="n">
         <f aca="false">A231 +1000</f>
@@ -7524,7 +7542,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">A232 +1000</f>
@@ -7542,7 +7560,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">A233 +1000</f>
@@ -7560,7 +7578,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">A234 +1000</f>
@@ -7578,7 +7596,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">A235 +1000</f>
@@ -7596,7 +7614,7 @@
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>9</v>
@@ -7605,7 +7623,7 @@
         <v>9</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">A236 +1000</f>
@@ -7623,7 +7641,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">A237 +1000</f>
@@ -7641,7 +7659,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">A238 +1000</f>
@@ -7659,7 +7677,7 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>9</v>
@@ -7683,7 +7701,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">A240 +1000</f>
@@ -7701,7 +7719,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">A241 +1000</f>
@@ -7719,7 +7737,7 @@
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">A242 +1000</f>
@@ -7737,7 +7755,7 @@
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">A243 +1000</f>
@@ -7755,7 +7773,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">A244 +1000</f>
@@ -7773,7 +7791,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">A245 +1000</f>
@@ -7791,7 +7809,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E246" s="2" t="n">
         <f aca="false">A246 +1000</f>
@@ -7809,7 +7827,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E247" s="2" t="n">
         <f aca="false">A247 +1000</f>
@@ -7827,7 +7845,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E248" s="2" t="n">
         <f aca="false">A248 +1000</f>
@@ -7845,7 +7863,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E249" s="2" t="n">
         <f aca="false">A249 +1000</f>
@@ -7863,7 +7881,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E250" s="2" t="n">
         <f aca="false">A250 +1000</f>
@@ -7881,7 +7899,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E251" s="2" t="n">
         <f aca="false">A251 +1000</f>
@@ -7899,7 +7917,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E252" s="2" t="n">
         <f aca="false">A252 +1000</f>
@@ -7917,7 +7935,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E253" s="2" t="n">
         <f aca="false">A253 +1000</f>
@@ -7935,7 +7953,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E254" s="2" t="n">
         <f aca="false">A254 +1000</f>
@@ -7953,7 +7971,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E255" s="2" t="n">
         <f aca="false">A255 +1000</f>
@@ -7971,7 +7989,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E256" s="2" t="n">
         <f aca="false">A256 +1000</f>
@@ -7989,7 +8007,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E257" s="2" t="n">
         <f aca="false">A257 +1000</f>
@@ -8007,7 +8025,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E258" s="2" t="n">
         <f aca="false">A258 +1000</f>
@@ -8025,7 +8043,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E259" s="2" t="n">
         <f aca="false">A259 +1000</f>
@@ -8043,7 +8061,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E260" s="2" t="n">
         <f aca="false">A260 +1000</f>
@@ -8061,7 +8079,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E261" s="2" t="n">
         <f aca="false">A261 +1000</f>
@@ -8079,7 +8097,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E262" s="2" t="n">
         <f aca="false">A262 +1000</f>
@@ -8097,7 +8115,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E263" s="2" t="n">
         <f aca="false">A263 +1000</f>
@@ -8115,7 +8133,7 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>9</v>
@@ -8145,7 +8163,7 @@
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E265" s="2" t="n">
         <f aca="false">A265 +1000</f>
@@ -8163,7 +8181,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E266" s="2" t="n">
         <f aca="false">A266 +1000</f>
@@ -8181,7 +8199,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E267" s="2" t="n">
         <f aca="false">A267 +1000</f>
@@ -8199,7 +8217,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E268" s="2" t="n">
         <f aca="false">A268 +1000</f>
@@ -8217,7 +8235,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E269" s="2" t="n">
         <f aca="false">A269 +1000</f>
@@ -8235,7 +8253,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E270" s="2" t="n">
         <f aca="false">A270 +1000</f>
@@ -8253,7 +8271,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E271" s="2" t="n">
         <f aca="false">A271 +1000</f>
@@ -8271,7 +8289,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E272" s="2" t="n">
         <f aca="false">A272 +1000</f>
@@ -8289,7 +8307,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E273" s="2" t="n">
         <f aca="false">A273 +1000</f>
@@ -8307,7 +8325,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E274" s="2" t="n">
         <f aca="false">A274 +1000</f>
@@ -8325,7 +8343,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E275" s="2" t="n">
         <f aca="false">A275 +1000</f>
@@ -8343,7 +8361,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E276" s="2" t="n">
         <f aca="false">A276 +1000</f>
@@ -8361,7 +8379,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E277" s="2" t="n">
         <f aca="false">A277 +1000</f>
@@ -8379,7 +8397,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E278" s="2" t="n">
         <f aca="false">A278 +1000</f>
@@ -8397,7 +8415,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E279" s="2" t="n">
         <f aca="false">A279 +1000</f>
@@ -8415,7 +8433,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E280" s="2" t="n">
         <f aca="false">A280 +1000</f>
@@ -8433,7 +8451,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E281" s="2" t="n">
         <f aca="false">A281 +1000</f>
@@ -8451,7 +8469,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E282" s="2" t="n">
         <f aca="false">A282 +1000</f>
@@ -8469,7 +8487,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E283" s="2" t="n">
         <f aca="false">A283 +1000</f>
@@ -8487,7 +8505,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E284" s="2" t="n">
         <f aca="false">A284 +1000</f>
@@ -8505,7 +8523,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E285" s="2" t="n">
         <f aca="false">A285 +1000</f>
@@ -8523,7 +8541,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E286" s="2" t="n">
         <f aca="false">A286 +1000</f>
@@ -8541,7 +8559,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E287" s="2" t="n">
         <f aca="false">A287 +1000</f>
@@ -8559,7 +8577,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E288" s="2" t="n">
         <f aca="false">A288 +1000</f>
@@ -8577,7 +8595,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E289" s="2" t="n">
         <f aca="false">A289 +1000</f>
@@ -8595,7 +8613,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E290" s="2" t="n">
         <f aca="false">A290 +1000</f>
@@ -8613,7 +8631,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E291" s="2" t="n">
         <f aca="false">A291 +1000</f>
@@ -8631,7 +8649,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E292" s="2" t="n">
         <f aca="false">A292 +1000</f>
@@ -8649,7 +8667,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E293" s="2" t="n">
         <f aca="false">A293 +1000</f>
@@ -8667,7 +8685,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E294" s="2" t="n">
         <f aca="false">A294 +1000</f>
@@ -8685,7 +8703,7 @@
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
@@ -8704,7 +8722,7 @@
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>9</v>
@@ -8728,7 +8746,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E297" s="2" t="n">
         <f aca="false">A297 +1000</f>
@@ -8746,7 +8764,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E298" s="2" t="n">
         <f aca="false">A298 +1000</f>
@@ -8764,7 +8782,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E299" s="2" t="n">
         <f aca="false">A299 +1000</f>
@@ -8782,7 +8800,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E300" s="2" t="n">
         <f aca="false">A300 +1000</f>
@@ -8800,7 +8818,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E301" s="2" t="n">
         <f aca="false">A301 +1000</f>
@@ -8818,7 +8836,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E302" s="2" t="n">
         <f aca="false">A302 +1000</f>
@@ -8836,7 +8854,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E303" s="2" t="n">
         <f aca="false">A303 +1000</f>
@@ -8854,7 +8872,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E304" s="2" t="n">
         <f aca="false">A304 +1000</f>
@@ -8872,7 +8890,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E305" s="2" t="n">
         <f aca="false">A305 +1000</f>
@@ -8890,7 +8908,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E306" s="2" t="n">
         <f aca="false">A306 +1000</f>
@@ -8908,7 +8926,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E307" s="2" t="n">
         <f aca="false">A307 +1000</f>
@@ -8926,7 +8944,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E308" s="2" t="n">
         <f aca="false">A308 +1000</f>
@@ -8944,7 +8962,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E309" s="2" t="n">
         <f aca="false">A309 +1000</f>
@@ -8962,7 +8980,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E310" s="2" t="n">
         <f aca="false">A310 +1000</f>
@@ -8980,7 +8998,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E311" s="2" t="n">
         <f aca="false">A311 +1000</f>
@@ -8998,7 +9016,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E312" s="2" t="n">
         <f aca="false">A312 +1000</f>
@@ -9016,7 +9034,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E313" s="2" t="n">
         <f aca="false">A313 +1000</f>
@@ -9034,7 +9052,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E314" s="2" t="n">
         <f aca="false">A314 +1000</f>
@@ -9052,7 +9070,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E315" s="2" t="n">
         <f aca="false">A315 +1000</f>
@@ -9070,7 +9088,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E316" s="2" t="n">
         <f aca="false">A316 +1000</f>
@@ -9088,7 +9106,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E317" s="2" t="n">
         <f aca="false">A317 +1000</f>
@@ -9106,7 +9124,7 @@
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E318" s="2" t="n">
         <f aca="false">A318 +1000</f>
@@ -9130,7 +9148,7 @@
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E319" s="2" t="n">
         <f aca="false">A319 +1000</f>
@@ -9148,7 +9166,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E320" s="2" t="n">
         <f aca="false">A320 +1000</f>
@@ -9166,7 +9184,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E321" s="2" t="n">
         <f aca="false">A321 +1000</f>
@@ -9184,7 +9202,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E322" s="2" t="n">
         <f aca="false">A322 +1000</f>
@@ -9202,7 +9220,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E323" s="2" t="n">
         <f aca="false">A323 +1000</f>
@@ -9220,7 +9238,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E324" s="2" t="n">
         <f aca="false">A324 +1000</f>
@@ -9238,7 +9256,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E325" s="2" t="n">
         <f aca="false">A325 +1000</f>
@@ -9256,7 +9274,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E326" s="2" t="n">
         <f aca="false">A326 +1000</f>
@@ -9274,7 +9292,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E327" s="2" t="n">
         <f aca="false">A327 +1000</f>
@@ -9292,7 +9310,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E328" s="2" t="n">
         <f aca="false">A328 +1000</f>
@@ -9310,7 +9328,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E329" s="2" t="n">
         <f aca="false">A329 +1000</f>
@@ -9328,7 +9346,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E330" s="2" t="n">
         <f aca="false">A330 +1000</f>
@@ -9346,7 +9364,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E331" s="2" t="n">
         <f aca="false">A331 +1000</f>
@@ -9364,7 +9382,7 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>9</v>
@@ -9388,7 +9406,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E333" s="2" t="n">
         <f aca="false">A333 +1000</f>
@@ -9406,7 +9424,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E334" s="2" t="n">
         <f aca="false">A334 +1000</f>
@@ -9424,7 +9442,7 @@
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E335" s="2" t="n">
         <f aca="false">A335 +1000</f>
@@ -9448,7 +9466,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E336" s="2" t="n">
         <f aca="false">A336 +1000</f>
@@ -9466,7 +9484,7 @@
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E337" s="2" t="n">
         <f aca="false">A337 +1000</f>
@@ -9490,7 +9508,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E338" s="2" t="n">
         <f aca="false">A338 +1000</f>
@@ -9508,7 +9526,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E339" s="2" t="n">
         <f aca="false">A339 +1000</f>
@@ -9526,7 +9544,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E340" s="2" t="n">
         <f aca="false">A340 +1000</f>
@@ -9544,7 +9562,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E341" s="2" t="n">
         <f aca="false">A341 +1000</f>
@@ -9562,7 +9580,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E342" s="2" t="n">
         <f aca="false">A342 +1000</f>
@@ -9580,7 +9598,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E343" s="2" t="n">
         <f aca="false">A343 +1000</f>
@@ -9598,7 +9616,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E344" s="2" t="n">
         <f aca="false">A344 +1000</f>
@@ -9616,7 +9634,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E345" s="2" t="n">
         <f aca="false">A345 +1000</f>
@@ -9634,7 +9652,7 @@
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E346" s="2" t="n">
         <f aca="false">A346 +1000</f>
@@ -9652,7 +9670,7 @@
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
@@ -9671,7 +9689,7 @@
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>9</v>
@@ -9695,7 +9713,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E349" s="2" t="n">
         <f aca="false">A349 +1000</f>
@@ -9713,7 +9731,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E350" s="2" t="n">
         <f aca="false">A350 +1000</f>
@@ -9731,7 +9749,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E351" s="2" t="n">
         <f aca="false">A351 +1000</f>
@@ -9749,7 +9767,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E352" s="2" t="n">
         <f aca="false">A352 +1000</f>
@@ -9767,7 +9785,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E353" s="2" t="n">
         <f aca="false">A353 +1000</f>
@@ -9785,7 +9803,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E354" s="2" t="n">
         <f aca="false">A354 +1000</f>
@@ -9803,7 +9821,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E355" s="2" t="n">
         <f aca="false">A355 +1000</f>
@@ -9821,7 +9839,7 @@
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>9</v>
@@ -9845,7 +9863,7 @@
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E357" s="2" t="n">
         <f aca="false">A357 +1000</f>
@@ -9869,7 +9887,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E358" s="2" t="n">
         <f aca="false">A358 +1000</f>
@@ -9887,7 +9905,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E359" s="2" t="n">
         <f aca="false">A359 +1000</f>
@@ -9905,7 +9923,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E360" s="2" t="n">
         <f aca="false">A360 +1000</f>
@@ -9923,7 +9941,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E361" s="2" t="n">
         <f aca="false">A361 +1000</f>
@@ -9941,7 +9959,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E362" s="2" t="n">
         <f aca="false">A362 +1000</f>
@@ -9959,7 +9977,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E363" s="2" t="n">
         <f aca="false">A363 +1000</f>
@@ -9977,7 +9995,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E364" s="2" t="n">
         <f aca="false">A364 +1000</f>
@@ -9995,7 +10013,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E365" s="2" t="n">
         <f aca="false">A365 +1000</f>
@@ -10013,7 +10031,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E366" s="2" t="n">
         <f aca="false">A366 +1000</f>
@@ -10031,7 +10049,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E367" s="2" t="n">
         <f aca="false">A367 +1000</f>
@@ -10049,7 +10067,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E368" s="2" t="n">
         <f aca="false">A368 +1000</f>
@@ -10067,7 +10085,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E369" s="2" t="n">
         <f aca="false">A369 +1000</f>
@@ -10085,7 +10103,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E370" s="2" t="n">
         <f aca="false">A370 +1000</f>
@@ -10103,7 +10121,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E371" s="2" t="n">
         <f aca="false">A371 +1000</f>
@@ -10121,7 +10139,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E372" s="2" t="n">
         <f aca="false">A372 +1000</f>
@@ -10139,7 +10157,7 @@
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>9</v>
@@ -10163,12 +10181,21 @@
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E374" s="2" t="n">
         <f aca="false">A374 +1000</f>
         <v>1373</v>
       </c>
+      <c r="F374" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G374" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H374" s="0" t="s">
+        <v>381</v>
+      </c>
       <c r="I374" s="2" t="n">
         <f aca="false">E374 +1000</f>
         <v>2373</v>
@@ -10181,7 +10208,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E375" s="2" t="n">
         <f aca="false">A375 +1000</f>
@@ -10199,7 +10226,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E376" s="2" t="n">
         <f aca="false">A376 +1000</f>
@@ -10217,7 +10244,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E377" s="2" t="n">
         <f aca="false">A377 +1000</f>
@@ -10235,7 +10262,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>9</v>
@@ -10259,7 +10286,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E379" s="2" t="n">
         <f aca="false">A379 +1000</f>
@@ -10277,7 +10304,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E380" s="2" t="n">
         <f aca="false">A380 +1000</f>
@@ -10295,7 +10322,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E381" s="2" t="n">
         <f aca="false">A381 +1000</f>
@@ -10313,7 +10340,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E382" s="2" t="n">
         <f aca="false">A382 +1000</f>
@@ -10331,7 +10358,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E383" s="2" t="n">
         <f aca="false">A383 +1000</f>
@@ -10349,7 +10376,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E384" s="2" t="n">
         <f aca="false">A384 +1000</f>
@@ -10367,7 +10394,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E385" s="2" t="n">
         <f aca="false">A385 +1000</f>
@@ -10385,7 +10412,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E386" s="2" t="n">
         <f aca="false">A386 +1000</f>
@@ -10403,7 +10430,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E387" s="2" t="n">
         <f aca="false">A387 +1000</f>
@@ -10421,7 +10448,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E388" s="2" t="n">
         <f aca="false">A388 +1000</f>
@@ -10439,7 +10466,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E389" s="2" t="n">
         <f aca="false">A389 +1000</f>
@@ -10457,7 +10484,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E390" s="2" t="n">
         <f aca="false">A390 +1000</f>
@@ -10475,7 +10502,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E391" s="2" t="n">
         <f aca="false">A391 +1000</f>
@@ -10493,7 +10520,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E392" s="2" t="n">
         <f aca="false">A392 +1000</f>
@@ -10511,7 +10538,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E393" s="2" t="n">
         <f aca="false">A393 +1000</f>
@@ -10529,7 +10556,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E394" s="2" t="n">
         <f aca="false">A394 +1000</f>
@@ -10547,7 +10574,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E395" s="2" t="n">
         <f aca="false">A395 +1000</f>
@@ -10565,7 +10592,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E396" s="2" t="n">
         <f aca="false">A396 +1000</f>
@@ -10583,7 +10610,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E397" s="2" t="n">
         <f aca="false">A397 +1000</f>
@@ -10601,7 +10628,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E398" s="2" t="n">
         <f aca="false">A398 +1000</f>
@@ -10619,7 +10646,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E399" s="2" t="n">
         <f aca="false">A399 +1000</f>
@@ -10637,7 +10664,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E400" s="2" t="n">
         <f aca="false">A400 +1000</f>
@@ -10655,7 +10682,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E401" s="2" t="n">
         <f aca="false">A401 +1000</f>
@@ -10673,7 +10700,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E402" s="2" t="n">
         <f aca="false">A402 +1000</f>
@@ -10691,7 +10718,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E403" s="2" t="n">
         <f aca="false">A403 +1000</f>
@@ -10709,7 +10736,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E404" s="2" t="n">
         <f aca="false">A404 +1000</f>
@@ -10727,7 +10754,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E405" s="2" t="n">
         <f aca="false">A405 +1000</f>
@@ -10745,7 +10772,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E406" s="2" t="n">
         <f aca="false">A406 +1000</f>
@@ -10763,7 +10790,7 @@
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>9</v>
@@ -10787,7 +10814,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E408" s="2" t="n">
         <f aca="false">A408 +1000</f>
@@ -10805,7 +10832,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E409" s="2" t="n">
         <f aca="false">A409 +1000</f>
@@ -10823,7 +10850,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E410" s="2" t="n">
         <f aca="false">A410 +1000</f>
@@ -10841,7 +10868,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E411" s="2" t="n">
         <f aca="false">A411 +1000</f>
@@ -10859,7 +10886,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E412" s="2" t="n">
         <f aca="false">A412 +1000</f>
@@ -10877,7 +10904,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E413" s="2" t="n">
         <f aca="false">A413 +1000</f>
@@ -10895,7 +10922,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E414" s="2" t="n">
         <f aca="false">A414 +1000</f>
@@ -10913,7 +10940,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E415" s="2" t="n">
         <f aca="false">A415 +1000</f>
@@ -10931,7 +10958,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E416" s="2" t="n">
         <f aca="false">A416 +1000</f>
@@ -10949,7 +10976,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E417" s="2" t="n">
         <f aca="false">A417 +1000</f>
@@ -10967,7 +10994,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E418" s="2" t="n">
         <f aca="false">A418 +1000</f>
@@ -10985,7 +11012,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E419" s="2" t="n">
         <f aca="false">A419 +1000</f>
@@ -11003,7 +11030,7 @@
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>9</v>
@@ -11027,7 +11054,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E421" s="2" t="n">
         <f aca="false">A421 +1000</f>
@@ -11045,7 +11072,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
@@ -11063,7 +11090,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E423" s="2" t="n">
         <f aca="false">A423 +1000</f>
@@ -11081,7 +11108,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E424" s="2" t="n">
         <f aca="false">A424 +1000</f>
@@ -11099,7 +11126,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E425" s="2" t="n">
         <f aca="false">A425 +1000</f>
@@ -11117,7 +11144,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E426" s="2" t="n">
         <f aca="false">A426 +1000</f>
@@ -11135,7 +11162,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E427" s="2" t="n">
         <f aca="false">A427 +1000</f>
@@ -11153,7 +11180,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E428" s="2" t="n">
         <f aca="false">A428 +1000</f>
@@ -11171,7 +11198,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E429" s="2" t="n">
         <f aca="false">A429 +1000</f>
@@ -11189,7 +11216,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E430" s="2" t="n">
         <f aca="false">A430 +1000</f>
@@ -11207,7 +11234,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E431" s="2" t="n">
         <f aca="false">A431 +1000</f>
@@ -11225,7 +11252,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E432" s="2" t="n">
         <f aca="false">A432 +1000</f>
@@ -11243,7 +11270,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E433" s="2" t="n">
         <f aca="false">A433 +1000</f>
@@ -11261,7 +11288,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E434" s="2" t="n">
         <f aca="false">A434 +1000</f>
@@ -11279,7 +11306,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E435" s="2" t="n">
         <f aca="false">A435 +1000</f>
@@ -11297,7 +11324,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E436" s="2" t="n">
         <f aca="false">A436 +1000</f>
@@ -11315,7 +11342,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E437" s="2" t="n">
         <f aca="false">A437 +1000</f>
@@ -11333,7 +11360,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E438" s="2" t="n">
         <f aca="false">A438 +1000</f>
@@ -11351,7 +11378,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E439" s="2" t="n">
         <f aca="false">A439 +1000</f>
@@ -11369,7 +11396,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E440" s="2" t="n">
         <f aca="false">A440 +1000</f>
@@ -11387,7 +11414,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E441" s="2" t="n">
         <f aca="false">A441 +1000</f>
@@ -11405,7 +11432,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E442" s="2" t="n">
         <f aca="false">A442 +1000</f>
@@ -11423,7 +11450,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E443" s="2" t="n">
         <f aca="false">A443 +1000</f>
@@ -11441,7 +11468,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E444" s="2" t="n">
         <f aca="false">A444 +1000</f>
@@ -11459,7 +11486,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E445" s="2" t="n">
         <f aca="false">A445 +1000</f>
@@ -11477,7 +11504,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E446" s="2" t="n">
         <f aca="false">A446 +1000</f>
@@ -11495,7 +11522,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E447" s="2" t="n">
         <f aca="false">A447 +1000</f>
@@ -11513,7 +11540,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E448" s="2" t="n">
         <f aca="false">A448 +1000</f>
@@ -11531,7 +11558,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E449" s="2" t="n">
         <f aca="false">A449 +1000</f>
@@ -11549,7 +11576,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E450" s="2" t="n">
         <f aca="false">A450 +1000</f>
@@ -11567,7 +11594,7 @@
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>9</v>
@@ -11591,7 +11618,7 @@
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E452" s="2" t="n">
         <f aca="false">A452 +1000</f>
@@ -11609,7 +11636,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E453" s="2" t="n">
         <f aca="false">A453 +1000</f>
@@ -11627,7 +11654,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E454" s="2" t="n">
         <f aca="false">A454 +1000</f>
@@ -11645,7 +11672,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E455" s="2" t="n">
         <f aca="false">A455 +1000</f>
@@ -11663,7 +11690,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E456" s="2" t="n">
         <f aca="false">A456 +1000</f>
@@ -11681,7 +11708,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E457" s="2" t="n">
         <f aca="false">A457 +1000</f>
@@ -11699,7 +11726,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E458" s="2" t="n">
         <f aca="false">A458 +1000</f>
@@ -11717,7 +11744,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E459" s="2" t="n">
         <f aca="false">A459 +1000</f>
@@ -11735,7 +11762,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E460" s="2" t="n">
         <f aca="false">A460 +1000</f>
@@ -11753,7 +11780,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E461" s="2" t="n">
         <f aca="false">A461 +1000</f>
@@ -11771,7 +11798,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E462" s="2" t="n">
         <f aca="false">A462 +1000</f>
@@ -11789,7 +11816,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E463" s="2" t="n">
         <f aca="false">A463 +1000</f>
@@ -11807,7 +11834,7 @@
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E464" s="2" t="n">
         <f aca="false">A464 +1000</f>
@@ -11831,7 +11858,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E465" s="2" t="n">
         <f aca="false">A465 +1000</f>
@@ -11849,7 +11876,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E466" s="2" t="n">
         <f aca="false">A466 +1000</f>
@@ -11867,7 +11894,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E467" s="2" t="n">
         <f aca="false">A467 +1000</f>
@@ -11885,7 +11912,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E468" s="2" t="n">
         <f aca="false">A468 +1000</f>
@@ -11903,7 +11930,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E469" s="2" t="n">
         <f aca="false">A469 +1000</f>
@@ -11921,7 +11948,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E470" s="2" t="n">
         <f aca="false">A470 +1000</f>
@@ -11939,7 +11966,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E471" s="2" t="n">
         <f aca="false">A471 +1000</f>
@@ -11957,7 +11984,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E472" s="2" t="n">
         <f aca="false">A472 +1000</f>
@@ -11975,7 +12002,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E473" s="2" t="n">
         <f aca="false">A473 +1000</f>
@@ -11993,7 +12020,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E474" s="2" t="n">
         <f aca="false">A474 +1000</f>
@@ -12011,7 +12038,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E475" s="2" t="n">
         <f aca="false">A475 +1000</f>
@@ -12029,7 +12056,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E476" s="2" t="n">
         <f aca="false">A476 +1000</f>
@@ -12047,7 +12074,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E477" s="2" t="n">
         <f aca="false">A477 +1000</f>
@@ -12065,7 +12092,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E478" s="2" t="n">
         <f aca="false">A478 +1000</f>
@@ -12083,7 +12110,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E479" s="2" t="n">
         <f aca="false">A479 +1000</f>
@@ -12101,7 +12128,7 @@
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
@@ -12120,7 +12147,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E481" s="2" t="n">
         <f aca="false">A481 +1000</f>
@@ -12138,7 +12165,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E482" s="2" t="n">
         <f aca="false">A482 +1000</f>
@@ -12156,7 +12183,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E483" s="2" t="n">
         <f aca="false">A483 +1000</f>
@@ -12174,7 +12201,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E484" s="2" t="n">
         <f aca="false">A484 +1000</f>
@@ -12192,7 +12219,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E485" s="2" t="n">
         <f aca="false">A485 +1000</f>
@@ -12210,7 +12237,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E486" s="2" t="n">
         <f aca="false">A486 +1000</f>
@@ -12228,7 +12255,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E487" s="2" t="n">
         <f aca="false">A487 +1000</f>
@@ -12246,7 +12273,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E488" s="2" t="n">
         <f aca="false">A488 +1000</f>
@@ -12264,7 +12291,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E489" s="2" t="n">
         <f aca="false">A489 +1000</f>
@@ -12282,7 +12309,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E490" s="2" t="n">
         <f aca="false">A490 +1000</f>
@@ -12300,7 +12327,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E491" s="2" t="n">
         <f aca="false">A491 +1000</f>
@@ -12318,7 +12345,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E492" s="2" t="n">
         <f aca="false">A492 +1000</f>
@@ -12336,7 +12363,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E493" s="2" t="n">
         <f aca="false">A493 +1000</f>
@@ -12354,7 +12381,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E494" s="2" t="n">
         <f aca="false">A494 +1000</f>
@@ -12372,7 +12399,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E495" s="2" t="n">
         <f aca="false">A495 +1000</f>
@@ -12390,7 +12417,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E496" s="2" t="n">
         <f aca="false">A496 +1000</f>
@@ -12408,7 +12435,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E497" s="2" t="n">
         <f aca="false">A497 +1000</f>
@@ -12426,7 +12453,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E498" s="2" t="n">
         <f aca="false">A498 +1000</f>
@@ -12444,7 +12471,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E499" s="2" t="n">
         <f aca="false">A499 +1000</f>
@@ -12462,7 +12489,7 @@
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E500" s="2" t="n">
         <f aca="false">A500 +1000</f>
@@ -12486,7 +12513,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E501" s="2" t="n">
         <f aca="false">A501 +1000</f>
@@ -12504,7 +12531,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E502" s="2" t="n">
         <f aca="false">A502 +1000</f>
@@ -12522,7 +12549,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E503" s="2" t="n">
         <f aca="false">A503 +1000</f>
@@ -12540,7 +12567,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E504" s="2" t="n">
         <f aca="false">A504 +1000</f>
@@ -12558,7 +12585,7 @@
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E505" s="2" t="n">
         <f aca="false">A505 +1000</f>
@@ -12576,7 +12603,7 @@
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>9</v>
@@ -12600,7 +12627,7 @@
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E507" s="2" t="n">
         <f aca="false">A507 +1000</f>
@@ -12624,7 +12651,7 @@
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E508" s="2" t="n">
         <f aca="false">A508 +1000</f>
@@ -12642,7 +12669,7 @@
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E509" s="2" t="n">
         <f aca="false">A509 +1000</f>
@@ -12660,7 +12687,7 @@
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E510" s="2" t="n">
         <f aca="false">A510 +1000</f>
@@ -12678,7 +12705,7 @@
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E511" s="2" t="n">
         <f aca="false">A511 +1000</f>
@@ -12696,7 +12723,7 @@
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E512" s="2" t="n">
         <f aca="false">A512 +1000</f>
@@ -12714,7 +12741,7 @@
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E513" s="2" t="n">
         <f aca="false">A513 +1000</f>
@@ -12732,7 +12759,7 @@
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E514" s="2" t="n">
         <f aca="false">A514 +1000</f>
@@ -12750,7 +12777,7 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E515" s="2" t="n">
         <f aca="false">A515 +1000</f>
@@ -12768,7 +12795,7 @@
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E516" s="2" t="n">
         <f aca="false">A516 +1000</f>
@@ -12786,7 +12813,7 @@
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E517" s="2" t="n">
         <f aca="false">A517 +1000</f>
@@ -12804,7 +12831,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E518" s="2" t="n">
         <f aca="false">A518 +1000</f>
@@ -12822,7 +12849,7 @@
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E519" s="2" t="n">
         <f aca="false">A519 +1000</f>
@@ -12840,7 +12867,7 @@
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E520" s="2" t="n">
         <f aca="false">A520 +1000</f>
@@ -12858,7 +12885,7 @@
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E521" s="2" t="n">
         <f aca="false">A521 +1000</f>
@@ -12876,7 +12903,7 @@
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E522" s="2" t="n">
         <f aca="false">A522 +1000</f>
@@ -12894,7 +12921,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E523" s="2" t="n">
         <f aca="false">A523 +1000</f>
@@ -12912,7 +12939,7 @@
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E524" s="2" t="n">
         <f aca="false">A524 +1000</f>
@@ -12930,7 +12957,7 @@
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E525" s="2" t="n">
         <f aca="false">A525 +1000</f>
@@ -12948,7 +12975,7 @@
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E526" s="2" t="n">
         <f aca="false">A526 +1000</f>
@@ -12966,7 +12993,7 @@
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E527" s="2" t="n">
         <f aca="false">A527 +1000</f>
@@ -12984,7 +13011,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E528" s="2" t="n">
         <f aca="false">A528 +1000</f>
@@ -13002,7 +13029,7 @@
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E529" s="2" t="n">
         <f aca="false">A529 +1000</f>
@@ -13020,7 +13047,7 @@
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E530" s="2" t="n">
         <f aca="false">A530 +1000</f>
@@ -13038,7 +13065,7 @@
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E531" s="2" t="n">
         <f aca="false">A531 +1000</f>
@@ -13056,7 +13083,7 @@
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E532" s="2" t="n">
         <f aca="false">A532 +1000</f>
@@ -13074,7 +13101,7 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E533" s="2" t="n">
         <f aca="false">A533 +1000</f>
@@ -13092,7 +13119,7 @@
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E534" s="2" t="n">
         <f aca="false">A534 +1000</f>
@@ -13110,7 +13137,7 @@
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E535" s="2" t="n">
         <f aca="false">A535 +1000</f>
@@ -13128,7 +13155,7 @@
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E536" s="2" t="n">
         <f aca="false">A536 +1000</f>
@@ -13146,7 +13173,7 @@
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E537" s="2" t="n">
         <f aca="false">A537 +1000</f>
@@ -13164,7 +13191,7 @@
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E538" s="2" t="n">
         <f aca="false">A538 +1000</f>
@@ -13182,7 +13209,7 @@
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E539" s="2" t="n">
         <f aca="false">A539 +1000</f>
@@ -13200,7 +13227,7 @@
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E540" s="2" t="n">
         <f aca="false">A540 +1000</f>
@@ -13218,7 +13245,7 @@
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E541" s="2" t="n">
         <f aca="false">A541 +1000</f>
@@ -13236,7 +13263,7 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E542" s="2" t="n">
         <f aca="false">A542 +1000</f>
@@ -13254,7 +13281,7 @@
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E543" s="2" t="n">
         <f aca="false">A543 +1000</f>
@@ -13272,7 +13299,7 @@
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E544" s="2" t="n">
         <f aca="false">A544 +1000</f>
@@ -13290,7 +13317,7 @@
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E545" s="2" t="n">
         <f aca="false">A545 +1000</f>
@@ -13308,7 +13335,7 @@
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E546" s="2" t="n">
         <f aca="false">A546 +1000</f>
@@ -13326,7 +13353,7 @@
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E547" s="2" t="n">
         <f aca="false">A547 +1000</f>
@@ -13344,7 +13371,7 @@
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E548" s="2" t="n">
         <f aca="false">A548 +1000</f>
@@ -13362,7 +13389,7 @@
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E549" s="2" t="n">
         <f aca="false">A549 +1000</f>
@@ -13380,7 +13407,7 @@
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E550" s="2" t="n">
         <f aca="false">A550 +1000</f>
@@ -13398,7 +13425,7 @@
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E551" s="2" t="n">
         <f aca="false">A551 +1000</f>
@@ -13416,7 +13443,7 @@
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E552" s="2" t="n">
         <f aca="false">A552 +1000</f>
@@ -13434,7 +13461,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E553" s="2" t="n">
         <f aca="false">A553 +1000</f>
@@ -13452,7 +13479,7 @@
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E554" s="2" t="n">
         <f aca="false">A554 +1000</f>
@@ -13470,7 +13497,7 @@
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E555" s="2" t="n">
         <f aca="false">A555 +1000</f>
@@ -13488,7 +13515,7 @@
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E556" s="2" t="n">
         <f aca="false">A556 +1000</f>
@@ -13506,7 +13533,7 @@
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E557" s="2" t="n">
         <f aca="false">A557 +1000</f>
@@ -13524,7 +13551,7 @@
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E558" s="2" t="n">
         <f aca="false">A558 +1000</f>
@@ -13548,7 +13575,7 @@
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E559" s="2" t="n">
         <f aca="false">A559 +1000</f>
@@ -13566,7 +13593,7 @@
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E560" s="2" t="n">
         <f aca="false">A560 +1000</f>
@@ -13584,7 +13611,7 @@
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E561" s="2" t="n">
         <f aca="false">A561 +1000</f>
@@ -13602,7 +13629,7 @@
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E562" s="2" t="n">
         <f aca="false">A562 +1000</f>
@@ -13620,7 +13647,7 @@
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E563" s="2" t="n">
         <f aca="false">A563 +1000</f>
@@ -13638,7 +13665,7 @@
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E564" s="2" t="n">
         <f aca="false">A564 +1000</f>
@@ -13656,7 +13683,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E565" s="2" t="n">
         <f aca="false">A565 +1000</f>
@@ -13674,7 +13701,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E566" s="2" t="n">
         <f aca="false">A566 +1000</f>
@@ -13692,7 +13719,7 @@
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E567" s="2" t="n">
         <f aca="false">A567 +1000</f>
@@ -13710,7 +13737,7 @@
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E568" s="2" t="n">
         <f aca="false">A568 +1000</f>
@@ -13728,7 +13755,7 @@
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E569" s="2" t="n">
         <f aca="false">A569 +1000</f>
@@ -13746,7 +13773,7 @@
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E570" s="2" t="n">
         <f aca="false">A570 +1000</f>
@@ -13764,7 +13791,7 @@
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E571" s="2" t="n">
         <f aca="false">A571 +1000</f>
@@ -13782,7 +13809,7 @@
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E572" s="2" t="n">
         <f aca="false">A572 +1000</f>
@@ -13800,7 +13827,7 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E573" s="2" t="n">
         <f aca="false">A573 +1000</f>
@@ -13818,7 +13845,7 @@
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E574" s="2" t="n">
         <f aca="false">A574 +1000</f>
@@ -13836,7 +13863,7 @@
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E575" s="2" t="n">
         <f aca="false">A575 +1000</f>
@@ -13854,7 +13881,7 @@
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E576" s="2" t="n">
         <f aca="false">A576 +1000</f>
@@ -13872,7 +13899,7 @@
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E577" s="2" t="n">
         <f aca="false">A577 +1000</f>
@@ -13890,7 +13917,7 @@
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E578" s="2" t="n">
         <f aca="false">A578 +1000</f>
@@ -13908,7 +13935,7 @@
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E579" s="2" t="n">
         <f aca="false">A579 +1000</f>
@@ -13926,7 +13953,7 @@
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E580" s="2" t="n">
         <f aca="false">A580 +1000</f>
@@ -13944,7 +13971,7 @@
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E581" s="2" t="n">
         <f aca="false">A581 +1000</f>
@@ -13962,7 +13989,7 @@
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E582" s="2" t="n">
         <f aca="false">A582 +1000</f>
@@ -13980,7 +14007,7 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E583" s="2" t="n">
         <f aca="false">A583 +1000</f>
@@ -13998,7 +14025,7 @@
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E584" s="2" t="n">
         <f aca="false">A584 +1000</f>
@@ -14016,7 +14043,7 @@
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E585" s="2" t="n">
         <f aca="false">A585 +1000</f>
@@ -14034,7 +14061,7 @@
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E586" s="2" t="n">
         <f aca="false">A586 +1000</f>
@@ -14052,7 +14079,7 @@
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E587" s="2" t="n">
         <f aca="false">A587 +1000</f>
@@ -14070,7 +14097,7 @@
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E588" s="2" t="n">
         <f aca="false">A588 +1000</f>
@@ -14088,7 +14115,7 @@
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E589" s="2" t="n">
         <f aca="false">A589 +1000</f>
@@ -14106,7 +14133,7 @@
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E590" s="2" t="n">
         <f aca="false">A590 +1000</f>
@@ -14124,7 +14151,7 @@
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E591" s="2" t="n">
         <f aca="false">A591 +1000</f>
@@ -14142,7 +14169,7 @@
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E592" s="2" t="n">
         <f aca="false">A592 +1000</f>
@@ -14160,7 +14187,7 @@
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E593" s="2" t="n">
         <f aca="false">A593 +1000</f>
@@ -14178,7 +14205,7 @@
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E594" s="2" t="n">
         <f aca="false">A594 +1000</f>
@@ -14196,7 +14223,7 @@
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E595" s="2" t="n">
         <f aca="false">A595 +1000</f>
@@ -14214,7 +14241,7 @@
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E596" s="2" t="n">
         <f aca="false">A596 +1000</f>
@@ -14232,7 +14259,7 @@
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E597" s="2" t="n">
         <f aca="false">A597 +1000</f>
@@ -14250,7 +14277,7 @@
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E598" s="2" t="n">
         <f aca="false">A598 +1000</f>
@@ -14268,7 +14295,7 @@
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E599" s="2" t="n">
         <f aca="false">A599 +1000</f>
@@ -14286,7 +14313,7 @@
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E600" s="2" t="n">
         <f aca="false">A600 +1000</f>
@@ -14304,7 +14331,7 @@
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E601" s="2" t="n">
         <f aca="false">A601 +1000</f>
@@ -14322,7 +14349,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E602" s="2" t="n">
         <f aca="false">A602 +1000</f>
@@ -14340,7 +14367,7 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E603" s="2" t="n">
         <f aca="false">A603 +1000</f>
@@ -14358,7 +14385,7 @@
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E604" s="2" t="n">
         <f aca="false">A604 +1000</f>
@@ -14376,7 +14403,7 @@
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E605" s="2" t="n">
         <f aca="false">A605 +1000</f>
@@ -14394,7 +14421,7 @@
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E606" s="2" t="n">
         <f aca="false">A606 +1000</f>
@@ -14412,7 +14439,7 @@
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E607" s="2" t="n">
         <f aca="false">A607 +1000</f>
@@ -14430,7 +14457,7 @@
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E608" s="2" t="n">
         <f aca="false">A608 +1000</f>
@@ -14448,7 +14475,7 @@
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E609" s="2" t="n">
         <f aca="false">A609 +1000</f>
@@ -14466,7 +14493,7 @@
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E610" s="2" t="n">
         <f aca="false">A610 +1000</f>
@@ -14484,7 +14511,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E611" s="2" t="n">
         <f aca="false">A611 +1000</f>
@@ -14502,7 +14529,7 @@
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E612" s="2" t="n">
         <f aca="false">A612 +1000</f>
@@ -14520,7 +14547,7 @@
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E613" s="2" t="n">
         <f aca="false">A613 +1000</f>
@@ -14538,7 +14565,7 @@
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E614" s="2" t="n">
         <f aca="false">A614 +1000</f>
@@ -14556,7 +14583,7 @@
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E615" s="2" t="n">
         <f aca="false">A615 +1000</f>
@@ -14574,7 +14601,7 @@
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E616" s="2" t="n">
         <f aca="false">A616 +1000</f>
@@ -14592,7 +14619,7 @@
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E617" s="2" t="n">
         <f aca="false">A617 +1000</f>
@@ -14610,7 +14637,7 @@
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E618" s="2" t="n">
         <f aca="false">A618 +1000</f>
@@ -14628,7 +14655,7 @@
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E619" s="2" t="n">
         <f aca="false">A619 +1000</f>
@@ -14646,7 +14673,7 @@
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E620" s="2" t="n">
         <f aca="false">A620 +1000</f>
@@ -14664,7 +14691,7 @@
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E621" s="2" t="n">
         <f aca="false">A621 +1000</f>
@@ -14682,7 +14709,7 @@
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>9</v>
@@ -14691,7 +14718,7 @@
         <v>9</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E622" s="2" t="n">
         <f aca="false">A622 +1000</f>
@@ -14709,7 +14736,7 @@
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E623" s="2" t="n">
         <f aca="false">A623 +1000</f>
@@ -14727,7 +14754,7 @@
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E624" s="2" t="n">
         <f aca="false">A624 +1000</f>
@@ -14745,7 +14772,7 @@
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E625" s="2" t="n">
         <f aca="false">A625 +1000</f>
@@ -14763,7 +14790,7 @@
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E626" s="2" t="n">
         <f aca="false">A626 +1000</f>
@@ -14781,7 +14808,7 @@
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E627" s="2" t="n">
         <f aca="false">A627 +1000</f>
@@ -14799,7 +14826,7 @@
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E628" s="2" t="n">
         <f aca="false">A628 +1000</f>
@@ -14817,7 +14844,7 @@
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E629" s="2" t="n">
         <f aca="false">A629 +1000</f>
@@ -14835,7 +14862,7 @@
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E630" s="2" t="n">
         <f aca="false">A630 +1000</f>
@@ -14853,7 +14880,7 @@
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E631" s="2" t="n">
         <f aca="false">A631 +1000</f>
@@ -14871,7 +14898,7 @@
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E632" s="2" t="n">
         <f aca="false">A632 +1000</f>
@@ -14889,7 +14916,7 @@
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E633" s="2" t="n">
         <f aca="false">A633 +1000</f>
@@ -14907,7 +14934,7 @@
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E634" s="2" t="n">
         <f aca="false">A634 +1000</f>
@@ -14925,7 +14952,7 @@
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E635" s="2" t="n">
         <f aca="false">A635 +1000</f>
@@ -14943,7 +14970,7 @@
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E636" s="2" t="n">
         <f aca="false">A636 +1000</f>
@@ -14961,7 +14988,7 @@
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E637" s="2" t="n">
         <f aca="false">A637 +1000</f>
@@ -14979,7 +15006,7 @@
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E638" s="2" t="n">
         <f aca="false">A638 +1000</f>
@@ -14997,7 +15024,7 @@
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E639" s="2" t="n">
         <f aca="false">A639 +1000</f>
@@ -15015,7 +15042,7 @@
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E640" s="2" t="n">
         <f aca="false">A640 +1000</f>
@@ -15033,7 +15060,7 @@
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E641" s="2" t="n">
         <f aca="false">A641 +1000</f>
@@ -15051,7 +15078,7 @@
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E642" s="2" t="n">
         <f aca="false">A642 +1000</f>
@@ -15069,7 +15096,7 @@
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E643" s="2" t="n">
         <f aca="false">A643 +1000</f>
@@ -15087,7 +15114,7 @@
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E644" s="2" t="n">
         <f aca="false">A644 +1000</f>
@@ -15105,7 +15132,7 @@
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E645" s="2" t="n">
         <f aca="false">A645 +1000</f>
@@ -15123,7 +15150,7 @@
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E646" s="2" t="n">
         <f aca="false">A646 +1000</f>
@@ -15141,7 +15168,7 @@
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E647" s="2" t="n">
         <f aca="false">A647 +1000</f>
@@ -15159,7 +15186,7 @@
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E648" s="2" t="n">
         <f aca="false">A648 +1000</f>
@@ -15177,7 +15204,7 @@
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E649" s="2" t="n">
         <f aca="false">A649 +1000</f>
@@ -15195,7 +15222,7 @@
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E650" s="2" t="n">
         <f aca="false">A650 +1000</f>
@@ -15213,7 +15240,7 @@
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E651" s="2" t="n">
         <f aca="false">A651 +1000</f>
@@ -15231,7 +15258,7 @@
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E652" s="2" t="n">
         <f aca="false">A652 +1000</f>
@@ -15249,7 +15276,7 @@
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E653" s="2" t="n">
         <f aca="false">A653 +1000</f>
@@ -15267,13 +15294,16 @@
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C654" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="D654" s="2" t="s">
+        <v>663</v>
       </c>
       <c r="E654" s="2" t="n">
         <f aca="false">A654 +1000</f>
@@ -15291,7 +15321,7 @@
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E655" s="2" t="n">
         <f aca="false">A655 +1000</f>
@@ -15309,7 +15339,7 @@
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E656" s="2" t="n">
         <f aca="false">A656 +1000</f>
@@ -15327,7 +15357,7 @@
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E657" s="2" t="n">
         <f aca="false">A657 +1000</f>
@@ -15345,7 +15375,7 @@
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E658" s="2" t="n">
         <f aca="false">A658 +1000</f>
@@ -15363,7 +15393,7 @@
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E659" s="2" t="n">
         <f aca="false">A659 +1000</f>
@@ -15381,7 +15411,7 @@
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E660" s="2" t="n">
         <f aca="false">A660 +1000</f>
@@ -15399,7 +15429,7 @@
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E661" s="2" t="n">
         <f aca="false">A661 +1000</f>
@@ -15417,7 +15447,7 @@
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E662" s="2" t="n">
         <f aca="false">A662 +1000</f>
@@ -15435,7 +15465,7 @@
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E663" s="2" t="n">
         <f aca="false">A663 +1000</f>
@@ -15453,7 +15483,7 @@
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E664" s="2" t="n">
         <f aca="false">A664 +1000</f>
@@ -15471,7 +15501,7 @@
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E665" s="2" t="n">
         <f aca="false">A665 +1000</f>
@@ -15489,7 +15519,7 @@
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E666" s="2" t="n">
         <f aca="false">A666 +1000</f>
@@ -15507,7 +15537,7 @@
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E667" s="2" t="n">
         <f aca="false">A667 +1000</f>
@@ -15525,7 +15555,7 @@
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E668" s="2" t="n">
         <f aca="false">A668 +1000</f>
@@ -15543,7 +15573,7 @@
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E669" s="2" t="n">
         <f aca="false">A669 +1000</f>
@@ -15561,7 +15591,7 @@
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E670" s="2" t="n">
         <f aca="false">A670 +1000</f>
@@ -15579,7 +15609,7 @@
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E671" s="2" t="n">
         <f aca="false">A671 +1000</f>
@@ -15597,7 +15627,7 @@
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E672" s="2" t="n">
         <f aca="false">A672 +1000</f>
@@ -15615,7 +15645,7 @@
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E673" s="2" t="n">
         <f aca="false">A673 +1000</f>
@@ -15633,7 +15663,7 @@
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E674" s="2" t="n">
         <f aca="false">A674 +1000</f>
@@ -15651,7 +15681,7 @@
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E675" s="2" t="n">
         <f aca="false">A675 +1000</f>
@@ -15669,7 +15699,7 @@
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E676" s="2" t="n">
         <f aca="false">A676 +1000</f>
@@ -15687,7 +15717,7 @@
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E677" s="2" t="n">
         <f aca="false">A677 +1000</f>
@@ -15705,7 +15735,7 @@
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E678" s="2" t="n">
         <f aca="false">A678 +1000</f>
@@ -15723,7 +15753,7 @@
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E679" s="2" t="n">
         <f aca="false">A679 +1000</f>
@@ -15741,7 +15771,7 @@
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E680" s="2" t="n">
         <f aca="false">A680 +1000</f>
@@ -15759,7 +15789,7 @@
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E681" s="2" t="n">
         <f aca="false">A681 +1000</f>
@@ -15777,7 +15807,7 @@
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="E682" s="2" t="n">
         <f aca="false">A682 +1000</f>
@@ -15795,7 +15825,7 @@
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E683" s="2" t="n">
         <f aca="false">A683 +1000</f>
@@ -15813,7 +15843,7 @@
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E684" s="2" t="n">
         <f aca="false">A684 +1000</f>
@@ -15831,7 +15861,7 @@
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E685" s="2" t="n">
         <f aca="false">A685 +1000</f>
@@ -15849,7 +15879,7 @@
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E686" s="2" t="n">
         <f aca="false">A686 +1000</f>
@@ -15867,7 +15897,7 @@
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E687" s="2" t="n">
         <f aca="false">A687 +1000</f>
@@ -15885,7 +15915,7 @@
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E688" s="2" t="n">
         <f aca="false">A688 +1000</f>
@@ -15903,7 +15933,7 @@
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E689" s="2" t="n">
         <f aca="false">A689 +1000</f>
@@ -15921,7 +15951,7 @@
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E690" s="2" t="n">
         <f aca="false">A690 +1000</f>
@@ -15939,7 +15969,7 @@
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E691" s="2" t="n">
         <f aca="false">A691 +1000</f>
@@ -15957,7 +15987,7 @@
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="E692" s="2" t="n">
         <f aca="false">A692 +1000</f>
@@ -15975,7 +16005,7 @@
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E693" s="2" t="n">
         <f aca="false">A693 +1000</f>
@@ -15993,7 +16023,7 @@
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="E694" s="2" t="n">
         <f aca="false">A694 +1000</f>
@@ -16011,7 +16041,7 @@
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="E695" s="2" t="n">
         <f aca="false">A695 +1000</f>
@@ -16029,7 +16059,7 @@
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E696" s="2" t="n">
         <f aca="false">A696 +1000</f>
@@ -16047,7 +16077,7 @@
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E697" s="2" t="n">
         <f aca="false">A697 +1000</f>
@@ -16065,7 +16095,7 @@
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="E698" s="2" t="n">
         <f aca="false">A698 +1000</f>
@@ -16083,7 +16113,7 @@
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E699" s="2" t="n">
         <f aca="false">A699 +1000</f>
@@ -16101,7 +16131,7 @@
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E700" s="2" t="n">
         <f aca="false">A700 +1000</f>
@@ -16119,7 +16149,7 @@
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>9</v>
@@ -16143,7 +16173,7 @@
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>9</v>
@@ -16167,7 +16197,7 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>9</v>
@@ -16191,7 +16221,7 @@
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>9</v>
@@ -16215,7 +16245,7 @@
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E705" s="2" t="n">
         <f aca="false">A705 +1000</f>
@@ -16233,7 +16263,7 @@
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E706" s="2" t="n">
         <f aca="false">A706 +1000</f>
@@ -16251,7 +16281,7 @@
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E707" s="2" t="n">
         <f aca="false">A707 +1000</f>
@@ -16269,7 +16299,7 @@
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
@@ -16287,7 +16317,7 @@
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E709" s="2" t="n">
         <f aca="false">A709 +1000</f>
@@ -16305,7 +16335,7 @@
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="E710" s="2" t="n">
         <f aca="false">A710 +1000</f>
@@ -16323,7 +16353,7 @@
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E711" s="2" t="n">
         <f aca="false">A711 +1000</f>
@@ -16341,7 +16371,7 @@
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E712" s="2" t="n">
         <f aca="false">A712 +1000</f>
@@ -16359,7 +16389,7 @@
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E713" s="2" t="n">
         <f aca="false">A713 +1000</f>
@@ -16377,7 +16407,7 @@
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E714" s="2" t="n">
         <f aca="false">A714 +1000</f>
@@ -16395,7 +16425,7 @@
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E715" s="2" t="n">
         <f aca="false">A715 +1000</f>
@@ -16413,7 +16443,7 @@
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E716" s="2" t="n">
         <f aca="false">A716 +1000</f>
@@ -16431,7 +16461,7 @@
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E717" s="2" t="n">
         <f aca="false">A717 +1000</f>
@@ -16449,7 +16479,7 @@
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="E718" s="2" t="n">
         <f aca="false">A718 +1000</f>
@@ -16467,7 +16497,7 @@
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E719" s="2" t="n">
         <f aca="false">A719 +1000</f>
@@ -16485,7 +16515,7 @@
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E720" s="2" t="n">
         <f aca="false">A720 +1000</f>
@@ -16503,7 +16533,7 @@
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E721" s="2" t="n">
         <f aca="false">A721 +1000</f>
@@ -16521,7 +16551,7 @@
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="E722" s="2" t="n">
         <f aca="false">A722 +1000</f>
@@ -16539,7 +16569,7 @@
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E723" s="2" t="n">
         <f aca="false">A723 +1000</f>
@@ -16557,7 +16587,7 @@
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E724" s="2" t="n">
         <f aca="false">A724 +1000</f>
@@ -16575,7 +16605,7 @@
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E725" s="2" t="n">
         <f aca="false">A725 +1000</f>
@@ -16593,7 +16623,7 @@
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E726" s="2" t="n">
         <f aca="false">A726 +1000</f>
@@ -16611,7 +16641,7 @@
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E727" s="2" t="n">
         <f aca="false">A727 +1000</f>
@@ -16629,7 +16659,7 @@
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="E728" s="2" t="n">
         <f aca="false">A728 +1000</f>
@@ -16647,7 +16677,7 @@
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E729" s="2" t="n">
         <f aca="false">A729 +1000</f>
@@ -16665,7 +16695,7 @@
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E730" s="2" t="n">
         <f aca="false">A730 +1000</f>
@@ -16683,7 +16713,7 @@
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="E731" s="2" t="n">
         <f aca="false">A731 +1000</f>
@@ -16701,7 +16731,7 @@
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E732" s="2" t="n">
         <f aca="false">A732 +1000</f>
@@ -16719,7 +16749,7 @@
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E733" s="2" t="n">
         <f aca="false">A733 +1000</f>
@@ -16737,7 +16767,7 @@
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="E734" s="2" t="n">
         <f aca="false">A734 +1000</f>
@@ -16755,7 +16785,7 @@
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E735" s="2" t="n">
         <f aca="false">A735 +1000</f>
@@ -16773,7 +16803,7 @@
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E736" s="2" t="n">
         <f aca="false">A736 +1000</f>
@@ -16791,7 +16821,7 @@
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="E737" s="2" t="n">
         <f aca="false">A737 +1000</f>
@@ -16809,7 +16839,7 @@
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="E738" s="2" t="n">
         <f aca="false">A738 +1000</f>
@@ -16827,7 +16857,7 @@
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E739" s="2" t="n">
         <f aca="false">A739 +1000</f>
@@ -16845,7 +16875,7 @@
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E740" s="2" t="n">
         <f aca="false">A740 +1000</f>
@@ -16863,7 +16893,7 @@
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E741" s="2" t="n">
         <f aca="false">A741 +1000</f>
@@ -16881,7 +16911,7 @@
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E742" s="2" t="n">
         <f aca="false">A742 +1000</f>
@@ -16899,7 +16929,7 @@
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="E743" s="2" t="n">
         <f aca="false">A743 +1000</f>
@@ -16917,7 +16947,7 @@
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E744" s="2" t="n">
         <f aca="false">A744 +1000</f>
@@ -16935,7 +16965,7 @@
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E745" s="2" t="n">
         <f aca="false">A745 +1000</f>
@@ -16953,7 +16983,7 @@
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="E746" s="2" t="n">
         <f aca="false">A746 +1000</f>
@@ -16971,7 +17001,7 @@
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="E747" s="2" t="n">
         <f aca="false">A747 +1000</f>
@@ -16989,7 +17019,7 @@
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="E748" s="2" t="n">
         <f aca="false">A748 +1000</f>
@@ -17007,7 +17037,7 @@
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E749" s="2" t="n">
         <f aca="false">A749 +1000</f>
@@ -17025,7 +17055,7 @@
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="E750" s="2" t="n">
         <f aca="false">A750 +1000</f>
@@ -17043,7 +17073,7 @@
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E751" s="2" t="n">
         <f aca="false">A751 +1000</f>
@@ -17061,7 +17091,7 @@
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E752" s="2" t="n">
         <f aca="false">A752 +1000</f>
@@ -17079,7 +17109,7 @@
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="E753" s="2" t="n">
         <f aca="false">A753 +1000</f>
@@ -17097,7 +17127,7 @@
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="E754" s="2" t="n">
         <f aca="false">A754 +1000</f>
@@ -17115,7 +17145,7 @@
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="E755" s="2" t="n">
         <f aca="false">A755 +1000</f>
@@ -17133,7 +17163,7 @@
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="E756" s="2" t="n">
         <f aca="false">A756 +1000</f>
@@ -17151,7 +17181,7 @@
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E757" s="2" t="n">
         <f aca="false">A757 +1000</f>
@@ -17169,7 +17199,7 @@
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="E758" s="2" t="n">
         <f aca="false">A758 +1000</f>
@@ -17187,7 +17217,7 @@
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="E759" s="2" t="n">
         <f aca="false">A759 +1000</f>
@@ -17205,7 +17235,7 @@
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E760" s="2" t="n">
         <f aca="false">A760 +1000</f>
@@ -17223,7 +17253,7 @@
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E761" s="2" t="n">
         <f aca="false">A761 +1000</f>
@@ -17241,7 +17271,7 @@
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E762" s="2" t="n">
         <f aca="false">A762 +1000</f>
@@ -17259,7 +17289,7 @@
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="E763" s="2" t="n">
         <f aca="false">A763 +1000</f>
@@ -17277,7 +17307,7 @@
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E764" s="2" t="n">
         <f aca="false">A764 +1000</f>
@@ -17295,7 +17325,7 @@
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E765" s="2" t="n">
         <f aca="false">A765 +1000</f>
@@ -17313,7 +17343,7 @@
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="E766" s="2" t="n">
         <f aca="false">A766 +1000</f>
@@ -17331,7 +17361,7 @@
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E767" s="2" t="n">
         <f aca="false">A767 +1000</f>
@@ -17349,7 +17379,7 @@
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="E768" s="2" t="n">
         <f aca="false">A768 +1000</f>
@@ -17367,7 +17397,7 @@
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E769" s="2" t="n">
         <f aca="false">A769 +1000</f>
@@ -17385,7 +17415,7 @@
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="E770" s="2" t="n">
         <f aca="false">A770 +1000</f>
@@ -17403,7 +17433,7 @@
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="E771" s="2" t="n">
         <f aca="false">A771 +1000</f>
@@ -17421,7 +17451,7 @@
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="E772" s="2" t="n">
         <f aca="false">A772 +1000</f>
@@ -17439,7 +17469,7 @@
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E773" s="2" t="n">
         <f aca="false">A773 +1000</f>
@@ -17457,7 +17487,7 @@
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="E774" s="2" t="n">
         <f aca="false">A774 +1000</f>
@@ -17475,7 +17505,7 @@
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E775" s="2" t="n">
         <f aca="false">A775 +1000</f>
@@ -17493,7 +17523,7 @@
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E776" s="2" t="n">
         <f aca="false">A776 +1000</f>
@@ -17511,7 +17541,7 @@
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="E777" s="2" t="n">
         <f aca="false">A777 +1000</f>
@@ -17529,7 +17559,7 @@
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="E778" s="2" t="n">
         <f aca="false">A778 +1000</f>
@@ -17547,7 +17577,7 @@
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="E779" s="2" t="n">
         <f aca="false">A779 +1000</f>
@@ -17565,7 +17595,7 @@
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="E780" s="2" t="n">
         <f aca="false">A780 +1000</f>
@@ -17583,7 +17613,7 @@
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E781" s="2" t="n">
         <f aca="false">A781 +1000</f>
@@ -17601,7 +17631,7 @@
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E782" s="2" t="n">
         <f aca="false">A782 +1000</f>
@@ -17619,7 +17649,7 @@
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="E783" s="2" t="n">
         <f aca="false">A783 +1000</f>
@@ -17637,7 +17667,7 @@
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E784" s="2" t="n">
         <f aca="false">A784 +1000</f>
@@ -17655,7 +17685,7 @@
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E785" s="2" t="n">
         <f aca="false">A785 +1000</f>
@@ -17673,7 +17703,7 @@
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E786" s="2" t="n">
         <f aca="false">A786 +1000</f>
@@ -17691,7 +17721,7 @@
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="E787" s="2" t="n">
         <f aca="false">A787 +1000</f>
@@ -17709,7 +17739,7 @@
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E788" s="2" t="n">
         <f aca="false">A788 +1000</f>
@@ -17727,7 +17757,7 @@
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E789" s="2" t="n">
         <f aca="false">A789 +1000</f>
@@ -17745,7 +17775,7 @@
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E790" s="2" t="n">
         <f aca="false">A790 +1000</f>
@@ -17763,7 +17793,7 @@
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="E791" s="2" t="n">
         <f aca="false">A791 +1000</f>
@@ -17781,7 +17811,7 @@
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="E792" s="2" t="n">
         <f aca="false">A792 +1000</f>
@@ -17799,7 +17829,7 @@
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E793" s="2" t="n">
         <f aca="false">A793 +1000</f>
@@ -17817,7 +17847,7 @@
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="E794" s="2" t="n">
         <f aca="false">A794 +1000</f>
@@ -17835,7 +17865,7 @@
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="E795" s="2" t="n">
         <f aca="false">A795 +1000</f>
@@ -17853,7 +17883,7 @@
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="E796" s="2" t="n">
         <f aca="false">A796 +1000</f>
@@ -17871,7 +17901,7 @@
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="E797" s="2" t="n">
         <f aca="false">A797 +1000</f>
@@ -17889,7 +17919,7 @@
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E798" s="2" t="n">
         <f aca="false">A798 +1000</f>
@@ -17907,7 +17937,7 @@
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="E799" s="2" t="n">
         <f aca="false">A799 +1000</f>
@@ -17925,7 +17955,7 @@
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="E800" s="2" t="n">
         <f aca="false">A800 +1000</f>
@@ -17943,7 +17973,7 @@
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E801" s="2" t="n">
         <f aca="false">A801 +1000</f>
@@ -17961,7 +17991,7 @@
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="E802" s="2" t="n">
         <f aca="false">A802 +1000</f>
@@ -17979,7 +18009,7 @@
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="E803" s="2" t="n">
         <f aca="false">A803 +1000</f>
@@ -17997,7 +18027,7 @@
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E804" s="2" t="n">
         <f aca="false">A804 +1000</f>
@@ -18015,7 +18045,7 @@
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E805" s="2" t="n">
         <f aca="false">A805 +1000</f>
@@ -18033,7 +18063,7 @@
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E806" s="2" t="n">
         <f aca="false">A806 +1000</f>
@@ -18051,7 +18081,7 @@
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="E807" s="2" t="n">
         <f aca="false">A807 +1000</f>
@@ -18069,7 +18099,7 @@
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="E808" s="2" t="n">
         <f aca="false">A808 +1000</f>
@@ -18087,7 +18117,7 @@
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E809" s="2" t="n">
         <f aca="false">A809 +1000</f>
@@ -18105,7 +18135,7 @@
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="E810" s="2" t="n">
         <f aca="false">A810 +1000</f>
@@ -18123,7 +18153,7 @@
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="E811" s="2" t="n">
         <f aca="false">A811 +1000</f>
@@ -18141,7 +18171,7 @@
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E812" s="2" t="n">
         <f aca="false">A812 +1000</f>
@@ -18159,7 +18189,7 @@
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E813" s="2" t="n">
         <f aca="false">A813 +1000</f>
@@ -18177,7 +18207,7 @@
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="E814" s="2" t="n">
         <f aca="false">A814 +1000</f>
@@ -18195,7 +18225,7 @@
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E815" s="2" t="n">
         <f aca="false">A815 +1000</f>
@@ -18213,7 +18243,7 @@
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="E816" s="2" t="n">
         <f aca="false">A816 +1000</f>
@@ -18231,7 +18261,7 @@
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E817" s="2" t="n">
         <f aca="false">A817 +1000</f>
@@ -18249,7 +18279,7 @@
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="E818" s="2" t="n">
         <f aca="false">A818 +1000</f>
@@ -18267,7 +18297,7 @@
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="E819" s="2" t="n">
         <f aca="false">A819 +1000</f>
@@ -18285,7 +18315,7 @@
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E820" s="2" t="n">
         <f aca="false">A820 +1000</f>
@@ -18303,7 +18333,7 @@
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E821" s="2" t="n">
         <f aca="false">A821 +1000</f>
@@ -18321,7 +18351,7 @@
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E822" s="2" t="n">
         <f aca="false">A822 +1000</f>
@@ -18339,7 +18369,7 @@
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="E823" s="2" t="n">
         <f aca="false">A823 +1000</f>
@@ -18357,7 +18387,7 @@
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="E824" s="2" t="n">
         <f aca="false">A824 +1000</f>
@@ -18375,7 +18405,7 @@
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E825" s="2" t="n">
         <f aca="false">A825 +1000</f>
@@ -18393,7 +18423,7 @@
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="E826" s="2" t="n">
         <f aca="false">A826 +1000</f>
@@ -18411,7 +18441,7 @@
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="E827" s="2" t="n">
         <f aca="false">A827 +1000</f>
@@ -18429,7 +18459,7 @@
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="E828" s="2" t="n">
         <f aca="false">A828 +1000</f>
@@ -18447,7 +18477,7 @@
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E829" s="2" t="n">
         <f aca="false">A829 +1000</f>
@@ -18465,7 +18495,7 @@
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="E830" s="2" t="n">
         <f aca="false">A830 +1000</f>
@@ -18483,7 +18513,7 @@
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E831" s="2" t="n">
         <f aca="false">A831 +1000</f>
@@ -18501,7 +18531,7 @@
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="E832" s="2" t="n">
         <f aca="false">A832 +1000</f>
@@ -18519,7 +18549,7 @@
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E833" s="2" t="n">
         <f aca="false">A833 +1000</f>
@@ -18537,7 +18567,7 @@
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="E834" s="2" t="n">
         <f aca="false">A834 +1000</f>
@@ -18555,7 +18585,7 @@
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="E835" s="2" t="n">
         <f aca="false">A835 +1000</f>
@@ -18573,7 +18603,7 @@
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E836" s="2" t="n">
         <f aca="false">A836 +1000</f>
@@ -18591,7 +18621,7 @@
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="E837" s="2" t="n">
         <f aca="false">A837 +1000</f>
@@ -18609,7 +18639,7 @@
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="E838" s="2" t="n">
         <f aca="false">A838 +1000</f>
@@ -18627,7 +18657,7 @@
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="E839" s="2" t="n">
         <f aca="false">A839 +1000</f>
@@ -18645,7 +18675,7 @@
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E840" s="2" t="n">
         <f aca="false">A840 +1000</f>
@@ -18663,7 +18693,7 @@
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E841" s="2" t="n">
         <f aca="false">A841 +1000</f>
@@ -18681,7 +18711,7 @@
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E842" s="2" t="n">
         <f aca="false">A842 +1000</f>
@@ -18699,7 +18729,7 @@
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="E843" s="2" t="n">
         <f aca="false">A843 +1000</f>
@@ -18717,7 +18747,7 @@
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="E844" s="2" t="n">
         <f aca="false">A844 +1000</f>
@@ -18735,7 +18765,7 @@
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E845" s="2" t="n">
         <f aca="false">A845 +1000</f>
@@ -18753,7 +18783,7 @@
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E846" s="2" t="n">
         <f aca="false">A846 +1000</f>
@@ -18771,7 +18801,7 @@
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B847" s="3" t="s">
         <v>9</v>
@@ -18780,7 +18810,7 @@
         <v>9</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E847" s="2" t="n">
         <f aca="false">A847 +1000</f>
@@ -18798,7 +18828,7 @@
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E848" s="2" t="n">
         <f aca="false">A848 +1000</f>
@@ -18816,7 +18846,7 @@
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="E849" s="2" t="n">
         <f aca="false">A849 +1000</f>
@@ -18834,7 +18864,7 @@
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="E850" s="2" t="n">
         <f aca="false">A850 +1000</f>
@@ -18852,7 +18882,7 @@
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="E851" s="2" t="n">
         <f aca="false">A851 +1000</f>
@@ -18870,7 +18900,7 @@
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="E852" s="2" t="n">
         <f aca="false">A852 +1000</f>
@@ -18888,7 +18918,7 @@
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="E853" s="2" t="n">
         <f aca="false">A853 +1000</f>
@@ -18906,7 +18936,7 @@
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E854" s="2" t="n">
         <f aca="false">A854 +1000</f>
@@ -18924,7 +18954,7 @@
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="E855" s="2" t="n">
         <f aca="false">A855 +1000</f>
@@ -18942,7 +18972,7 @@
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E856" s="2" t="n">
         <f aca="false">A856 +1000</f>
@@ -18960,7 +18990,7 @@
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="E857" s="2" t="n">
         <f aca="false">A857 +1000</f>
@@ -18978,7 +19008,7 @@
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="E858" s="2" t="n">
         <f aca="false">A858 +1000</f>
@@ -18996,7 +19026,7 @@
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="E859" s="2" t="n">
         <f aca="false">A859 +1000</f>
@@ -19014,7 +19044,7 @@
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E860" s="2" t="n">
         <f aca="false">A860 +1000</f>
@@ -19032,7 +19062,7 @@
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E861" s="2" t="n">
         <f aca="false">A861 +1000</f>
@@ -19050,7 +19080,7 @@
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E862" s="2" t="n">
         <f aca="false">A862 +1000</f>
@@ -19068,7 +19098,7 @@
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="E863" s="2" t="n">
         <f aca="false">A863 +1000</f>
@@ -19086,7 +19116,7 @@
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E864" s="2" t="n">
         <f aca="false">A864 +1000</f>
@@ -19104,7 +19134,7 @@
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="E865" s="2" t="n">
         <f aca="false">A865 +1000</f>
@@ -19122,7 +19152,7 @@
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="E866" s="2" t="n">
         <f aca="false">A866 +1000</f>
@@ -19140,7 +19170,7 @@
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E867" s="2" t="n">
         <f aca="false">A867 +1000</f>
@@ -19158,7 +19188,7 @@
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="E868" s="2" t="n">
         <f aca="false">A868 +1000</f>
@@ -19176,7 +19206,7 @@
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E869" s="2" t="n">
         <f aca="false">A869 +1000</f>
@@ -19194,7 +19224,7 @@
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="E870" s="2" t="n">
         <f aca="false">A870 +1000</f>
@@ -19212,7 +19242,7 @@
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E871" s="2" t="n">
         <f aca="false">A871 +1000</f>
@@ -19230,7 +19260,7 @@
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E872" s="2" t="n">
         <f aca="false">A872 +1000</f>
@@ -19248,7 +19278,7 @@
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E873" s="2" t="n">
         <f aca="false">A873 +1000</f>
@@ -19266,7 +19296,7 @@
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E874" s="2" t="n">
         <f aca="false">A874 +1000</f>
@@ -19284,7 +19314,7 @@
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="E875" s="2" t="n">
         <f aca="false">A875 +1000</f>
@@ -19302,7 +19332,7 @@
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="E876" s="2" t="n">
         <f aca="false">A876 +1000</f>
@@ -19320,7 +19350,7 @@
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E877" s="2" t="n">
         <f aca="false">A877 +1000</f>
@@ -19338,7 +19368,7 @@
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="E878" s="2" t="n">
         <f aca="false">A878 +1000</f>
@@ -19356,7 +19386,7 @@
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="E879" s="2" t="n">
         <f aca="false">A879 +1000</f>
@@ -19374,7 +19404,7 @@
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="E880" s="2" t="n">
         <f aca="false">A880 +1000</f>
@@ -19392,7 +19422,7 @@
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="E881" s="2" t="n">
         <f aca="false">A881 +1000</f>
@@ -19410,7 +19440,7 @@
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="E882" s="2" t="n">
         <f aca="false">A882 +1000</f>
@@ -19428,7 +19458,7 @@
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E883" s="2" t="n">
         <f aca="false">A883 +1000</f>
@@ -19446,7 +19476,7 @@
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="E884" s="2" t="n">
         <f aca="false">A884 +1000</f>
@@ -19464,7 +19494,7 @@
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="E885" s="2" t="n">
         <f aca="false">A885 +1000</f>
@@ -19482,7 +19512,7 @@
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E886" s="2" t="n">
         <f aca="false">A886 +1000</f>
@@ -19500,7 +19530,7 @@
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="E887" s="2" t="n">
         <f aca="false">A887 +1000</f>
@@ -19518,7 +19548,7 @@
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="E888" s="2" t="n">
         <f aca="false">A888 +1000</f>
@@ -19536,7 +19566,7 @@
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E889" s="2" t="n">
         <f aca="false">A889 +1000</f>
@@ -19554,7 +19584,7 @@
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="E890" s="2" t="n">
         <f aca="false">A890 +1000</f>
@@ -19572,7 +19602,7 @@
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E891" s="2" t="n">
         <f aca="false">A891 +1000</f>
@@ -19590,7 +19620,7 @@
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E892" s="2" t="n">
         <f aca="false">A892 +1000</f>
@@ -19608,7 +19638,7 @@
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E893" s="2" t="n">
         <f aca="false">A893 +1000</f>
@@ -19626,7 +19656,7 @@
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="E894" s="2" t="n">
         <f aca="false">A894 +1000</f>
@@ -19644,7 +19674,7 @@
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E895" s="2" t="n">
         <f aca="false">A895 +1000</f>
@@ -19662,7 +19692,7 @@
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="E896" s="2" t="n">
         <f aca="false">A896 +1000</f>
@@ -19680,7 +19710,7 @@
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="E897" s="2" t="n">
         <f aca="false">A897 +1000</f>
@@ -19698,7 +19728,7 @@
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E898" s="2" t="n">
         <f aca="false">A898 +1000</f>
@@ -19716,7 +19746,7 @@
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="E899" s="2" t="n">
         <f aca="false">A899 +1000</f>
@@ -19734,7 +19764,7 @@
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E900" s="2" t="n">
         <f aca="false">A900 +1000</f>
@@ -19752,7 +19782,7 @@
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E901" s="2" t="n">
         <f aca="false">A901 +1000</f>
@@ -19770,7 +19800,7 @@
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="E902" s="2" t="n">
         <f aca="false">A902 +1000</f>
@@ -19788,7 +19818,7 @@
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E903" s="2" t="n">
         <f aca="false">A903 +1000</f>
@@ -19806,7 +19836,7 @@
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E904" s="2" t="n">
         <f aca="false">A904 +1000</f>
@@ -19824,7 +19854,7 @@
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E905" s="2" t="n">
         <f aca="false">A905 +1000</f>
@@ -19842,7 +19872,7 @@
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="E906" s="2" t="n">
         <f aca="false">A906 +1000</f>
@@ -19860,7 +19890,7 @@
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E907" s="2" t="n">
         <f aca="false">A907 +1000</f>
@@ -19878,7 +19908,7 @@
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="E908" s="2" t="n">
         <f aca="false">A908 +1000</f>
@@ -19896,7 +19926,7 @@
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="E909" s="2" t="n">
         <f aca="false">A909 +1000</f>
@@ -19914,7 +19944,7 @@
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E910" s="2" t="n">
         <f aca="false">A910 +1000</f>
@@ -19932,7 +19962,7 @@
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E911" s="2" t="n">
         <f aca="false">A911 +1000</f>
@@ -19950,7 +19980,7 @@
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E912" s="2" t="n">
         <f aca="false">A912 +1000</f>
@@ -19968,7 +19998,7 @@
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E913" s="2" t="n">
         <f aca="false">A913 +1000</f>
@@ -19986,7 +20016,7 @@
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E914" s="2" t="n">
         <f aca="false">A914 +1000</f>
@@ -20004,7 +20034,7 @@
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E915" s="2" t="n">
         <f aca="false">A915 +1000</f>
@@ -20022,7 +20052,7 @@
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="1" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="E916" s="2" t="n">
         <f aca="false">A916 +1000</f>
@@ -20040,7 +20070,7 @@
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E917" s="2" t="n">
         <f aca="false">A917 +1000</f>
@@ -20058,7 +20088,7 @@
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E918" s="2" t="n">
         <f aca="false">A918 +1000</f>
@@ -20076,7 +20106,7 @@
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E919" s="2" t="n">
         <f aca="false">A919 +1000</f>
@@ -20094,7 +20124,7 @@
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="1" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E920" s="2" t="n">
         <f aca="false">A920 +1000</f>
@@ -20112,7 +20142,7 @@
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="1" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E921" s="2" t="n">
         <f aca="false">A921 +1000</f>
@@ -20130,7 +20160,7 @@
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E922" s="2" t="n">
         <f aca="false">A922 +1000</f>
@@ -20148,7 +20178,7 @@
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="1" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E923" s="2" t="n">
         <f aca="false">A923 +1000</f>
@@ -20166,7 +20196,7 @@
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="E924" s="2" t="n">
         <f aca="false">A924 +1000</f>
@@ -20184,7 +20214,7 @@
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E925" s="2" t="n">
         <f aca="false">A925 +1000</f>
@@ -20202,7 +20232,7 @@
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="E926" s="2" t="n">
         <f aca="false">A926 +1000</f>
@@ -20220,7 +20250,7 @@
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="E927" s="2" t="n">
         <f aca="false">A927 +1000</f>
@@ -20238,7 +20268,7 @@
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="1" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E928" s="2" t="n">
         <f aca="false">A928 +1000</f>
@@ -20256,7 +20286,7 @@
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="1" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="E929" s="2" t="n">
         <f aca="false">A929 +1000</f>
@@ -20274,7 +20304,7 @@
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="1" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="E930" s="2" t="n">
         <f aca="false">A930 +1000</f>
@@ -20292,7 +20322,7 @@
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E931" s="2" t="n">
         <f aca="false">A931 +1000</f>
@@ -20310,7 +20340,7 @@
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="E932" s="2" t="n">
         <f aca="false">A932 +1000</f>
@@ -20328,7 +20358,7 @@
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="E933" s="2" t="n">
         <f aca="false">A933 +1000</f>
@@ -20346,7 +20376,7 @@
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="1" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E934" s="2" t="n">
         <f aca="false">A934 +1000</f>
@@ -20364,7 +20394,7 @@
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="E935" s="2" t="n">
         <f aca="false">A935 +1000</f>
@@ -20382,7 +20412,7 @@
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E936" s="2" t="n">
         <f aca="false">A936 +1000</f>
@@ -20400,7 +20430,7 @@
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="E937" s="2" t="n">
         <f aca="false">A937 +1000</f>
@@ -20418,7 +20448,7 @@
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="1" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="E938" s="2" t="n">
         <f aca="false">A938 +1000</f>
@@ -20436,7 +20466,7 @@
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="E939" s="2" t="n">
         <f aca="false">A939 +1000</f>
@@ -20454,7 +20484,7 @@
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="1" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="E940" s="2" t="n">
         <f aca="false">A940 +1000</f>
@@ -20472,7 +20502,7 @@
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E941" s="2" t="n">
         <f aca="false">A941 +1000</f>
@@ -20490,7 +20520,7 @@
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="1" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="E942" s="2" t="n">
         <f aca="false">A942 +1000</f>
@@ -20508,7 +20538,7 @@
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="1" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E943" s="2" t="n">
         <f aca="false">A943 +1000</f>
@@ -20526,7 +20556,7 @@
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="1" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="E944" s="2" t="n">
         <f aca="false">A944 +1000</f>
@@ -20544,7 +20574,7 @@
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E945" s="2" t="n">
         <f aca="false">A945 +1000</f>
@@ -20562,7 +20592,7 @@
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="E946" s="2" t="n">
         <f aca="false">A946 +1000</f>
@@ -20580,7 +20610,7 @@
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="E947" s="2" t="n">
         <f aca="false">A947 +1000</f>
@@ -20598,7 +20628,7 @@
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="E948" s="2" t="n">
         <f aca="false">A948 +1000</f>
@@ -20616,7 +20646,7 @@
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E949" s="2" t="n">
         <f aca="false">A949 +1000</f>
@@ -20634,7 +20664,7 @@
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="E950" s="2" t="n">
         <f aca="false">A950 +1000</f>
@@ -20652,7 +20682,7 @@
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="E951" s="2" t="n">
         <f aca="false">A951 +1000</f>
@@ -20670,7 +20700,7 @@
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="E952" s="2" t="n">
         <f aca="false">A952 +1000</f>
@@ -20688,7 +20718,7 @@
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E953" s="2" t="n">
         <f aca="false">A953 +1000</f>
@@ -20706,7 +20736,7 @@
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="E954" s="2" t="n">
         <f aca="false">A954 +1000</f>
@@ -20724,7 +20754,7 @@
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="E955" s="2" t="n">
         <f aca="false">A955 +1000</f>
@@ -20742,7 +20772,7 @@
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="E956" s="2" t="n">
         <f aca="false">A956 +1000</f>
@@ -20760,7 +20790,7 @@
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="E957" s="2" t="n">
         <f aca="false">A957 +1000</f>
@@ -20778,7 +20808,7 @@
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="E958" s="2" t="n">
         <f aca="false">A958 +1000</f>
@@ -20796,7 +20826,7 @@
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="E959" s="2" t="n">
         <f aca="false">A959 +1000</f>
@@ -20814,7 +20844,7 @@
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="E960" s="2" t="n">
         <f aca="false">A960 +1000</f>
@@ -20832,7 +20862,7 @@
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E961" s="2" t="n">
         <f aca="false">A961 +1000</f>
@@ -20850,7 +20880,7 @@
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E962" s="2" t="n">
         <f aca="false">A962 +1000</f>
@@ -20868,7 +20898,7 @@
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E963" s="2" t="n">
         <f aca="false">A963 +1000</f>
@@ -20886,7 +20916,7 @@
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="1" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="E964" s="2" t="n">
         <f aca="false">A964 +1000</f>
@@ -20904,7 +20934,7 @@
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E965" s="2" t="n">
         <f aca="false">A965 +1000</f>
@@ -20922,7 +20952,7 @@
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E966" s="2" t="n">
         <f aca="false">A966 +1000</f>
@@ -20940,7 +20970,7 @@
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="1" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="E967" s="2" t="n">
         <f aca="false">A967 +1000</f>
@@ -20958,7 +20988,7 @@
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="1" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="E968" s="2" t="n">
         <f aca="false">A968 +1000</f>
@@ -20976,7 +21006,7 @@
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E969" s="2" t="n">
         <f aca="false">A969 +1000</f>
@@ -20994,7 +21024,7 @@
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="E970" s="2" t="n">
         <f aca="false">A970 +1000</f>
@@ -21012,7 +21042,7 @@
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="E971" s="2" t="n">
         <f aca="false">A971 +1000</f>
@@ -21030,7 +21060,7 @@
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="E972" s="2" t="n">
         <f aca="false">A972 +1000</f>
@@ -21048,7 +21078,7 @@
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="1" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E973" s="2" t="n">
         <f aca="false">A973 +1000</f>
@@ -21066,7 +21096,7 @@
     </row>
     <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E974" s="2" t="n">
         <f aca="false">A974 +1000</f>
@@ -21090,7 +21120,7 @@
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E975" s="2" t="n">
         <f aca="false">A975 +1000</f>
@@ -21108,7 +21138,7 @@
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="1" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="E976" s="2" t="n">
         <f aca="false">A976 +1000</f>
@@ -21126,7 +21156,7 @@
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="1" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="E977" s="2" t="n">
         <f aca="false">A977 +1000</f>
@@ -21144,7 +21174,7 @@
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="E978" s="2" t="n">
         <f aca="false">A978 +1000</f>
@@ -21162,7 +21192,7 @@
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="1" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="E979" s="2" t="n">
         <f aca="false">A979 +1000</f>
@@ -21180,7 +21210,7 @@
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="E980" s="2" t="n">
         <f aca="false">A980 +1000</f>
@@ -21198,7 +21228,7 @@
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="1" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="E981" s="2" t="n">
         <f aca="false">A981 +1000</f>
@@ -21216,7 +21246,7 @@
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="E982" s="2" t="n">
         <f aca="false">A982 +1000</f>
@@ -21234,7 +21264,7 @@
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="1" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="E983" s="2" t="n">
         <f aca="false">A983 +1000</f>
@@ -21252,7 +21282,7 @@
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E984" s="2" t="n">
         <f aca="false">A984 +1000</f>
@@ -21270,7 +21300,7 @@
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="1" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="E985" s="2" t="n">
         <f aca="false">A985 +1000</f>
@@ -21288,7 +21318,7 @@
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E986" s="2" t="n">
         <f aca="false">A986 +1000</f>
@@ -21306,7 +21336,7 @@
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="1" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="E987" s="2" t="n">
         <f aca="false">A987 +1000</f>
@@ -21324,7 +21354,7 @@
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="1" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="E988" s="2" t="n">
         <f aca="false">A988 +1000</f>
@@ -21342,7 +21372,7 @@
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="1" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="E989" s="2" t="n">
         <f aca="false">A989 +1000</f>
@@ -21360,7 +21390,7 @@
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="E990" s="2" t="n">
         <f aca="false">A990 +1000</f>
@@ -21378,7 +21408,7 @@
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="1" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E991" s="2" t="n">
         <f aca="false">A991 +1000</f>
@@ -21396,7 +21426,7 @@
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="E992" s="2" t="n">
         <f aca="false">A992 +1000</f>
@@ -21414,7 +21444,7 @@
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="E993" s="2" t="n">
         <f aca="false">A993 +1000</f>
@@ -21432,7 +21462,7 @@
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="1" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="E994" s="2" t="n">
         <f aca="false">A994 +1000</f>
@@ -21450,7 +21480,7 @@
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E995" s="2" t="n">
         <f aca="false">A995 +1000</f>
@@ -21468,7 +21498,7 @@
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E996" s="2" t="n">
         <f aca="false">A996 +1000</f>
@@ -21486,7 +21516,7 @@
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E997" s="2" t="n">
         <f aca="false">A997 +1000</f>
@@ -21504,7 +21534,7 @@
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="1" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="E998" s="2" t="n">
         <f aca="false">A998 +1000</f>
@@ -21522,7 +21552,7 @@
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="1" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="E999" s="2" t="n">
         <f aca="false">A999 +1000</f>
@@ -21540,7 +21570,7 @@
     </row>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="1" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E1000" s="2" t="n">
         <f aca="false">A1000 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="1012">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -662,6 +662,9 @@
   </si>
   <si>
     <t xml:space="preserve">0208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trie</t>
   </si>
   <si>
     <t xml:space="preserve">0209</t>
@@ -3364,7 +3367,9 @@
         <f aca="false">I4 +1000</f>
         <v>3003</v>
       </c>
-      <c r="Q4" s="2"/>
+      <c r="Q4" s="2" t="n">
+        <v>4004</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -3382,7 +3387,9 @@
         <f aca="false">I5 +1000</f>
         <v>3004</v>
       </c>
-      <c r="Q5" s="2"/>
+      <c r="Q5" s="2" t="n">
+        <v>4005</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
@@ -3400,7 +3407,9 @@
         <f aca="false">I6 +1000</f>
         <v>3005</v>
       </c>
-      <c r="Q6" s="2"/>
+      <c r="Q6" s="2" t="n">
+        <v>4006</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -3418,7 +3427,9 @@
         <f aca="false">I7 +1000</f>
         <v>3006</v>
       </c>
-      <c r="Q7" s="2"/>
+      <c r="Q7" s="2" t="n">
+        <v>4007</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -3436,7 +3447,9 @@
         <f aca="false">I8 +1000</f>
         <v>3007</v>
       </c>
-      <c r="Q8" s="2"/>
+      <c r="Q8" s="2" t="n">
+        <v>4008</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -3463,7 +3476,9 @@
         <f aca="false">I9 +1000</f>
         <v>3008</v>
       </c>
-      <c r="Q9" s="2"/>
+      <c r="Q9" s="2" t="n">
+        <v>4009</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
@@ -3481,7 +3496,9 @@
         <f aca="false">I10 +1000</f>
         <v>3009</v>
       </c>
-      <c r="Q10" s="2"/>
+      <c r="Q10" s="2" t="n">
+        <v>4010</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
@@ -3499,7 +3516,9 @@
         <f aca="false">I11 +1000</f>
         <v>3010</v>
       </c>
-      <c r="Q11" s="2"/>
+      <c r="Q11" s="2" t="n">
+        <v>4011</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -3517,7 +3536,9 @@
         <f aca="false">I12 +1000</f>
         <v>3011</v>
       </c>
-      <c r="Q12" s="2"/>
+      <c r="Q12" s="2" t="n">
+        <v>4012</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -3535,7 +3556,9 @@
         <f aca="false">I13 +1000</f>
         <v>3012</v>
       </c>
-      <c r="Q13" s="2"/>
+      <c r="Q13" s="2" t="n">
+        <v>4013</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -3553,7 +3576,9 @@
         <f aca="false">I14 +1000</f>
         <v>3013</v>
       </c>
-      <c r="Q14" s="2"/>
+      <c r="Q14" s="2" t="n">
+        <v>4014</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
@@ -3571,7 +3596,9 @@
         <f aca="false">I15 +1000</f>
         <v>3014</v>
       </c>
-      <c r="Q15" s="2"/>
+      <c r="Q15" s="2" t="n">
+        <v>4015</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
@@ -3589,7 +3616,9 @@
         <f aca="false">I16 +1000</f>
         <v>3015</v>
       </c>
-      <c r="Q16" s="2"/>
+      <c r="Q16" s="2" t="n">
+        <v>4016</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -3607,7 +3636,9 @@
         <f aca="false">I17 +1000</f>
         <v>3016</v>
       </c>
-      <c r="Q17" s="2"/>
+      <c r="Q17" s="2" t="n">
+        <v>4017</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
@@ -7102,6 +7133,15 @@
       <c r="A209" s="1" t="s">
         <v>213</v>
       </c>
+      <c r="B209" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="E209" s="2" t="n">
         <f aca="false">A209 +1000</f>
         <v>1208</v>
@@ -7118,7 +7158,7 @@
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E210" s="2" t="n">
         <f aca="false">A210 +1000</f>
@@ -7136,7 +7176,7 @@
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E211" s="2" t="n">
         <f aca="false">A211 +1000</f>
@@ -7154,7 +7194,7 @@
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E212" s="2" t="n">
         <f aca="false">A212 +1000</f>
@@ -7172,7 +7212,7 @@
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E213" s="2" t="n">
         <f aca="false">A213 +1000</f>
@@ -7190,7 +7230,7 @@
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E214" s="2" t="n">
         <f aca="false">A214 +1000</f>
@@ -7208,7 +7248,7 @@
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B215" s="3"/>
       <c r="E215" s="2" t="n">
@@ -7227,7 +7267,7 @@
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>9</v>
@@ -7251,7 +7291,7 @@
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E217" s="2" t="n">
         <f aca="false">A217 +1000</f>
@@ -7269,7 +7309,7 @@
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>9</v>
@@ -7293,7 +7333,7 @@
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E219" s="2" t="n">
         <f aca="false">A219 +1000</f>
@@ -7311,7 +7351,7 @@
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E220" s="2" t="n">
         <f aca="false">A220 +1000</f>
@@ -7329,7 +7369,7 @@
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E221" s="2" t="n">
         <f aca="false">A221 +1000</f>
@@ -7347,7 +7387,7 @@
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E222" s="2" t="n">
         <f aca="false">A222 +1000</f>
@@ -7365,7 +7405,7 @@
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E223" s="2" t="n">
         <f aca="false">A223 +1000</f>
@@ -7383,7 +7423,7 @@
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E224" s="2" t="n">
         <f aca="false">A224 +1000</f>
@@ -7401,7 +7441,7 @@
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E225" s="2" t="n">
         <f aca="false">A225 +1000</f>
@@ -7419,7 +7459,7 @@
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E226" s="2" t="n">
         <f aca="false">A226 +1000</f>
@@ -7437,7 +7477,7 @@
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E227" s="2" t="n">
         <f aca="false">A227 +1000</f>
@@ -7455,7 +7495,7 @@
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E228" s="2" t="n">
         <f aca="false">A228 +1000</f>
@@ -7473,7 +7513,7 @@
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E229" s="2" t="n">
         <f aca="false">A229 +1000</f>
@@ -7491,7 +7531,7 @@
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E230" s="2" t="n">
         <f aca="false">A230 +1000</f>
@@ -7509,7 +7549,7 @@
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>9</v>
@@ -7518,7 +7558,7 @@
         <v>9</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E231" s="2" t="n">
         <f aca="false">A231 +1000</f>
@@ -7542,7 +7582,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">A232 +1000</f>
@@ -7560,7 +7600,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">A233 +1000</f>
@@ -7578,7 +7618,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">A234 +1000</f>
@@ -7596,7 +7636,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">A235 +1000</f>
@@ -7614,7 +7654,7 @@
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>9</v>
@@ -7623,7 +7663,7 @@
         <v>9</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">A236 +1000</f>
@@ -7641,7 +7681,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">A237 +1000</f>
@@ -7659,7 +7699,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">A238 +1000</f>
@@ -7677,7 +7717,7 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>9</v>
@@ -7701,7 +7741,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">A240 +1000</f>
@@ -7719,7 +7759,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">A241 +1000</f>
@@ -7737,7 +7777,7 @@
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">A242 +1000</f>
@@ -7755,7 +7795,7 @@
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">A243 +1000</f>
@@ -7773,7 +7813,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">A244 +1000</f>
@@ -7791,7 +7831,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">A245 +1000</f>
@@ -7809,7 +7849,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E246" s="2" t="n">
         <f aca="false">A246 +1000</f>
@@ -7827,7 +7867,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E247" s="2" t="n">
         <f aca="false">A247 +1000</f>
@@ -7845,7 +7885,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E248" s="2" t="n">
         <f aca="false">A248 +1000</f>
@@ -7863,7 +7903,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E249" s="2" t="n">
         <f aca="false">A249 +1000</f>
@@ -7881,7 +7921,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E250" s="2" t="n">
         <f aca="false">A250 +1000</f>
@@ -7899,7 +7939,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E251" s="2" t="n">
         <f aca="false">A251 +1000</f>
@@ -7917,7 +7957,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E252" s="2" t="n">
         <f aca="false">A252 +1000</f>
@@ -7935,7 +7975,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E253" s="2" t="n">
         <f aca="false">A253 +1000</f>
@@ -7953,7 +7993,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E254" s="2" t="n">
         <f aca="false">A254 +1000</f>
@@ -7971,7 +8011,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E255" s="2" t="n">
         <f aca="false">A255 +1000</f>
@@ -7989,7 +8029,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E256" s="2" t="n">
         <f aca="false">A256 +1000</f>
@@ -8007,7 +8047,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E257" s="2" t="n">
         <f aca="false">A257 +1000</f>
@@ -8025,7 +8065,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E258" s="2" t="n">
         <f aca="false">A258 +1000</f>
@@ -8043,7 +8083,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E259" s="2" t="n">
         <f aca="false">A259 +1000</f>
@@ -8061,7 +8101,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E260" s="2" t="n">
         <f aca="false">A260 +1000</f>
@@ -8079,7 +8119,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E261" s="2" t="n">
         <f aca="false">A261 +1000</f>
@@ -8097,7 +8137,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E262" s="2" t="n">
         <f aca="false">A262 +1000</f>
@@ -8115,7 +8155,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E263" s="2" t="n">
         <f aca="false">A263 +1000</f>
@@ -8133,7 +8173,7 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>9</v>
@@ -8163,7 +8203,7 @@
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E265" s="2" t="n">
         <f aca="false">A265 +1000</f>
@@ -8181,7 +8221,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E266" s="2" t="n">
         <f aca="false">A266 +1000</f>
@@ -8199,7 +8239,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E267" s="2" t="n">
         <f aca="false">A267 +1000</f>
@@ -8217,7 +8257,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E268" s="2" t="n">
         <f aca="false">A268 +1000</f>
@@ -8235,7 +8275,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E269" s="2" t="n">
         <f aca="false">A269 +1000</f>
@@ -8253,7 +8293,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E270" s="2" t="n">
         <f aca="false">A270 +1000</f>
@@ -8271,7 +8311,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E271" s="2" t="n">
         <f aca="false">A271 +1000</f>
@@ -8289,7 +8329,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E272" s="2" t="n">
         <f aca="false">A272 +1000</f>
@@ -8307,7 +8347,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E273" s="2" t="n">
         <f aca="false">A273 +1000</f>
@@ -8325,7 +8365,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E274" s="2" t="n">
         <f aca="false">A274 +1000</f>
@@ -8343,7 +8383,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E275" s="2" t="n">
         <f aca="false">A275 +1000</f>
@@ -8361,7 +8401,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E276" s="2" t="n">
         <f aca="false">A276 +1000</f>
@@ -8379,7 +8419,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E277" s="2" t="n">
         <f aca="false">A277 +1000</f>
@@ -8397,7 +8437,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E278" s="2" t="n">
         <f aca="false">A278 +1000</f>
@@ -8415,7 +8455,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E279" s="2" t="n">
         <f aca="false">A279 +1000</f>
@@ -8433,7 +8473,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E280" s="2" t="n">
         <f aca="false">A280 +1000</f>
@@ -8451,7 +8491,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E281" s="2" t="n">
         <f aca="false">A281 +1000</f>
@@ -8469,7 +8509,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E282" s="2" t="n">
         <f aca="false">A282 +1000</f>
@@ -8487,7 +8527,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E283" s="2" t="n">
         <f aca="false">A283 +1000</f>
@@ -8505,7 +8545,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E284" s="2" t="n">
         <f aca="false">A284 +1000</f>
@@ -8523,7 +8563,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E285" s="2" t="n">
         <f aca="false">A285 +1000</f>
@@ -8541,7 +8581,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E286" s="2" t="n">
         <f aca="false">A286 +1000</f>
@@ -8559,7 +8599,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E287" s="2" t="n">
         <f aca="false">A287 +1000</f>
@@ -8577,7 +8617,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E288" s="2" t="n">
         <f aca="false">A288 +1000</f>
@@ -8595,7 +8635,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E289" s="2" t="n">
         <f aca="false">A289 +1000</f>
@@ -8613,7 +8653,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E290" s="2" t="n">
         <f aca="false">A290 +1000</f>
@@ -8631,7 +8671,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E291" s="2" t="n">
         <f aca="false">A291 +1000</f>
@@ -8649,7 +8689,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E292" s="2" t="n">
         <f aca="false">A292 +1000</f>
@@ -8667,7 +8707,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E293" s="2" t="n">
         <f aca="false">A293 +1000</f>
@@ -8685,7 +8725,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E294" s="2" t="n">
         <f aca="false">A294 +1000</f>
@@ -8703,7 +8743,7 @@
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
@@ -8722,7 +8762,7 @@
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>9</v>
@@ -8746,7 +8786,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E297" s="2" t="n">
         <f aca="false">A297 +1000</f>
@@ -8764,7 +8804,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E298" s="2" t="n">
         <f aca="false">A298 +1000</f>
@@ -8782,7 +8822,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E299" s="2" t="n">
         <f aca="false">A299 +1000</f>
@@ -8800,7 +8840,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E300" s="2" t="n">
         <f aca="false">A300 +1000</f>
@@ -8818,7 +8858,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E301" s="2" t="n">
         <f aca="false">A301 +1000</f>
@@ -8836,7 +8876,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E302" s="2" t="n">
         <f aca="false">A302 +1000</f>
@@ -8854,7 +8894,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E303" s="2" t="n">
         <f aca="false">A303 +1000</f>
@@ -8872,7 +8912,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E304" s="2" t="n">
         <f aca="false">A304 +1000</f>
@@ -8890,7 +8930,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E305" s="2" t="n">
         <f aca="false">A305 +1000</f>
@@ -8908,7 +8948,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E306" s="2" t="n">
         <f aca="false">A306 +1000</f>
@@ -8926,7 +8966,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E307" s="2" t="n">
         <f aca="false">A307 +1000</f>
@@ -8944,7 +8984,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E308" s="2" t="n">
         <f aca="false">A308 +1000</f>
@@ -8962,7 +9002,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E309" s="2" t="n">
         <f aca="false">A309 +1000</f>
@@ -8980,7 +9020,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E310" s="2" t="n">
         <f aca="false">A310 +1000</f>
@@ -8998,7 +9038,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E311" s="2" t="n">
         <f aca="false">A311 +1000</f>
@@ -9016,7 +9056,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E312" s="2" t="n">
         <f aca="false">A312 +1000</f>
@@ -9034,7 +9074,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E313" s="2" t="n">
         <f aca="false">A313 +1000</f>
@@ -9052,7 +9092,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E314" s="2" t="n">
         <f aca="false">A314 +1000</f>
@@ -9070,7 +9110,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E315" s="2" t="n">
         <f aca="false">A315 +1000</f>
@@ -9088,7 +9128,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E316" s="2" t="n">
         <f aca="false">A316 +1000</f>
@@ -9106,7 +9146,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E317" s="2" t="n">
         <f aca="false">A317 +1000</f>
@@ -9124,7 +9164,7 @@
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E318" s="2" t="n">
         <f aca="false">A318 +1000</f>
@@ -9148,7 +9188,7 @@
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E319" s="2" t="n">
         <f aca="false">A319 +1000</f>
@@ -9166,7 +9206,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E320" s="2" t="n">
         <f aca="false">A320 +1000</f>
@@ -9184,7 +9224,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E321" s="2" t="n">
         <f aca="false">A321 +1000</f>
@@ -9202,7 +9242,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E322" s="2" t="n">
         <f aca="false">A322 +1000</f>
@@ -9220,7 +9260,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E323" s="2" t="n">
         <f aca="false">A323 +1000</f>
@@ -9238,7 +9278,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E324" s="2" t="n">
         <f aca="false">A324 +1000</f>
@@ -9256,7 +9296,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E325" s="2" t="n">
         <f aca="false">A325 +1000</f>
@@ -9274,7 +9314,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E326" s="2" t="n">
         <f aca="false">A326 +1000</f>
@@ -9292,7 +9332,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E327" s="2" t="n">
         <f aca="false">A327 +1000</f>
@@ -9310,7 +9350,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E328" s="2" t="n">
         <f aca="false">A328 +1000</f>
@@ -9328,7 +9368,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E329" s="2" t="n">
         <f aca="false">A329 +1000</f>
@@ -9346,7 +9386,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E330" s="2" t="n">
         <f aca="false">A330 +1000</f>
@@ -9364,7 +9404,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E331" s="2" t="n">
         <f aca="false">A331 +1000</f>
@@ -9382,7 +9422,7 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>9</v>
@@ -9406,7 +9446,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E333" s="2" t="n">
         <f aca="false">A333 +1000</f>
@@ -9424,7 +9464,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E334" s="2" t="n">
         <f aca="false">A334 +1000</f>
@@ -9442,7 +9482,7 @@
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E335" s="2" t="n">
         <f aca="false">A335 +1000</f>
@@ -9466,7 +9506,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E336" s="2" t="n">
         <f aca="false">A336 +1000</f>
@@ -9484,7 +9524,7 @@
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E337" s="2" t="n">
         <f aca="false">A337 +1000</f>
@@ -9508,7 +9548,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E338" s="2" t="n">
         <f aca="false">A338 +1000</f>
@@ -9526,7 +9566,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E339" s="2" t="n">
         <f aca="false">A339 +1000</f>
@@ -9544,7 +9584,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E340" s="2" t="n">
         <f aca="false">A340 +1000</f>
@@ -9562,7 +9602,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E341" s="2" t="n">
         <f aca="false">A341 +1000</f>
@@ -9580,7 +9620,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E342" s="2" t="n">
         <f aca="false">A342 +1000</f>
@@ -9598,7 +9638,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E343" s="2" t="n">
         <f aca="false">A343 +1000</f>
@@ -9616,7 +9656,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E344" s="2" t="n">
         <f aca="false">A344 +1000</f>
@@ -9634,7 +9674,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E345" s="2" t="n">
         <f aca="false">A345 +1000</f>
@@ -9652,7 +9692,7 @@
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E346" s="2" t="n">
         <f aca="false">A346 +1000</f>
@@ -9670,7 +9710,7 @@
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
@@ -9689,7 +9729,7 @@
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>9</v>
@@ -9713,7 +9753,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E349" s="2" t="n">
         <f aca="false">A349 +1000</f>
@@ -9731,7 +9771,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E350" s="2" t="n">
         <f aca="false">A350 +1000</f>
@@ -9749,7 +9789,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E351" s="2" t="n">
         <f aca="false">A351 +1000</f>
@@ -9767,7 +9807,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E352" s="2" t="n">
         <f aca="false">A352 +1000</f>
@@ -9785,7 +9825,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E353" s="2" t="n">
         <f aca="false">A353 +1000</f>
@@ -9803,7 +9843,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E354" s="2" t="n">
         <f aca="false">A354 +1000</f>
@@ -9821,7 +9861,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E355" s="2" t="n">
         <f aca="false">A355 +1000</f>
@@ -9839,7 +9879,7 @@
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>9</v>
@@ -9863,7 +9903,7 @@
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E357" s="2" t="n">
         <f aca="false">A357 +1000</f>
@@ -9887,7 +9927,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E358" s="2" t="n">
         <f aca="false">A358 +1000</f>
@@ -9905,7 +9945,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E359" s="2" t="n">
         <f aca="false">A359 +1000</f>
@@ -9923,7 +9963,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E360" s="2" t="n">
         <f aca="false">A360 +1000</f>
@@ -9941,7 +9981,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E361" s="2" t="n">
         <f aca="false">A361 +1000</f>
@@ -9959,7 +9999,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E362" s="2" t="n">
         <f aca="false">A362 +1000</f>
@@ -9977,7 +10017,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E363" s="2" t="n">
         <f aca="false">A363 +1000</f>
@@ -9995,7 +10035,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E364" s="2" t="n">
         <f aca="false">A364 +1000</f>
@@ -10013,7 +10053,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E365" s="2" t="n">
         <f aca="false">A365 +1000</f>
@@ -10031,7 +10071,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E366" s="2" t="n">
         <f aca="false">A366 +1000</f>
@@ -10049,7 +10089,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E367" s="2" t="n">
         <f aca="false">A367 +1000</f>
@@ -10067,7 +10107,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E368" s="2" t="n">
         <f aca="false">A368 +1000</f>
@@ -10085,7 +10125,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E369" s="2" t="n">
         <f aca="false">A369 +1000</f>
@@ -10103,7 +10143,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E370" s="2" t="n">
         <f aca="false">A370 +1000</f>
@@ -10121,7 +10161,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E371" s="2" t="n">
         <f aca="false">A371 +1000</f>
@@ -10139,7 +10179,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E372" s="2" t="n">
         <f aca="false">A372 +1000</f>
@@ -10157,7 +10197,7 @@
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>9</v>
@@ -10181,7 +10221,7 @@
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E374" s="2" t="n">
         <f aca="false">A374 +1000</f>
@@ -10193,8 +10233,8 @@
       <c r="G374" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H374" s="0" t="s">
-        <v>381</v>
+      <c r="H374" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="I374" s="2" t="n">
         <f aca="false">E374 +1000</f>
@@ -10208,7 +10248,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E375" s="2" t="n">
         <f aca="false">A375 +1000</f>
@@ -10226,7 +10266,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E376" s="2" t="n">
         <f aca="false">A376 +1000</f>
@@ -10244,7 +10284,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E377" s="2" t="n">
         <f aca="false">A377 +1000</f>
@@ -10262,7 +10302,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>9</v>
@@ -10286,7 +10326,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E379" s="2" t="n">
         <f aca="false">A379 +1000</f>
@@ -10304,7 +10344,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E380" s="2" t="n">
         <f aca="false">A380 +1000</f>
@@ -10322,7 +10362,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E381" s="2" t="n">
         <f aca="false">A381 +1000</f>
@@ -10340,7 +10380,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E382" s="2" t="n">
         <f aca="false">A382 +1000</f>
@@ -10358,7 +10398,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E383" s="2" t="n">
         <f aca="false">A383 +1000</f>
@@ -10376,7 +10416,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E384" s="2" t="n">
         <f aca="false">A384 +1000</f>
@@ -10394,7 +10434,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E385" s="2" t="n">
         <f aca="false">A385 +1000</f>
@@ -10412,7 +10452,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E386" s="2" t="n">
         <f aca="false">A386 +1000</f>
@@ -10430,7 +10470,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E387" s="2" t="n">
         <f aca="false">A387 +1000</f>
@@ -10448,7 +10488,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E388" s="2" t="n">
         <f aca="false">A388 +1000</f>
@@ -10466,7 +10506,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E389" s="2" t="n">
         <f aca="false">A389 +1000</f>
@@ -10484,7 +10524,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E390" s="2" t="n">
         <f aca="false">A390 +1000</f>
@@ -10502,7 +10542,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E391" s="2" t="n">
         <f aca="false">A391 +1000</f>
@@ -10520,7 +10560,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E392" s="2" t="n">
         <f aca="false">A392 +1000</f>
@@ -10538,7 +10578,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E393" s="2" t="n">
         <f aca="false">A393 +1000</f>
@@ -10556,7 +10596,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E394" s="2" t="n">
         <f aca="false">A394 +1000</f>
@@ -10574,7 +10614,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E395" s="2" t="n">
         <f aca="false">A395 +1000</f>
@@ -10592,7 +10632,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E396" s="2" t="n">
         <f aca="false">A396 +1000</f>
@@ -10610,7 +10650,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E397" s="2" t="n">
         <f aca="false">A397 +1000</f>
@@ -10628,7 +10668,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E398" s="2" t="n">
         <f aca="false">A398 +1000</f>
@@ -10646,7 +10686,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E399" s="2" t="n">
         <f aca="false">A399 +1000</f>
@@ -10664,7 +10704,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E400" s="2" t="n">
         <f aca="false">A400 +1000</f>
@@ -10682,7 +10722,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E401" s="2" t="n">
         <f aca="false">A401 +1000</f>
@@ -10700,7 +10740,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E402" s="2" t="n">
         <f aca="false">A402 +1000</f>
@@ -10718,7 +10758,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E403" s="2" t="n">
         <f aca="false">A403 +1000</f>
@@ -10736,7 +10776,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E404" s="2" t="n">
         <f aca="false">A404 +1000</f>
@@ -10754,7 +10794,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E405" s="2" t="n">
         <f aca="false">A405 +1000</f>
@@ -10772,7 +10812,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E406" s="2" t="n">
         <f aca="false">A406 +1000</f>
@@ -10790,7 +10830,7 @@
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>9</v>
@@ -10814,7 +10854,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E408" s="2" t="n">
         <f aca="false">A408 +1000</f>
@@ -10832,7 +10872,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E409" s="2" t="n">
         <f aca="false">A409 +1000</f>
@@ -10850,7 +10890,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E410" s="2" t="n">
         <f aca="false">A410 +1000</f>
@@ -10868,7 +10908,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E411" s="2" t="n">
         <f aca="false">A411 +1000</f>
@@ -10886,7 +10926,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E412" s="2" t="n">
         <f aca="false">A412 +1000</f>
@@ -10904,7 +10944,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E413" s="2" t="n">
         <f aca="false">A413 +1000</f>
@@ -10922,7 +10962,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E414" s="2" t="n">
         <f aca="false">A414 +1000</f>
@@ -10940,7 +10980,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E415" s="2" t="n">
         <f aca="false">A415 +1000</f>
@@ -10958,7 +10998,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E416" s="2" t="n">
         <f aca="false">A416 +1000</f>
@@ -10976,7 +11016,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E417" s="2" t="n">
         <f aca="false">A417 +1000</f>
@@ -10994,7 +11034,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E418" s="2" t="n">
         <f aca="false">A418 +1000</f>
@@ -11012,7 +11052,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E419" s="2" t="n">
         <f aca="false">A419 +1000</f>
@@ -11030,7 +11070,7 @@
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>9</v>
@@ -11054,7 +11094,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E421" s="2" t="n">
         <f aca="false">A421 +1000</f>
@@ -11072,7 +11112,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
@@ -11090,7 +11130,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E423" s="2" t="n">
         <f aca="false">A423 +1000</f>
@@ -11108,7 +11148,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E424" s="2" t="n">
         <f aca="false">A424 +1000</f>
@@ -11126,7 +11166,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E425" s="2" t="n">
         <f aca="false">A425 +1000</f>
@@ -11144,7 +11184,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E426" s="2" t="n">
         <f aca="false">A426 +1000</f>
@@ -11162,7 +11202,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E427" s="2" t="n">
         <f aca="false">A427 +1000</f>
@@ -11180,7 +11220,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E428" s="2" t="n">
         <f aca="false">A428 +1000</f>
@@ -11198,7 +11238,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E429" s="2" t="n">
         <f aca="false">A429 +1000</f>
@@ -11216,7 +11256,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E430" s="2" t="n">
         <f aca="false">A430 +1000</f>
@@ -11234,7 +11274,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E431" s="2" t="n">
         <f aca="false">A431 +1000</f>
@@ -11252,7 +11292,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E432" s="2" t="n">
         <f aca="false">A432 +1000</f>
@@ -11270,7 +11310,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E433" s="2" t="n">
         <f aca="false">A433 +1000</f>
@@ -11288,7 +11328,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E434" s="2" t="n">
         <f aca="false">A434 +1000</f>
@@ -11306,7 +11346,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E435" s="2" t="n">
         <f aca="false">A435 +1000</f>
@@ -11324,7 +11364,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E436" s="2" t="n">
         <f aca="false">A436 +1000</f>
@@ -11342,7 +11382,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E437" s="2" t="n">
         <f aca="false">A437 +1000</f>
@@ -11360,7 +11400,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E438" s="2" t="n">
         <f aca="false">A438 +1000</f>
@@ -11378,7 +11418,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E439" s="2" t="n">
         <f aca="false">A439 +1000</f>
@@ -11396,7 +11436,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E440" s="2" t="n">
         <f aca="false">A440 +1000</f>
@@ -11414,7 +11454,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E441" s="2" t="n">
         <f aca="false">A441 +1000</f>
@@ -11432,7 +11472,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E442" s="2" t="n">
         <f aca="false">A442 +1000</f>
@@ -11450,7 +11490,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E443" s="2" t="n">
         <f aca="false">A443 +1000</f>
@@ -11468,7 +11508,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E444" s="2" t="n">
         <f aca="false">A444 +1000</f>
@@ -11486,7 +11526,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E445" s="2" t="n">
         <f aca="false">A445 +1000</f>
@@ -11504,7 +11544,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E446" s="2" t="n">
         <f aca="false">A446 +1000</f>
@@ -11522,7 +11562,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E447" s="2" t="n">
         <f aca="false">A447 +1000</f>
@@ -11540,7 +11580,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E448" s="2" t="n">
         <f aca="false">A448 +1000</f>
@@ -11558,7 +11598,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E449" s="2" t="n">
         <f aca="false">A449 +1000</f>
@@ -11576,7 +11616,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E450" s="2" t="n">
         <f aca="false">A450 +1000</f>
@@ -11594,7 +11634,7 @@
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>9</v>
@@ -11618,7 +11658,7 @@
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E452" s="2" t="n">
         <f aca="false">A452 +1000</f>
@@ -11636,7 +11676,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E453" s="2" t="n">
         <f aca="false">A453 +1000</f>
@@ -11654,7 +11694,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E454" s="2" t="n">
         <f aca="false">A454 +1000</f>
@@ -11672,7 +11712,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E455" s="2" t="n">
         <f aca="false">A455 +1000</f>
@@ -11690,7 +11730,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E456" s="2" t="n">
         <f aca="false">A456 +1000</f>
@@ -11708,7 +11748,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E457" s="2" t="n">
         <f aca="false">A457 +1000</f>
@@ -11726,7 +11766,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E458" s="2" t="n">
         <f aca="false">A458 +1000</f>
@@ -11744,7 +11784,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E459" s="2" t="n">
         <f aca="false">A459 +1000</f>
@@ -11762,7 +11802,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E460" s="2" t="n">
         <f aca="false">A460 +1000</f>
@@ -11780,7 +11820,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E461" s="2" t="n">
         <f aca="false">A461 +1000</f>
@@ -11798,7 +11838,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E462" s="2" t="n">
         <f aca="false">A462 +1000</f>
@@ -11816,7 +11856,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E463" s="2" t="n">
         <f aca="false">A463 +1000</f>
@@ -11834,7 +11874,7 @@
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E464" s="2" t="n">
         <f aca="false">A464 +1000</f>
@@ -11858,7 +11898,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E465" s="2" t="n">
         <f aca="false">A465 +1000</f>
@@ -11876,7 +11916,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E466" s="2" t="n">
         <f aca="false">A466 +1000</f>
@@ -11894,7 +11934,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E467" s="2" t="n">
         <f aca="false">A467 +1000</f>
@@ -11912,7 +11952,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E468" s="2" t="n">
         <f aca="false">A468 +1000</f>
@@ -11930,7 +11970,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E469" s="2" t="n">
         <f aca="false">A469 +1000</f>
@@ -11948,7 +11988,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E470" s="2" t="n">
         <f aca="false">A470 +1000</f>
@@ -11966,7 +12006,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E471" s="2" t="n">
         <f aca="false">A471 +1000</f>
@@ -11984,7 +12024,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E472" s="2" t="n">
         <f aca="false">A472 +1000</f>
@@ -12002,7 +12042,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E473" s="2" t="n">
         <f aca="false">A473 +1000</f>
@@ -12020,7 +12060,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E474" s="2" t="n">
         <f aca="false">A474 +1000</f>
@@ -12038,7 +12078,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E475" s="2" t="n">
         <f aca="false">A475 +1000</f>
@@ -12056,7 +12096,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E476" s="2" t="n">
         <f aca="false">A476 +1000</f>
@@ -12074,7 +12114,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E477" s="2" t="n">
         <f aca="false">A477 +1000</f>
@@ -12092,7 +12132,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E478" s="2" t="n">
         <f aca="false">A478 +1000</f>
@@ -12110,7 +12150,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E479" s="2" t="n">
         <f aca="false">A479 +1000</f>
@@ -12128,7 +12168,7 @@
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
@@ -12147,7 +12187,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E481" s="2" t="n">
         <f aca="false">A481 +1000</f>
@@ -12165,7 +12205,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E482" s="2" t="n">
         <f aca="false">A482 +1000</f>
@@ -12183,7 +12223,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E483" s="2" t="n">
         <f aca="false">A483 +1000</f>
@@ -12201,7 +12241,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E484" s="2" t="n">
         <f aca="false">A484 +1000</f>
@@ -12219,7 +12259,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E485" s="2" t="n">
         <f aca="false">A485 +1000</f>
@@ -12237,7 +12277,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E486" s="2" t="n">
         <f aca="false">A486 +1000</f>
@@ -12255,7 +12295,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E487" s="2" t="n">
         <f aca="false">A487 +1000</f>
@@ -12273,7 +12313,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E488" s="2" t="n">
         <f aca="false">A488 +1000</f>
@@ -12291,7 +12331,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E489" s="2" t="n">
         <f aca="false">A489 +1000</f>
@@ -12309,7 +12349,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E490" s="2" t="n">
         <f aca="false">A490 +1000</f>
@@ -12327,7 +12367,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E491" s="2" t="n">
         <f aca="false">A491 +1000</f>
@@ -12345,7 +12385,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E492" s="2" t="n">
         <f aca="false">A492 +1000</f>
@@ -12363,7 +12403,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E493" s="2" t="n">
         <f aca="false">A493 +1000</f>
@@ -12381,7 +12421,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E494" s="2" t="n">
         <f aca="false">A494 +1000</f>
@@ -12399,7 +12439,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E495" s="2" t="n">
         <f aca="false">A495 +1000</f>
@@ -12417,7 +12457,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E496" s="2" t="n">
         <f aca="false">A496 +1000</f>
@@ -12435,7 +12475,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E497" s="2" t="n">
         <f aca="false">A497 +1000</f>
@@ -12453,7 +12493,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E498" s="2" t="n">
         <f aca="false">A498 +1000</f>
@@ -12471,7 +12511,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E499" s="2" t="n">
         <f aca="false">A499 +1000</f>
@@ -12489,7 +12529,7 @@
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E500" s="2" t="n">
         <f aca="false">A500 +1000</f>
@@ -12513,7 +12553,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E501" s="2" t="n">
         <f aca="false">A501 +1000</f>
@@ -12531,7 +12571,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E502" s="2" t="n">
         <f aca="false">A502 +1000</f>
@@ -12549,7 +12589,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E503" s="2" t="n">
         <f aca="false">A503 +1000</f>
@@ -12567,7 +12607,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E504" s="2" t="n">
         <f aca="false">A504 +1000</f>
@@ -12585,7 +12625,7 @@
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E505" s="2" t="n">
         <f aca="false">A505 +1000</f>
@@ -12603,7 +12643,7 @@
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>9</v>
@@ -12627,7 +12667,7 @@
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E507" s="2" t="n">
         <f aca="false">A507 +1000</f>
@@ -12651,7 +12691,7 @@
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E508" s="2" t="n">
         <f aca="false">A508 +1000</f>
@@ -12669,7 +12709,7 @@
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E509" s="2" t="n">
         <f aca="false">A509 +1000</f>
@@ -12687,7 +12727,7 @@
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E510" s="2" t="n">
         <f aca="false">A510 +1000</f>
@@ -12705,7 +12745,7 @@
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E511" s="2" t="n">
         <f aca="false">A511 +1000</f>
@@ -12723,7 +12763,7 @@
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E512" s="2" t="n">
         <f aca="false">A512 +1000</f>
@@ -12741,7 +12781,7 @@
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E513" s="2" t="n">
         <f aca="false">A513 +1000</f>
@@ -12759,7 +12799,7 @@
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E514" s="2" t="n">
         <f aca="false">A514 +1000</f>
@@ -12777,7 +12817,7 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E515" s="2" t="n">
         <f aca="false">A515 +1000</f>
@@ -12795,7 +12835,7 @@
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E516" s="2" t="n">
         <f aca="false">A516 +1000</f>
@@ -12813,7 +12853,7 @@
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E517" s="2" t="n">
         <f aca="false">A517 +1000</f>
@@ -12831,7 +12871,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E518" s="2" t="n">
         <f aca="false">A518 +1000</f>
@@ -12849,7 +12889,7 @@
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E519" s="2" t="n">
         <f aca="false">A519 +1000</f>
@@ -12867,7 +12907,7 @@
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E520" s="2" t="n">
         <f aca="false">A520 +1000</f>
@@ -12885,7 +12925,7 @@
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E521" s="2" t="n">
         <f aca="false">A521 +1000</f>
@@ -12903,7 +12943,7 @@
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E522" s="2" t="n">
         <f aca="false">A522 +1000</f>
@@ -12921,7 +12961,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E523" s="2" t="n">
         <f aca="false">A523 +1000</f>
@@ -12939,7 +12979,7 @@
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E524" s="2" t="n">
         <f aca="false">A524 +1000</f>
@@ -12957,7 +12997,7 @@
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E525" s="2" t="n">
         <f aca="false">A525 +1000</f>
@@ -12975,7 +13015,7 @@
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E526" s="2" t="n">
         <f aca="false">A526 +1000</f>
@@ -12993,7 +13033,7 @@
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E527" s="2" t="n">
         <f aca="false">A527 +1000</f>
@@ -13011,7 +13051,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E528" s="2" t="n">
         <f aca="false">A528 +1000</f>
@@ -13029,7 +13069,7 @@
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E529" s="2" t="n">
         <f aca="false">A529 +1000</f>
@@ -13047,7 +13087,7 @@
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E530" s="2" t="n">
         <f aca="false">A530 +1000</f>
@@ -13065,7 +13105,7 @@
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E531" s="2" t="n">
         <f aca="false">A531 +1000</f>
@@ -13083,7 +13123,7 @@
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E532" s="2" t="n">
         <f aca="false">A532 +1000</f>
@@ -13101,7 +13141,7 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E533" s="2" t="n">
         <f aca="false">A533 +1000</f>
@@ -13119,7 +13159,7 @@
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E534" s="2" t="n">
         <f aca="false">A534 +1000</f>
@@ -13137,7 +13177,7 @@
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E535" s="2" t="n">
         <f aca="false">A535 +1000</f>
@@ -13155,7 +13195,7 @@
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E536" s="2" t="n">
         <f aca="false">A536 +1000</f>
@@ -13173,7 +13213,7 @@
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E537" s="2" t="n">
         <f aca="false">A537 +1000</f>
@@ -13191,7 +13231,7 @@
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E538" s="2" t="n">
         <f aca="false">A538 +1000</f>
@@ -13209,7 +13249,7 @@
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E539" s="2" t="n">
         <f aca="false">A539 +1000</f>
@@ -13227,7 +13267,7 @@
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E540" s="2" t="n">
         <f aca="false">A540 +1000</f>
@@ -13245,7 +13285,7 @@
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E541" s="2" t="n">
         <f aca="false">A541 +1000</f>
@@ -13263,7 +13303,7 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E542" s="2" t="n">
         <f aca="false">A542 +1000</f>
@@ -13281,7 +13321,7 @@
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E543" s="2" t="n">
         <f aca="false">A543 +1000</f>
@@ -13299,7 +13339,7 @@
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E544" s="2" t="n">
         <f aca="false">A544 +1000</f>
@@ -13317,7 +13357,7 @@
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E545" s="2" t="n">
         <f aca="false">A545 +1000</f>
@@ -13335,7 +13375,7 @@
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E546" s="2" t="n">
         <f aca="false">A546 +1000</f>
@@ -13353,7 +13393,7 @@
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E547" s="2" t="n">
         <f aca="false">A547 +1000</f>
@@ -13371,7 +13411,7 @@
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E548" s="2" t="n">
         <f aca="false">A548 +1000</f>
@@ -13389,7 +13429,7 @@
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E549" s="2" t="n">
         <f aca="false">A549 +1000</f>
@@ -13407,7 +13447,7 @@
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E550" s="2" t="n">
         <f aca="false">A550 +1000</f>
@@ -13425,7 +13465,7 @@
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E551" s="2" t="n">
         <f aca="false">A551 +1000</f>
@@ -13443,7 +13483,7 @@
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E552" s="2" t="n">
         <f aca="false">A552 +1000</f>
@@ -13461,7 +13501,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E553" s="2" t="n">
         <f aca="false">A553 +1000</f>
@@ -13479,7 +13519,7 @@
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E554" s="2" t="n">
         <f aca="false">A554 +1000</f>
@@ -13497,7 +13537,7 @@
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E555" s="2" t="n">
         <f aca="false">A555 +1000</f>
@@ -13515,7 +13555,7 @@
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E556" s="2" t="n">
         <f aca="false">A556 +1000</f>
@@ -13533,7 +13573,7 @@
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E557" s="2" t="n">
         <f aca="false">A557 +1000</f>
@@ -13551,7 +13591,7 @@
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E558" s="2" t="n">
         <f aca="false">A558 +1000</f>
@@ -13575,7 +13615,7 @@
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E559" s="2" t="n">
         <f aca="false">A559 +1000</f>
@@ -13593,7 +13633,7 @@
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E560" s="2" t="n">
         <f aca="false">A560 +1000</f>
@@ -13611,7 +13651,7 @@
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E561" s="2" t="n">
         <f aca="false">A561 +1000</f>
@@ -13629,7 +13669,7 @@
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E562" s="2" t="n">
         <f aca="false">A562 +1000</f>
@@ -13647,7 +13687,7 @@
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E563" s="2" t="n">
         <f aca="false">A563 +1000</f>
@@ -13665,7 +13705,7 @@
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E564" s="2" t="n">
         <f aca="false">A564 +1000</f>
@@ -13683,7 +13723,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E565" s="2" t="n">
         <f aca="false">A565 +1000</f>
@@ -13701,7 +13741,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E566" s="2" t="n">
         <f aca="false">A566 +1000</f>
@@ -13719,7 +13759,7 @@
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E567" s="2" t="n">
         <f aca="false">A567 +1000</f>
@@ -13737,7 +13777,7 @@
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E568" s="2" t="n">
         <f aca="false">A568 +1000</f>
@@ -13755,7 +13795,7 @@
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E569" s="2" t="n">
         <f aca="false">A569 +1000</f>
@@ -13773,7 +13813,7 @@
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E570" s="2" t="n">
         <f aca="false">A570 +1000</f>
@@ -13791,7 +13831,7 @@
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E571" s="2" t="n">
         <f aca="false">A571 +1000</f>
@@ -13809,7 +13849,7 @@
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E572" s="2" t="n">
         <f aca="false">A572 +1000</f>
@@ -13827,7 +13867,7 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E573" s="2" t="n">
         <f aca="false">A573 +1000</f>
@@ -13845,7 +13885,7 @@
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E574" s="2" t="n">
         <f aca="false">A574 +1000</f>
@@ -13863,7 +13903,7 @@
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E575" s="2" t="n">
         <f aca="false">A575 +1000</f>
@@ -13881,7 +13921,7 @@
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E576" s="2" t="n">
         <f aca="false">A576 +1000</f>
@@ -13899,7 +13939,7 @@
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E577" s="2" t="n">
         <f aca="false">A577 +1000</f>
@@ -13917,7 +13957,7 @@
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E578" s="2" t="n">
         <f aca="false">A578 +1000</f>
@@ -13935,7 +13975,7 @@
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E579" s="2" t="n">
         <f aca="false">A579 +1000</f>
@@ -13953,7 +13993,7 @@
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E580" s="2" t="n">
         <f aca="false">A580 +1000</f>
@@ -13971,7 +14011,7 @@
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E581" s="2" t="n">
         <f aca="false">A581 +1000</f>
@@ -13989,7 +14029,7 @@
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E582" s="2" t="n">
         <f aca="false">A582 +1000</f>
@@ -14007,7 +14047,7 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E583" s="2" t="n">
         <f aca="false">A583 +1000</f>
@@ -14025,7 +14065,7 @@
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E584" s="2" t="n">
         <f aca="false">A584 +1000</f>
@@ -14043,7 +14083,7 @@
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E585" s="2" t="n">
         <f aca="false">A585 +1000</f>
@@ -14061,7 +14101,7 @@
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E586" s="2" t="n">
         <f aca="false">A586 +1000</f>
@@ -14079,7 +14119,7 @@
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E587" s="2" t="n">
         <f aca="false">A587 +1000</f>
@@ -14097,7 +14137,7 @@
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E588" s="2" t="n">
         <f aca="false">A588 +1000</f>
@@ -14115,7 +14155,7 @@
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E589" s="2" t="n">
         <f aca="false">A589 +1000</f>
@@ -14133,7 +14173,7 @@
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E590" s="2" t="n">
         <f aca="false">A590 +1000</f>
@@ -14151,7 +14191,7 @@
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E591" s="2" t="n">
         <f aca="false">A591 +1000</f>
@@ -14169,7 +14209,7 @@
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E592" s="2" t="n">
         <f aca="false">A592 +1000</f>
@@ -14187,7 +14227,7 @@
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E593" s="2" t="n">
         <f aca="false">A593 +1000</f>
@@ -14205,7 +14245,7 @@
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E594" s="2" t="n">
         <f aca="false">A594 +1000</f>
@@ -14223,7 +14263,7 @@
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E595" s="2" t="n">
         <f aca="false">A595 +1000</f>
@@ -14241,7 +14281,7 @@
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E596" s="2" t="n">
         <f aca="false">A596 +1000</f>
@@ -14259,7 +14299,7 @@
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E597" s="2" t="n">
         <f aca="false">A597 +1000</f>
@@ -14277,7 +14317,7 @@
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E598" s="2" t="n">
         <f aca="false">A598 +1000</f>
@@ -14295,7 +14335,7 @@
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E599" s="2" t="n">
         <f aca="false">A599 +1000</f>
@@ -14313,7 +14353,7 @@
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E600" s="2" t="n">
         <f aca="false">A600 +1000</f>
@@ -14331,7 +14371,7 @@
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E601" s="2" t="n">
         <f aca="false">A601 +1000</f>
@@ -14349,7 +14389,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E602" s="2" t="n">
         <f aca="false">A602 +1000</f>
@@ -14367,7 +14407,7 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E603" s="2" t="n">
         <f aca="false">A603 +1000</f>
@@ -14385,7 +14425,7 @@
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E604" s="2" t="n">
         <f aca="false">A604 +1000</f>
@@ -14403,7 +14443,7 @@
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E605" s="2" t="n">
         <f aca="false">A605 +1000</f>
@@ -14421,7 +14461,7 @@
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E606" s="2" t="n">
         <f aca="false">A606 +1000</f>
@@ -14439,7 +14479,7 @@
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E607" s="2" t="n">
         <f aca="false">A607 +1000</f>
@@ -14457,7 +14497,7 @@
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E608" s="2" t="n">
         <f aca="false">A608 +1000</f>
@@ -14475,7 +14515,7 @@
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E609" s="2" t="n">
         <f aca="false">A609 +1000</f>
@@ -14493,7 +14533,7 @@
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E610" s="2" t="n">
         <f aca="false">A610 +1000</f>
@@ -14511,7 +14551,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E611" s="2" t="n">
         <f aca="false">A611 +1000</f>
@@ -14529,7 +14569,7 @@
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E612" s="2" t="n">
         <f aca="false">A612 +1000</f>
@@ -14547,7 +14587,7 @@
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E613" s="2" t="n">
         <f aca="false">A613 +1000</f>
@@ -14565,7 +14605,7 @@
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E614" s="2" t="n">
         <f aca="false">A614 +1000</f>
@@ -14583,7 +14623,7 @@
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E615" s="2" t="n">
         <f aca="false">A615 +1000</f>
@@ -14601,7 +14641,7 @@
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E616" s="2" t="n">
         <f aca="false">A616 +1000</f>
@@ -14619,7 +14659,7 @@
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E617" s="2" t="n">
         <f aca="false">A617 +1000</f>
@@ -14637,7 +14677,7 @@
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E618" s="2" t="n">
         <f aca="false">A618 +1000</f>
@@ -14655,7 +14695,7 @@
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E619" s="2" t="n">
         <f aca="false">A619 +1000</f>
@@ -14673,7 +14713,7 @@
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E620" s="2" t="n">
         <f aca="false">A620 +1000</f>
@@ -14691,7 +14731,7 @@
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E621" s="2" t="n">
         <f aca="false">A621 +1000</f>
@@ -14709,7 +14749,7 @@
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>9</v>
@@ -14718,7 +14758,7 @@
         <v>9</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E622" s="2" t="n">
         <f aca="false">A622 +1000</f>
@@ -14736,7 +14776,7 @@
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E623" s="2" t="n">
         <f aca="false">A623 +1000</f>
@@ -14754,7 +14794,7 @@
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E624" s="2" t="n">
         <f aca="false">A624 +1000</f>
@@ -14772,7 +14812,7 @@
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E625" s="2" t="n">
         <f aca="false">A625 +1000</f>
@@ -14790,7 +14830,7 @@
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E626" s="2" t="n">
         <f aca="false">A626 +1000</f>
@@ -14808,7 +14848,7 @@
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E627" s="2" t="n">
         <f aca="false">A627 +1000</f>
@@ -14826,7 +14866,7 @@
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E628" s="2" t="n">
         <f aca="false">A628 +1000</f>
@@ -14844,7 +14884,7 @@
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E629" s="2" t="n">
         <f aca="false">A629 +1000</f>
@@ -14862,7 +14902,7 @@
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E630" s="2" t="n">
         <f aca="false">A630 +1000</f>
@@ -14880,7 +14920,7 @@
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E631" s="2" t="n">
         <f aca="false">A631 +1000</f>
@@ -14898,7 +14938,7 @@
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E632" s="2" t="n">
         <f aca="false">A632 +1000</f>
@@ -14916,7 +14956,7 @@
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E633" s="2" t="n">
         <f aca="false">A633 +1000</f>
@@ -14934,7 +14974,7 @@
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E634" s="2" t="n">
         <f aca="false">A634 +1000</f>
@@ -14952,7 +14992,7 @@
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E635" s="2" t="n">
         <f aca="false">A635 +1000</f>
@@ -14970,7 +15010,7 @@
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E636" s="2" t="n">
         <f aca="false">A636 +1000</f>
@@ -14988,7 +15028,7 @@
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E637" s="2" t="n">
         <f aca="false">A637 +1000</f>
@@ -15006,7 +15046,7 @@
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E638" s="2" t="n">
         <f aca="false">A638 +1000</f>
@@ -15024,7 +15064,7 @@
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E639" s="2" t="n">
         <f aca="false">A639 +1000</f>
@@ -15042,7 +15082,7 @@
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E640" s="2" t="n">
         <f aca="false">A640 +1000</f>
@@ -15060,7 +15100,7 @@
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E641" s="2" t="n">
         <f aca="false">A641 +1000</f>
@@ -15078,7 +15118,7 @@
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E642" s="2" t="n">
         <f aca="false">A642 +1000</f>
@@ -15096,7 +15136,7 @@
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E643" s="2" t="n">
         <f aca="false">A643 +1000</f>
@@ -15114,7 +15154,7 @@
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E644" s="2" t="n">
         <f aca="false">A644 +1000</f>
@@ -15132,7 +15172,7 @@
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E645" s="2" t="n">
         <f aca="false">A645 +1000</f>
@@ -15150,7 +15190,7 @@
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E646" s="2" t="n">
         <f aca="false">A646 +1000</f>
@@ -15168,7 +15208,7 @@
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E647" s="2" t="n">
         <f aca="false">A647 +1000</f>
@@ -15186,7 +15226,7 @@
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E648" s="2" t="n">
         <f aca="false">A648 +1000</f>
@@ -15204,7 +15244,7 @@
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E649" s="2" t="n">
         <f aca="false">A649 +1000</f>
@@ -15222,7 +15262,7 @@
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E650" s="2" t="n">
         <f aca="false">A650 +1000</f>
@@ -15240,7 +15280,7 @@
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E651" s="2" t="n">
         <f aca="false">A651 +1000</f>
@@ -15258,7 +15298,7 @@
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E652" s="2" t="n">
         <f aca="false">A652 +1000</f>
@@ -15276,7 +15316,7 @@
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E653" s="2" t="n">
         <f aca="false">A653 +1000</f>
@@ -15294,7 +15334,7 @@
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>9</v>
@@ -15303,7 +15343,7 @@
         <v>9</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E654" s="2" t="n">
         <f aca="false">A654 +1000</f>
@@ -15321,7 +15361,7 @@
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E655" s="2" t="n">
         <f aca="false">A655 +1000</f>
@@ -15339,7 +15379,7 @@
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E656" s="2" t="n">
         <f aca="false">A656 +1000</f>
@@ -15357,7 +15397,7 @@
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E657" s="2" t="n">
         <f aca="false">A657 +1000</f>
@@ -15375,7 +15415,7 @@
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E658" s="2" t="n">
         <f aca="false">A658 +1000</f>
@@ -15393,7 +15433,7 @@
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E659" s="2" t="n">
         <f aca="false">A659 +1000</f>
@@ -15411,7 +15451,7 @@
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E660" s="2" t="n">
         <f aca="false">A660 +1000</f>
@@ -15429,7 +15469,7 @@
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E661" s="2" t="n">
         <f aca="false">A661 +1000</f>
@@ -15447,7 +15487,7 @@
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E662" s="2" t="n">
         <f aca="false">A662 +1000</f>
@@ -15465,7 +15505,7 @@
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E663" s="2" t="n">
         <f aca="false">A663 +1000</f>
@@ -15483,7 +15523,7 @@
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E664" s="2" t="n">
         <f aca="false">A664 +1000</f>
@@ -15501,7 +15541,7 @@
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E665" s="2" t="n">
         <f aca="false">A665 +1000</f>
@@ -15519,7 +15559,7 @@
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E666" s="2" t="n">
         <f aca="false">A666 +1000</f>
@@ -15537,7 +15577,7 @@
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E667" s="2" t="n">
         <f aca="false">A667 +1000</f>
@@ -15555,7 +15595,7 @@
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E668" s="2" t="n">
         <f aca="false">A668 +1000</f>
@@ -15573,7 +15613,7 @@
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E669" s="2" t="n">
         <f aca="false">A669 +1000</f>
@@ -15591,7 +15631,7 @@
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E670" s="2" t="n">
         <f aca="false">A670 +1000</f>
@@ -15609,7 +15649,7 @@
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E671" s="2" t="n">
         <f aca="false">A671 +1000</f>
@@ -15627,7 +15667,7 @@
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E672" s="2" t="n">
         <f aca="false">A672 +1000</f>
@@ -15645,7 +15685,7 @@
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E673" s="2" t="n">
         <f aca="false">A673 +1000</f>
@@ -15663,7 +15703,7 @@
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E674" s="2" t="n">
         <f aca="false">A674 +1000</f>
@@ -15681,7 +15721,7 @@
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E675" s="2" t="n">
         <f aca="false">A675 +1000</f>
@@ -15699,7 +15739,7 @@
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E676" s="2" t="n">
         <f aca="false">A676 +1000</f>
@@ -15717,7 +15757,7 @@
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E677" s="2" t="n">
         <f aca="false">A677 +1000</f>
@@ -15735,7 +15775,7 @@
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E678" s="2" t="n">
         <f aca="false">A678 +1000</f>
@@ -15753,7 +15793,7 @@
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E679" s="2" t="n">
         <f aca="false">A679 +1000</f>
@@ -15771,7 +15811,7 @@
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E680" s="2" t="n">
         <f aca="false">A680 +1000</f>
@@ -15789,7 +15829,7 @@
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E681" s="2" t="n">
         <f aca="false">A681 +1000</f>
@@ -15807,7 +15847,7 @@
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E682" s="2" t="n">
         <f aca="false">A682 +1000</f>
@@ -15825,7 +15865,7 @@
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E683" s="2" t="n">
         <f aca="false">A683 +1000</f>
@@ -15843,7 +15883,7 @@
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E684" s="2" t="n">
         <f aca="false">A684 +1000</f>
@@ -15861,7 +15901,7 @@
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E685" s="2" t="n">
         <f aca="false">A685 +1000</f>
@@ -15879,7 +15919,7 @@
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E686" s="2" t="n">
         <f aca="false">A686 +1000</f>
@@ -15897,7 +15937,7 @@
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E687" s="2" t="n">
         <f aca="false">A687 +1000</f>
@@ -15915,7 +15955,7 @@
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E688" s="2" t="n">
         <f aca="false">A688 +1000</f>
@@ -15933,7 +15973,7 @@
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E689" s="2" t="n">
         <f aca="false">A689 +1000</f>
@@ -15951,7 +15991,7 @@
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E690" s="2" t="n">
         <f aca="false">A690 +1000</f>
@@ -15969,7 +16009,7 @@
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E691" s="2" t="n">
         <f aca="false">A691 +1000</f>
@@ -15987,7 +16027,7 @@
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E692" s="2" t="n">
         <f aca="false">A692 +1000</f>
@@ -16005,7 +16045,7 @@
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E693" s="2" t="n">
         <f aca="false">A693 +1000</f>
@@ -16023,7 +16063,7 @@
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E694" s="2" t="n">
         <f aca="false">A694 +1000</f>
@@ -16041,7 +16081,7 @@
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E695" s="2" t="n">
         <f aca="false">A695 +1000</f>
@@ -16059,7 +16099,7 @@
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E696" s="2" t="n">
         <f aca="false">A696 +1000</f>
@@ -16077,7 +16117,7 @@
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E697" s="2" t="n">
         <f aca="false">A697 +1000</f>
@@ -16095,7 +16135,7 @@
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E698" s="2" t="n">
         <f aca="false">A698 +1000</f>
@@ -16113,7 +16153,7 @@
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E699" s="2" t="n">
         <f aca="false">A699 +1000</f>
@@ -16131,7 +16171,7 @@
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E700" s="2" t="n">
         <f aca="false">A700 +1000</f>
@@ -16149,7 +16189,7 @@
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>9</v>
@@ -16173,7 +16213,7 @@
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>9</v>
@@ -16197,7 +16237,7 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>9</v>
@@ -16221,7 +16261,7 @@
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>9</v>
@@ -16245,7 +16285,7 @@
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E705" s="2" t="n">
         <f aca="false">A705 +1000</f>
@@ -16263,7 +16303,7 @@
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E706" s="2" t="n">
         <f aca="false">A706 +1000</f>
@@ -16281,7 +16321,7 @@
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E707" s="2" t="n">
         <f aca="false">A707 +1000</f>
@@ -16299,7 +16339,7 @@
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
@@ -16317,7 +16357,7 @@
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E709" s="2" t="n">
         <f aca="false">A709 +1000</f>
@@ -16335,7 +16375,7 @@
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E710" s="2" t="n">
         <f aca="false">A710 +1000</f>
@@ -16353,7 +16393,7 @@
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E711" s="2" t="n">
         <f aca="false">A711 +1000</f>
@@ -16371,7 +16411,7 @@
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E712" s="2" t="n">
         <f aca="false">A712 +1000</f>
@@ -16389,7 +16429,7 @@
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E713" s="2" t="n">
         <f aca="false">A713 +1000</f>
@@ -16407,7 +16447,7 @@
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E714" s="2" t="n">
         <f aca="false">A714 +1000</f>
@@ -16425,7 +16465,7 @@
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E715" s="2" t="n">
         <f aca="false">A715 +1000</f>
@@ -16443,7 +16483,7 @@
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E716" s="2" t="n">
         <f aca="false">A716 +1000</f>
@@ -16461,7 +16501,7 @@
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E717" s="2" t="n">
         <f aca="false">A717 +1000</f>
@@ -16479,7 +16519,7 @@
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E718" s="2" t="n">
         <f aca="false">A718 +1000</f>
@@ -16497,7 +16537,7 @@
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E719" s="2" t="n">
         <f aca="false">A719 +1000</f>
@@ -16515,7 +16555,7 @@
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E720" s="2" t="n">
         <f aca="false">A720 +1000</f>
@@ -16533,7 +16573,7 @@
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E721" s="2" t="n">
         <f aca="false">A721 +1000</f>
@@ -16551,7 +16591,7 @@
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E722" s="2" t="n">
         <f aca="false">A722 +1000</f>
@@ -16569,7 +16609,7 @@
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E723" s="2" t="n">
         <f aca="false">A723 +1000</f>
@@ -16587,7 +16627,7 @@
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E724" s="2" t="n">
         <f aca="false">A724 +1000</f>
@@ -16605,7 +16645,7 @@
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E725" s="2" t="n">
         <f aca="false">A725 +1000</f>
@@ -16623,7 +16663,7 @@
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E726" s="2" t="n">
         <f aca="false">A726 +1000</f>
@@ -16641,7 +16681,7 @@
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E727" s="2" t="n">
         <f aca="false">A727 +1000</f>
@@ -16659,7 +16699,7 @@
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E728" s="2" t="n">
         <f aca="false">A728 +1000</f>
@@ -16677,7 +16717,7 @@
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E729" s="2" t="n">
         <f aca="false">A729 +1000</f>
@@ -16695,7 +16735,7 @@
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E730" s="2" t="n">
         <f aca="false">A730 +1000</f>
@@ -16713,7 +16753,7 @@
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E731" s="2" t="n">
         <f aca="false">A731 +1000</f>
@@ -16731,7 +16771,7 @@
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E732" s="2" t="n">
         <f aca="false">A732 +1000</f>
@@ -16749,7 +16789,7 @@
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E733" s="2" t="n">
         <f aca="false">A733 +1000</f>
@@ -16767,7 +16807,7 @@
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E734" s="2" t="n">
         <f aca="false">A734 +1000</f>
@@ -16785,7 +16825,7 @@
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E735" s="2" t="n">
         <f aca="false">A735 +1000</f>
@@ -16803,7 +16843,7 @@
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E736" s="2" t="n">
         <f aca="false">A736 +1000</f>
@@ -16821,7 +16861,7 @@
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E737" s="2" t="n">
         <f aca="false">A737 +1000</f>
@@ -16839,7 +16879,7 @@
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E738" s="2" t="n">
         <f aca="false">A738 +1000</f>
@@ -16857,7 +16897,7 @@
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E739" s="2" t="n">
         <f aca="false">A739 +1000</f>
@@ -16875,7 +16915,7 @@
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E740" s="2" t="n">
         <f aca="false">A740 +1000</f>
@@ -16893,7 +16933,7 @@
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E741" s="2" t="n">
         <f aca="false">A741 +1000</f>
@@ -16911,7 +16951,7 @@
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E742" s="2" t="n">
         <f aca="false">A742 +1000</f>
@@ -16929,7 +16969,7 @@
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E743" s="2" t="n">
         <f aca="false">A743 +1000</f>
@@ -16947,7 +16987,7 @@
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E744" s="2" t="n">
         <f aca="false">A744 +1000</f>
@@ -16965,7 +17005,7 @@
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E745" s="2" t="n">
         <f aca="false">A745 +1000</f>
@@ -16983,7 +17023,7 @@
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E746" s="2" t="n">
         <f aca="false">A746 +1000</f>
@@ -17001,7 +17041,7 @@
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E747" s="2" t="n">
         <f aca="false">A747 +1000</f>
@@ -17019,7 +17059,7 @@
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E748" s="2" t="n">
         <f aca="false">A748 +1000</f>
@@ -17037,7 +17077,7 @@
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E749" s="2" t="n">
         <f aca="false">A749 +1000</f>
@@ -17055,7 +17095,7 @@
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E750" s="2" t="n">
         <f aca="false">A750 +1000</f>
@@ -17073,7 +17113,7 @@
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E751" s="2" t="n">
         <f aca="false">A751 +1000</f>
@@ -17091,7 +17131,7 @@
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E752" s="2" t="n">
         <f aca="false">A752 +1000</f>
@@ -17109,7 +17149,7 @@
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E753" s="2" t="n">
         <f aca="false">A753 +1000</f>
@@ -17127,7 +17167,7 @@
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E754" s="2" t="n">
         <f aca="false">A754 +1000</f>
@@ -17145,7 +17185,7 @@
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E755" s="2" t="n">
         <f aca="false">A755 +1000</f>
@@ -17163,7 +17203,7 @@
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E756" s="2" t="n">
         <f aca="false">A756 +1000</f>
@@ -17181,7 +17221,7 @@
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E757" s="2" t="n">
         <f aca="false">A757 +1000</f>
@@ -17199,7 +17239,7 @@
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E758" s="2" t="n">
         <f aca="false">A758 +1000</f>
@@ -17217,7 +17257,7 @@
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E759" s="2" t="n">
         <f aca="false">A759 +1000</f>
@@ -17235,7 +17275,7 @@
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E760" s="2" t="n">
         <f aca="false">A760 +1000</f>
@@ -17253,7 +17293,7 @@
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E761" s="2" t="n">
         <f aca="false">A761 +1000</f>
@@ -17271,7 +17311,7 @@
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E762" s="2" t="n">
         <f aca="false">A762 +1000</f>
@@ -17289,7 +17329,7 @@
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E763" s="2" t="n">
         <f aca="false">A763 +1000</f>
@@ -17307,7 +17347,7 @@
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E764" s="2" t="n">
         <f aca="false">A764 +1000</f>
@@ -17325,7 +17365,7 @@
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E765" s="2" t="n">
         <f aca="false">A765 +1000</f>
@@ -17343,7 +17383,7 @@
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E766" s="2" t="n">
         <f aca="false">A766 +1000</f>
@@ -17361,7 +17401,7 @@
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E767" s="2" t="n">
         <f aca="false">A767 +1000</f>
@@ -17379,7 +17419,7 @@
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E768" s="2" t="n">
         <f aca="false">A768 +1000</f>
@@ -17397,7 +17437,7 @@
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E769" s="2" t="n">
         <f aca="false">A769 +1000</f>
@@ -17415,7 +17455,7 @@
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E770" s="2" t="n">
         <f aca="false">A770 +1000</f>
@@ -17433,7 +17473,7 @@
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E771" s="2" t="n">
         <f aca="false">A771 +1000</f>
@@ -17451,7 +17491,7 @@
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E772" s="2" t="n">
         <f aca="false">A772 +1000</f>
@@ -17469,7 +17509,7 @@
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E773" s="2" t="n">
         <f aca="false">A773 +1000</f>
@@ -17487,7 +17527,7 @@
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E774" s="2" t="n">
         <f aca="false">A774 +1000</f>
@@ -17505,7 +17545,7 @@
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E775" s="2" t="n">
         <f aca="false">A775 +1000</f>
@@ -17523,7 +17563,7 @@
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E776" s="2" t="n">
         <f aca="false">A776 +1000</f>
@@ -17541,7 +17581,7 @@
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E777" s="2" t="n">
         <f aca="false">A777 +1000</f>
@@ -17559,7 +17599,7 @@
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E778" s="2" t="n">
         <f aca="false">A778 +1000</f>
@@ -17577,7 +17617,7 @@
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E779" s="2" t="n">
         <f aca="false">A779 +1000</f>
@@ -17595,7 +17635,7 @@
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E780" s="2" t="n">
         <f aca="false">A780 +1000</f>
@@ -17613,7 +17653,7 @@
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E781" s="2" t="n">
         <f aca="false">A781 +1000</f>
@@ -17631,7 +17671,7 @@
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E782" s="2" t="n">
         <f aca="false">A782 +1000</f>
@@ -17649,7 +17689,7 @@
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E783" s="2" t="n">
         <f aca="false">A783 +1000</f>
@@ -17667,7 +17707,7 @@
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E784" s="2" t="n">
         <f aca="false">A784 +1000</f>
@@ -17685,7 +17725,7 @@
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E785" s="2" t="n">
         <f aca="false">A785 +1000</f>
@@ -17703,7 +17743,7 @@
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E786" s="2" t="n">
         <f aca="false">A786 +1000</f>
@@ -17721,7 +17761,7 @@
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E787" s="2" t="n">
         <f aca="false">A787 +1000</f>
@@ -17739,7 +17779,7 @@
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E788" s="2" t="n">
         <f aca="false">A788 +1000</f>
@@ -17757,7 +17797,7 @@
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E789" s="2" t="n">
         <f aca="false">A789 +1000</f>
@@ -17775,7 +17815,7 @@
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E790" s="2" t="n">
         <f aca="false">A790 +1000</f>
@@ -17793,7 +17833,7 @@
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E791" s="2" t="n">
         <f aca="false">A791 +1000</f>
@@ -17811,7 +17851,7 @@
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E792" s="2" t="n">
         <f aca="false">A792 +1000</f>
@@ -17829,7 +17869,7 @@
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E793" s="2" t="n">
         <f aca="false">A793 +1000</f>
@@ -17847,7 +17887,7 @@
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E794" s="2" t="n">
         <f aca="false">A794 +1000</f>
@@ -17865,7 +17905,7 @@
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E795" s="2" t="n">
         <f aca="false">A795 +1000</f>
@@ -17883,7 +17923,7 @@
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E796" s="2" t="n">
         <f aca="false">A796 +1000</f>
@@ -17901,7 +17941,7 @@
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E797" s="2" t="n">
         <f aca="false">A797 +1000</f>
@@ -17919,7 +17959,7 @@
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E798" s="2" t="n">
         <f aca="false">A798 +1000</f>
@@ -17937,7 +17977,7 @@
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E799" s="2" t="n">
         <f aca="false">A799 +1000</f>
@@ -17955,7 +17995,7 @@
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E800" s="2" t="n">
         <f aca="false">A800 +1000</f>
@@ -17973,7 +18013,7 @@
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E801" s="2" t="n">
         <f aca="false">A801 +1000</f>
@@ -17991,7 +18031,7 @@
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E802" s="2" t="n">
         <f aca="false">A802 +1000</f>
@@ -18009,7 +18049,7 @@
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E803" s="2" t="n">
         <f aca="false">A803 +1000</f>
@@ -18027,7 +18067,7 @@
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E804" s="2" t="n">
         <f aca="false">A804 +1000</f>
@@ -18045,7 +18085,7 @@
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E805" s="2" t="n">
         <f aca="false">A805 +1000</f>
@@ -18063,7 +18103,7 @@
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E806" s="2" t="n">
         <f aca="false">A806 +1000</f>
@@ -18081,7 +18121,7 @@
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E807" s="2" t="n">
         <f aca="false">A807 +1000</f>
@@ -18099,7 +18139,7 @@
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E808" s="2" t="n">
         <f aca="false">A808 +1000</f>
@@ -18117,7 +18157,7 @@
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E809" s="2" t="n">
         <f aca="false">A809 +1000</f>
@@ -18135,7 +18175,7 @@
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E810" s="2" t="n">
         <f aca="false">A810 +1000</f>
@@ -18153,7 +18193,7 @@
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E811" s="2" t="n">
         <f aca="false">A811 +1000</f>
@@ -18171,7 +18211,7 @@
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E812" s="2" t="n">
         <f aca="false">A812 +1000</f>
@@ -18189,7 +18229,7 @@
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E813" s="2" t="n">
         <f aca="false">A813 +1000</f>
@@ -18207,7 +18247,7 @@
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E814" s="2" t="n">
         <f aca="false">A814 +1000</f>
@@ -18225,7 +18265,7 @@
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E815" s="2" t="n">
         <f aca="false">A815 +1000</f>
@@ -18243,7 +18283,7 @@
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E816" s="2" t="n">
         <f aca="false">A816 +1000</f>
@@ -18261,7 +18301,7 @@
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E817" s="2" t="n">
         <f aca="false">A817 +1000</f>
@@ -18279,7 +18319,7 @@
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E818" s="2" t="n">
         <f aca="false">A818 +1000</f>
@@ -18297,7 +18337,7 @@
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E819" s="2" t="n">
         <f aca="false">A819 +1000</f>
@@ -18315,7 +18355,7 @@
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E820" s="2" t="n">
         <f aca="false">A820 +1000</f>
@@ -18333,7 +18373,7 @@
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E821" s="2" t="n">
         <f aca="false">A821 +1000</f>
@@ -18351,7 +18391,7 @@
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E822" s="2" t="n">
         <f aca="false">A822 +1000</f>
@@ -18369,7 +18409,7 @@
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E823" s="2" t="n">
         <f aca="false">A823 +1000</f>
@@ -18387,7 +18427,7 @@
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E824" s="2" t="n">
         <f aca="false">A824 +1000</f>
@@ -18405,7 +18445,7 @@
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E825" s="2" t="n">
         <f aca="false">A825 +1000</f>
@@ -18423,7 +18463,7 @@
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E826" s="2" t="n">
         <f aca="false">A826 +1000</f>
@@ -18441,7 +18481,7 @@
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E827" s="2" t="n">
         <f aca="false">A827 +1000</f>
@@ -18459,7 +18499,7 @@
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E828" s="2" t="n">
         <f aca="false">A828 +1000</f>
@@ -18477,7 +18517,7 @@
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E829" s="2" t="n">
         <f aca="false">A829 +1000</f>
@@ -18495,7 +18535,7 @@
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E830" s="2" t="n">
         <f aca="false">A830 +1000</f>
@@ -18513,7 +18553,7 @@
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E831" s="2" t="n">
         <f aca="false">A831 +1000</f>
@@ -18531,7 +18571,7 @@
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E832" s="2" t="n">
         <f aca="false">A832 +1000</f>
@@ -18549,7 +18589,7 @@
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E833" s="2" t="n">
         <f aca="false">A833 +1000</f>
@@ -18567,7 +18607,7 @@
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E834" s="2" t="n">
         <f aca="false">A834 +1000</f>
@@ -18585,7 +18625,7 @@
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E835" s="2" t="n">
         <f aca="false">A835 +1000</f>
@@ -18603,7 +18643,7 @@
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E836" s="2" t="n">
         <f aca="false">A836 +1000</f>
@@ -18621,7 +18661,7 @@
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E837" s="2" t="n">
         <f aca="false">A837 +1000</f>
@@ -18639,7 +18679,7 @@
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E838" s="2" t="n">
         <f aca="false">A838 +1000</f>
@@ -18657,7 +18697,7 @@
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E839" s="2" t="n">
         <f aca="false">A839 +1000</f>
@@ -18675,7 +18715,7 @@
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E840" s="2" t="n">
         <f aca="false">A840 +1000</f>
@@ -18693,7 +18733,7 @@
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E841" s="2" t="n">
         <f aca="false">A841 +1000</f>
@@ -18711,7 +18751,7 @@
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E842" s="2" t="n">
         <f aca="false">A842 +1000</f>
@@ -18729,7 +18769,7 @@
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E843" s="2" t="n">
         <f aca="false">A843 +1000</f>
@@ -18747,7 +18787,7 @@
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E844" s="2" t="n">
         <f aca="false">A844 +1000</f>
@@ -18765,7 +18805,7 @@
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E845" s="2" t="n">
         <f aca="false">A845 +1000</f>
@@ -18783,7 +18823,7 @@
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E846" s="2" t="n">
         <f aca="false">A846 +1000</f>
@@ -18801,7 +18841,7 @@
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B847" s="3" t="s">
         <v>9</v>
@@ -18810,7 +18850,7 @@
         <v>9</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E847" s="2" t="n">
         <f aca="false">A847 +1000</f>
@@ -18828,7 +18868,7 @@
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E848" s="2" t="n">
         <f aca="false">A848 +1000</f>
@@ -18846,7 +18886,7 @@
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E849" s="2" t="n">
         <f aca="false">A849 +1000</f>
@@ -18864,7 +18904,7 @@
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E850" s="2" t="n">
         <f aca="false">A850 +1000</f>
@@ -18882,7 +18922,7 @@
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E851" s="2" t="n">
         <f aca="false">A851 +1000</f>
@@ -18900,7 +18940,7 @@
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E852" s="2" t="n">
         <f aca="false">A852 +1000</f>
@@ -18918,7 +18958,7 @@
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E853" s="2" t="n">
         <f aca="false">A853 +1000</f>
@@ -18936,7 +18976,7 @@
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E854" s="2" t="n">
         <f aca="false">A854 +1000</f>
@@ -18954,7 +18994,7 @@
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E855" s="2" t="n">
         <f aca="false">A855 +1000</f>
@@ -18972,7 +19012,7 @@
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E856" s="2" t="n">
         <f aca="false">A856 +1000</f>
@@ -18990,7 +19030,7 @@
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E857" s="2" t="n">
         <f aca="false">A857 +1000</f>
@@ -19008,7 +19048,7 @@
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E858" s="2" t="n">
         <f aca="false">A858 +1000</f>
@@ -19026,7 +19066,7 @@
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E859" s="2" t="n">
         <f aca="false">A859 +1000</f>
@@ -19044,7 +19084,7 @@
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E860" s="2" t="n">
         <f aca="false">A860 +1000</f>
@@ -19062,7 +19102,7 @@
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E861" s="2" t="n">
         <f aca="false">A861 +1000</f>
@@ -19080,7 +19120,7 @@
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E862" s="2" t="n">
         <f aca="false">A862 +1000</f>
@@ -19098,7 +19138,7 @@
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E863" s="2" t="n">
         <f aca="false">A863 +1000</f>
@@ -19116,7 +19156,7 @@
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E864" s="2" t="n">
         <f aca="false">A864 +1000</f>
@@ -19134,7 +19174,7 @@
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E865" s="2" t="n">
         <f aca="false">A865 +1000</f>
@@ -19152,7 +19192,7 @@
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E866" s="2" t="n">
         <f aca="false">A866 +1000</f>
@@ -19170,7 +19210,7 @@
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E867" s="2" t="n">
         <f aca="false">A867 +1000</f>
@@ -19188,7 +19228,7 @@
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E868" s="2" t="n">
         <f aca="false">A868 +1000</f>
@@ -19206,7 +19246,7 @@
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E869" s="2" t="n">
         <f aca="false">A869 +1000</f>
@@ -19224,7 +19264,7 @@
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E870" s="2" t="n">
         <f aca="false">A870 +1000</f>
@@ -19242,7 +19282,7 @@
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E871" s="2" t="n">
         <f aca="false">A871 +1000</f>
@@ -19260,7 +19300,7 @@
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E872" s="2" t="n">
         <f aca="false">A872 +1000</f>
@@ -19278,7 +19318,7 @@
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E873" s="2" t="n">
         <f aca="false">A873 +1000</f>
@@ -19296,7 +19336,7 @@
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E874" s="2" t="n">
         <f aca="false">A874 +1000</f>
@@ -19314,7 +19354,7 @@
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E875" s="2" t="n">
         <f aca="false">A875 +1000</f>
@@ -19332,7 +19372,7 @@
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E876" s="2" t="n">
         <f aca="false">A876 +1000</f>
@@ -19350,7 +19390,7 @@
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E877" s="2" t="n">
         <f aca="false">A877 +1000</f>
@@ -19368,7 +19408,7 @@
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E878" s="2" t="n">
         <f aca="false">A878 +1000</f>
@@ -19386,7 +19426,7 @@
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E879" s="2" t="n">
         <f aca="false">A879 +1000</f>
@@ -19404,7 +19444,7 @@
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E880" s="2" t="n">
         <f aca="false">A880 +1000</f>
@@ -19422,7 +19462,7 @@
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E881" s="2" t="n">
         <f aca="false">A881 +1000</f>
@@ -19440,7 +19480,7 @@
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E882" s="2" t="n">
         <f aca="false">A882 +1000</f>
@@ -19458,7 +19498,7 @@
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E883" s="2" t="n">
         <f aca="false">A883 +1000</f>
@@ -19476,7 +19516,7 @@
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E884" s="2" t="n">
         <f aca="false">A884 +1000</f>
@@ -19494,7 +19534,7 @@
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E885" s="2" t="n">
         <f aca="false">A885 +1000</f>
@@ -19512,7 +19552,7 @@
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E886" s="2" t="n">
         <f aca="false">A886 +1000</f>
@@ -19530,7 +19570,7 @@
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E887" s="2" t="n">
         <f aca="false">A887 +1000</f>
@@ -19548,7 +19588,7 @@
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E888" s="2" t="n">
         <f aca="false">A888 +1000</f>
@@ -19566,7 +19606,7 @@
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E889" s="2" t="n">
         <f aca="false">A889 +1000</f>
@@ -19584,7 +19624,7 @@
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E890" s="2" t="n">
         <f aca="false">A890 +1000</f>
@@ -19602,7 +19642,7 @@
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E891" s="2" t="n">
         <f aca="false">A891 +1000</f>
@@ -19620,7 +19660,7 @@
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E892" s="2" t="n">
         <f aca="false">A892 +1000</f>
@@ -19638,7 +19678,7 @@
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E893" s="2" t="n">
         <f aca="false">A893 +1000</f>
@@ -19656,7 +19696,7 @@
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E894" s="2" t="n">
         <f aca="false">A894 +1000</f>
@@ -19674,7 +19714,7 @@
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E895" s="2" t="n">
         <f aca="false">A895 +1000</f>
@@ -19692,7 +19732,7 @@
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E896" s="2" t="n">
         <f aca="false">A896 +1000</f>
@@ -19710,7 +19750,7 @@
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E897" s="2" t="n">
         <f aca="false">A897 +1000</f>
@@ -19728,7 +19768,7 @@
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E898" s="2" t="n">
         <f aca="false">A898 +1000</f>
@@ -19746,7 +19786,7 @@
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E899" s="2" t="n">
         <f aca="false">A899 +1000</f>
@@ -19764,7 +19804,7 @@
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E900" s="2" t="n">
         <f aca="false">A900 +1000</f>
@@ -19782,7 +19822,7 @@
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E901" s="2" t="n">
         <f aca="false">A901 +1000</f>
@@ -19800,7 +19840,7 @@
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E902" s="2" t="n">
         <f aca="false">A902 +1000</f>
@@ -19818,7 +19858,7 @@
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E903" s="2" t="n">
         <f aca="false">A903 +1000</f>
@@ -19836,7 +19876,7 @@
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E904" s="2" t="n">
         <f aca="false">A904 +1000</f>
@@ -19854,7 +19894,7 @@
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E905" s="2" t="n">
         <f aca="false">A905 +1000</f>
@@ -19872,7 +19912,7 @@
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E906" s="2" t="n">
         <f aca="false">A906 +1000</f>
@@ -19890,7 +19930,7 @@
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E907" s="2" t="n">
         <f aca="false">A907 +1000</f>
@@ -19908,7 +19948,7 @@
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E908" s="2" t="n">
         <f aca="false">A908 +1000</f>
@@ -19926,7 +19966,7 @@
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E909" s="2" t="n">
         <f aca="false">A909 +1000</f>
@@ -19944,7 +19984,7 @@
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E910" s="2" t="n">
         <f aca="false">A910 +1000</f>
@@ -19962,7 +20002,7 @@
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E911" s="2" t="n">
         <f aca="false">A911 +1000</f>
@@ -19980,7 +20020,7 @@
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E912" s="2" t="n">
         <f aca="false">A912 +1000</f>
@@ -19998,7 +20038,7 @@
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E913" s="2" t="n">
         <f aca="false">A913 +1000</f>
@@ -20016,7 +20056,7 @@
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E914" s="2" t="n">
         <f aca="false">A914 +1000</f>
@@ -20034,7 +20074,7 @@
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E915" s="2" t="n">
         <f aca="false">A915 +1000</f>
@@ -20052,7 +20092,7 @@
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E916" s="2" t="n">
         <f aca="false">A916 +1000</f>
@@ -20070,7 +20110,7 @@
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E917" s="2" t="n">
         <f aca="false">A917 +1000</f>
@@ -20088,7 +20128,7 @@
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E918" s="2" t="n">
         <f aca="false">A918 +1000</f>
@@ -20106,7 +20146,7 @@
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E919" s="2" t="n">
         <f aca="false">A919 +1000</f>
@@ -20124,7 +20164,7 @@
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E920" s="2" t="n">
         <f aca="false">A920 +1000</f>
@@ -20142,7 +20182,7 @@
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E921" s="2" t="n">
         <f aca="false">A921 +1000</f>
@@ -20160,7 +20200,7 @@
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E922" s="2" t="n">
         <f aca="false">A922 +1000</f>
@@ -20178,7 +20218,7 @@
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E923" s="2" t="n">
         <f aca="false">A923 +1000</f>
@@ -20196,7 +20236,7 @@
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E924" s="2" t="n">
         <f aca="false">A924 +1000</f>
@@ -20214,7 +20254,7 @@
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E925" s="2" t="n">
         <f aca="false">A925 +1000</f>
@@ -20232,7 +20272,7 @@
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E926" s="2" t="n">
         <f aca="false">A926 +1000</f>
@@ -20250,7 +20290,7 @@
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E927" s="2" t="n">
         <f aca="false">A927 +1000</f>
@@ -20268,7 +20308,7 @@
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E928" s="2" t="n">
         <f aca="false">A928 +1000</f>
@@ -20286,7 +20326,7 @@
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E929" s="2" t="n">
         <f aca="false">A929 +1000</f>
@@ -20304,7 +20344,7 @@
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="E930" s="2" t="n">
         <f aca="false">A930 +1000</f>
@@ -20322,7 +20362,7 @@
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E931" s="2" t="n">
         <f aca="false">A931 +1000</f>
@@ -20340,7 +20380,7 @@
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E932" s="2" t="n">
         <f aca="false">A932 +1000</f>
@@ -20358,7 +20398,7 @@
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E933" s="2" t="n">
         <f aca="false">A933 +1000</f>
@@ -20376,7 +20416,7 @@
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E934" s="2" t="n">
         <f aca="false">A934 +1000</f>
@@ -20394,7 +20434,7 @@
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E935" s="2" t="n">
         <f aca="false">A935 +1000</f>
@@ -20412,7 +20452,7 @@
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E936" s="2" t="n">
         <f aca="false">A936 +1000</f>
@@ -20430,7 +20470,7 @@
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E937" s="2" t="n">
         <f aca="false">A937 +1000</f>
@@ -20448,7 +20488,7 @@
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E938" s="2" t="n">
         <f aca="false">A938 +1000</f>
@@ -20466,7 +20506,7 @@
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E939" s="2" t="n">
         <f aca="false">A939 +1000</f>
@@ -20484,7 +20524,7 @@
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="E940" s="2" t="n">
         <f aca="false">A940 +1000</f>
@@ -20502,7 +20542,7 @@
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E941" s="2" t="n">
         <f aca="false">A941 +1000</f>
@@ -20520,7 +20560,7 @@
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="E942" s="2" t="n">
         <f aca="false">A942 +1000</f>
@@ -20538,7 +20578,7 @@
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E943" s="2" t="n">
         <f aca="false">A943 +1000</f>
@@ -20556,7 +20596,7 @@
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E944" s="2" t="n">
         <f aca="false">A944 +1000</f>
@@ -20574,7 +20614,7 @@
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E945" s="2" t="n">
         <f aca="false">A945 +1000</f>
@@ -20592,7 +20632,7 @@
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E946" s="2" t="n">
         <f aca="false">A946 +1000</f>
@@ -20610,7 +20650,7 @@
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E947" s="2" t="n">
         <f aca="false">A947 +1000</f>
@@ -20628,7 +20668,7 @@
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E948" s="2" t="n">
         <f aca="false">A948 +1000</f>
@@ -20646,7 +20686,7 @@
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E949" s="2" t="n">
         <f aca="false">A949 +1000</f>
@@ -20664,7 +20704,7 @@
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E950" s="2" t="n">
         <f aca="false">A950 +1000</f>
@@ -20682,7 +20722,7 @@
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="E951" s="2" t="n">
         <f aca="false">A951 +1000</f>
@@ -20700,7 +20740,7 @@
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E952" s="2" t="n">
         <f aca="false">A952 +1000</f>
@@ -20718,7 +20758,7 @@
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E953" s="2" t="n">
         <f aca="false">A953 +1000</f>
@@ -20736,7 +20776,7 @@
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E954" s="2" t="n">
         <f aca="false">A954 +1000</f>
@@ -20754,7 +20794,7 @@
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E955" s="2" t="n">
         <f aca="false">A955 +1000</f>
@@ -20772,7 +20812,7 @@
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E956" s="2" t="n">
         <f aca="false">A956 +1000</f>
@@ -20790,7 +20830,7 @@
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E957" s="2" t="n">
         <f aca="false">A957 +1000</f>
@@ -20808,7 +20848,7 @@
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E958" s="2" t="n">
         <f aca="false">A958 +1000</f>
@@ -20826,7 +20866,7 @@
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E959" s="2" t="n">
         <f aca="false">A959 +1000</f>
@@ -20844,7 +20884,7 @@
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E960" s="2" t="n">
         <f aca="false">A960 +1000</f>
@@ -20862,7 +20902,7 @@
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E961" s="2" t="n">
         <f aca="false">A961 +1000</f>
@@ -20880,7 +20920,7 @@
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E962" s="2" t="n">
         <f aca="false">A962 +1000</f>
@@ -20898,7 +20938,7 @@
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E963" s="2" t="n">
         <f aca="false">A963 +1000</f>
@@ -20916,7 +20956,7 @@
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E964" s="2" t="n">
         <f aca="false">A964 +1000</f>
@@ -20934,7 +20974,7 @@
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E965" s="2" t="n">
         <f aca="false">A965 +1000</f>
@@ -20952,7 +20992,7 @@
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E966" s="2" t="n">
         <f aca="false">A966 +1000</f>
@@ -20970,7 +21010,7 @@
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E967" s="2" t="n">
         <f aca="false">A967 +1000</f>
@@ -20988,7 +21028,7 @@
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E968" s="2" t="n">
         <f aca="false">A968 +1000</f>
@@ -21006,7 +21046,7 @@
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E969" s="2" t="n">
         <f aca="false">A969 +1000</f>
@@ -21024,7 +21064,7 @@
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E970" s="2" t="n">
         <f aca="false">A970 +1000</f>
@@ -21042,7 +21082,7 @@
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E971" s="2" t="n">
         <f aca="false">A971 +1000</f>
@@ -21060,7 +21100,7 @@
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E972" s="2" t="n">
         <f aca="false">A972 +1000</f>
@@ -21078,7 +21118,7 @@
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E973" s="2" t="n">
         <f aca="false">A973 +1000</f>
@@ -21096,7 +21136,7 @@
     </row>
     <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="E974" s="2" t="n">
         <f aca="false">A974 +1000</f>
@@ -21120,7 +21160,7 @@
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E975" s="2" t="n">
         <f aca="false">A975 +1000</f>
@@ -21138,7 +21178,7 @@
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E976" s="2" t="n">
         <f aca="false">A976 +1000</f>
@@ -21156,7 +21196,7 @@
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E977" s="2" t="n">
         <f aca="false">A977 +1000</f>
@@ -21174,7 +21214,7 @@
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E978" s="2" t="n">
         <f aca="false">A978 +1000</f>
@@ -21192,7 +21232,7 @@
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E979" s="2" t="n">
         <f aca="false">A979 +1000</f>
@@ -21210,7 +21250,7 @@
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E980" s="2" t="n">
         <f aca="false">A980 +1000</f>
@@ -21228,7 +21268,7 @@
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E981" s="2" t="n">
         <f aca="false">A981 +1000</f>
@@ -21246,7 +21286,7 @@
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E982" s="2" t="n">
         <f aca="false">A982 +1000</f>
@@ -21264,7 +21304,7 @@
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E983" s="2" t="n">
         <f aca="false">A983 +1000</f>
@@ -21282,7 +21322,7 @@
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E984" s="2" t="n">
         <f aca="false">A984 +1000</f>
@@ -21300,7 +21340,7 @@
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E985" s="2" t="n">
         <f aca="false">A985 +1000</f>
@@ -21318,7 +21358,7 @@
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E986" s="2" t="n">
         <f aca="false">A986 +1000</f>
@@ -21336,7 +21376,7 @@
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E987" s="2" t="n">
         <f aca="false">A987 +1000</f>
@@ -21354,7 +21394,7 @@
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="E988" s="2" t="n">
         <f aca="false">A988 +1000</f>
@@ -21372,7 +21412,7 @@
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E989" s="2" t="n">
         <f aca="false">A989 +1000</f>
@@ -21390,7 +21430,7 @@
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E990" s="2" t="n">
         <f aca="false">A990 +1000</f>
@@ -21408,7 +21448,7 @@
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E991" s="2" t="n">
         <f aca="false">A991 +1000</f>
@@ -21426,7 +21466,7 @@
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E992" s="2" t="n">
         <f aca="false">A992 +1000</f>
@@ -21444,7 +21484,7 @@
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E993" s="2" t="n">
         <f aca="false">A993 +1000</f>
@@ -21462,7 +21502,7 @@
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E994" s="2" t="n">
         <f aca="false">A994 +1000</f>
@@ -21480,7 +21520,7 @@
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E995" s="2" t="n">
         <f aca="false">A995 +1000</f>
@@ -21498,7 +21538,7 @@
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E996" s="2" t="n">
         <f aca="false">A996 +1000</f>
@@ -21516,7 +21556,7 @@
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E997" s="2" t="n">
         <f aca="false">A997 +1000</f>
@@ -21534,7 +21574,7 @@
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E998" s="2" t="n">
         <f aca="false">A998 +1000</f>
@@ -21552,7 +21592,7 @@
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E999" s="2" t="n">
         <f aca="false">A999 +1000</f>
@@ -21570,7 +21610,7 @@
     </row>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E1000" s="2" t="n">
         <f aca="false">A1000 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="1012">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -11114,6 +11114,15 @@
       <c r="A422" s="1" t="s">
         <v>430</v>
       </c>
+      <c r="B422" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
         <v>1421</v>
@@ -16344,6 +16353,15 @@
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
         <v>1707</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G708" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H708" s="0" t="s">
+        <v>214</v>
       </c>
       <c r="I708" s="2" t="n">
         <f aca="false">E708 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="1013">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -34,6 +34,12 @@
     <t xml:space="preserve">0003</t>
   </si>
   <si>
+    <t xml:space="preserve">✅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sliding Window</t>
+  </si>
+  <si>
     <t xml:space="preserve">0004</t>
   </si>
   <si>
@@ -47,9 +53,6 @@
   </si>
   <si>
     <t xml:space="preserve">0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✅</t>
   </si>
   <si>
     <t xml:space="preserve">Use in &amp; pre </t>
@@ -3355,6 +3358,15 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="E4" s="2" t="n">
         <f aca="false">A4 +1000</f>
         <v>1003</v>
@@ -3373,12 +3385,21 @@
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="n">
         <f aca="false">A5 +1000</f>
         <v>1004</v>
       </c>
+      <c r="F5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="I5" s="2" t="n">
         <f aca="false">E5 +1000</f>
         <v>2004</v>
@@ -3393,7 +3414,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
         <f aca="false">A6 +1000</f>
@@ -3413,7 +3434,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <f aca="false">A7 +1000</f>
@@ -3433,7 +3454,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
         <f aca="false">A8 +1000</f>
@@ -3453,20 +3474,20 @@
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="n">
         <f aca="false">A9 +1000</f>
         <v>1008</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="2" t="n">
         <f aca="false">E9 +1000</f>
@@ -3482,7 +3503,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">A10 +1000</f>
@@ -3502,7 +3523,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">A11 +1000</f>
@@ -3522,7 +3543,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">A12 +1000</f>
@@ -3542,7 +3563,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">A13 +1000</f>
@@ -3562,7 +3583,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">A14 +1000</f>
@@ -3582,7 +3603,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2" t="n">
         <f aca="false">A15 +1000</f>
@@ -3602,7 +3623,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="n">
         <f aca="false">A16 +1000</f>
@@ -3622,7 +3643,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2" t="n">
         <f aca="false">A17 +1000</f>
@@ -3642,7 +3663,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2" t="n">
         <f aca="false">A18 +1000</f>
@@ -3660,7 +3681,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2" t="n">
         <f aca="false">A19 +1000</f>
@@ -3678,7 +3699,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="2" t="n">
         <f aca="false">A20 +1000</f>
@@ -3696,7 +3717,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" s="2" t="n">
         <f aca="false">A21 +1000</f>
@@ -3714,7 +3735,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="n">
         <f aca="false">A22 +1000</f>
@@ -3732,13 +3753,13 @@
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="n">
         <f aca="false">A23 +1000</f>
@@ -3756,13 +3777,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="n">
         <f aca="false">A24 +1000</f>
@@ -3780,7 +3801,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="2" t="n">
         <f aca="false">A25 +1000</f>
@@ -3798,7 +3819,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" s="2" t="n">
         <f aca="false">A26 +1000</f>
@@ -3816,7 +3837,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2" t="n">
         <f aca="false">A27 +1000</f>
@@ -3834,7 +3855,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="n">
         <f aca="false">A28 +1000</f>
@@ -3852,7 +3873,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="n">
         <f aca="false">A29 +1000</f>
@@ -3870,7 +3891,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">A30 +1000</f>
@@ -3888,7 +3909,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">A31 +1000</f>
@@ -3906,7 +3927,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">A32 +1000</f>
@@ -3924,7 +3945,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">A33 +1000</f>
@@ -3942,7 +3963,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2" t="n">
         <f aca="false">A34 +1000</f>
@@ -3960,7 +3981,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E35" s="2" t="n">
         <f aca="false">A35 +1000</f>
@@ -3978,7 +3999,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
         <f aca="false">A36 +1000</f>
@@ -3996,7 +4017,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="n">
         <f aca="false">A37 +1000</f>
@@ -4014,7 +4035,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E38" s="2" t="n">
         <f aca="false">A38 +1000</f>
@@ -4032,7 +4053,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="n">
         <f aca="false">A39 +1000</f>
@@ -4050,7 +4071,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E40" s="2" t="n">
         <f aca="false">A40 +1000</f>
@@ -4068,7 +4089,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E41" s="2" t="n">
         <f aca="false">A41 +1000</f>
@@ -4086,7 +4107,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E42" s="2" t="n">
         <f aca="false">A42 +1000</f>
@@ -4104,7 +4125,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E43" s="2" t="n">
         <f aca="false">A43 +1000</f>
@@ -4122,7 +4143,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E44" s="2" t="n">
         <f aca="false">A44 +1000</f>
@@ -4140,7 +4161,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E45" s="2" t="n">
         <f aca="false">A45 +1000</f>
@@ -4158,17 +4179,17 @@
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E46" s="2" t="n">
         <f aca="false">A46 +1000</f>
         <v>1045</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I46" s="2" t="n">
         <f aca="false">E46 +1000</f>
@@ -4182,7 +4203,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E47" s="2" t="n">
         <f aca="false">A47 +1000</f>
@@ -4200,7 +4221,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E48" s="2" t="n">
         <f aca="false">A48 +1000</f>
@@ -4218,7 +4239,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E49" s="2" t="n">
         <f aca="false">A49 +1000</f>
@@ -4236,7 +4257,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E50" s="2" t="n">
         <f aca="false">A50 +1000</f>
@@ -4254,7 +4275,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E51" s="2" t="n">
         <f aca="false">A51 +1000</f>
@@ -4272,7 +4293,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E52" s="2" t="n">
         <f aca="false">A52 +1000</f>
@@ -4290,7 +4311,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E53" s="2" t="n">
         <f aca="false">A53 +1000</f>
@@ -4308,7 +4329,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E54" s="2" t="n">
         <f aca="false">A54 +1000</f>
@@ -4326,7 +4347,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E55" s="2" t="n">
         <f aca="false">A55 +1000</f>
@@ -4344,7 +4365,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E56" s="2" t="n">
         <f aca="false">A56 +1000</f>
@@ -4362,7 +4383,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E57" s="2" t="n">
         <f aca="false">A57 +1000</f>
@@ -4380,7 +4401,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E58" s="2" t="n">
         <f aca="false">A58 +1000</f>
@@ -4398,7 +4419,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E59" s="2" t="n">
         <f aca="false">A59 +1000</f>
@@ -4416,7 +4437,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E60" s="2" t="n">
         <f aca="false">A60 +1000</f>
@@ -4434,7 +4455,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E61" s="2" t="n">
         <f aca="false">A61 +1000</f>
@@ -4452,7 +4473,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E62" s="2" t="n">
         <f aca="false">A62 +1000</f>
@@ -4470,7 +4491,7 @@
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E63" s="2" t="n">
         <f aca="false">A63 +1000</f>
@@ -4488,7 +4509,7 @@
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E64" s="2" t="n">
         <f aca="false">A64 +1000</f>
@@ -4506,7 +4527,7 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E65" s="2" t="n">
         <f aca="false">A65 +1000</f>
@@ -4524,7 +4545,7 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E66" s="2" t="n">
         <f aca="false">A66 +1000</f>
@@ -4542,7 +4563,7 @@
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E67" s="2" t="n">
         <f aca="false">A67 +1000</f>
@@ -4560,7 +4581,7 @@
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E68" s="2" t="n">
         <f aca="false">A68 +1000</f>
@@ -4578,7 +4599,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E69" s="2" t="n">
         <f aca="false">A69 +1000</f>
@@ -4596,7 +4617,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E70" s="2" t="n">
         <f aca="false">A70 +1000</f>
@@ -4614,7 +4635,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E71" s="2" t="n">
         <f aca="false">A71 +1000</f>
@@ -4632,7 +4653,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E72" s="2" t="n">
         <f aca="false">A72 +1000</f>
@@ -4650,7 +4671,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E73" s="2" t="n">
         <f aca="false">A73 +1000</f>
@@ -4668,7 +4689,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E74" s="2" t="n">
         <f aca="false">A74 +1000</f>
@@ -4686,7 +4707,7 @@
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2" t="n">
         <f aca="false">A75 +1000</f>
@@ -4704,7 +4725,7 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2" t="n">
         <f aca="false">A76 +1000</f>
@@ -4722,7 +4743,7 @@
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E77" s="2" t="n">
         <f aca="false">A77 +1000</f>
@@ -4740,7 +4761,7 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2" t="n">
         <f aca="false">A78 +1000</f>
@@ -4758,7 +4779,7 @@
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E79" s="2" t="n">
         <f aca="false">A79 +1000</f>
@@ -4776,7 +4797,7 @@
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2" t="n">
         <f aca="false">A80 +1000</f>
@@ -4794,7 +4815,7 @@
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E81" s="2" t="n">
         <f aca="false">A81 +1000</f>
@@ -4812,7 +4833,7 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E82" s="2" t="n">
         <f aca="false">A82 +1000</f>
@@ -4830,7 +4851,7 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E83" s="2" t="n">
         <f aca="false">A83 +1000</f>
@@ -4848,7 +4869,7 @@
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E84" s="2" t="n">
         <f aca="false">A84 +1000</f>
@@ -4866,7 +4887,7 @@
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E85" s="2" t="n">
         <f aca="false">A85 +1000</f>
@@ -4884,7 +4905,7 @@
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E86" s="2" t="n">
         <f aca="false">A86 +1000</f>
@@ -4902,7 +4923,7 @@
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E87" s="2" t="n">
         <f aca="false">A87 +1000</f>
@@ -4920,7 +4941,7 @@
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E88" s="2" t="n">
         <f aca="false">A88 +1000</f>
@@ -4938,7 +4959,7 @@
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E89" s="2" t="n">
         <f aca="false">A89 +1000</f>
@@ -4956,7 +4977,7 @@
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E90" s="2" t="n">
         <f aca="false">A90 +1000</f>
@@ -4974,7 +4995,7 @@
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E91" s="2" t="n">
         <f aca="false">A91 +1000</f>
@@ -4992,7 +5013,7 @@
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E92" s="2" t="n">
         <f aca="false">A92 +1000</f>
@@ -5010,7 +5031,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E93" s="2" t="n">
         <f aca="false">A93 +1000</f>
@@ -5028,7 +5049,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E94" s="2" t="n">
         <f aca="false">A94 +1000</f>
@@ -5046,7 +5067,7 @@
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E95" s="2" t="n">
         <f aca="false">A95 +1000</f>
@@ -5064,7 +5085,7 @@
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E96" s="2" t="n">
         <f aca="false">A96 +1000</f>
@@ -5082,7 +5103,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E97" s="2" t="n">
         <f aca="false">A97 +1000</f>
@@ -5100,7 +5121,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E98" s="2" t="n">
         <f aca="false">A98 +1000</f>
@@ -5118,16 +5139,16 @@
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E99" s="2" t="n">
         <f aca="false">A99 +1000</f>
@@ -5138,10 +5159,10 @@
         <v>2098</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M99" s="2" t="n">
         <f aca="false">I99 +1000</f>
@@ -5151,16 +5172,16 @@
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E100" s="2" t="n">
         <f aca="false">A100 +1000</f>
@@ -5178,7 +5199,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E101" s="2" t="n">
         <f aca="false">A101 +1000</f>
@@ -5196,7 +5217,7 @@
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E102" s="2" t="n">
         <f aca="false">A102 +1000</f>
@@ -5214,7 +5235,7 @@
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E103" s="2" t="n">
         <f aca="false">A103 +1000</f>
@@ -5232,7 +5253,7 @@
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E104" s="2" t="n">
         <f aca="false">A104 +1000</f>
@@ -5250,7 +5271,7 @@
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E105" s="2" t="n">
         <f aca="false">A105 +1000</f>
@@ -5268,7 +5289,7 @@
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E106" s="2" t="n">
         <f aca="false">A106 +1000</f>
@@ -5286,7 +5307,7 @@
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E107" s="2" t="n">
         <f aca="false">A107 +1000</f>
@@ -5304,7 +5325,7 @@
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E108" s="2" t="n">
         <f aca="false">A108 +1000</f>
@@ -5322,7 +5343,7 @@
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E109" s="2" t="n">
         <f aca="false">A109 +1000</f>
@@ -5340,7 +5361,7 @@
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E110" s="2" t="n">
         <f aca="false">A110 +1000</f>
@@ -5358,7 +5379,7 @@
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E111" s="2" t="n">
         <f aca="false">A111 +1000</f>
@@ -5376,7 +5397,7 @@
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E112" s="2" t="n">
         <f aca="false">A112 +1000</f>
@@ -5394,7 +5415,7 @@
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E113" s="2" t="n">
         <f aca="false">A113 +1000</f>
@@ -5412,7 +5433,7 @@
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E114" s="2" t="n">
         <f aca="false">A114 +1000</f>
@@ -5430,7 +5451,7 @@
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E115" s="2" t="n">
         <f aca="false">A115 +1000</f>
@@ -5448,7 +5469,7 @@
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E116" s="2" t="n">
         <f aca="false">A116 +1000</f>
@@ -5466,7 +5487,7 @@
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E117" s="2" t="n">
         <f aca="false">A117 +1000</f>
@@ -5484,7 +5505,7 @@
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E118" s="2" t="n">
         <f aca="false">A118 +1000</f>
@@ -5502,7 +5523,7 @@
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E119" s="2" t="n">
         <f aca="false">A119 +1000</f>
@@ -5520,7 +5541,7 @@
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E120" s="2" t="n">
         <f aca="false">A120 +1000</f>
@@ -5538,7 +5559,7 @@
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E121" s="2" t="n">
         <f aca="false">A121 +1000</f>
@@ -5556,7 +5577,7 @@
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E122" s="2" t="n">
         <f aca="false">A122 +1000</f>
@@ -5574,7 +5595,7 @@
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E123" s="2" t="n">
         <f aca="false">A123 +1000</f>
@@ -5592,7 +5613,7 @@
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E124" s="2" t="n">
         <f aca="false">A124 +1000</f>
@@ -5610,7 +5631,7 @@
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E125" s="2" t="n">
         <f aca="false">A125 +1000</f>
@@ -5628,7 +5649,7 @@
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E126" s="2" t="n">
         <f aca="false">A126 +1000</f>
@@ -5646,7 +5667,7 @@
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E127" s="2" t="n">
         <f aca="false">A127 +1000</f>
@@ -5664,7 +5685,7 @@
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E128" s="2" t="n">
         <f aca="false">A128 +1000</f>
@@ -5682,7 +5703,7 @@
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E129" s="2" t="n">
         <f aca="false">A129 +1000</f>
@@ -5700,7 +5721,7 @@
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E130" s="2" t="n">
         <f aca="false">A130 +1000</f>
@@ -5718,7 +5739,7 @@
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E131" s="2" t="n">
         <f aca="false">A131 +1000</f>
@@ -5736,7 +5757,7 @@
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E132" s="2" t="n">
         <f aca="false">A132 +1000</f>
@@ -5754,7 +5775,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E133" s="2" t="n">
         <f aca="false">A133 +1000</f>
@@ -5772,7 +5793,7 @@
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E134" s="2" t="n">
         <f aca="false">A134 +1000</f>
@@ -5790,7 +5811,7 @@
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E135" s="2" t="n">
         <f aca="false">A135 +1000</f>
@@ -5808,7 +5829,7 @@
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E136" s="2" t="n">
         <f aca="false">A136 +1000</f>
@@ -5826,7 +5847,7 @@
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E137" s="2" t="n">
         <f aca="false">A137 +1000</f>
@@ -5844,7 +5865,7 @@
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E138" s="2" t="n">
         <f aca="false">A138 +1000</f>
@@ -5862,7 +5883,7 @@
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E139" s="2" t="n">
         <f aca="false">A139 +1000</f>
@@ -5880,7 +5901,7 @@
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E140" s="2" t="n">
         <f aca="false">A140 +1000</f>
@@ -5898,7 +5919,7 @@
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E141" s="2" t="n">
         <f aca="false">A141 +1000</f>
@@ -5916,7 +5937,7 @@
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E142" s="2" t="n">
         <f aca="false">A142 +1000</f>
@@ -5934,7 +5955,7 @@
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E143" s="2" t="n">
         <f aca="false">A143 +1000</f>
@@ -5952,7 +5973,7 @@
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E144" s="2" t="n">
         <f aca="false">A144 +1000</f>
@@ -5970,7 +5991,7 @@
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E145" s="2" t="n">
         <f aca="false">A145 +1000</f>
@@ -5988,7 +6009,7 @@
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E146" s="2" t="n">
         <f aca="false">A146 +1000</f>
@@ -6006,7 +6027,7 @@
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E147" s="2" t="n">
         <f aca="false">A147 +1000</f>
@@ -6024,7 +6045,7 @@
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E148" s="2" t="n">
         <f aca="false">A148 +1000</f>
@@ -6042,7 +6063,7 @@
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E149" s="2" t="n">
         <f aca="false">A149 +1000</f>
@@ -6060,7 +6081,7 @@
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E150" s="2" t="n">
         <f aca="false">A150 +1000</f>
@@ -6078,7 +6099,7 @@
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E151" s="2" t="n">
         <f aca="false">A151 +1000</f>
@@ -6096,7 +6117,7 @@
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E152" s="2" t="n">
         <f aca="false">A152 +1000</f>
@@ -6114,7 +6135,7 @@
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E153" s="2" t="n">
         <f aca="false">A153 +1000</f>
@@ -6132,7 +6153,7 @@
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E154" s="2" t="n">
         <f aca="false">A154 +1000</f>
@@ -6150,7 +6171,7 @@
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E155" s="2" t="n">
         <f aca="false">A155 +1000</f>
@@ -6168,7 +6189,7 @@
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E156" s="2" t="n">
         <f aca="false">A156 +1000</f>
@@ -6186,7 +6207,7 @@
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E157" s="2" t="n">
         <f aca="false">A157 +1000</f>
@@ -6204,7 +6225,7 @@
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E158" s="2" t="n">
         <f aca="false">A158 +1000</f>
@@ -6222,7 +6243,7 @@
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E159" s="2" t="n">
         <f aca="false">A159 +1000</f>
@@ -6240,7 +6261,7 @@
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E160" s="2" t="n">
         <f aca="false">A160 +1000</f>
@@ -6258,7 +6279,7 @@
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E161" s="2" t="n">
         <f aca="false">A161 +1000</f>
@@ -6276,7 +6297,7 @@
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E162" s="2" t="n">
         <f aca="false">A162 +1000</f>
@@ -6294,7 +6315,7 @@
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E163" s="2" t="n">
         <f aca="false">A163 +1000</f>
@@ -6312,7 +6333,7 @@
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E164" s="2" t="n">
         <f aca="false">A164 +1000</f>
@@ -6330,7 +6351,7 @@
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E165" s="2" t="n">
         <f aca="false">A165 +1000</f>
@@ -6348,7 +6369,7 @@
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E166" s="2" t="n">
         <f aca="false">A166 +1000</f>
@@ -6366,7 +6387,7 @@
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E167" s="2" t="n">
         <f aca="false">A167 +1000</f>
@@ -6384,7 +6405,7 @@
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E168" s="2" t="n">
         <f aca="false">A168 +1000</f>
@@ -6402,7 +6423,7 @@
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E169" s="2" t="n">
         <f aca="false">A169 +1000</f>
@@ -6420,7 +6441,7 @@
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E170" s="2" t="n">
         <f aca="false">A170 +1000</f>
@@ -6438,7 +6459,7 @@
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E171" s="2" t="n">
         <f aca="false">A171 +1000</f>
@@ -6456,7 +6477,7 @@
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E172" s="2" t="n">
         <f aca="false">A172 +1000</f>
@@ -6474,7 +6495,7 @@
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E173" s="2" t="n">
         <f aca="false">A173 +1000</f>
@@ -6492,16 +6513,16 @@
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E174" s="2" t="n">
         <f aca="false">A174 +1000</f>
@@ -6519,7 +6540,7 @@
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E175" s="2" t="n">
         <f aca="false">A175 +1000</f>
@@ -6537,7 +6558,7 @@
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E176" s="2" t="n">
         <f aca="false">A176 +1000</f>
@@ -6555,7 +6576,7 @@
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E177" s="2" t="n">
         <f aca="false">A177 +1000</f>
@@ -6573,7 +6594,7 @@
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E178" s="2" t="n">
         <f aca="false">A178 +1000</f>
@@ -6591,7 +6612,7 @@
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E179" s="2" t="n">
         <f aca="false">A179 +1000</f>
@@ -6609,7 +6630,7 @@
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E180" s="2" t="n">
         <f aca="false">A180 +1000</f>
@@ -6627,7 +6648,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E181" s="2" t="n">
         <f aca="false">A181 +1000</f>
@@ -6645,7 +6666,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E182" s="2" t="n">
         <f aca="false">A182 +1000</f>
@@ -6663,7 +6684,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E183" s="2" t="n">
         <f aca="false">A183 +1000</f>
@@ -6681,7 +6702,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E184" s="2" t="n">
         <f aca="false">A184 +1000</f>
@@ -6699,7 +6720,7 @@
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E185" s="2" t="n">
         <f aca="false">A185 +1000</f>
@@ -6717,7 +6738,7 @@
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E186" s="2" t="n">
         <f aca="false">A186 +1000</f>
@@ -6735,7 +6756,7 @@
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E187" s="2" t="n">
         <f aca="false">A187 +1000</f>
@@ -6753,7 +6774,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E188" s="2" t="n">
         <f aca="false">A188 +1000</f>
@@ -6771,7 +6792,7 @@
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E189" s="2" t="n">
         <f aca="false">A189 +1000</f>
@@ -6789,7 +6810,7 @@
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E190" s="2" t="n">
         <f aca="false">A190 +1000</f>
@@ -6807,7 +6828,7 @@
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E191" s="2" t="n">
         <f aca="false">A191 +1000</f>
@@ -6825,7 +6846,7 @@
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E192" s="2" t="n">
         <f aca="false">A192 +1000</f>
@@ -6843,7 +6864,7 @@
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E193" s="2" t="n">
         <f aca="false">A193 +1000</f>
@@ -6861,7 +6882,7 @@
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E194" s="2" t="n">
         <f aca="false">A194 +1000</f>
@@ -6879,7 +6900,7 @@
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E195" s="2" t="n">
         <f aca="false">A195 +1000</f>
@@ -6897,7 +6918,7 @@
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E196" s="2" t="n">
         <f aca="false">A196 +1000</f>
@@ -6915,7 +6936,7 @@
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E197" s="2" t="n">
         <f aca="false">A197 +1000</f>
@@ -6933,7 +6954,7 @@
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E198" s="2" t="n">
         <f aca="false">A198 +1000</f>
@@ -6951,7 +6972,7 @@
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E199" s="2" t="n">
         <f aca="false">A199 +1000</f>
@@ -6969,7 +6990,7 @@
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E200" s="2" t="n">
         <f aca="false">A200 +1000</f>
@@ -6987,7 +7008,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E201" s="2" t="n">
         <f aca="false">A201 +1000</f>
@@ -7005,7 +7026,7 @@
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E202" s="2" t="n">
         <f aca="false">A202 +1000</f>
@@ -7023,7 +7044,7 @@
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E203" s="2" t="n">
         <f aca="false">A203 +1000</f>
@@ -7041,7 +7062,7 @@
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E204" s="2" t="n">
         <f aca="false">A204 +1000</f>
@@ -7059,7 +7080,7 @@
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E205" s="2" t="n">
         <f aca="false">A205 +1000</f>
@@ -7077,7 +7098,7 @@
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E206" s="2" t="n">
         <f aca="false">A206 +1000</f>
@@ -7095,7 +7116,7 @@
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E207" s="2" t="n">
         <f aca="false">A207 +1000</f>
@@ -7113,7 +7134,7 @@
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E208" s="2" t="n">
         <f aca="false">A208 +1000</f>
@@ -7131,16 +7152,16 @@
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E209" s="2" t="n">
         <f aca="false">A209 +1000</f>
@@ -7158,7 +7179,7 @@
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E210" s="2" t="n">
         <f aca="false">A210 +1000</f>
@@ -7176,7 +7197,7 @@
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E211" s="2" t="n">
         <f aca="false">A211 +1000</f>
@@ -7194,7 +7215,7 @@
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E212" s="2" t="n">
         <f aca="false">A212 +1000</f>
@@ -7212,7 +7233,7 @@
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E213" s="2" t="n">
         <f aca="false">A213 +1000</f>
@@ -7230,7 +7251,7 @@
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E214" s="2" t="n">
         <f aca="false">A214 +1000</f>
@@ -7248,7 +7269,7 @@
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B215" s="3"/>
       <c r="E215" s="2" t="n">
@@ -7267,13 +7288,13 @@
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E216" s="2" t="n">
         <f aca="false">A216 +1000</f>
@@ -7291,7 +7312,7 @@
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E217" s="2" t="n">
         <f aca="false">A217 +1000</f>
@@ -7309,13 +7330,13 @@
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E218" s="2" t="n">
         <f aca="false">A218 +1000</f>
@@ -7333,7 +7354,7 @@
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E219" s="2" t="n">
         <f aca="false">A219 +1000</f>
@@ -7351,7 +7372,7 @@
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E220" s="2" t="n">
         <f aca="false">A220 +1000</f>
@@ -7369,7 +7390,7 @@
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E221" s="2" t="n">
         <f aca="false">A221 +1000</f>
@@ -7387,7 +7408,7 @@
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E222" s="2" t="n">
         <f aca="false">A222 +1000</f>
@@ -7405,7 +7426,7 @@
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E223" s="2" t="n">
         <f aca="false">A223 +1000</f>
@@ -7423,7 +7444,7 @@
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E224" s="2" t="n">
         <f aca="false">A224 +1000</f>
@@ -7441,7 +7462,7 @@
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E225" s="2" t="n">
         <f aca="false">A225 +1000</f>
@@ -7459,7 +7480,7 @@
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E226" s="2" t="n">
         <f aca="false">A226 +1000</f>
@@ -7477,7 +7498,7 @@
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E227" s="2" t="n">
         <f aca="false">A227 +1000</f>
@@ -7495,7 +7516,7 @@
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E228" s="2" t="n">
         <f aca="false">A228 +1000</f>
@@ -7513,7 +7534,7 @@
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E229" s="2" t="n">
         <f aca="false">A229 +1000</f>
@@ -7531,7 +7552,7 @@
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E230" s="2" t="n">
         <f aca="false">A230 +1000</f>
@@ -7549,16 +7570,16 @@
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E231" s="2" t="n">
         <f aca="false">A231 +1000</f>
@@ -7569,10 +7590,10 @@
         <v>2230</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K231" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M231" s="2" t="n">
         <f aca="false">I231 +1000</f>
@@ -7582,7 +7603,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">A232 +1000</f>
@@ -7600,7 +7621,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">A233 +1000</f>
@@ -7618,7 +7639,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">A234 +1000</f>
@@ -7636,7 +7657,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">A235 +1000</f>
@@ -7654,16 +7675,16 @@
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">A236 +1000</f>
@@ -7681,7 +7702,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">A237 +1000</f>
@@ -7699,7 +7720,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">A238 +1000</f>
@@ -7717,13 +7738,13 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E239" s="2" t="n">
         <f aca="false">A239 +1000</f>
@@ -7741,7 +7762,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">A240 +1000</f>
@@ -7759,7 +7780,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">A241 +1000</f>
@@ -7777,7 +7798,7 @@
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">A242 +1000</f>
@@ -7795,7 +7816,7 @@
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">A243 +1000</f>
@@ -7813,7 +7834,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">A244 +1000</f>
@@ -7831,7 +7852,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">A245 +1000</f>
@@ -7849,7 +7870,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E246" s="2" t="n">
         <f aca="false">A246 +1000</f>
@@ -7867,7 +7888,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E247" s="2" t="n">
         <f aca="false">A247 +1000</f>
@@ -7885,7 +7906,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E248" s="2" t="n">
         <f aca="false">A248 +1000</f>
@@ -7903,7 +7924,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E249" s="2" t="n">
         <f aca="false">A249 +1000</f>
@@ -7921,7 +7942,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E250" s="2" t="n">
         <f aca="false">A250 +1000</f>
@@ -7939,7 +7960,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E251" s="2" t="n">
         <f aca="false">A251 +1000</f>
@@ -7957,7 +7978,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E252" s="2" t="n">
         <f aca="false">A252 +1000</f>
@@ -7975,7 +7996,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E253" s="2" t="n">
         <f aca="false">A253 +1000</f>
@@ -7993,7 +8014,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E254" s="2" t="n">
         <f aca="false">A254 +1000</f>
@@ -8011,7 +8032,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E255" s="2" t="n">
         <f aca="false">A255 +1000</f>
@@ -8029,7 +8050,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E256" s="2" t="n">
         <f aca="false">A256 +1000</f>
@@ -8047,7 +8068,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E257" s="2" t="n">
         <f aca="false">A257 +1000</f>
@@ -8065,7 +8086,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E258" s="2" t="n">
         <f aca="false">A258 +1000</f>
@@ -8083,7 +8104,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E259" s="2" t="n">
         <f aca="false">A259 +1000</f>
@@ -8101,7 +8122,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E260" s="2" t="n">
         <f aca="false">A260 +1000</f>
@@ -8119,7 +8140,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E261" s="2" t="n">
         <f aca="false">A261 +1000</f>
@@ -8137,7 +8158,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E262" s="2" t="n">
         <f aca="false">A262 +1000</f>
@@ -8155,7 +8176,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E263" s="2" t="n">
         <f aca="false">A263 +1000</f>
@@ -8173,13 +8194,13 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E264" s="2" t="n">
         <f aca="false">A264 +1000</f>
@@ -8194,16 +8215,16 @@
         <v>3263</v>
       </c>
       <c r="N264" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O264" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q264" s="2"/>
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E265" s="2" t="n">
         <f aca="false">A265 +1000</f>
@@ -8221,7 +8242,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E266" s="2" t="n">
         <f aca="false">A266 +1000</f>
@@ -8239,7 +8260,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E267" s="2" t="n">
         <f aca="false">A267 +1000</f>
@@ -8257,7 +8278,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E268" s="2" t="n">
         <f aca="false">A268 +1000</f>
@@ -8275,7 +8296,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E269" s="2" t="n">
         <f aca="false">A269 +1000</f>
@@ -8293,7 +8314,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E270" s="2" t="n">
         <f aca="false">A270 +1000</f>
@@ -8311,7 +8332,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E271" s="2" t="n">
         <f aca="false">A271 +1000</f>
@@ -8329,7 +8350,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E272" s="2" t="n">
         <f aca="false">A272 +1000</f>
@@ -8347,7 +8368,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E273" s="2" t="n">
         <f aca="false">A273 +1000</f>
@@ -8365,7 +8386,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E274" s="2" t="n">
         <f aca="false">A274 +1000</f>
@@ -8383,7 +8404,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E275" s="2" t="n">
         <f aca="false">A275 +1000</f>
@@ -8401,7 +8422,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E276" s="2" t="n">
         <f aca="false">A276 +1000</f>
@@ -8419,7 +8440,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E277" s="2" t="n">
         <f aca="false">A277 +1000</f>
@@ -8437,7 +8458,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E278" s="2" t="n">
         <f aca="false">A278 +1000</f>
@@ -8455,7 +8476,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E279" s="2" t="n">
         <f aca="false">A279 +1000</f>
@@ -8473,7 +8494,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E280" s="2" t="n">
         <f aca="false">A280 +1000</f>
@@ -8491,7 +8512,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E281" s="2" t="n">
         <f aca="false">A281 +1000</f>
@@ -8509,7 +8530,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E282" s="2" t="n">
         <f aca="false">A282 +1000</f>
@@ -8527,7 +8548,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E283" s="2" t="n">
         <f aca="false">A283 +1000</f>
@@ -8545,7 +8566,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E284" s="2" t="n">
         <f aca="false">A284 +1000</f>
@@ -8563,7 +8584,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E285" s="2" t="n">
         <f aca="false">A285 +1000</f>
@@ -8581,7 +8602,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E286" s="2" t="n">
         <f aca="false">A286 +1000</f>
@@ -8599,7 +8620,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E287" s="2" t="n">
         <f aca="false">A287 +1000</f>
@@ -8617,7 +8638,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E288" s="2" t="n">
         <f aca="false">A288 +1000</f>
@@ -8635,7 +8656,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E289" s="2" t="n">
         <f aca="false">A289 +1000</f>
@@ -8653,7 +8674,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E290" s="2" t="n">
         <f aca="false">A290 +1000</f>
@@ -8671,7 +8692,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E291" s="2" t="n">
         <f aca="false">A291 +1000</f>
@@ -8689,7 +8710,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E292" s="2" t="n">
         <f aca="false">A292 +1000</f>
@@ -8707,7 +8728,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E293" s="2" t="n">
         <f aca="false">A293 +1000</f>
@@ -8725,7 +8746,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E294" s="2" t="n">
         <f aca="false">A294 +1000</f>
@@ -8743,7 +8764,7 @@
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
@@ -8762,13 +8783,13 @@
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E296" s="2" t="n">
         <f aca="false">A296 +1000</f>
@@ -8786,7 +8807,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E297" s="2" t="n">
         <f aca="false">A297 +1000</f>
@@ -8804,7 +8825,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E298" s="2" t="n">
         <f aca="false">A298 +1000</f>
@@ -8822,7 +8843,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E299" s="2" t="n">
         <f aca="false">A299 +1000</f>
@@ -8840,7 +8861,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E300" s="2" t="n">
         <f aca="false">A300 +1000</f>
@@ -8858,7 +8879,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E301" s="2" t="n">
         <f aca="false">A301 +1000</f>
@@ -8876,7 +8897,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E302" s="2" t="n">
         <f aca="false">A302 +1000</f>
@@ -8894,7 +8915,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E303" s="2" t="n">
         <f aca="false">A303 +1000</f>
@@ -8912,7 +8933,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E304" s="2" t="n">
         <f aca="false">A304 +1000</f>
@@ -8930,7 +8951,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E305" s="2" t="n">
         <f aca="false">A305 +1000</f>
@@ -8948,7 +8969,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E306" s="2" t="n">
         <f aca="false">A306 +1000</f>
@@ -8966,7 +8987,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E307" s="2" t="n">
         <f aca="false">A307 +1000</f>
@@ -8984,7 +9005,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E308" s="2" t="n">
         <f aca="false">A308 +1000</f>
@@ -9002,7 +9023,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E309" s="2" t="n">
         <f aca="false">A309 +1000</f>
@@ -9020,7 +9041,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E310" s="2" t="n">
         <f aca="false">A310 +1000</f>
@@ -9038,7 +9059,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E311" s="2" t="n">
         <f aca="false">A311 +1000</f>
@@ -9056,7 +9077,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E312" s="2" t="n">
         <f aca="false">A312 +1000</f>
@@ -9074,7 +9095,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E313" s="2" t="n">
         <f aca="false">A313 +1000</f>
@@ -9092,7 +9113,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E314" s="2" t="n">
         <f aca="false">A314 +1000</f>
@@ -9110,7 +9131,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E315" s="2" t="n">
         <f aca="false">A315 +1000</f>
@@ -9128,7 +9149,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E316" s="2" t="n">
         <f aca="false">A316 +1000</f>
@@ -9146,7 +9167,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E317" s="2" t="n">
         <f aca="false">A317 +1000</f>
@@ -9164,7 +9185,7 @@
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E318" s="2" t="n">
         <f aca="false">A318 +1000</f>
@@ -9179,16 +9200,16 @@
         <v>3317</v>
       </c>
       <c r="N318" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q318" s="2"/>
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E319" s="2" t="n">
         <f aca="false">A319 +1000</f>
@@ -9206,7 +9227,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E320" s="2" t="n">
         <f aca="false">A320 +1000</f>
@@ -9224,7 +9245,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E321" s="2" t="n">
         <f aca="false">A321 +1000</f>
@@ -9242,7 +9263,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E322" s="2" t="n">
         <f aca="false">A322 +1000</f>
@@ -9260,7 +9281,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E323" s="2" t="n">
         <f aca="false">A323 +1000</f>
@@ -9278,7 +9299,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E324" s="2" t="n">
         <f aca="false">A324 +1000</f>
@@ -9296,7 +9317,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E325" s="2" t="n">
         <f aca="false">A325 +1000</f>
@@ -9314,7 +9335,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E326" s="2" t="n">
         <f aca="false">A326 +1000</f>
@@ -9332,7 +9353,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E327" s="2" t="n">
         <f aca="false">A327 +1000</f>
@@ -9350,7 +9371,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E328" s="2" t="n">
         <f aca="false">A328 +1000</f>
@@ -9368,7 +9389,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E329" s="2" t="n">
         <f aca="false">A329 +1000</f>
@@ -9386,7 +9407,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E330" s="2" t="n">
         <f aca="false">A330 +1000</f>
@@ -9404,7 +9425,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E331" s="2" t="n">
         <f aca="false">A331 +1000</f>
@@ -9422,13 +9443,13 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E332" s="2" t="n">
         <f aca="false">A332 +1000</f>
@@ -9446,7 +9467,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E333" s="2" t="n">
         <f aca="false">A333 +1000</f>
@@ -9464,7 +9485,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E334" s="2" t="n">
         <f aca="false">A334 +1000</f>
@@ -9482,7 +9503,7 @@
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E335" s="2" t="n">
         <f aca="false">A335 +1000</f>
@@ -9493,10 +9514,10 @@
         <v>2334</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K335" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M335" s="2" t="n">
         <f aca="false">I335 +1000</f>
@@ -9506,7 +9527,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E336" s="2" t="n">
         <f aca="false">A336 +1000</f>
@@ -9524,17 +9545,17 @@
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E337" s="2" t="n">
         <f aca="false">A337 +1000</f>
         <v>1336</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I337" s="2" t="n">
         <f aca="false">E337 +1000</f>
@@ -9548,7 +9569,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E338" s="2" t="n">
         <f aca="false">A338 +1000</f>
@@ -9566,7 +9587,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E339" s="2" t="n">
         <f aca="false">A339 +1000</f>
@@ -9584,7 +9605,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E340" s="2" t="n">
         <f aca="false">A340 +1000</f>
@@ -9602,7 +9623,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E341" s="2" t="n">
         <f aca="false">A341 +1000</f>
@@ -9620,7 +9641,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E342" s="2" t="n">
         <f aca="false">A342 +1000</f>
@@ -9638,7 +9659,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E343" s="2" t="n">
         <f aca="false">A343 +1000</f>
@@ -9656,7 +9677,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E344" s="2" t="n">
         <f aca="false">A344 +1000</f>
@@ -9674,7 +9695,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E345" s="2" t="n">
         <f aca="false">A345 +1000</f>
@@ -9692,7 +9713,7 @@
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E346" s="2" t="n">
         <f aca="false">A346 +1000</f>
@@ -9710,7 +9731,7 @@
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
@@ -9729,13 +9750,13 @@
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E348" s="2" t="n">
         <f aca="false">A348 +1000</f>
@@ -9753,7 +9774,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E349" s="2" t="n">
         <f aca="false">A349 +1000</f>
@@ -9771,7 +9792,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E350" s="2" t="n">
         <f aca="false">A350 +1000</f>
@@ -9789,7 +9810,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E351" s="2" t="n">
         <f aca="false">A351 +1000</f>
@@ -9807,7 +9828,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E352" s="2" t="n">
         <f aca="false">A352 +1000</f>
@@ -9825,7 +9846,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E353" s="2" t="n">
         <f aca="false">A353 +1000</f>
@@ -9843,7 +9864,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E354" s="2" t="n">
         <f aca="false">A354 +1000</f>
@@ -9861,7 +9882,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E355" s="2" t="n">
         <f aca="false">A355 +1000</f>
@@ -9879,13 +9900,13 @@
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E356" s="2" t="n">
         <f aca="false">A356 +1000</f>
@@ -9903,7 +9924,7 @@
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E357" s="2" t="n">
         <f aca="false">A357 +1000</f>
@@ -9914,10 +9935,10 @@
         <v>2356</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K357" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M357" s="2" t="n">
         <f aca="false">I357 +1000</f>
@@ -9927,7 +9948,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E358" s="2" t="n">
         <f aca="false">A358 +1000</f>
@@ -9945,7 +9966,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E359" s="2" t="n">
         <f aca="false">A359 +1000</f>
@@ -9963,7 +9984,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E360" s="2" t="n">
         <f aca="false">A360 +1000</f>
@@ -9981,7 +10002,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E361" s="2" t="n">
         <f aca="false">A361 +1000</f>
@@ -9999,7 +10020,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E362" s="2" t="n">
         <f aca="false">A362 +1000</f>
@@ -10017,7 +10038,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E363" s="2" t="n">
         <f aca="false">A363 +1000</f>
@@ -10035,7 +10056,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E364" s="2" t="n">
         <f aca="false">A364 +1000</f>
@@ -10053,7 +10074,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E365" s="2" t="n">
         <f aca="false">A365 +1000</f>
@@ -10071,7 +10092,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E366" s="2" t="n">
         <f aca="false">A366 +1000</f>
@@ -10089,7 +10110,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E367" s="2" t="n">
         <f aca="false">A367 +1000</f>
@@ -10107,7 +10128,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E368" s="2" t="n">
         <f aca="false">A368 +1000</f>
@@ -10125,7 +10146,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E369" s="2" t="n">
         <f aca="false">A369 +1000</f>
@@ -10143,7 +10164,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E370" s="2" t="n">
         <f aca="false">A370 +1000</f>
@@ -10161,7 +10182,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E371" s="2" t="n">
         <f aca="false">A371 +1000</f>
@@ -10179,7 +10200,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E372" s="2" t="n">
         <f aca="false">A372 +1000</f>
@@ -10197,13 +10218,13 @@
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E373" s="2" t="n">
         <f aca="false">A373 +1000</f>
@@ -10221,20 +10242,20 @@
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E374" s="2" t="n">
         <f aca="false">A374 +1000</f>
         <v>1373</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G374" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I374" s="2" t="n">
         <f aca="false">E374 +1000</f>
@@ -10248,7 +10269,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E375" s="2" t="n">
         <f aca="false">A375 +1000</f>
@@ -10266,7 +10287,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E376" s="2" t="n">
         <f aca="false">A376 +1000</f>
@@ -10284,7 +10305,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E377" s="2" t="n">
         <f aca="false">A377 +1000</f>
@@ -10302,13 +10323,13 @@
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E378" s="2" t="n">
         <f aca="false">A378 +1000</f>
@@ -10326,7 +10347,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E379" s="2" t="n">
         <f aca="false">A379 +1000</f>
@@ -10344,7 +10365,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E380" s="2" t="n">
         <f aca="false">A380 +1000</f>
@@ -10362,7 +10383,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E381" s="2" t="n">
         <f aca="false">A381 +1000</f>
@@ -10380,7 +10401,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E382" s="2" t="n">
         <f aca="false">A382 +1000</f>
@@ -10398,7 +10419,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E383" s="2" t="n">
         <f aca="false">A383 +1000</f>
@@ -10416,7 +10437,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E384" s="2" t="n">
         <f aca="false">A384 +1000</f>
@@ -10434,7 +10455,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E385" s="2" t="n">
         <f aca="false">A385 +1000</f>
@@ -10452,7 +10473,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E386" s="2" t="n">
         <f aca="false">A386 +1000</f>
@@ -10470,7 +10491,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E387" s="2" t="n">
         <f aca="false">A387 +1000</f>
@@ -10488,7 +10509,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E388" s="2" t="n">
         <f aca="false">A388 +1000</f>
@@ -10506,7 +10527,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E389" s="2" t="n">
         <f aca="false">A389 +1000</f>
@@ -10524,7 +10545,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E390" s="2" t="n">
         <f aca="false">A390 +1000</f>
@@ -10542,7 +10563,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E391" s="2" t="n">
         <f aca="false">A391 +1000</f>
@@ -10560,7 +10581,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E392" s="2" t="n">
         <f aca="false">A392 +1000</f>
@@ -10578,7 +10599,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E393" s="2" t="n">
         <f aca="false">A393 +1000</f>
@@ -10596,7 +10617,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E394" s="2" t="n">
         <f aca="false">A394 +1000</f>
@@ -10614,7 +10635,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E395" s="2" t="n">
         <f aca="false">A395 +1000</f>
@@ -10632,7 +10653,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E396" s="2" t="n">
         <f aca="false">A396 +1000</f>
@@ -10650,7 +10671,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E397" s="2" t="n">
         <f aca="false">A397 +1000</f>
@@ -10668,7 +10689,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E398" s="2" t="n">
         <f aca="false">A398 +1000</f>
@@ -10686,7 +10707,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E399" s="2" t="n">
         <f aca="false">A399 +1000</f>
@@ -10704,7 +10725,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E400" s="2" t="n">
         <f aca="false">A400 +1000</f>
@@ -10722,7 +10743,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E401" s="2" t="n">
         <f aca="false">A401 +1000</f>
@@ -10740,7 +10761,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E402" s="2" t="n">
         <f aca="false">A402 +1000</f>
@@ -10758,7 +10779,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E403" s="2" t="n">
         <f aca="false">A403 +1000</f>
@@ -10776,7 +10797,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E404" s="2" t="n">
         <f aca="false">A404 +1000</f>
@@ -10794,7 +10815,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E405" s="2" t="n">
         <f aca="false">A405 +1000</f>
@@ -10812,7 +10833,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E406" s="2" t="n">
         <f aca="false">A406 +1000</f>
@@ -10830,13 +10851,13 @@
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E407" s="2" t="n">
         <f aca="false">A407 +1000</f>
@@ -10854,7 +10875,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E408" s="2" t="n">
         <f aca="false">A408 +1000</f>
@@ -10872,7 +10893,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E409" s="2" t="n">
         <f aca="false">A409 +1000</f>
@@ -10890,7 +10911,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E410" s="2" t="n">
         <f aca="false">A410 +1000</f>
@@ -10908,7 +10929,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E411" s="2" t="n">
         <f aca="false">A411 +1000</f>
@@ -10926,7 +10947,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E412" s="2" t="n">
         <f aca="false">A412 +1000</f>
@@ -10944,7 +10965,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E413" s="2" t="n">
         <f aca="false">A413 +1000</f>
@@ -10962,7 +10983,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E414" s="2" t="n">
         <f aca="false">A414 +1000</f>
@@ -10980,7 +11001,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E415" s="2" t="n">
         <f aca="false">A415 +1000</f>
@@ -10998,7 +11019,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E416" s="2" t="n">
         <f aca="false">A416 +1000</f>
@@ -11016,7 +11037,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E417" s="2" t="n">
         <f aca="false">A417 +1000</f>
@@ -11034,7 +11055,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E418" s="2" t="n">
         <f aca="false">A418 +1000</f>
@@ -11052,7 +11073,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E419" s="2" t="n">
         <f aca="false">A419 +1000</f>
@@ -11070,13 +11091,13 @@
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E420" s="2" t="n">
         <f aca="false">A420 +1000</f>
@@ -11094,7 +11115,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E421" s="2" t="n">
         <f aca="false">A421 +1000</f>
@@ -11112,16 +11133,16 @@
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
@@ -11139,7 +11160,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E423" s="2" t="n">
         <f aca="false">A423 +1000</f>
@@ -11157,7 +11178,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E424" s="2" t="n">
         <f aca="false">A424 +1000</f>
@@ -11175,7 +11196,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E425" s="2" t="n">
         <f aca="false">A425 +1000</f>
@@ -11193,7 +11214,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E426" s="2" t="n">
         <f aca="false">A426 +1000</f>
@@ -11211,7 +11232,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E427" s="2" t="n">
         <f aca="false">A427 +1000</f>
@@ -11229,7 +11250,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E428" s="2" t="n">
         <f aca="false">A428 +1000</f>
@@ -11247,7 +11268,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E429" s="2" t="n">
         <f aca="false">A429 +1000</f>
@@ -11265,7 +11286,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E430" s="2" t="n">
         <f aca="false">A430 +1000</f>
@@ -11283,7 +11304,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E431" s="2" t="n">
         <f aca="false">A431 +1000</f>
@@ -11301,7 +11322,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E432" s="2" t="n">
         <f aca="false">A432 +1000</f>
@@ -11319,7 +11340,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E433" s="2" t="n">
         <f aca="false">A433 +1000</f>
@@ -11337,7 +11358,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E434" s="2" t="n">
         <f aca="false">A434 +1000</f>
@@ -11355,7 +11376,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E435" s="2" t="n">
         <f aca="false">A435 +1000</f>
@@ -11373,7 +11394,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E436" s="2" t="n">
         <f aca="false">A436 +1000</f>
@@ -11391,7 +11412,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E437" s="2" t="n">
         <f aca="false">A437 +1000</f>
@@ -11409,7 +11430,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E438" s="2" t="n">
         <f aca="false">A438 +1000</f>
@@ -11427,7 +11448,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E439" s="2" t="n">
         <f aca="false">A439 +1000</f>
@@ -11445,7 +11466,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E440" s="2" t="n">
         <f aca="false">A440 +1000</f>
@@ -11463,7 +11484,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E441" s="2" t="n">
         <f aca="false">A441 +1000</f>
@@ -11481,7 +11502,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E442" s="2" t="n">
         <f aca="false">A442 +1000</f>
@@ -11499,7 +11520,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E443" s="2" t="n">
         <f aca="false">A443 +1000</f>
@@ -11517,7 +11538,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E444" s="2" t="n">
         <f aca="false">A444 +1000</f>
@@ -11535,7 +11556,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E445" s="2" t="n">
         <f aca="false">A445 +1000</f>
@@ -11553,7 +11574,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E446" s="2" t="n">
         <f aca="false">A446 +1000</f>
@@ -11571,7 +11592,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E447" s="2" t="n">
         <f aca="false">A447 +1000</f>
@@ -11589,7 +11610,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E448" s="2" t="n">
         <f aca="false">A448 +1000</f>
@@ -11607,7 +11628,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E449" s="2" t="n">
         <f aca="false">A449 +1000</f>
@@ -11625,7 +11646,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E450" s="2" t="n">
         <f aca="false">A450 +1000</f>
@@ -11643,13 +11664,13 @@
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E451" s="2" t="n">
         <f aca="false">A451 +1000</f>
@@ -11667,7 +11688,7 @@
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E452" s="2" t="n">
         <f aca="false">A452 +1000</f>
@@ -11685,7 +11706,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E453" s="2" t="n">
         <f aca="false">A453 +1000</f>
@@ -11703,7 +11724,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E454" s="2" t="n">
         <f aca="false">A454 +1000</f>
@@ -11721,7 +11742,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E455" s="2" t="n">
         <f aca="false">A455 +1000</f>
@@ -11739,7 +11760,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E456" s="2" t="n">
         <f aca="false">A456 +1000</f>
@@ -11757,7 +11778,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E457" s="2" t="n">
         <f aca="false">A457 +1000</f>
@@ -11775,7 +11796,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E458" s="2" t="n">
         <f aca="false">A458 +1000</f>
@@ -11793,7 +11814,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E459" s="2" t="n">
         <f aca="false">A459 +1000</f>
@@ -11811,7 +11832,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E460" s="2" t="n">
         <f aca="false">A460 +1000</f>
@@ -11829,7 +11850,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E461" s="2" t="n">
         <f aca="false">A461 +1000</f>
@@ -11847,7 +11868,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E462" s="2" t="n">
         <f aca="false">A462 +1000</f>
@@ -11865,7 +11886,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E463" s="2" t="n">
         <f aca="false">A463 +1000</f>
@@ -11883,17 +11904,17 @@
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E464" s="2" t="n">
         <f aca="false">A464 +1000</f>
         <v>1463</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G464" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I464" s="2" t="n">
         <f aca="false">E464 +1000</f>
@@ -11907,7 +11928,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E465" s="2" t="n">
         <f aca="false">A465 +1000</f>
@@ -11925,7 +11946,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E466" s="2" t="n">
         <f aca="false">A466 +1000</f>
@@ -11943,7 +11964,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E467" s="2" t="n">
         <f aca="false">A467 +1000</f>
@@ -11961,7 +11982,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E468" s="2" t="n">
         <f aca="false">A468 +1000</f>
@@ -11979,7 +12000,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E469" s="2" t="n">
         <f aca="false">A469 +1000</f>
@@ -11997,7 +12018,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E470" s="2" t="n">
         <f aca="false">A470 +1000</f>
@@ -12015,7 +12036,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E471" s="2" t="n">
         <f aca="false">A471 +1000</f>
@@ -12033,7 +12054,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E472" s="2" t="n">
         <f aca="false">A472 +1000</f>
@@ -12051,7 +12072,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E473" s="2" t="n">
         <f aca="false">A473 +1000</f>
@@ -12069,7 +12090,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E474" s="2" t="n">
         <f aca="false">A474 +1000</f>
@@ -12087,7 +12108,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E475" s="2" t="n">
         <f aca="false">A475 +1000</f>
@@ -12105,7 +12126,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E476" s="2" t="n">
         <f aca="false">A476 +1000</f>
@@ -12123,7 +12144,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E477" s="2" t="n">
         <f aca="false">A477 +1000</f>
@@ -12141,7 +12162,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E478" s="2" t="n">
         <f aca="false">A478 +1000</f>
@@ -12159,7 +12180,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E479" s="2" t="n">
         <f aca="false">A479 +1000</f>
@@ -12177,7 +12198,7 @@
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
@@ -12196,7 +12217,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E481" s="2" t="n">
         <f aca="false">A481 +1000</f>
@@ -12214,7 +12235,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E482" s="2" t="n">
         <f aca="false">A482 +1000</f>
@@ -12232,7 +12253,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E483" s="2" t="n">
         <f aca="false">A483 +1000</f>
@@ -12250,7 +12271,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E484" s="2" t="n">
         <f aca="false">A484 +1000</f>
@@ -12268,7 +12289,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E485" s="2" t="n">
         <f aca="false">A485 +1000</f>
@@ -12286,7 +12307,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E486" s="2" t="n">
         <f aca="false">A486 +1000</f>
@@ -12304,7 +12325,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E487" s="2" t="n">
         <f aca="false">A487 +1000</f>
@@ -12322,7 +12343,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E488" s="2" t="n">
         <f aca="false">A488 +1000</f>
@@ -12340,7 +12361,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E489" s="2" t="n">
         <f aca="false">A489 +1000</f>
@@ -12358,7 +12379,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E490" s="2" t="n">
         <f aca="false">A490 +1000</f>
@@ -12376,7 +12397,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E491" s="2" t="n">
         <f aca="false">A491 +1000</f>
@@ -12394,7 +12415,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E492" s="2" t="n">
         <f aca="false">A492 +1000</f>
@@ -12412,7 +12433,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E493" s="2" t="n">
         <f aca="false">A493 +1000</f>
@@ -12430,7 +12451,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E494" s="2" t="n">
         <f aca="false">A494 +1000</f>
@@ -12448,7 +12469,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E495" s="2" t="n">
         <f aca="false">A495 +1000</f>
@@ -12466,7 +12487,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E496" s="2" t="n">
         <f aca="false">A496 +1000</f>
@@ -12484,7 +12505,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E497" s="2" t="n">
         <f aca="false">A497 +1000</f>
@@ -12502,7 +12523,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E498" s="2" t="n">
         <f aca="false">A498 +1000</f>
@@ -12520,7 +12541,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E499" s="2" t="n">
         <f aca="false">A499 +1000</f>
@@ -12538,7 +12559,7 @@
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E500" s="2" t="n">
         <f aca="false">A500 +1000</f>
@@ -12549,10 +12570,10 @@
         <v>2499</v>
       </c>
       <c r="J500" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K500" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M500" s="2" t="n">
         <f aca="false">I500 +1000</f>
@@ -12562,7 +12583,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E501" s="2" t="n">
         <f aca="false">A501 +1000</f>
@@ -12580,7 +12601,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E502" s="2" t="n">
         <f aca="false">A502 +1000</f>
@@ -12598,7 +12619,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E503" s="2" t="n">
         <f aca="false">A503 +1000</f>
@@ -12616,7 +12637,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E504" s="2" t="n">
         <f aca="false">A504 +1000</f>
@@ -12634,7 +12655,7 @@
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E505" s="2" t="n">
         <f aca="false">A505 +1000</f>
@@ -12652,13 +12673,13 @@
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E506" s="2" t="n">
         <f aca="false">A506 +1000</f>
@@ -12676,7 +12697,7 @@
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E507" s="2" t="n">
         <f aca="false">A507 +1000</f>
@@ -12691,16 +12712,16 @@
         <v>3506</v>
       </c>
       <c r="N507" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O507" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q507" s="2"/>
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E508" s="2" t="n">
         <f aca="false">A508 +1000</f>
@@ -12718,7 +12739,7 @@
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E509" s="2" t="n">
         <f aca="false">A509 +1000</f>
@@ -12736,7 +12757,7 @@
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E510" s="2" t="n">
         <f aca="false">A510 +1000</f>
@@ -12754,7 +12775,7 @@
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E511" s="2" t="n">
         <f aca="false">A511 +1000</f>
@@ -12772,7 +12793,7 @@
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E512" s="2" t="n">
         <f aca="false">A512 +1000</f>
@@ -12790,7 +12811,7 @@
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E513" s="2" t="n">
         <f aca="false">A513 +1000</f>
@@ -12808,7 +12829,7 @@
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E514" s="2" t="n">
         <f aca="false">A514 +1000</f>
@@ -12826,7 +12847,7 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E515" s="2" t="n">
         <f aca="false">A515 +1000</f>
@@ -12844,7 +12865,7 @@
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E516" s="2" t="n">
         <f aca="false">A516 +1000</f>
@@ -12862,7 +12883,7 @@
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E517" s="2" t="n">
         <f aca="false">A517 +1000</f>
@@ -12880,7 +12901,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E518" s="2" t="n">
         <f aca="false">A518 +1000</f>
@@ -12898,7 +12919,7 @@
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E519" s="2" t="n">
         <f aca="false">A519 +1000</f>
@@ -12916,7 +12937,7 @@
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E520" s="2" t="n">
         <f aca="false">A520 +1000</f>
@@ -12934,7 +12955,7 @@
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E521" s="2" t="n">
         <f aca="false">A521 +1000</f>
@@ -12952,7 +12973,7 @@
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E522" s="2" t="n">
         <f aca="false">A522 +1000</f>
@@ -12970,7 +12991,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E523" s="2" t="n">
         <f aca="false">A523 +1000</f>
@@ -12988,7 +13009,7 @@
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E524" s="2" t="n">
         <f aca="false">A524 +1000</f>
@@ -13006,7 +13027,7 @@
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E525" s="2" t="n">
         <f aca="false">A525 +1000</f>
@@ -13024,7 +13045,7 @@
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E526" s="2" t="n">
         <f aca="false">A526 +1000</f>
@@ -13042,7 +13063,7 @@
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E527" s="2" t="n">
         <f aca="false">A527 +1000</f>
@@ -13060,7 +13081,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E528" s="2" t="n">
         <f aca="false">A528 +1000</f>
@@ -13078,7 +13099,7 @@
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E529" s="2" t="n">
         <f aca="false">A529 +1000</f>
@@ -13096,7 +13117,7 @@
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E530" s="2" t="n">
         <f aca="false">A530 +1000</f>
@@ -13114,7 +13135,7 @@
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E531" s="2" t="n">
         <f aca="false">A531 +1000</f>
@@ -13132,7 +13153,7 @@
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E532" s="2" t="n">
         <f aca="false">A532 +1000</f>
@@ -13150,7 +13171,7 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E533" s="2" t="n">
         <f aca="false">A533 +1000</f>
@@ -13168,7 +13189,7 @@
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E534" s="2" t="n">
         <f aca="false">A534 +1000</f>
@@ -13186,7 +13207,7 @@
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E535" s="2" t="n">
         <f aca="false">A535 +1000</f>
@@ -13204,7 +13225,7 @@
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E536" s="2" t="n">
         <f aca="false">A536 +1000</f>
@@ -13222,7 +13243,7 @@
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E537" s="2" t="n">
         <f aca="false">A537 +1000</f>
@@ -13240,7 +13261,7 @@
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E538" s="2" t="n">
         <f aca="false">A538 +1000</f>
@@ -13258,7 +13279,7 @@
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E539" s="2" t="n">
         <f aca="false">A539 +1000</f>
@@ -13276,7 +13297,7 @@
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E540" s="2" t="n">
         <f aca="false">A540 +1000</f>
@@ -13294,7 +13315,7 @@
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E541" s="2" t="n">
         <f aca="false">A541 +1000</f>
@@ -13312,7 +13333,7 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E542" s="2" t="n">
         <f aca="false">A542 +1000</f>
@@ -13330,7 +13351,7 @@
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E543" s="2" t="n">
         <f aca="false">A543 +1000</f>
@@ -13348,7 +13369,7 @@
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E544" s="2" t="n">
         <f aca="false">A544 +1000</f>
@@ -13366,7 +13387,7 @@
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E545" s="2" t="n">
         <f aca="false">A545 +1000</f>
@@ -13384,7 +13405,7 @@
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E546" s="2" t="n">
         <f aca="false">A546 +1000</f>
@@ -13402,7 +13423,7 @@
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E547" s="2" t="n">
         <f aca="false">A547 +1000</f>
@@ -13420,7 +13441,7 @@
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E548" s="2" t="n">
         <f aca="false">A548 +1000</f>
@@ -13438,7 +13459,7 @@
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E549" s="2" t="n">
         <f aca="false">A549 +1000</f>
@@ -13456,7 +13477,7 @@
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E550" s="2" t="n">
         <f aca="false">A550 +1000</f>
@@ -13474,7 +13495,7 @@
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E551" s="2" t="n">
         <f aca="false">A551 +1000</f>
@@ -13492,7 +13513,7 @@
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E552" s="2" t="n">
         <f aca="false">A552 +1000</f>
@@ -13510,7 +13531,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E553" s="2" t="n">
         <f aca="false">A553 +1000</f>
@@ -13528,7 +13549,7 @@
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E554" s="2" t="n">
         <f aca="false">A554 +1000</f>
@@ -13546,7 +13567,7 @@
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E555" s="2" t="n">
         <f aca="false">A555 +1000</f>
@@ -13564,7 +13585,7 @@
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E556" s="2" t="n">
         <f aca="false">A556 +1000</f>
@@ -13582,7 +13603,7 @@
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E557" s="2" t="n">
         <f aca="false">A557 +1000</f>
@@ -13600,7 +13621,7 @@
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E558" s="2" t="n">
         <f aca="false">A558 +1000</f>
@@ -13611,10 +13632,10 @@
         <v>2557</v>
       </c>
       <c r="J558" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K558" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M558" s="2" t="n">
         <f aca="false">I558 +1000</f>
@@ -13624,7 +13645,7 @@
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E559" s="2" t="n">
         <f aca="false">A559 +1000</f>
@@ -13642,7 +13663,7 @@
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E560" s="2" t="n">
         <f aca="false">A560 +1000</f>
@@ -13660,7 +13681,7 @@
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E561" s="2" t="n">
         <f aca="false">A561 +1000</f>
@@ -13678,7 +13699,7 @@
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E562" s="2" t="n">
         <f aca="false">A562 +1000</f>
@@ -13696,7 +13717,7 @@
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E563" s="2" t="n">
         <f aca="false">A563 +1000</f>
@@ -13714,7 +13735,7 @@
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E564" s="2" t="n">
         <f aca="false">A564 +1000</f>
@@ -13732,7 +13753,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E565" s="2" t="n">
         <f aca="false">A565 +1000</f>
@@ -13750,7 +13771,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E566" s="2" t="n">
         <f aca="false">A566 +1000</f>
@@ -13768,7 +13789,7 @@
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E567" s="2" t="n">
         <f aca="false">A567 +1000</f>
@@ -13786,7 +13807,7 @@
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E568" s="2" t="n">
         <f aca="false">A568 +1000</f>
@@ -13804,7 +13825,7 @@
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E569" s="2" t="n">
         <f aca="false">A569 +1000</f>
@@ -13822,7 +13843,7 @@
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E570" s="2" t="n">
         <f aca="false">A570 +1000</f>
@@ -13840,7 +13861,7 @@
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E571" s="2" t="n">
         <f aca="false">A571 +1000</f>
@@ -13858,7 +13879,7 @@
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E572" s="2" t="n">
         <f aca="false">A572 +1000</f>
@@ -13876,7 +13897,7 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E573" s="2" t="n">
         <f aca="false">A573 +1000</f>
@@ -13894,7 +13915,7 @@
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E574" s="2" t="n">
         <f aca="false">A574 +1000</f>
@@ -13912,7 +13933,7 @@
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E575" s="2" t="n">
         <f aca="false">A575 +1000</f>
@@ -13930,7 +13951,7 @@
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E576" s="2" t="n">
         <f aca="false">A576 +1000</f>
@@ -13948,7 +13969,7 @@
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E577" s="2" t="n">
         <f aca="false">A577 +1000</f>
@@ -13966,7 +13987,7 @@
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E578" s="2" t="n">
         <f aca="false">A578 +1000</f>
@@ -13984,7 +14005,7 @@
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E579" s="2" t="n">
         <f aca="false">A579 +1000</f>
@@ -14002,7 +14023,7 @@
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E580" s="2" t="n">
         <f aca="false">A580 +1000</f>
@@ -14020,7 +14041,7 @@
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E581" s="2" t="n">
         <f aca="false">A581 +1000</f>
@@ -14038,7 +14059,7 @@
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E582" s="2" t="n">
         <f aca="false">A582 +1000</f>
@@ -14056,7 +14077,7 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E583" s="2" t="n">
         <f aca="false">A583 +1000</f>
@@ -14074,7 +14095,7 @@
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E584" s="2" t="n">
         <f aca="false">A584 +1000</f>
@@ -14092,7 +14113,7 @@
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E585" s="2" t="n">
         <f aca="false">A585 +1000</f>
@@ -14110,7 +14131,7 @@
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E586" s="2" t="n">
         <f aca="false">A586 +1000</f>
@@ -14128,7 +14149,7 @@
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E587" s="2" t="n">
         <f aca="false">A587 +1000</f>
@@ -14146,7 +14167,7 @@
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E588" s="2" t="n">
         <f aca="false">A588 +1000</f>
@@ -14164,7 +14185,7 @@
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E589" s="2" t="n">
         <f aca="false">A589 +1000</f>
@@ -14182,7 +14203,7 @@
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E590" s="2" t="n">
         <f aca="false">A590 +1000</f>
@@ -14200,7 +14221,7 @@
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E591" s="2" t="n">
         <f aca="false">A591 +1000</f>
@@ -14218,7 +14239,7 @@
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E592" s="2" t="n">
         <f aca="false">A592 +1000</f>
@@ -14236,7 +14257,7 @@
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E593" s="2" t="n">
         <f aca="false">A593 +1000</f>
@@ -14254,7 +14275,7 @@
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E594" s="2" t="n">
         <f aca="false">A594 +1000</f>
@@ -14272,7 +14293,7 @@
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E595" s="2" t="n">
         <f aca="false">A595 +1000</f>
@@ -14290,7 +14311,7 @@
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E596" s="2" t="n">
         <f aca="false">A596 +1000</f>
@@ -14308,7 +14329,7 @@
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E597" s="2" t="n">
         <f aca="false">A597 +1000</f>
@@ -14326,7 +14347,7 @@
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E598" s="2" t="n">
         <f aca="false">A598 +1000</f>
@@ -14344,7 +14365,7 @@
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E599" s="2" t="n">
         <f aca="false">A599 +1000</f>
@@ -14362,7 +14383,7 @@
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E600" s="2" t="n">
         <f aca="false">A600 +1000</f>
@@ -14380,7 +14401,7 @@
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E601" s="2" t="n">
         <f aca="false">A601 +1000</f>
@@ -14398,7 +14419,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E602" s="2" t="n">
         <f aca="false">A602 +1000</f>
@@ -14416,7 +14437,7 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E603" s="2" t="n">
         <f aca="false">A603 +1000</f>
@@ -14434,7 +14455,7 @@
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E604" s="2" t="n">
         <f aca="false">A604 +1000</f>
@@ -14452,7 +14473,7 @@
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E605" s="2" t="n">
         <f aca="false">A605 +1000</f>
@@ -14470,7 +14491,7 @@
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E606" s="2" t="n">
         <f aca="false">A606 +1000</f>
@@ -14488,7 +14509,7 @@
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E607" s="2" t="n">
         <f aca="false">A607 +1000</f>
@@ -14506,7 +14527,7 @@
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E608" s="2" t="n">
         <f aca="false">A608 +1000</f>
@@ -14524,7 +14545,7 @@
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E609" s="2" t="n">
         <f aca="false">A609 +1000</f>
@@ -14542,7 +14563,7 @@
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E610" s="2" t="n">
         <f aca="false">A610 +1000</f>
@@ -14560,7 +14581,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E611" s="2" t="n">
         <f aca="false">A611 +1000</f>
@@ -14578,7 +14599,7 @@
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E612" s="2" t="n">
         <f aca="false">A612 +1000</f>
@@ -14596,7 +14617,7 @@
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E613" s="2" t="n">
         <f aca="false">A613 +1000</f>
@@ -14614,7 +14635,7 @@
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E614" s="2" t="n">
         <f aca="false">A614 +1000</f>
@@ -14632,7 +14653,7 @@
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E615" s="2" t="n">
         <f aca="false">A615 +1000</f>
@@ -14650,7 +14671,7 @@
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E616" s="2" t="n">
         <f aca="false">A616 +1000</f>
@@ -14668,7 +14689,7 @@
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E617" s="2" t="n">
         <f aca="false">A617 +1000</f>
@@ -14686,7 +14707,7 @@
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E618" s="2" t="n">
         <f aca="false">A618 +1000</f>
@@ -14704,7 +14725,7 @@
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E619" s="2" t="n">
         <f aca="false">A619 +1000</f>
@@ -14722,7 +14743,7 @@
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E620" s="2" t="n">
         <f aca="false">A620 +1000</f>
@@ -14740,7 +14761,7 @@
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E621" s="2" t="n">
         <f aca="false">A621 +1000</f>
@@ -14758,16 +14779,16 @@
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C622" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E622" s="2" t="n">
         <f aca="false">A622 +1000</f>
@@ -14785,7 +14806,7 @@
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E623" s="2" t="n">
         <f aca="false">A623 +1000</f>
@@ -14803,7 +14824,7 @@
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E624" s="2" t="n">
         <f aca="false">A624 +1000</f>
@@ -14821,7 +14842,7 @@
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E625" s="2" t="n">
         <f aca="false">A625 +1000</f>
@@ -14839,7 +14860,7 @@
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E626" s="2" t="n">
         <f aca="false">A626 +1000</f>
@@ -14857,7 +14878,7 @@
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E627" s="2" t="n">
         <f aca="false">A627 +1000</f>
@@ -14875,7 +14896,7 @@
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E628" s="2" t="n">
         <f aca="false">A628 +1000</f>
@@ -14893,7 +14914,7 @@
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E629" s="2" t="n">
         <f aca="false">A629 +1000</f>
@@ -14911,7 +14932,7 @@
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E630" s="2" t="n">
         <f aca="false">A630 +1000</f>
@@ -14929,7 +14950,7 @@
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E631" s="2" t="n">
         <f aca="false">A631 +1000</f>
@@ -14947,7 +14968,7 @@
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E632" s="2" t="n">
         <f aca="false">A632 +1000</f>
@@ -14965,7 +14986,7 @@
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E633" s="2" t="n">
         <f aca="false">A633 +1000</f>
@@ -14983,7 +15004,7 @@
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E634" s="2" t="n">
         <f aca="false">A634 +1000</f>
@@ -15001,7 +15022,7 @@
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E635" s="2" t="n">
         <f aca="false">A635 +1000</f>
@@ -15019,7 +15040,7 @@
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E636" s="2" t="n">
         <f aca="false">A636 +1000</f>
@@ -15037,7 +15058,7 @@
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E637" s="2" t="n">
         <f aca="false">A637 +1000</f>
@@ -15055,7 +15076,7 @@
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E638" s="2" t="n">
         <f aca="false">A638 +1000</f>
@@ -15073,7 +15094,7 @@
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E639" s="2" t="n">
         <f aca="false">A639 +1000</f>
@@ -15091,7 +15112,7 @@
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E640" s="2" t="n">
         <f aca="false">A640 +1000</f>
@@ -15109,7 +15130,7 @@
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E641" s="2" t="n">
         <f aca="false">A641 +1000</f>
@@ -15127,7 +15148,7 @@
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E642" s="2" t="n">
         <f aca="false">A642 +1000</f>
@@ -15145,7 +15166,7 @@
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E643" s="2" t="n">
         <f aca="false">A643 +1000</f>
@@ -15163,7 +15184,7 @@
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E644" s="2" t="n">
         <f aca="false">A644 +1000</f>
@@ -15181,7 +15202,7 @@
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E645" s="2" t="n">
         <f aca="false">A645 +1000</f>
@@ -15199,7 +15220,7 @@
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E646" s="2" t="n">
         <f aca="false">A646 +1000</f>
@@ -15217,7 +15238,7 @@
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E647" s="2" t="n">
         <f aca="false">A647 +1000</f>
@@ -15235,7 +15256,7 @@
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E648" s="2" t="n">
         <f aca="false">A648 +1000</f>
@@ -15253,7 +15274,7 @@
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E649" s="2" t="n">
         <f aca="false">A649 +1000</f>
@@ -15271,7 +15292,7 @@
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E650" s="2" t="n">
         <f aca="false">A650 +1000</f>
@@ -15289,7 +15310,7 @@
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E651" s="2" t="n">
         <f aca="false">A651 +1000</f>
@@ -15307,7 +15328,7 @@
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E652" s="2" t="n">
         <f aca="false">A652 +1000</f>
@@ -15325,7 +15346,7 @@
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E653" s="2" t="n">
         <f aca="false">A653 +1000</f>
@@ -15343,16 +15364,16 @@
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C654" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E654" s="2" t="n">
         <f aca="false">A654 +1000</f>
@@ -15370,7 +15391,7 @@
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E655" s="2" t="n">
         <f aca="false">A655 +1000</f>
@@ -15388,7 +15409,7 @@
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E656" s="2" t="n">
         <f aca="false">A656 +1000</f>
@@ -15406,7 +15427,7 @@
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E657" s="2" t="n">
         <f aca="false">A657 +1000</f>
@@ -15424,7 +15445,7 @@
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E658" s="2" t="n">
         <f aca="false">A658 +1000</f>
@@ -15442,7 +15463,7 @@
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E659" s="2" t="n">
         <f aca="false">A659 +1000</f>
@@ -15460,7 +15481,7 @@
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E660" s="2" t="n">
         <f aca="false">A660 +1000</f>
@@ -15478,7 +15499,7 @@
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E661" s="2" t="n">
         <f aca="false">A661 +1000</f>
@@ -15496,7 +15517,7 @@
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E662" s="2" t="n">
         <f aca="false">A662 +1000</f>
@@ -15514,7 +15535,7 @@
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E663" s="2" t="n">
         <f aca="false">A663 +1000</f>
@@ -15532,7 +15553,7 @@
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E664" s="2" t="n">
         <f aca="false">A664 +1000</f>
@@ -15550,7 +15571,7 @@
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E665" s="2" t="n">
         <f aca="false">A665 +1000</f>
@@ -15568,7 +15589,7 @@
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E666" s="2" t="n">
         <f aca="false">A666 +1000</f>
@@ -15586,7 +15607,7 @@
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E667" s="2" t="n">
         <f aca="false">A667 +1000</f>
@@ -15604,7 +15625,7 @@
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E668" s="2" t="n">
         <f aca="false">A668 +1000</f>
@@ -15622,7 +15643,7 @@
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E669" s="2" t="n">
         <f aca="false">A669 +1000</f>
@@ -15640,7 +15661,7 @@
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E670" s="2" t="n">
         <f aca="false">A670 +1000</f>
@@ -15658,7 +15679,7 @@
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E671" s="2" t="n">
         <f aca="false">A671 +1000</f>
@@ -15676,7 +15697,7 @@
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E672" s="2" t="n">
         <f aca="false">A672 +1000</f>
@@ -15694,7 +15715,7 @@
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E673" s="2" t="n">
         <f aca="false">A673 +1000</f>
@@ -15712,7 +15733,7 @@
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E674" s="2" t="n">
         <f aca="false">A674 +1000</f>
@@ -15730,7 +15751,7 @@
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E675" s="2" t="n">
         <f aca="false">A675 +1000</f>
@@ -15748,7 +15769,7 @@
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E676" s="2" t="n">
         <f aca="false">A676 +1000</f>
@@ -15766,7 +15787,7 @@
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E677" s="2" t="n">
         <f aca="false">A677 +1000</f>
@@ -15784,7 +15805,7 @@
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E678" s="2" t="n">
         <f aca="false">A678 +1000</f>
@@ -15802,7 +15823,7 @@
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E679" s="2" t="n">
         <f aca="false">A679 +1000</f>
@@ -15820,7 +15841,7 @@
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E680" s="2" t="n">
         <f aca="false">A680 +1000</f>
@@ -15838,7 +15859,7 @@
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E681" s="2" t="n">
         <f aca="false">A681 +1000</f>
@@ -15856,7 +15877,7 @@
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E682" s="2" t="n">
         <f aca="false">A682 +1000</f>
@@ -15874,7 +15895,7 @@
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E683" s="2" t="n">
         <f aca="false">A683 +1000</f>
@@ -15892,7 +15913,7 @@
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E684" s="2" t="n">
         <f aca="false">A684 +1000</f>
@@ -15910,7 +15931,7 @@
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E685" s="2" t="n">
         <f aca="false">A685 +1000</f>
@@ -15928,7 +15949,7 @@
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E686" s="2" t="n">
         <f aca="false">A686 +1000</f>
@@ -15946,7 +15967,7 @@
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E687" s="2" t="n">
         <f aca="false">A687 +1000</f>
@@ -15964,7 +15985,7 @@
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E688" s="2" t="n">
         <f aca="false">A688 +1000</f>
@@ -15982,7 +16003,7 @@
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E689" s="2" t="n">
         <f aca="false">A689 +1000</f>
@@ -16000,7 +16021,7 @@
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E690" s="2" t="n">
         <f aca="false">A690 +1000</f>
@@ -16018,7 +16039,7 @@
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E691" s="2" t="n">
         <f aca="false">A691 +1000</f>
@@ -16036,7 +16057,7 @@
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E692" s="2" t="n">
         <f aca="false">A692 +1000</f>
@@ -16054,7 +16075,7 @@
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E693" s="2" t="n">
         <f aca="false">A693 +1000</f>
@@ -16072,7 +16093,7 @@
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E694" s="2" t="n">
         <f aca="false">A694 +1000</f>
@@ -16090,7 +16111,7 @@
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E695" s="2" t="n">
         <f aca="false">A695 +1000</f>
@@ -16108,7 +16129,7 @@
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E696" s="2" t="n">
         <f aca="false">A696 +1000</f>
@@ -16126,7 +16147,7 @@
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E697" s="2" t="n">
         <f aca="false">A697 +1000</f>
@@ -16144,7 +16165,7 @@
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E698" s="2" t="n">
         <f aca="false">A698 +1000</f>
@@ -16162,7 +16183,7 @@
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E699" s="2" t="n">
         <f aca="false">A699 +1000</f>
@@ -16180,7 +16201,7 @@
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E700" s="2" t="n">
         <f aca="false">A700 +1000</f>
@@ -16198,13 +16219,13 @@
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B701" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C701" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E701" s="2" t="n">
         <f aca="false">A701 +1000</f>
@@ -16222,13 +16243,13 @@
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B702" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C702" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E702" s="2" t="n">
         <f aca="false">A702 +1000</f>
@@ -16246,13 +16267,13 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B703" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C703" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E703" s="2" t="n">
         <f aca="false">A703 +1000</f>
@@ -16270,13 +16291,13 @@
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B704" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C704" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E704" s="2" t="n">
         <f aca="false">A704 +1000</f>
@@ -16294,7 +16315,7 @@
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E705" s="2" t="n">
         <f aca="false">A705 +1000</f>
@@ -16312,7 +16333,7 @@
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E706" s="2" t="n">
         <f aca="false">A706 +1000</f>
@@ -16330,7 +16351,7 @@
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E707" s="2" t="n">
         <f aca="false">A707 +1000</f>
@@ -16348,20 +16369,20 @@
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
         <v>1707</v>
       </c>
       <c r="F708" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G708" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H708" s="0" t="s">
-        <v>214</v>
+        <v>4</v>
+      </c>
+      <c r="H708" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="I708" s="2" t="n">
         <f aca="false">E708 +1000</f>
@@ -16375,12 +16396,15 @@
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E709" s="2" t="n">
         <f aca="false">A709 +1000</f>
         <v>1708</v>
       </c>
+      <c r="H709" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="I709" s="2" t="n">
         <f aca="false">E709 +1000</f>
         <v>2708</v>
@@ -16393,7 +16417,7 @@
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E710" s="2" t="n">
         <f aca="false">A710 +1000</f>
@@ -16411,7 +16435,7 @@
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E711" s="2" t="n">
         <f aca="false">A711 +1000</f>
@@ -16429,7 +16453,7 @@
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E712" s="2" t="n">
         <f aca="false">A712 +1000</f>
@@ -16447,7 +16471,7 @@
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E713" s="2" t="n">
         <f aca="false">A713 +1000</f>
@@ -16465,7 +16489,7 @@
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E714" s="2" t="n">
         <f aca="false">A714 +1000</f>
@@ -16483,7 +16507,7 @@
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E715" s="2" t="n">
         <f aca="false">A715 +1000</f>
@@ -16501,7 +16525,7 @@
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E716" s="2" t="n">
         <f aca="false">A716 +1000</f>
@@ -16519,7 +16543,7 @@
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E717" s="2" t="n">
         <f aca="false">A717 +1000</f>
@@ -16537,7 +16561,7 @@
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E718" s="2" t="n">
         <f aca="false">A718 +1000</f>
@@ -16555,7 +16579,7 @@
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E719" s="2" t="n">
         <f aca="false">A719 +1000</f>
@@ -16573,7 +16597,7 @@
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E720" s="2" t="n">
         <f aca="false">A720 +1000</f>
@@ -16591,7 +16615,7 @@
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E721" s="2" t="n">
         <f aca="false">A721 +1000</f>
@@ -16609,7 +16633,7 @@
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E722" s="2" t="n">
         <f aca="false">A722 +1000</f>
@@ -16627,7 +16651,7 @@
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E723" s="2" t="n">
         <f aca="false">A723 +1000</f>
@@ -16645,7 +16669,7 @@
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E724" s="2" t="n">
         <f aca="false">A724 +1000</f>
@@ -16663,7 +16687,7 @@
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E725" s="2" t="n">
         <f aca="false">A725 +1000</f>
@@ -16681,7 +16705,7 @@
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E726" s="2" t="n">
         <f aca="false">A726 +1000</f>
@@ -16699,7 +16723,7 @@
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E727" s="2" t="n">
         <f aca="false">A727 +1000</f>
@@ -16717,7 +16741,7 @@
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E728" s="2" t="n">
         <f aca="false">A728 +1000</f>
@@ -16735,7 +16759,7 @@
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E729" s="2" t="n">
         <f aca="false">A729 +1000</f>
@@ -16753,7 +16777,7 @@
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E730" s="2" t="n">
         <f aca="false">A730 +1000</f>
@@ -16771,7 +16795,7 @@
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E731" s="2" t="n">
         <f aca="false">A731 +1000</f>
@@ -16789,7 +16813,7 @@
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E732" s="2" t="n">
         <f aca="false">A732 +1000</f>
@@ -16807,7 +16831,7 @@
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E733" s="2" t="n">
         <f aca="false">A733 +1000</f>
@@ -16825,7 +16849,7 @@
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E734" s="2" t="n">
         <f aca="false">A734 +1000</f>
@@ -16843,7 +16867,7 @@
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E735" s="2" t="n">
         <f aca="false">A735 +1000</f>
@@ -16861,7 +16885,7 @@
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E736" s="2" t="n">
         <f aca="false">A736 +1000</f>
@@ -16879,7 +16903,7 @@
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E737" s="2" t="n">
         <f aca="false">A737 +1000</f>
@@ -16897,7 +16921,7 @@
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E738" s="2" t="n">
         <f aca="false">A738 +1000</f>
@@ -16915,7 +16939,7 @@
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E739" s="2" t="n">
         <f aca="false">A739 +1000</f>
@@ -16933,7 +16957,7 @@
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E740" s="2" t="n">
         <f aca="false">A740 +1000</f>
@@ -16951,7 +16975,7 @@
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E741" s="2" t="n">
         <f aca="false">A741 +1000</f>
@@ -16969,7 +16993,7 @@
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E742" s="2" t="n">
         <f aca="false">A742 +1000</f>
@@ -16987,7 +17011,7 @@
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E743" s="2" t="n">
         <f aca="false">A743 +1000</f>
@@ -17005,7 +17029,7 @@
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E744" s="2" t="n">
         <f aca="false">A744 +1000</f>
@@ -17023,7 +17047,7 @@
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E745" s="2" t="n">
         <f aca="false">A745 +1000</f>
@@ -17041,7 +17065,7 @@
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E746" s="2" t="n">
         <f aca="false">A746 +1000</f>
@@ -17059,7 +17083,7 @@
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E747" s="2" t="n">
         <f aca="false">A747 +1000</f>
@@ -17077,7 +17101,7 @@
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E748" s="2" t="n">
         <f aca="false">A748 +1000</f>
@@ -17095,7 +17119,7 @@
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E749" s="2" t="n">
         <f aca="false">A749 +1000</f>
@@ -17113,7 +17137,7 @@
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E750" s="2" t="n">
         <f aca="false">A750 +1000</f>
@@ -17131,7 +17155,7 @@
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E751" s="2" t="n">
         <f aca="false">A751 +1000</f>
@@ -17149,7 +17173,7 @@
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E752" s="2" t="n">
         <f aca="false">A752 +1000</f>
@@ -17167,7 +17191,7 @@
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E753" s="2" t="n">
         <f aca="false">A753 +1000</f>
@@ -17185,7 +17209,7 @@
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E754" s="2" t="n">
         <f aca="false">A754 +1000</f>
@@ -17203,7 +17227,7 @@
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E755" s="2" t="n">
         <f aca="false">A755 +1000</f>
@@ -17221,7 +17245,7 @@
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E756" s="2" t="n">
         <f aca="false">A756 +1000</f>
@@ -17239,7 +17263,7 @@
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E757" s="2" t="n">
         <f aca="false">A757 +1000</f>
@@ -17257,7 +17281,7 @@
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E758" s="2" t="n">
         <f aca="false">A758 +1000</f>
@@ -17275,7 +17299,7 @@
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E759" s="2" t="n">
         <f aca="false">A759 +1000</f>
@@ -17293,7 +17317,7 @@
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E760" s="2" t="n">
         <f aca="false">A760 +1000</f>
@@ -17311,7 +17335,7 @@
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E761" s="2" t="n">
         <f aca="false">A761 +1000</f>
@@ -17329,7 +17353,7 @@
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E762" s="2" t="n">
         <f aca="false">A762 +1000</f>
@@ -17347,7 +17371,7 @@
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E763" s="2" t="n">
         <f aca="false">A763 +1000</f>
@@ -17365,7 +17389,7 @@
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E764" s="2" t="n">
         <f aca="false">A764 +1000</f>
@@ -17383,7 +17407,7 @@
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E765" s="2" t="n">
         <f aca="false">A765 +1000</f>
@@ -17401,7 +17425,7 @@
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E766" s="2" t="n">
         <f aca="false">A766 +1000</f>
@@ -17419,7 +17443,7 @@
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E767" s="2" t="n">
         <f aca="false">A767 +1000</f>
@@ -17437,7 +17461,7 @@
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E768" s="2" t="n">
         <f aca="false">A768 +1000</f>
@@ -17455,7 +17479,7 @@
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E769" s="2" t="n">
         <f aca="false">A769 +1000</f>
@@ -17473,7 +17497,7 @@
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E770" s="2" t="n">
         <f aca="false">A770 +1000</f>
@@ -17491,7 +17515,7 @@
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E771" s="2" t="n">
         <f aca="false">A771 +1000</f>
@@ -17509,7 +17533,7 @@
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E772" s="2" t="n">
         <f aca="false">A772 +1000</f>
@@ -17527,7 +17551,7 @@
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E773" s="2" t="n">
         <f aca="false">A773 +1000</f>
@@ -17545,7 +17569,7 @@
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E774" s="2" t="n">
         <f aca="false">A774 +1000</f>
@@ -17563,7 +17587,7 @@
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E775" s="2" t="n">
         <f aca="false">A775 +1000</f>
@@ -17581,7 +17605,7 @@
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E776" s="2" t="n">
         <f aca="false">A776 +1000</f>
@@ -17599,7 +17623,7 @@
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E777" s="2" t="n">
         <f aca="false">A777 +1000</f>
@@ -17617,7 +17641,7 @@
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E778" s="2" t="n">
         <f aca="false">A778 +1000</f>
@@ -17635,7 +17659,7 @@
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E779" s="2" t="n">
         <f aca="false">A779 +1000</f>
@@ -17653,7 +17677,7 @@
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E780" s="2" t="n">
         <f aca="false">A780 +1000</f>
@@ -17671,7 +17695,7 @@
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E781" s="2" t="n">
         <f aca="false">A781 +1000</f>
@@ -17689,7 +17713,7 @@
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E782" s="2" t="n">
         <f aca="false">A782 +1000</f>
@@ -17707,7 +17731,7 @@
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E783" s="2" t="n">
         <f aca="false">A783 +1000</f>
@@ -17725,7 +17749,7 @@
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E784" s="2" t="n">
         <f aca="false">A784 +1000</f>
@@ -17743,7 +17767,7 @@
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E785" s="2" t="n">
         <f aca="false">A785 +1000</f>
@@ -17761,7 +17785,7 @@
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E786" s="2" t="n">
         <f aca="false">A786 +1000</f>
@@ -17779,7 +17803,7 @@
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E787" s="2" t="n">
         <f aca="false">A787 +1000</f>
@@ -17797,7 +17821,7 @@
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E788" s="2" t="n">
         <f aca="false">A788 +1000</f>
@@ -17815,7 +17839,7 @@
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E789" s="2" t="n">
         <f aca="false">A789 +1000</f>
@@ -17833,7 +17857,7 @@
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E790" s="2" t="n">
         <f aca="false">A790 +1000</f>
@@ -17851,7 +17875,7 @@
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E791" s="2" t="n">
         <f aca="false">A791 +1000</f>
@@ -17869,7 +17893,7 @@
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E792" s="2" t="n">
         <f aca="false">A792 +1000</f>
@@ -17887,7 +17911,7 @@
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E793" s="2" t="n">
         <f aca="false">A793 +1000</f>
@@ -17905,7 +17929,7 @@
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E794" s="2" t="n">
         <f aca="false">A794 +1000</f>
@@ -17923,7 +17947,7 @@
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E795" s="2" t="n">
         <f aca="false">A795 +1000</f>
@@ -17941,7 +17965,7 @@
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E796" s="2" t="n">
         <f aca="false">A796 +1000</f>
@@ -17959,7 +17983,7 @@
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E797" s="2" t="n">
         <f aca="false">A797 +1000</f>
@@ -17977,7 +18001,7 @@
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E798" s="2" t="n">
         <f aca="false">A798 +1000</f>
@@ -17995,7 +18019,7 @@
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E799" s="2" t="n">
         <f aca="false">A799 +1000</f>
@@ -18013,7 +18037,7 @@
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E800" s="2" t="n">
         <f aca="false">A800 +1000</f>
@@ -18031,7 +18055,7 @@
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E801" s="2" t="n">
         <f aca="false">A801 +1000</f>
@@ -18049,7 +18073,7 @@
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E802" s="2" t="n">
         <f aca="false">A802 +1000</f>
@@ -18067,7 +18091,7 @@
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E803" s="2" t="n">
         <f aca="false">A803 +1000</f>
@@ -18085,7 +18109,7 @@
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E804" s="2" t="n">
         <f aca="false">A804 +1000</f>
@@ -18103,7 +18127,7 @@
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E805" s="2" t="n">
         <f aca="false">A805 +1000</f>
@@ -18121,7 +18145,7 @@
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E806" s="2" t="n">
         <f aca="false">A806 +1000</f>
@@ -18139,7 +18163,7 @@
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E807" s="2" t="n">
         <f aca="false">A807 +1000</f>
@@ -18157,7 +18181,7 @@
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E808" s="2" t="n">
         <f aca="false">A808 +1000</f>
@@ -18175,7 +18199,7 @@
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E809" s="2" t="n">
         <f aca="false">A809 +1000</f>
@@ -18193,7 +18217,7 @@
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E810" s="2" t="n">
         <f aca="false">A810 +1000</f>
@@ -18211,7 +18235,7 @@
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E811" s="2" t="n">
         <f aca="false">A811 +1000</f>
@@ -18229,7 +18253,7 @@
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E812" s="2" t="n">
         <f aca="false">A812 +1000</f>
@@ -18247,7 +18271,7 @@
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E813" s="2" t="n">
         <f aca="false">A813 +1000</f>
@@ -18265,7 +18289,7 @@
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E814" s="2" t="n">
         <f aca="false">A814 +1000</f>
@@ -18283,7 +18307,7 @@
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E815" s="2" t="n">
         <f aca="false">A815 +1000</f>
@@ -18301,7 +18325,7 @@
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E816" s="2" t="n">
         <f aca="false">A816 +1000</f>
@@ -18319,7 +18343,7 @@
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E817" s="2" t="n">
         <f aca="false">A817 +1000</f>
@@ -18337,7 +18361,7 @@
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E818" s="2" t="n">
         <f aca="false">A818 +1000</f>
@@ -18355,7 +18379,7 @@
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E819" s="2" t="n">
         <f aca="false">A819 +1000</f>
@@ -18373,7 +18397,7 @@
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E820" s="2" t="n">
         <f aca="false">A820 +1000</f>
@@ -18391,7 +18415,7 @@
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E821" s="2" t="n">
         <f aca="false">A821 +1000</f>
@@ -18409,7 +18433,7 @@
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E822" s="2" t="n">
         <f aca="false">A822 +1000</f>
@@ -18427,7 +18451,7 @@
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E823" s="2" t="n">
         <f aca="false">A823 +1000</f>
@@ -18445,7 +18469,7 @@
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E824" s="2" t="n">
         <f aca="false">A824 +1000</f>
@@ -18463,7 +18487,7 @@
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E825" s="2" t="n">
         <f aca="false">A825 +1000</f>
@@ -18481,7 +18505,7 @@
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E826" s="2" t="n">
         <f aca="false">A826 +1000</f>
@@ -18499,7 +18523,7 @@
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E827" s="2" t="n">
         <f aca="false">A827 +1000</f>
@@ -18517,7 +18541,7 @@
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E828" s="2" t="n">
         <f aca="false">A828 +1000</f>
@@ -18535,7 +18559,7 @@
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E829" s="2" t="n">
         <f aca="false">A829 +1000</f>
@@ -18553,7 +18577,7 @@
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E830" s="2" t="n">
         <f aca="false">A830 +1000</f>
@@ -18571,7 +18595,7 @@
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E831" s="2" t="n">
         <f aca="false">A831 +1000</f>
@@ -18589,7 +18613,7 @@
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E832" s="2" t="n">
         <f aca="false">A832 +1000</f>
@@ -18607,7 +18631,7 @@
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E833" s="2" t="n">
         <f aca="false">A833 +1000</f>
@@ -18625,7 +18649,7 @@
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E834" s="2" t="n">
         <f aca="false">A834 +1000</f>
@@ -18643,7 +18667,7 @@
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E835" s="2" t="n">
         <f aca="false">A835 +1000</f>
@@ -18661,7 +18685,7 @@
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E836" s="2" t="n">
         <f aca="false">A836 +1000</f>
@@ -18679,7 +18703,7 @@
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E837" s="2" t="n">
         <f aca="false">A837 +1000</f>
@@ -18697,7 +18721,7 @@
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E838" s="2" t="n">
         <f aca="false">A838 +1000</f>
@@ -18715,7 +18739,7 @@
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E839" s="2" t="n">
         <f aca="false">A839 +1000</f>
@@ -18733,7 +18757,7 @@
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E840" s="2" t="n">
         <f aca="false">A840 +1000</f>
@@ -18751,7 +18775,7 @@
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E841" s="2" t="n">
         <f aca="false">A841 +1000</f>
@@ -18769,7 +18793,7 @@
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E842" s="2" t="n">
         <f aca="false">A842 +1000</f>
@@ -18787,7 +18811,7 @@
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E843" s="2" t="n">
         <f aca="false">A843 +1000</f>
@@ -18805,7 +18829,7 @@
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E844" s="2" t="n">
         <f aca="false">A844 +1000</f>
@@ -18823,7 +18847,7 @@
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E845" s="2" t="n">
         <f aca="false">A845 +1000</f>
@@ -18841,7 +18865,7 @@
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E846" s="2" t="n">
         <f aca="false">A846 +1000</f>
@@ -18859,16 +18883,16 @@
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B847" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C847" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E847" s="2" t="n">
         <f aca="false">A847 +1000</f>
@@ -18886,7 +18910,7 @@
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E848" s="2" t="n">
         <f aca="false">A848 +1000</f>
@@ -18904,7 +18928,7 @@
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E849" s="2" t="n">
         <f aca="false">A849 +1000</f>
@@ -18922,7 +18946,7 @@
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E850" s="2" t="n">
         <f aca="false">A850 +1000</f>
@@ -18940,7 +18964,7 @@
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E851" s="2" t="n">
         <f aca="false">A851 +1000</f>
@@ -18958,7 +18982,7 @@
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E852" s="2" t="n">
         <f aca="false">A852 +1000</f>
@@ -18976,7 +19000,7 @@
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E853" s="2" t="n">
         <f aca="false">A853 +1000</f>
@@ -18994,7 +19018,7 @@
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E854" s="2" t="n">
         <f aca="false">A854 +1000</f>
@@ -19012,7 +19036,7 @@
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E855" s="2" t="n">
         <f aca="false">A855 +1000</f>
@@ -19030,7 +19054,7 @@
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E856" s="2" t="n">
         <f aca="false">A856 +1000</f>
@@ -19048,7 +19072,7 @@
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E857" s="2" t="n">
         <f aca="false">A857 +1000</f>
@@ -19066,7 +19090,7 @@
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E858" s="2" t="n">
         <f aca="false">A858 +1000</f>
@@ -19084,7 +19108,7 @@
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E859" s="2" t="n">
         <f aca="false">A859 +1000</f>
@@ -19102,7 +19126,7 @@
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E860" s="2" t="n">
         <f aca="false">A860 +1000</f>
@@ -19120,7 +19144,7 @@
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E861" s="2" t="n">
         <f aca="false">A861 +1000</f>
@@ -19138,7 +19162,7 @@
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E862" s="2" t="n">
         <f aca="false">A862 +1000</f>
@@ -19156,7 +19180,7 @@
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E863" s="2" t="n">
         <f aca="false">A863 +1000</f>
@@ -19174,7 +19198,7 @@
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E864" s="2" t="n">
         <f aca="false">A864 +1000</f>
@@ -19192,7 +19216,7 @@
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E865" s="2" t="n">
         <f aca="false">A865 +1000</f>
@@ -19210,7 +19234,7 @@
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E866" s="2" t="n">
         <f aca="false">A866 +1000</f>
@@ -19228,7 +19252,7 @@
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E867" s="2" t="n">
         <f aca="false">A867 +1000</f>
@@ -19246,7 +19270,7 @@
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E868" s="2" t="n">
         <f aca="false">A868 +1000</f>
@@ -19264,7 +19288,7 @@
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E869" s="2" t="n">
         <f aca="false">A869 +1000</f>
@@ -19282,7 +19306,7 @@
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E870" s="2" t="n">
         <f aca="false">A870 +1000</f>
@@ -19300,7 +19324,7 @@
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E871" s="2" t="n">
         <f aca="false">A871 +1000</f>
@@ -19318,7 +19342,7 @@
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E872" s="2" t="n">
         <f aca="false">A872 +1000</f>
@@ -19336,7 +19360,7 @@
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E873" s="2" t="n">
         <f aca="false">A873 +1000</f>
@@ -19354,7 +19378,7 @@
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E874" s="2" t="n">
         <f aca="false">A874 +1000</f>
@@ -19372,7 +19396,7 @@
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E875" s="2" t="n">
         <f aca="false">A875 +1000</f>
@@ -19390,7 +19414,7 @@
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E876" s="2" t="n">
         <f aca="false">A876 +1000</f>
@@ -19408,7 +19432,7 @@
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E877" s="2" t="n">
         <f aca="false">A877 +1000</f>
@@ -19426,7 +19450,7 @@
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E878" s="2" t="n">
         <f aca="false">A878 +1000</f>
@@ -19444,7 +19468,7 @@
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E879" s="2" t="n">
         <f aca="false">A879 +1000</f>
@@ -19462,7 +19486,7 @@
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E880" s="2" t="n">
         <f aca="false">A880 +1000</f>
@@ -19480,7 +19504,7 @@
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E881" s="2" t="n">
         <f aca="false">A881 +1000</f>
@@ -19498,7 +19522,7 @@
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E882" s="2" t="n">
         <f aca="false">A882 +1000</f>
@@ -19516,7 +19540,7 @@
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E883" s="2" t="n">
         <f aca="false">A883 +1000</f>
@@ -19534,7 +19558,7 @@
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E884" s="2" t="n">
         <f aca="false">A884 +1000</f>
@@ -19552,7 +19576,7 @@
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E885" s="2" t="n">
         <f aca="false">A885 +1000</f>
@@ -19570,7 +19594,7 @@
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E886" s="2" t="n">
         <f aca="false">A886 +1000</f>
@@ -19588,7 +19612,7 @@
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E887" s="2" t="n">
         <f aca="false">A887 +1000</f>
@@ -19606,7 +19630,7 @@
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E888" s="2" t="n">
         <f aca="false">A888 +1000</f>
@@ -19624,7 +19648,7 @@
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E889" s="2" t="n">
         <f aca="false">A889 +1000</f>
@@ -19642,7 +19666,7 @@
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E890" s="2" t="n">
         <f aca="false">A890 +1000</f>
@@ -19660,7 +19684,7 @@
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E891" s="2" t="n">
         <f aca="false">A891 +1000</f>
@@ -19678,7 +19702,7 @@
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E892" s="2" t="n">
         <f aca="false">A892 +1000</f>
@@ -19696,7 +19720,7 @@
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E893" s="2" t="n">
         <f aca="false">A893 +1000</f>
@@ -19714,7 +19738,7 @@
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E894" s="2" t="n">
         <f aca="false">A894 +1000</f>
@@ -19732,7 +19756,7 @@
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E895" s="2" t="n">
         <f aca="false">A895 +1000</f>
@@ -19750,7 +19774,7 @@
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E896" s="2" t="n">
         <f aca="false">A896 +1000</f>
@@ -19768,7 +19792,7 @@
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E897" s="2" t="n">
         <f aca="false">A897 +1000</f>
@@ -19786,7 +19810,7 @@
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E898" s="2" t="n">
         <f aca="false">A898 +1000</f>
@@ -19804,7 +19828,7 @@
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E899" s="2" t="n">
         <f aca="false">A899 +1000</f>
@@ -19822,7 +19846,7 @@
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E900" s="2" t="n">
         <f aca="false">A900 +1000</f>
@@ -19840,7 +19864,7 @@
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E901" s="2" t="n">
         <f aca="false">A901 +1000</f>
@@ -19858,7 +19882,7 @@
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E902" s="2" t="n">
         <f aca="false">A902 +1000</f>
@@ -19876,7 +19900,7 @@
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E903" s="2" t="n">
         <f aca="false">A903 +1000</f>
@@ -19894,7 +19918,7 @@
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E904" s="2" t="n">
         <f aca="false">A904 +1000</f>
@@ -19912,7 +19936,16 @@
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
+      </c>
+      <c r="B905" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C905" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D905" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="E905" s="2" t="n">
         <f aca="false">A905 +1000</f>
@@ -19930,7 +19963,7 @@
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E906" s="2" t="n">
         <f aca="false">A906 +1000</f>
@@ -19948,7 +19981,7 @@
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E907" s="2" t="n">
         <f aca="false">A907 +1000</f>
@@ -19966,7 +19999,7 @@
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E908" s="2" t="n">
         <f aca="false">A908 +1000</f>
@@ -19984,7 +20017,7 @@
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E909" s="2" t="n">
         <f aca="false">A909 +1000</f>
@@ -20002,7 +20035,7 @@
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E910" s="2" t="n">
         <f aca="false">A910 +1000</f>
@@ -20020,7 +20053,7 @@
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E911" s="2" t="n">
         <f aca="false">A911 +1000</f>
@@ -20038,7 +20071,7 @@
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E912" s="2" t="n">
         <f aca="false">A912 +1000</f>
@@ -20056,7 +20089,7 @@
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E913" s="2" t="n">
         <f aca="false">A913 +1000</f>
@@ -20074,7 +20107,7 @@
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E914" s="2" t="n">
         <f aca="false">A914 +1000</f>
@@ -20092,7 +20125,7 @@
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E915" s="2" t="n">
         <f aca="false">A915 +1000</f>
@@ -20110,7 +20143,7 @@
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E916" s="2" t="n">
         <f aca="false">A916 +1000</f>
@@ -20128,7 +20161,7 @@
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E917" s="2" t="n">
         <f aca="false">A917 +1000</f>
@@ -20146,7 +20179,7 @@
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E918" s="2" t="n">
         <f aca="false">A918 +1000</f>
@@ -20164,7 +20197,7 @@
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E919" s="2" t="n">
         <f aca="false">A919 +1000</f>
@@ -20182,7 +20215,7 @@
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E920" s="2" t="n">
         <f aca="false">A920 +1000</f>
@@ -20200,7 +20233,7 @@
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E921" s="2" t="n">
         <f aca="false">A921 +1000</f>
@@ -20218,7 +20251,7 @@
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E922" s="2" t="n">
         <f aca="false">A922 +1000</f>
@@ -20236,7 +20269,7 @@
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E923" s="2" t="n">
         <f aca="false">A923 +1000</f>
@@ -20254,7 +20287,7 @@
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E924" s="2" t="n">
         <f aca="false">A924 +1000</f>
@@ -20272,7 +20305,7 @@
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E925" s="2" t="n">
         <f aca="false">A925 +1000</f>
@@ -20290,7 +20323,7 @@
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E926" s="2" t="n">
         <f aca="false">A926 +1000</f>
@@ -20308,7 +20341,7 @@
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E927" s="2" t="n">
         <f aca="false">A927 +1000</f>
@@ -20326,7 +20359,7 @@
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E928" s="2" t="n">
         <f aca="false">A928 +1000</f>
@@ -20344,7 +20377,7 @@
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="E929" s="2" t="n">
         <f aca="false">A929 +1000</f>
@@ -20362,7 +20395,7 @@
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E930" s="2" t="n">
         <f aca="false">A930 +1000</f>
@@ -20380,7 +20413,7 @@
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E931" s="2" t="n">
         <f aca="false">A931 +1000</f>
@@ -20398,7 +20431,7 @@
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E932" s="2" t="n">
         <f aca="false">A932 +1000</f>
@@ -20416,7 +20449,7 @@
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E933" s="2" t="n">
         <f aca="false">A933 +1000</f>
@@ -20434,7 +20467,7 @@
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E934" s="2" t="n">
         <f aca="false">A934 +1000</f>
@@ -20452,7 +20485,7 @@
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E935" s="2" t="n">
         <f aca="false">A935 +1000</f>
@@ -20470,7 +20503,7 @@
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E936" s="2" t="n">
         <f aca="false">A936 +1000</f>
@@ -20488,7 +20521,7 @@
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E937" s="2" t="n">
         <f aca="false">A937 +1000</f>
@@ -20506,7 +20539,7 @@
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E938" s="2" t="n">
         <f aca="false">A938 +1000</f>
@@ -20524,7 +20557,7 @@
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="E939" s="2" t="n">
         <f aca="false">A939 +1000</f>
@@ -20542,7 +20575,7 @@
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E940" s="2" t="n">
         <f aca="false">A940 +1000</f>
@@ -20560,7 +20593,7 @@
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="E941" s="2" t="n">
         <f aca="false">A941 +1000</f>
@@ -20578,7 +20611,7 @@
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="E942" s="2" t="n">
         <f aca="false">A942 +1000</f>
@@ -20596,7 +20629,7 @@
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E943" s="2" t="n">
         <f aca="false">A943 +1000</f>
@@ -20614,7 +20647,7 @@
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E944" s="2" t="n">
         <f aca="false">A944 +1000</f>
@@ -20632,7 +20665,7 @@
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="E945" s="2" t="n">
         <f aca="false">A945 +1000</f>
@@ -20650,7 +20683,7 @@
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E946" s="2" t="n">
         <f aca="false">A946 +1000</f>
@@ -20668,7 +20701,7 @@
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E947" s="2" t="n">
         <f aca="false">A947 +1000</f>
@@ -20686,7 +20719,7 @@
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E948" s="2" t="n">
         <f aca="false">A948 +1000</f>
@@ -20704,7 +20737,7 @@
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E949" s="2" t="n">
         <f aca="false">A949 +1000</f>
@@ -20722,7 +20755,7 @@
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="E950" s="2" t="n">
         <f aca="false">A950 +1000</f>
@@ -20740,7 +20773,7 @@
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E951" s="2" t="n">
         <f aca="false">A951 +1000</f>
@@ -20758,7 +20791,7 @@
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E952" s="2" t="n">
         <f aca="false">A952 +1000</f>
@@ -20776,7 +20809,7 @@
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E953" s="2" t="n">
         <f aca="false">A953 +1000</f>
@@ -20794,7 +20827,7 @@
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E954" s="2" t="n">
         <f aca="false">A954 +1000</f>
@@ -20812,7 +20845,7 @@
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E955" s="2" t="n">
         <f aca="false">A955 +1000</f>
@@ -20830,7 +20863,7 @@
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E956" s="2" t="n">
         <f aca="false">A956 +1000</f>
@@ -20848,7 +20881,7 @@
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E957" s="2" t="n">
         <f aca="false">A957 +1000</f>
@@ -20866,7 +20899,7 @@
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E958" s="2" t="n">
         <f aca="false">A958 +1000</f>
@@ -20884,7 +20917,7 @@
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E959" s="2" t="n">
         <f aca="false">A959 +1000</f>
@@ -20902,7 +20935,7 @@
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E960" s="2" t="n">
         <f aca="false">A960 +1000</f>
@@ -20920,7 +20953,7 @@
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E961" s="2" t="n">
         <f aca="false">A961 +1000</f>
@@ -20938,7 +20971,7 @@
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E962" s="2" t="n">
         <f aca="false">A962 +1000</f>
@@ -20956,7 +20989,7 @@
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E963" s="2" t="n">
         <f aca="false">A963 +1000</f>
@@ -20974,7 +21007,7 @@
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E964" s="2" t="n">
         <f aca="false">A964 +1000</f>
@@ -20992,7 +21025,7 @@
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E965" s="2" t="n">
         <f aca="false">A965 +1000</f>
@@ -21010,7 +21043,7 @@
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E966" s="2" t="n">
         <f aca="false">A966 +1000</f>
@@ -21028,7 +21061,7 @@
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E967" s="2" t="n">
         <f aca="false">A967 +1000</f>
@@ -21046,7 +21079,7 @@
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E968" s="2" t="n">
         <f aca="false">A968 +1000</f>
@@ -21064,7 +21097,7 @@
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E969" s="2" t="n">
         <f aca="false">A969 +1000</f>
@@ -21082,7 +21115,7 @@
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E970" s="2" t="n">
         <f aca="false">A970 +1000</f>
@@ -21100,7 +21133,7 @@
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E971" s="2" t="n">
         <f aca="false">A971 +1000</f>
@@ -21118,7 +21151,7 @@
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E972" s="2" t="n">
         <f aca="false">A972 +1000</f>
@@ -21136,7 +21169,7 @@
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="E973" s="2" t="n">
         <f aca="false">A973 +1000</f>
@@ -21154,7 +21187,7 @@
     </row>
     <row r="974" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E974" s="2" t="n">
         <f aca="false">A974 +1000</f>
@@ -21165,10 +21198,10 @@
         <v>2973</v>
       </c>
       <c r="J974" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K974" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M974" s="2" t="n">
         <f aca="false">I974 +1000</f>
@@ -21178,7 +21211,7 @@
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E975" s="2" t="n">
         <f aca="false">A975 +1000</f>
@@ -21196,7 +21229,7 @@
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E976" s="2" t="n">
         <f aca="false">A976 +1000</f>
@@ -21214,7 +21247,7 @@
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E977" s="2" t="n">
         <f aca="false">A977 +1000</f>
@@ -21232,7 +21265,7 @@
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E978" s="2" t="n">
         <f aca="false">A978 +1000</f>
@@ -21250,7 +21283,7 @@
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E979" s="2" t="n">
         <f aca="false">A979 +1000</f>
@@ -21268,7 +21301,7 @@
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E980" s="2" t="n">
         <f aca="false">A980 +1000</f>
@@ -21286,7 +21319,7 @@
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E981" s="2" t="n">
         <f aca="false">A981 +1000</f>
@@ -21304,7 +21337,7 @@
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E982" s="2" t="n">
         <f aca="false">A982 +1000</f>
@@ -21322,7 +21355,7 @@
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E983" s="2" t="n">
         <f aca="false">A983 +1000</f>
@@ -21340,7 +21373,7 @@
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E984" s="2" t="n">
         <f aca="false">A984 +1000</f>
@@ -21358,7 +21391,7 @@
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E985" s="2" t="n">
         <f aca="false">A985 +1000</f>
@@ -21376,7 +21409,7 @@
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E986" s="2" t="n">
         <f aca="false">A986 +1000</f>
@@ -21394,7 +21427,7 @@
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="E987" s="2" t="n">
         <f aca="false">A987 +1000</f>
@@ -21412,7 +21445,7 @@
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E988" s="2" t="n">
         <f aca="false">A988 +1000</f>
@@ -21430,7 +21463,7 @@
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E989" s="2" t="n">
         <f aca="false">A989 +1000</f>
@@ -21448,7 +21481,7 @@
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E990" s="2" t="n">
         <f aca="false">A990 +1000</f>
@@ -21466,7 +21499,7 @@
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E991" s="2" t="n">
         <f aca="false">A991 +1000</f>
@@ -21484,7 +21517,7 @@
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E992" s="2" t="n">
         <f aca="false">A992 +1000</f>
@@ -21502,7 +21535,7 @@
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E993" s="2" t="n">
         <f aca="false">A993 +1000</f>
@@ -21520,7 +21553,7 @@
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E994" s="2" t="n">
         <f aca="false">A994 +1000</f>
@@ -21538,7 +21571,7 @@
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E995" s="2" t="n">
         <f aca="false">A995 +1000</f>
@@ -21556,7 +21589,7 @@
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E996" s="2" t="n">
         <f aca="false">A996 +1000</f>
@@ -21574,7 +21607,7 @@
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E997" s="2" t="n">
         <f aca="false">A997 +1000</f>
@@ -21592,7 +21625,7 @@
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E998" s="2" t="n">
         <f aca="false">A998 +1000</f>
@@ -21610,7 +21643,7 @@
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E999" s="2" t="n">
         <f aca="false">A999 +1000</f>
@@ -21628,7 +21661,7 @@
     </row>
     <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E1000" s="2" t="n">
         <f aca="false">A1000 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1013">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -3291,7 +3291,8 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.02"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7930,6 +7931,15 @@
         <f aca="false">A249 +1000</f>
         <v>1248</v>
       </c>
+      <c r="F249" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H249" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="I249" s="2" t="n">
         <f aca="false">E249 +1000</f>
         <v>2248</v>
@@ -9972,6 +9982,15 @@
         <f aca="false">A359 +1000</f>
         <v>1358</v>
       </c>
+      <c r="F359" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G359" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H359" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="I359" s="2" t="n">
         <f aca="false">E359 +1000</f>
         <v>2358</v>
@@ -11184,6 +11203,15 @@
         <f aca="false">A424 +1000</f>
         <v>1423</v>
       </c>
+      <c r="F424" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G424" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H424" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="I424" s="2" t="n">
         <f aca="false">E424 +1000</f>
         <v>2423</v>
@@ -11197,6 +11225,15 @@
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
         <v>434</v>
+      </c>
+      <c r="B425" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="E425" s="2" t="n">
         <f aca="false">A425 +1000</f>
@@ -16402,7 +16439,7 @@
         <f aca="false">A709 +1000</f>
         <v>1708</v>
       </c>
-      <c r="H709" s="0" t="n">
+      <c r="H709" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I709" s="2" t="n">
@@ -20414,6 +20451,15 @@
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="1" t="s">
         <v>943</v>
+      </c>
+      <c r="B931" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D931" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="E931" s="2" t="n">
         <f aca="false">A931 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="1013">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -3291,8 +3291,8 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="14.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.02"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4746,6 +4746,15 @@
       <c r="A77" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="B77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="E77" s="2" t="n">
         <f aca="false">A77 +1000</f>
         <v>1076</v>
@@ -21582,6 +21591,15 @@
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="1" t="s">
         <v>1005</v>
+      </c>
+      <c r="B993" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C993" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D993" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="E993" s="2" t="n">
         <f aca="false">A993 +1000</f>

--- a/LC Tracker.xlsx
+++ b/LC Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1014">
   <si>
     <t xml:space="preserve">0000</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t xml:space="preserve">0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String</t>
   </si>
   <si>
     <t xml:space="preserve">0006</t>
@@ -3417,6 +3420,15 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E6" s="2" t="n">
         <f aca="false">A6 +1000</f>
         <v>1005</v>
@@ -3435,7 +3447,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="n">
         <f aca="false">A7 +1000</f>
@@ -3455,7 +3467,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
         <f aca="false">A8 +1000</f>
@@ -3475,7 +3487,16 @@
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
         <f aca="false">A9 +1000</f>
@@ -3488,7 +3509,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" s="2" t="n">
         <f aca="false">E9 +1000</f>
@@ -3504,7 +3525,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="2" t="n">
         <f aca="false">A10 +1000</f>
@@ -3524,7 +3545,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="n">
         <f aca="false">A11 +1000</f>
@@ -3544,7 +3565,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="n">
         <f aca="false">A12 +1000</f>
@@ -3564,7 +3585,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">A13 +1000</f>
@@ -3584,7 +3605,16 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">A14 +1000</f>
@@ -3604,7 +3634,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="n">
         <f aca="false">A15 +1000</f>
@@ -3624,7 +3663,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2" t="n">
         <f aca="false">A16 +1000</f>
@@ -3644,7 +3683,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2" t="n">
         <f aca="false">A17 +1000</f>
@@ -3664,7 +3703,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="n">
         <f aca="false">A18 +1000</f>
@@ -3682,7 +3721,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="2" t="n">
         <f aca="false">A19 +1000</f>
@@ -3700,7 +3739,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="2" t="n">
         <f aca="false">A20 +1000</f>
@@ -3718,7 +3757,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="n">
         <f aca="false">A21 +1000</f>
@@ -3736,12 +3775,21 @@
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" s="2" t="n">
         <f aca="false">A22 +1000</f>
         <v>1021</v>
       </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I22" s="2" t="n">
         <f aca="false">E22 +1000</f>
         <v>2021</v>
@@ -3754,7 +3802,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>4</v>
@@ -3778,7 +3826,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>4</v>
@@ -3802,7 +3850,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E25" s="2" t="n">
         <f aca="false">A25 +1000</f>
@@ -3820,7 +3868,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2" t="n">
         <f aca="false">A26 +1000</f>
@@ -3838,7 +3886,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2" t="n">
         <f aca="false">A27 +1000</f>
@@ -3856,7 +3904,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="n">
         <f aca="false">A28 +1000</f>
@@ -3874,7 +3922,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="n">
         <f aca="false">A29 +1000</f>
@@ -3892,7 +3940,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E30" s="2" t="n">
         <f aca="false">A30 +1000</f>
@@ -3910,7 +3958,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2" t="n">
         <f aca="false">A31 +1000</f>
@@ -3928,7 +3976,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2" t="n">
         <f aca="false">A32 +1000</f>
@@ -3946,7 +3994,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2" t="n">
         <f aca="false">A33 +1000</f>
@@ -3964,7 +4012,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E34" s="2" t="n">
         <f aca="false">A34 +1000</f>
@@ -3982,7 +4030,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E35" s="2" t="n">
         <f aca="false">A35 +1000</f>
@@ -4000,7 +4048,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E36" s="2" t="n">
         <f aca="false">A36 +1000</f>
@@ -4018,7 +4066,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2" t="n">
         <f aca="false">A37 +1000</f>
@@ -4036,7 +4084,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="n">
         <f aca="false">A38 +1000</f>
@@ -4054,7 +4102,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E39" s="2" t="n">
         <f aca="false">A39 +1000</f>
@@ -4072,7 +4120,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E40" s="2" t="n">
         <f aca="false">A40 +1000</f>
@@ -4090,7 +4138,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E41" s="2" t="n">
         <f aca="false">A41 +1000</f>
@@ -4108,7 +4156,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E42" s="2" t="n">
         <f aca="false">A42 +1000</f>
@@ -4126,7 +4174,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E43" s="2" t="n">
         <f aca="false">A43 +1000</f>
@@ -4144,7 +4192,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E44" s="2" t="n">
         <f aca="false">A44 +1000</f>
@@ -4162,7 +4210,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E45" s="2" t="n">
         <f aca="false">A45 +1000</f>
@@ -4180,7 +4228,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E46" s="2" t="n">
         <f aca="false">A46 +1000</f>
@@ -4204,7 +4252,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E47" s="2" t="n">
         <f aca="false">A47 +1000</f>
@@ -4222,7 +4270,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E48" s="2" t="n">
         <f aca="false">A48 +1000</f>
@@ -4240,7 +4288,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E49" s="2" t="n">
         <f aca="false">A49 +1000</f>
@@ -4258,7 +4306,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E50" s="2" t="n">
         <f aca="false">A50 +1000</f>
@@ -4276,7 +4324,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E51" s="2" t="n">
         <f aca="false">A51 +1000</f>
@@ -4294,7 +4342,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E52" s="2" t="n">
         <f aca="false">A52 +1000</f>
@@ -4312,7 +4360,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E53" s="2" t="n">
         <f aca="false">A53 +1000</f>
@@ -4330,7 +4378,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E54" s="2" t="n">
         <f aca="false">A54 +1000</f>
@@ -4348,7 +4396,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E55" s="2" t="n">
         <f aca="false">A55 +1000</f>
@@ -4366,7 +4414,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E56" s="2" t="n">
         <f aca="false">A56 +1000</f>
@@ -4384,7 +4432,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2" t="n">
         <f aca="false">A57 +1000</f>
@@ -4402,7 +4450,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E58" s="2" t="n">
         <f aca="false">A58 +1000</f>
@@ -4420,7 +4468,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E59" s="2" t="n">
         <f aca="false">A59 +1000</f>
@@ -4438,7 +4486,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E60" s="2" t="n">
         <f aca="false">A60 +1000</f>
@@ -4456,7 +4504,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E61" s="2" t="n">
         <f aca="false">A61 +1000</f>
@@ -4474,7 +4522,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E62" s="2" t="n">
         <f aca="false">A62 +1000</f>
@@ -4492,7 +4540,7 @@
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E63" s="2" t="n">
         <f aca="false">A63 +1000</f>
@@ -4510,7 +4558,7 @@
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E64" s="2" t="n">
         <f aca="false">A64 +1000</f>
@@ -4528,7 +4576,7 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E65" s="2" t="n">
         <f aca="false">A65 +1000</f>
@@ -4546,7 +4594,7 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E66" s="2" t="n">
         <f aca="false">A66 +1000</f>
@@ -4564,7 +4612,7 @@
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E67" s="2" t="n">
         <f aca="false">A67 +1000</f>
@@ -4582,7 +4630,7 @@
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E68" s="2" t="n">
         <f aca="false">A68 +1000</f>
@@ -4600,7 +4648,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E69" s="2" t="n">
         <f aca="false">A69 +1000</f>
@@ -4618,7 +4666,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E70" s="2" t="n">
         <f aca="false">A70 +1000</f>
@@ -4636,7 +4684,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E71" s="2" t="n">
         <f aca="false">A71 +1000</f>
@@ -4654,7 +4702,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E72" s="2" t="n">
         <f aca="false">A72 +1000</f>
@@ -4672,7 +4720,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E73" s="2" t="n">
         <f aca="false">A73 +1000</f>
@@ -4690,7 +4738,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2" t="n">
         <f aca="false">A74 +1000</f>
@@ -4708,7 +4756,7 @@
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E75" s="2" t="n">
         <f aca="false">A75 +1000</f>
@@ -4726,7 +4774,7 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E76" s="2" t="n">
         <f aca="false">A76 +1000</f>
@@ -4744,7 +4792,7 @@
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>4</v>
@@ -4771,7 +4819,7 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E78" s="2" t="n">
         <f aca="false">A78 +1000</f>
@@ -4789,7 +4837,7 @@
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2" t="n">
         <f aca="false">A79 +1000</f>
@@ -4807,7 +4855,7 @@
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E80" s="2" t="n">
         <f aca="false">A80 +1000</f>
@@ -4825,7 +4873,7 @@
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E81" s="2" t="n">
         <f aca="false">A81 +1000</f>
@@ -4843,7 +4891,7 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E82" s="2" t="n">
         <f aca="false">A82 +1000</f>
@@ -4861,7 +4909,7 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E83" s="2" t="n">
         <f aca="false">A83 +1000</f>
@@ -4879,7 +4927,7 @@
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E84" s="2" t="n">
         <f aca="false">A84 +1000</f>
@@ -4897,7 +4945,7 @@
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E85" s="2" t="n">
         <f aca="false">A85 +1000</f>
@@ -4915,7 +4963,7 @@
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E86" s="2" t="n">
         <f aca="false">A86 +1000</f>
@@ -4933,7 +4981,7 @@
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E87" s="2" t="n">
         <f aca="false">A87 +1000</f>
@@ -4951,7 +4999,7 @@
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E88" s="2" t="n">
         <f aca="false">A88 +1000</f>
@@ -4969,7 +5017,7 @@
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E89" s="2" t="n">
         <f aca="false">A89 +1000</f>
@@ -4987,7 +5035,7 @@
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E90" s="2" t="n">
         <f aca="false">A90 +1000</f>
@@ -5005,7 +5053,7 @@
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E91" s="2" t="n">
         <f aca="false">A91 +1000</f>
@@ -5023,7 +5071,7 @@
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E92" s="2" t="n">
         <f aca="false">A92 +1000</f>
@@ -5041,7 +5089,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E93" s="2" t="n">
         <f aca="false">A93 +1000</f>
@@ -5059,7 +5107,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E94" s="2" t="n">
         <f aca="false">A94 +1000</f>
@@ -5077,7 +5125,7 @@
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E95" s="2" t="n">
         <f aca="false">A95 +1000</f>
@@ -5095,7 +5143,7 @@
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E96" s="2" t="n">
         <f aca="false">A96 +1000</f>
@@ -5113,7 +5161,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E97" s="2" t="n">
         <f aca="false">A97 +1000</f>
@@ -5131,7 +5179,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E98" s="2" t="n">
         <f aca="false">A98 +1000</f>
@@ -5149,7 +5197,7 @@
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>4</v>
@@ -5158,7 +5206,7 @@
         <v>4</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E99" s="2" t="n">
         <f aca="false">A99 +1000</f>
@@ -5182,7 +5230,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>4</v>
@@ -5191,7 +5239,7 @@
         <v>4</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E100" s="2" t="n">
         <f aca="false">A100 +1000</f>
@@ -5209,7 +5257,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E101" s="2" t="n">
         <f aca="false">A101 +1000</f>
@@ -5227,7 +5275,7 @@
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E102" s="2" t="n">
         <f aca="false">A102 +1000</f>
@@ -5245,7 +5293,7 @@
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E103" s="2" t="n">
         <f aca="false">A103 +1000</f>
@@ -5263,7 +5311,7 @@
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E104" s="2" t="n">
         <f aca="false">A104 +1000</f>
@@ -5281,7 +5329,7 @@
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E105" s="2" t="n">
         <f aca="false">A105 +1000</f>
@@ -5299,7 +5347,7 @@
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E106" s="2" t="n">
         <f aca="false">A106 +1000</f>
@@ -5317,7 +5365,7 @@
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E107" s="2" t="n">
         <f aca="false">A107 +1000</f>
@@ -5335,7 +5383,7 @@
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E108" s="2" t="n">
         <f aca="false">A108 +1000</f>
@@ -5353,7 +5401,7 @@
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E109" s="2" t="n">
         <f aca="false">A109 +1000</f>
@@ -5371,7 +5419,7 @@
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E110" s="2" t="n">
         <f aca="false">A110 +1000</f>
@@ -5389,7 +5437,7 @@
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E111" s="2" t="n">
         <f aca="false">A111 +1000</f>
@@ -5407,7 +5455,7 @@
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E112" s="2" t="n">
         <f aca="false">A112 +1000</f>
@@ -5425,7 +5473,7 @@
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E113" s="2" t="n">
         <f aca="false">A113 +1000</f>
@@ -5443,7 +5491,7 @@
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E114" s="2" t="n">
         <f aca="false">A114 +1000</f>
@@ -5461,7 +5509,7 @@
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E115" s="2" t="n">
         <f aca="false">A115 +1000</f>
@@ -5479,7 +5527,7 @@
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E116" s="2" t="n">
         <f aca="false">A116 +1000</f>
@@ -5497,7 +5545,7 @@
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E117" s="2" t="n">
         <f aca="false">A117 +1000</f>
@@ -5515,7 +5563,7 @@
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E118" s="2" t="n">
         <f aca="false">A118 +1000</f>
@@ -5533,7 +5581,7 @@
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E119" s="2" t="n">
         <f aca="false">A119 +1000</f>
@@ -5551,7 +5599,7 @@
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E120" s="2" t="n">
         <f aca="false">A120 +1000</f>
@@ -5569,7 +5617,7 @@
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E121" s="2" t="n">
         <f aca="false">A121 +1000</f>
@@ -5587,7 +5635,7 @@
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E122" s="2" t="n">
         <f aca="false">A122 +1000</f>
@@ -5605,7 +5653,7 @@
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E123" s="2" t="n">
         <f aca="false">A123 +1000</f>
@@ -5623,7 +5671,7 @@
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E124" s="2" t="n">
         <f aca="false">A124 +1000</f>
@@ -5641,7 +5689,7 @@
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E125" s="2" t="n">
         <f aca="false">A125 +1000</f>
@@ -5659,7 +5707,7 @@
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E126" s="2" t="n">
         <f aca="false">A126 +1000</f>
@@ -5677,7 +5725,7 @@
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E127" s="2" t="n">
         <f aca="false">A127 +1000</f>
@@ -5695,7 +5743,7 @@
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E128" s="2" t="n">
         <f aca="false">A128 +1000</f>
@@ -5713,7 +5761,7 @@
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E129" s="2" t="n">
         <f aca="false">A129 +1000</f>
@@ -5731,7 +5779,7 @@
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E130" s="2" t="n">
         <f aca="false">A130 +1000</f>
@@ -5749,7 +5797,7 @@
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E131" s="2" t="n">
         <f aca="false">A131 +1000</f>
@@ -5767,7 +5815,7 @@
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E132" s="2" t="n">
         <f aca="false">A132 +1000</f>
@@ -5785,7 +5833,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E133" s="2" t="n">
         <f aca="false">A133 +1000</f>
@@ -5803,7 +5851,7 @@
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E134" s="2" t="n">
         <f aca="false">A134 +1000</f>
@@ -5821,7 +5869,7 @@
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E135" s="2" t="n">
         <f aca="false">A135 +1000</f>
@@ -5839,7 +5887,7 @@
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E136" s="2" t="n">
         <f aca="false">A136 +1000</f>
@@ -5857,7 +5905,7 @@
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E137" s="2" t="n">
         <f aca="false">A137 +1000</f>
@@ -5875,7 +5923,7 @@
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E138" s="2" t="n">
         <f aca="false">A138 +1000</f>
@@ -5893,7 +5941,7 @@
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E139" s="2" t="n">
         <f aca="false">A139 +1000</f>
@@ -5911,7 +5959,7 @@
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E140" s="2" t="n">
         <f aca="false">A140 +1000</f>
@@ -5929,7 +5977,7 @@
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E141" s="2" t="n">
         <f aca="false">A141 +1000</f>
@@ -5947,7 +5995,7 @@
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E142" s="2" t="n">
         <f aca="false">A142 +1000</f>
@@ -5965,7 +6013,7 @@
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E143" s="2" t="n">
         <f aca="false">A143 +1000</f>
@@ -5983,7 +6031,7 @@
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E144" s="2" t="n">
         <f aca="false">A144 +1000</f>
@@ -6001,7 +6049,7 @@
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E145" s="2" t="n">
         <f aca="false">A145 +1000</f>
@@ -6019,7 +6067,7 @@
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E146" s="2" t="n">
         <f aca="false">A146 +1000</f>
@@ -6037,7 +6085,7 @@
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E147" s="2" t="n">
         <f aca="false">A147 +1000</f>
@@ -6055,7 +6103,7 @@
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E148" s="2" t="n">
         <f aca="false">A148 +1000</f>
@@ -6073,7 +6121,7 @@
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E149" s="2" t="n">
         <f aca="false">A149 +1000</f>
@@ -6091,7 +6139,7 @@
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E150" s="2" t="n">
         <f aca="false">A150 +1000</f>
@@ -6109,7 +6157,7 @@
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E151" s="2" t="n">
         <f aca="false">A151 +1000</f>
@@ -6127,7 +6175,16 @@
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E152" s="2" t="n">
         <f aca="false">A152 +1000</f>
@@ -6145,7 +6202,7 @@
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E153" s="2" t="n">
         <f aca="false">A153 +1000</f>
@@ -6163,7 +6220,7 @@
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E154" s="2" t="n">
         <f aca="false">A154 +1000</f>
@@ -6181,7 +6238,7 @@
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E155" s="2" t="n">
         <f aca="false">A155 +1000</f>
@@ -6199,7 +6256,7 @@
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E156" s="2" t="n">
         <f aca="false">A156 +1000</f>
@@ -6217,7 +6274,7 @@
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E157" s="2" t="n">
         <f aca="false">A157 +1000</f>
@@ -6235,7 +6292,7 @@
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E158" s="2" t="n">
         <f aca="false">A158 +1000</f>
@@ -6253,7 +6310,7 @@
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E159" s="2" t="n">
         <f aca="false">A159 +1000</f>
@@ -6271,7 +6328,7 @@
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E160" s="2" t="n">
         <f aca="false">A160 +1000</f>
@@ -6289,7 +6346,7 @@
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E161" s="2" t="n">
         <f aca="false">A161 +1000</f>
@@ -6307,7 +6364,7 @@
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E162" s="2" t="n">
         <f aca="false">A162 +1000</f>
@@ -6325,7 +6382,7 @@
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E163" s="2" t="n">
         <f aca="false">A163 +1000</f>
@@ -6343,7 +6400,7 @@
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E164" s="2" t="n">
         <f aca="false">A164 +1000</f>
@@ -6361,7 +6418,7 @@
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E165" s="2" t="n">
         <f aca="false">A165 +1000</f>
@@ -6379,7 +6436,7 @@
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E166" s="2" t="n">
         <f aca="false">A166 +1000</f>
@@ -6397,7 +6454,7 @@
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E167" s="2" t="n">
         <f aca="false">A167 +1000</f>
@@ -6415,7 +6472,7 @@
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E168" s="2" t="n">
         <f aca="false">A168 +1000</f>
@@ -6433,7 +6490,7 @@
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E169" s="2" t="n">
         <f aca="false">A169 +1000</f>
@@ -6451,7 +6508,7 @@
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E170" s="2" t="n">
         <f aca="false">A170 +1000</f>
@@ -6469,7 +6526,7 @@
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E171" s="2" t="n">
         <f aca="false">A171 +1000</f>
@@ -6487,7 +6544,7 @@
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E172" s="2" t="n">
         <f aca="false">A172 +1000</f>
@@ -6505,7 +6562,7 @@
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E173" s="2" t="n">
         <f aca="false">A173 +1000</f>
@@ -6523,7 +6580,7 @@
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>4</v>
@@ -6532,7 +6589,7 @@
         <v>4</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E174" s="2" t="n">
         <f aca="false">A174 +1000</f>
@@ -6550,7 +6607,7 @@
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E175" s="2" t="n">
         <f aca="false">A175 +1000</f>
@@ -6568,7 +6625,7 @@
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E176" s="2" t="n">
         <f aca="false">A176 +1000</f>
@@ -6586,7 +6643,7 @@
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E177" s="2" t="n">
         <f aca="false">A177 +1000</f>
@@ -6604,7 +6661,7 @@
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E178" s="2" t="n">
         <f aca="false">A178 +1000</f>
@@ -6622,7 +6679,7 @@
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E179" s="2" t="n">
         <f aca="false">A179 +1000</f>
@@ -6640,7 +6697,7 @@
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E180" s="2" t="n">
         <f aca="false">A180 +1000</f>
@@ -6658,7 +6715,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E181" s="2" t="n">
         <f aca="false">A181 +1000</f>
@@ -6676,7 +6733,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E182" s="2" t="n">
         <f aca="false">A182 +1000</f>
@@ -6694,7 +6751,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E183" s="2" t="n">
         <f aca="false">A183 +1000</f>
@@ -6712,7 +6769,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E184" s="2" t="n">
         <f aca="false">A184 +1000</f>
@@ -6730,7 +6787,7 @@
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E185" s="2" t="n">
         <f aca="false">A185 +1000</f>
@@ -6748,7 +6805,7 @@
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E186" s="2" t="n">
         <f aca="false">A186 +1000</f>
@@ -6766,7 +6823,7 @@
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E187" s="2" t="n">
         <f aca="false">A187 +1000</f>
@@ -6784,7 +6841,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E188" s="2" t="n">
         <f aca="false">A188 +1000</f>
@@ -6802,7 +6859,7 @@
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E189" s="2" t="n">
         <f aca="false">A189 +1000</f>
@@ -6820,7 +6877,7 @@
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E190" s="2" t="n">
         <f aca="false">A190 +1000</f>
@@ -6838,7 +6895,7 @@
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E191" s="2" t="n">
         <f aca="false">A191 +1000</f>
@@ -6856,7 +6913,7 @@
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E192" s="2" t="n">
         <f aca="false">A192 +1000</f>
@@ -6874,7 +6931,7 @@
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E193" s="2" t="n">
         <f aca="false">A193 +1000</f>
@@ -6892,7 +6949,7 @@
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E194" s="2" t="n">
         <f aca="false">A194 +1000</f>
@@ -6910,7 +6967,7 @@
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E195" s="2" t="n">
         <f aca="false">A195 +1000</f>
@@ -6928,7 +6985,7 @@
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E196" s="2" t="n">
         <f aca="false">A196 +1000</f>
@@ -6946,7 +7003,7 @@
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E197" s="2" t="n">
         <f aca="false">A197 +1000</f>
@@ -6964,7 +7021,7 @@
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E198" s="2" t="n">
         <f aca="false">A198 +1000</f>
@@ -6982,7 +7039,7 @@
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E199" s="2" t="n">
         <f aca="false">A199 +1000</f>
@@ -7000,7 +7057,7 @@
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E200" s="2" t="n">
         <f aca="false">A200 +1000</f>
@@ -7018,7 +7075,7 @@
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E201" s="2" t="n">
         <f aca="false">A201 +1000</f>
@@ -7036,7 +7093,7 @@
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E202" s="2" t="n">
         <f aca="false">A202 +1000</f>
@@ -7054,7 +7111,7 @@
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E203" s="2" t="n">
         <f aca="false">A203 +1000</f>
@@ -7072,7 +7129,7 @@
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E204" s="2" t="n">
         <f aca="false">A204 +1000</f>
@@ -7090,7 +7147,7 @@
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E205" s="2" t="n">
         <f aca="false">A205 +1000</f>
@@ -7108,7 +7165,16 @@
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E206" s="2" t="n">
         <f aca="false">A206 +1000</f>
@@ -7126,7 +7192,7 @@
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E207" s="2" t="n">
         <f aca="false">A207 +1000</f>
@@ -7144,7 +7210,7 @@
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E208" s="2" t="n">
         <f aca="false">A208 +1000</f>
@@ -7162,7 +7228,7 @@
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>4</v>
@@ -7171,7 +7237,7 @@
         <v>4</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E209" s="2" t="n">
         <f aca="false">A209 +1000</f>
@@ -7189,7 +7255,7 @@
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E210" s="2" t="n">
         <f aca="false">A210 +1000</f>
@@ -7207,7 +7273,7 @@
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E211" s="2" t="n">
         <f aca="false">A211 +1000</f>
@@ -7225,7 +7291,7 @@
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E212" s="2" t="n">
         <f aca="false">A212 +1000</f>
@@ -7243,7 +7309,7 @@
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E213" s="2" t="n">
         <f aca="false">A213 +1000</f>
@@ -7261,7 +7327,7 @@
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E214" s="2" t="n">
         <f aca="false">A214 +1000</f>
@@ -7279,7 +7345,7 @@
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B215" s="3"/>
       <c r="E215" s="2" t="n">
@@ -7298,7 +7364,7 @@
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>4</v>
@@ -7322,7 +7388,7 @@
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E217" s="2" t="n">
         <f aca="false">A217 +1000</f>
@@ -7340,7 +7406,7 @@
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>4</v>
@@ -7364,7 +7430,7 @@
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E219" s="2" t="n">
         <f aca="false">A219 +1000</f>
@@ -7382,7 +7448,7 @@
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E220" s="2" t="n">
         <f aca="false">A220 +1000</f>
@@ -7400,7 +7466,7 @@
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E221" s="2" t="n">
         <f aca="false">A221 +1000</f>
@@ -7418,7 +7484,7 @@
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E222" s="2" t="n">
         <f aca="false">A222 +1000</f>
@@ -7436,7 +7502,7 @@
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E223" s="2" t="n">
         <f aca="false">A223 +1000</f>
@@ -7454,7 +7520,7 @@
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E224" s="2" t="n">
         <f aca="false">A224 +1000</f>
@@ -7472,7 +7538,7 @@
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E225" s="2" t="n">
         <f aca="false">A225 +1000</f>
@@ -7490,7 +7556,7 @@
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E226" s="2" t="n">
         <f aca="false">A226 +1000</f>
@@ -7508,7 +7574,7 @@
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E227" s="2" t="n">
         <f aca="false">A227 +1000</f>
@@ -7526,7 +7592,7 @@
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E228" s="2" t="n">
         <f aca="false">A228 +1000</f>
@@ -7544,7 +7610,7 @@
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E229" s="2" t="n">
         <f aca="false">A229 +1000</f>
@@ -7562,7 +7628,7 @@
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E230" s="2" t="n">
         <f aca="false">A230 +1000</f>
@@ -7580,7 +7646,7 @@
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>4</v>
@@ -7589,7 +7655,7 @@
         <v>4</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E231" s="2" t="n">
         <f aca="false">A231 +1000</f>
@@ -7613,7 +7679,7 @@
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E232" s="2" t="n">
         <f aca="false">A232 +1000</f>
@@ -7631,7 +7697,7 @@
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E233" s="2" t="n">
         <f aca="false">A233 +1000</f>
@@ -7649,7 +7715,7 @@
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E234" s="2" t="n">
         <f aca="false">A234 +1000</f>
@@ -7667,7 +7733,7 @@
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E235" s="2" t="n">
         <f aca="false">A235 +1000</f>
@@ -7685,7 +7751,7 @@
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>4</v>
@@ -7694,7 +7760,7 @@
         <v>4</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E236" s="2" t="n">
         <f aca="false">A236 +1000</f>
@@ -7712,7 +7778,7 @@
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E237" s="2" t="n">
         <f aca="false">A237 +1000</f>
@@ -7730,7 +7796,7 @@
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E238" s="2" t="n">
         <f aca="false">A238 +1000</f>
@@ -7748,7 +7814,7 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>4</v>
@@ -7772,7 +7838,7 @@
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E240" s="2" t="n">
         <f aca="false">A240 +1000</f>
@@ -7790,7 +7856,7 @@
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E241" s="2" t="n">
         <f aca="false">A241 +1000</f>
@@ -7808,7 +7874,16 @@
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E242" s="2" t="n">
         <f aca="false">A242 +1000</f>
@@ -7826,7 +7901,16 @@
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E243" s="2" t="n">
         <f aca="false">A243 +1000</f>
@@ -7844,7 +7928,7 @@
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E244" s="2" t="n">
         <f aca="false">A244 +1000</f>
@@ -7862,7 +7946,7 @@
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E245" s="2" t="n">
         <f aca="false">A245 +1000</f>
@@ -7880,7 +7964,7 @@
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E246" s="2" t="n">
         <f aca="false">A246 +1000</f>
@@ -7898,7 +7982,7 @@
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E247" s="2" t="n">
         <f aca="false">A247 +1000</f>
@@ -7916,7 +8000,7 @@
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E248" s="2" t="n">
         <f aca="false">A248 +1000</f>
@@ -7934,7 +8018,7 @@
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E249" s="2" t="n">
         <f aca="false">A249 +1000</f>
@@ -7961,7 +8045,7 @@
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E250" s="2" t="n">
         <f aca="false">A250 +1000</f>
@@ -7979,7 +8063,7 @@
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E251" s="2" t="n">
         <f aca="false">A251 +1000</f>
@@ -7997,7 +8081,7 @@
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E252" s="2" t="n">
         <f aca="false">A252 +1000</f>
@@ -8015,7 +8099,7 @@
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E253" s="2" t="n">
         <f aca="false">A253 +1000</f>
@@ -8033,7 +8117,7 @@
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E254" s="2" t="n">
         <f aca="false">A254 +1000</f>
@@ -8051,7 +8135,7 @@
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E255" s="2" t="n">
         <f aca="false">A255 +1000</f>
@@ -8069,7 +8153,7 @@
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E256" s="2" t="n">
         <f aca="false">A256 +1000</f>
@@ -8087,7 +8171,7 @@
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E257" s="2" t="n">
         <f aca="false">A257 +1000</f>
@@ -8105,7 +8189,7 @@
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E258" s="2" t="n">
         <f aca="false">A258 +1000</f>
@@ -8123,7 +8207,7 @@
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E259" s="2" t="n">
         <f aca="false">A259 +1000</f>
@@ -8141,7 +8225,7 @@
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E260" s="2" t="n">
         <f aca="false">A260 +1000</f>
@@ -8159,7 +8243,7 @@
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E261" s="2" t="n">
         <f aca="false">A261 +1000</f>
@@ -8177,7 +8261,7 @@
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E262" s="2" t="n">
         <f aca="false">A262 +1000</f>
@@ -8195,7 +8279,7 @@
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E263" s="2" t="n">
         <f aca="false">A263 +1000</f>
@@ -8213,7 +8297,7 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>4</v>
@@ -8243,7 +8327,7 @@
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E265" s="2" t="n">
         <f aca="false">A265 +1000</f>
@@ -8261,7 +8345,7 @@
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E266" s="2" t="n">
         <f aca="false">A266 +1000</f>
@@ -8279,7 +8363,7 @@
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E267" s="2" t="n">
         <f aca="false">A267 +1000</f>
@@ -8297,7 +8381,7 @@
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E268" s="2" t="n">
         <f aca="false">A268 +1000</f>
@@ -8315,7 +8399,7 @@
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E269" s="2" t="n">
         <f aca="false">A269 +1000</f>
@@ -8333,7 +8417,7 @@
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E270" s="2" t="n">
         <f aca="false">A270 +1000</f>
@@ -8351,7 +8435,7 @@
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E271" s="2" t="n">
         <f aca="false">A271 +1000</f>
@@ -8369,7 +8453,7 @@
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E272" s="2" t="n">
         <f aca="false">A272 +1000</f>
@@ -8387,7 +8471,7 @@
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E273" s="2" t="n">
         <f aca="false">A273 +1000</f>
@@ -8405,7 +8489,7 @@
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E274" s="2" t="n">
         <f aca="false">A274 +1000</f>
@@ -8423,7 +8507,7 @@
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E275" s="2" t="n">
         <f aca="false">A275 +1000</f>
@@ -8441,7 +8525,7 @@
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E276" s="2" t="n">
         <f aca="false">A276 +1000</f>
@@ -8459,7 +8543,7 @@
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E277" s="2" t="n">
         <f aca="false">A277 +1000</f>
@@ -8477,7 +8561,7 @@
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E278" s="2" t="n">
         <f aca="false">A278 +1000</f>
@@ -8495,7 +8579,7 @@
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E279" s="2" t="n">
         <f aca="false">A279 +1000</f>
@@ -8513,7 +8597,7 @@
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E280" s="2" t="n">
         <f aca="false">A280 +1000</f>
@@ -8531,7 +8615,7 @@
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E281" s="2" t="n">
         <f aca="false">A281 +1000</f>
@@ -8549,7 +8633,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E282" s="2" t="n">
         <f aca="false">A282 +1000</f>
@@ -8567,7 +8651,7 @@
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E283" s="2" t="n">
         <f aca="false">A283 +1000</f>
@@ -8585,7 +8669,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E284" s="2" t="n">
         <f aca="false">A284 +1000</f>
@@ -8603,7 +8687,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E285" s="2" t="n">
         <f aca="false">A285 +1000</f>
@@ -8621,7 +8705,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E286" s="2" t="n">
         <f aca="false">A286 +1000</f>
@@ -8639,7 +8723,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E287" s="2" t="n">
         <f aca="false">A287 +1000</f>
@@ -8657,7 +8741,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E288" s="2" t="n">
         <f aca="false">A288 +1000</f>
@@ -8675,7 +8759,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E289" s="2" t="n">
         <f aca="false">A289 +1000</f>
@@ -8693,7 +8777,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E290" s="2" t="n">
         <f aca="false">A290 +1000</f>
@@ -8711,7 +8795,7 @@
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E291" s="2" t="n">
         <f aca="false">A291 +1000</f>
@@ -8729,7 +8813,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E292" s="2" t="n">
         <f aca="false">A292 +1000</f>
@@ -8747,7 +8831,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E293" s="2" t="n">
         <f aca="false">A293 +1000</f>
@@ -8765,7 +8849,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E294" s="2" t="n">
         <f aca="false">A294 +1000</f>
@@ -8783,7 +8867,7 @@
     </row>
     <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B295" s="3"/>
       <c r="E295" s="2" t="n">
@@ -8802,7 +8886,7 @@
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>4</v>
@@ -8826,7 +8910,7 @@
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E297" s="2" t="n">
         <f aca="false">A297 +1000</f>
@@ -8844,7 +8928,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E298" s="2" t="n">
         <f aca="false">A298 +1000</f>
@@ -8862,7 +8946,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E299" s="2" t="n">
         <f aca="false">A299 +1000</f>
@@ -8880,7 +8964,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E300" s="2" t="n">
         <f aca="false">A300 +1000</f>
@@ -8898,7 +8982,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E301" s="2" t="n">
         <f aca="false">A301 +1000</f>
@@ -8916,7 +9000,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E302" s="2" t="n">
         <f aca="false">A302 +1000</f>
@@ -8934,7 +9018,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E303" s="2" t="n">
         <f aca="false">A303 +1000</f>
@@ -8952,7 +9036,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E304" s="2" t="n">
         <f aca="false">A304 +1000</f>
@@ -8970,7 +9054,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E305" s="2" t="n">
         <f aca="false">A305 +1000</f>
@@ -8988,7 +9072,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E306" s="2" t="n">
         <f aca="false">A306 +1000</f>
@@ -9006,7 +9090,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E307" s="2" t="n">
         <f aca="false">A307 +1000</f>
@@ -9024,7 +9108,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E308" s="2" t="n">
         <f aca="false">A308 +1000</f>
@@ -9042,7 +9126,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E309" s="2" t="n">
         <f aca="false">A309 +1000</f>
@@ -9060,7 +9144,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E310" s="2" t="n">
         <f aca="false">A310 +1000</f>
@@ -9078,7 +9162,7 @@
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E311" s="2" t="n">
         <f aca="false">A311 +1000</f>
@@ -9096,7 +9180,7 @@
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E312" s="2" t="n">
         <f aca="false">A312 +1000</f>
@@ -9114,7 +9198,7 @@
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E313" s="2" t="n">
         <f aca="false">A313 +1000</f>
@@ -9132,7 +9216,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E314" s="2" t="n">
         <f aca="false">A314 +1000</f>
@@ -9150,7 +9234,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E315" s="2" t="n">
         <f aca="false">A315 +1000</f>
@@ -9168,7 +9252,7 @@
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E316" s="2" t="n">
         <f aca="false">A316 +1000</f>
@@ -9186,7 +9270,7 @@
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E317" s="2" t="n">
         <f aca="false">A317 +1000</f>
@@ -9204,7 +9288,7 @@
     </row>
     <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E318" s="2" t="n">
         <f aca="false">A318 +1000</f>
@@ -9228,7 +9312,7 @@
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E319" s="2" t="n">
         <f aca="false">A319 +1000</f>
@@ -9246,7 +9330,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E320" s="2" t="n">
         <f aca="false">A320 +1000</f>
@@ -9264,7 +9348,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E321" s="2" t="n">
         <f aca="false">A321 +1000</f>
@@ -9282,7 +9366,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E322" s="2" t="n">
         <f aca="false">A322 +1000</f>
@@ -9300,7 +9384,7 @@
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E323" s="2" t="n">
         <f aca="false">A323 +1000</f>
@@ -9318,7 +9402,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E324" s="2" t="n">
         <f aca="false">A324 +1000</f>
@@ -9336,7 +9420,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E325" s="2" t="n">
         <f aca="false">A325 +1000</f>
@@ -9354,7 +9438,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E326" s="2" t="n">
         <f aca="false">A326 +1000</f>
@@ -9372,7 +9456,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E327" s="2" t="n">
         <f aca="false">A327 +1000</f>
@@ -9390,7 +9474,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E328" s="2" t="n">
         <f aca="false">A328 +1000</f>
@@ -9408,7 +9492,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E329" s="2" t="n">
         <f aca="false">A329 +1000</f>
@@ -9426,7 +9510,7 @@
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E330" s="2" t="n">
         <f aca="false">A330 +1000</f>
@@ -9444,7 +9528,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E331" s="2" t="n">
         <f aca="false">A331 +1000</f>
@@ -9462,7 +9546,7 @@
     </row>
     <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>4</v>
@@ -9486,7 +9570,7 @@
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E333" s="2" t="n">
         <f aca="false">A333 +1000</f>
@@ -9504,7 +9588,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E334" s="2" t="n">
         <f aca="false">A334 +1000</f>
@@ -9522,7 +9606,7 @@
     </row>
     <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E335" s="2" t="n">
         <f aca="false">A335 +1000</f>
@@ -9546,7 +9630,7 @@
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E336" s="2" t="n">
         <f aca="false">A336 +1000</f>
@@ -9564,7 +9648,7 @@
     </row>
     <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E337" s="2" t="n">
         <f aca="false">A337 +1000</f>
@@ -9588,7 +9672,7 @@
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E338" s="2" t="n">
         <f aca="false">A338 +1000</f>
@@ -9606,7 +9690,7 @@
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E339" s="2" t="n">
         <f aca="false">A339 +1000</f>
@@ -9624,7 +9708,7 @@
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E340" s="2" t="n">
         <f aca="false">A340 +1000</f>
@@ -9642,7 +9726,7 @@
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E341" s="2" t="n">
         <f aca="false">A341 +1000</f>
@@ -9660,7 +9744,7 @@
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E342" s="2" t="n">
         <f aca="false">A342 +1000</f>
@@ -9678,7 +9762,7 @@
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E343" s="2" t="n">
         <f aca="false">A343 +1000</f>
@@ -9696,7 +9780,7 @@
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E344" s="2" t="n">
         <f aca="false">A344 +1000</f>
@@ -9714,7 +9798,7 @@
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E345" s="2" t="n">
         <f aca="false">A345 +1000</f>
@@ -9732,7 +9816,7 @@
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E346" s="2" t="n">
         <f aca="false">A346 +1000</f>
@@ -9750,7 +9834,7 @@
     </row>
     <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B347" s="3"/>
       <c r="E347" s="2" t="n">
@@ -9769,7 +9853,7 @@
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>4</v>
@@ -9793,7 +9877,7 @@
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E349" s="2" t="n">
         <f aca="false">A349 +1000</f>
@@ -9811,7 +9895,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E350" s="2" t="n">
         <f aca="false">A350 +1000</f>
@@ -9829,7 +9913,7 @@
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E351" s="2" t="n">
         <f aca="false">A351 +1000</f>
@@ -9847,7 +9931,7 @@
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E352" s="2" t="n">
         <f aca="false">A352 +1000</f>
@@ -9865,7 +9949,7 @@
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E353" s="2" t="n">
         <f aca="false">A353 +1000</f>
@@ -9883,7 +9967,7 @@
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E354" s="2" t="n">
         <f aca="false">A354 +1000</f>
@@ -9901,7 +9985,7 @@
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E355" s="2" t="n">
         <f aca="false">A355 +1000</f>
@@ -9919,7 +10003,7 @@
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>4</v>
@@ -9943,7 +10027,7 @@
     </row>
     <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E357" s="2" t="n">
         <f aca="false">A357 +1000</f>
@@ -9967,7 +10051,7 @@
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E358" s="2" t="n">
         <f aca="false">A358 +1000</f>
@@ -9985,7 +10069,7 @@
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E359" s="2" t="n">
         <f aca="false">A359 +1000</f>
@@ -10012,7 +10096,7 @@
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E360" s="2" t="n">
         <f aca="false">A360 +1000</f>
@@ -10030,7 +10114,7 @@
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E361" s="2" t="n">
         <f aca="false">A361 +1000</f>
@@ -10048,7 +10132,7 @@
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E362" s="2" t="n">
         <f aca="false">A362 +1000</f>
@@ -10066,7 +10150,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E363" s="2" t="n">
         <f aca="false">A363 +1000</f>
@@ -10084,7 +10168,7 @@
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E364" s="2" t="n">
         <f aca="false">A364 +1000</f>
@@ -10102,7 +10186,7 @@
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E365" s="2" t="n">
         <f aca="false">A365 +1000</f>
@@ -10120,7 +10204,7 @@
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E366" s="2" t="n">
         <f aca="false">A366 +1000</f>
@@ -10138,7 +10222,7 @@
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E367" s="2" t="n">
         <f aca="false">A367 +1000</f>
@@ -10156,7 +10240,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E368" s="2" t="n">
         <f aca="false">A368 +1000</f>
@@ -10174,7 +10258,7 @@
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E369" s="2" t="n">
         <f aca="false">A369 +1000</f>
@@ -10192,7 +10276,7 @@
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E370" s="2" t="n">
         <f aca="false">A370 +1000</f>
@@ -10210,7 +10294,7 @@
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E371" s="2" t="n">
         <f aca="false">A371 +1000</f>
@@ -10228,7 +10312,7 @@
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E372" s="2" t="n">
         <f aca="false">A372 +1000</f>
@@ -10246,7 +10330,7 @@
     </row>
     <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>4</v>
@@ -10270,7 +10354,7 @@
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E374" s="2" t="n">
         <f aca="false">A374 +1000</f>
@@ -10283,7 +10367,7 @@
         <v>4</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I374" s="2" t="n">
         <f aca="false">E374 +1000</f>
@@ -10297,7 +10381,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E375" s="2" t="n">
         <f aca="false">A375 +1000</f>
@@ -10315,7 +10399,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E376" s="2" t="n">
         <f aca="false">A376 +1000</f>
@@ -10333,7 +10417,7 @@
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E377" s="2" t="n">
         <f aca="false">A377 +1000</f>
@@ -10351,7 +10435,7 @@
     </row>
     <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>4</v>
@@ -10375,7 +10459,7 @@
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E379" s="2" t="n">
         <f aca="false">A379 +1000</f>
@@ -10393,7 +10477,7 @@
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E380" s="2" t="n">
         <f aca="false">A380 +1000</f>
@@ -10411,7 +10495,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E381" s="2" t="n">
         <f aca="false">A381 +1000</f>
@@ -10429,7 +10513,7 @@
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E382" s="2" t="n">
         <f aca="false">A382 +1000</f>
@@ -10447,7 +10531,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E383" s="2" t="n">
         <f aca="false">A383 +1000</f>
@@ -10465,7 +10549,7 @@
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E384" s="2" t="n">
         <f aca="false">A384 +1000</f>
@@ -10483,7 +10567,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E385" s="2" t="n">
         <f aca="false">A385 +1000</f>
@@ -10501,7 +10585,7 @@
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E386" s="2" t="n">
         <f aca="false">A386 +1000</f>
@@ -10519,7 +10603,7 @@
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E387" s="2" t="n">
         <f aca="false">A387 +1000</f>
@@ -10537,7 +10621,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E388" s="2" t="n">
         <f aca="false">A388 +1000</f>
@@ -10555,7 +10639,7 @@
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E389" s="2" t="n">
         <f aca="false">A389 +1000</f>
@@ -10573,7 +10657,7 @@
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E390" s="2" t="n">
         <f aca="false">A390 +1000</f>
@@ -10591,7 +10675,7 @@
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E391" s="2" t="n">
         <f aca="false">A391 +1000</f>
@@ -10609,7 +10693,7 @@
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E392" s="2" t="n">
         <f aca="false">A392 +1000</f>
@@ -10627,7 +10711,7 @@
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E393" s="2" t="n">
         <f aca="false">A393 +1000</f>
@@ -10645,7 +10729,7 @@
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E394" s="2" t="n">
         <f aca="false">A394 +1000</f>
@@ -10663,7 +10747,7 @@
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E395" s="2" t="n">
         <f aca="false">A395 +1000</f>
@@ -10681,7 +10765,7 @@
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E396" s="2" t="n">
         <f aca="false">A396 +1000</f>
@@ -10699,7 +10783,7 @@
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E397" s="2" t="n">
         <f aca="false">A397 +1000</f>
@@ -10717,7 +10801,7 @@
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E398" s="2" t="n">
         <f aca="false">A398 +1000</f>
@@ -10735,7 +10819,7 @@
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E399" s="2" t="n">
         <f aca="false">A399 +1000</f>
@@ -10753,7 +10837,7 @@
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E400" s="2" t="n">
         <f aca="false">A400 +1000</f>
@@ -10771,7 +10855,7 @@
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E401" s="2" t="n">
         <f aca="false">A401 +1000</f>
@@ -10789,7 +10873,7 @@
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E402" s="2" t="n">
         <f aca="false">A402 +1000</f>
@@ -10807,7 +10891,7 @@
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E403" s="2" t="n">
         <f aca="false">A403 +1000</f>
@@ -10825,7 +10909,7 @@
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E404" s="2" t="n">
         <f aca="false">A404 +1000</f>
@@ -10843,7 +10927,7 @@
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E405" s="2" t="n">
         <f aca="false">A405 +1000</f>
@@ -10861,7 +10945,7 @@
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E406" s="2" t="n">
         <f aca="false">A406 +1000</f>
@@ -10879,7 +10963,7 @@
     </row>
     <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>4</v>
@@ -10903,7 +10987,7 @@
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E408" s="2" t="n">
         <f aca="false">A408 +1000</f>
@@ -10921,7 +11005,7 @@
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E409" s="2" t="n">
         <f aca="false">A409 +1000</f>
@@ -10939,7 +11023,7 @@
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E410" s="2" t="n">
         <f aca="false">A410 +1000</f>
@@ -10957,7 +11041,7 @@
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E411" s="2" t="n">
         <f aca="false">A411 +1000</f>
@@ -10975,7 +11059,7 @@
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E412" s="2" t="n">
         <f aca="false">A412 +1000</f>
@@ -10993,7 +11077,7 @@
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E413" s="2" t="n">
         <f aca="false">A413 +1000</f>
@@ -11011,7 +11095,7 @@
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E414" s="2" t="n">
         <f aca="false">A414 +1000</f>
@@ -11029,7 +11113,7 @@
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E415" s="2" t="n">
         <f aca="false">A415 +1000</f>
@@ -11047,7 +11131,7 @@
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E416" s="2" t="n">
         <f aca="false">A416 +1000</f>
@@ -11065,7 +11149,7 @@
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E417" s="2" t="n">
         <f aca="false">A417 +1000</f>
@@ -11083,7 +11167,7 @@
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E418" s="2" t="n">
         <f aca="false">A418 +1000</f>
@@ -11101,7 +11185,7 @@
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E419" s="2" t="n">
         <f aca="false">A419 +1000</f>
@@ -11119,7 +11203,7 @@
     </row>
     <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>4</v>
@@ -11143,7 +11227,7 @@
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E421" s="2" t="n">
         <f aca="false">A421 +1000</f>
@@ -11161,7 +11245,7 @@
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>4</v>
@@ -11170,7 +11254,7 @@
         <v>4</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E422" s="2" t="n">
         <f aca="false">A422 +1000</f>
@@ -11188,7 +11272,7 @@
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E423" s="2" t="n">
         <f aca="false">A423 +1000</f>
@@ -11206,7 +11290,7 @@
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E424" s="2" t="n">
         <f aca="false">A424 +1000</f>
@@ -11233,7 +11317,7 @@
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>4</v>
@@ -11260,7 +11344,7 @@
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E426" s="2" t="n">
         <f aca="false">A426 +1000</f>
@@ -11278,7 +11362,7 @@
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E427" s="2" t="n">
         <f aca="false">A427 +1000</f>
@@ -11296,7 +11380,7 @@
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E428" s="2" t="n">
         <f aca="false">A428 +1000</f>
@@ -11314,7 +11398,7 @@
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E429" s="2" t="n">
         <f aca="false">A429 +1000</f>
@@ -11332,7 +11416,7 @@
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E430" s="2" t="n">
         <f aca="false">A430 +1000</f>
@@ -11350,7 +11434,7 @@
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E431" s="2" t="n">
         <f aca="false">A431 +1000</f>
@@ -11368,7 +11452,7 @@
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E432" s="2" t="n">
         <f aca="false">A432 +1000</f>
@@ -11386,7 +11470,7 @@
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E433" s="2" t="n">
         <f aca="false">A433 +1000</f>
@@ -11404,7 +11488,7 @@
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E434" s="2" t="n">
         <f aca="false">A434 +1000</f>
@@ -11422,7 +11506,7 @@
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E435" s="2" t="n">
         <f aca="false">A435 +1000</f>
@@ -11440,7 +11524,7 @@
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E436" s="2" t="n">
         <f aca="false">A436 +1000</f>
@@ -11458,7 +11542,7 @@
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E437" s="2" t="n">
         <f aca="false">A437 +1000</f>
@@ -11476,7 +11560,7 @@
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E438" s="2" t="n">
         <f aca="false">A438 +1000</f>
@@ -11494,7 +11578,7 @@
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E439" s="2" t="n">
         <f aca="false">A439 +1000</f>
@@ -11512,7 +11596,7 @@
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E440" s="2" t="n">
         <f aca="false">A440 +1000</f>
@@ -11530,7 +11614,7 @@
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E441" s="2" t="n">
         <f aca="false">A441 +1000</f>
@@ -11548,7 +11632,7 @@
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E442" s="2" t="n">
         <f aca="false">A442 +1000</f>
@@ -11566,7 +11650,7 @@
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E443" s="2" t="n">
         <f aca="false">A443 +1000</f>
@@ -11584,7 +11668,7 @@
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E444" s="2" t="n">
         <f aca="false">A444 +1000</f>
@@ -11602,7 +11686,7 @@
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E445" s="2" t="n">
         <f aca="false">A445 +1000</f>
@@ -11620,7 +11704,7 @@
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E446" s="2" t="n">
         <f aca="false">A446 +1000</f>
@@ -11638,7 +11722,7 @@
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E447" s="2" t="n">
         <f aca="false">A447 +1000</f>
@@ -11656,7 +11740,7 @@
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E448" s="2" t="n">
         <f aca="false">A448 +1000</f>
@@ -11674,7 +11758,7 @@
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E449" s="2" t="n">
         <f aca="false">A449 +1000</f>
@@ -11692,7 +11776,7 @@
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E450" s="2" t="n">
         <f aca="false">A450 +1000</f>
@@ -11710,7 +11794,7 @@
     </row>
     <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>4</v>
@@ -11734,7 +11818,16 @@
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
+      </c>
+      <c r="B452" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E452" s="2" t="n">
         <f aca="false">A452 +1000</f>
@@ -11752,7 +11845,7 @@
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E453" s="2" t="n">
         <f aca="false">A453 +1000</f>
@@ -11770,7 +11863,7 @@
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E454" s="2" t="n">
         <f aca="false">A454 +1000</f>
@@ -11788,7 +11881,7 @@
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E455" s="2" t="n">
         <f aca="false">A455 +1000</f>
@@ -11806,7 +11899,7 @@
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E456" s="2" t="n">
         <f aca="false">A456 +1000</f>
@@ -11824,7 +11917,7 @@
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E457" s="2" t="n">
         <f aca="false">A457 +1000</f>
@@ -11842,7 +11935,7 @@
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E458" s="2" t="n">
         <f aca="false">A458 +1000</f>
@@ -11860,7 +11953,7 @@
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E459" s="2" t="n">
         <f aca="false">A459 +1000</f>
@@ -11878,7 +11971,7 @@
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E460" s="2" t="n">
         <f aca="false">A460 +1000</f>
@@ -11896,7 +11989,7 @@
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E461" s="2" t="n">
         <f aca="false">A461 +1000</f>
@@ -11914,7 +12007,7 @@
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E462" s="2" t="n">
         <f aca="false">A462 +1000</f>
@@ -11932,7 +12025,7 @@
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E463" s="2" t="n">
         <f aca="false">A463 +1000</f>
@@ -11950,7 +12043,7 @@
     </row>
     <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E464" s="2" t="n">
         <f aca="false">A464 +1000</f>
@@ -11974,7 +12067,7 @@
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E465" s="2" t="n">
         <f aca="false">A465 +1000</f>
@@ -11992,7 +12085,7 @@
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E466" s="2" t="n">
         <f aca="false">A466 +1000</f>
@@ -12010,7 +12103,7 @@
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E467" s="2" t="n">
         <f aca="false">A467 +1000</f>
@@ -12028,7 +12121,7 @@
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E468" s="2" t="n">
         <f aca="false">A468 +1000</f>
@@ -12046,7 +12139,7 @@
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E469" s="2" t="n">
         <f aca="false">A469 +1000</f>
@@ -12064,7 +12157,7 @@
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E470" s="2" t="n">
         <f aca="false">A470 +1000</f>
@@ -12082,7 +12175,7 @@
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E471" s="2" t="n">
         <f aca="false">A471 +1000</f>
@@ -12100,7 +12193,7 @@
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E472" s="2" t="n">
         <f aca="false">A472 +1000</f>
@@ -12118,7 +12211,7 @@
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E473" s="2" t="n">
         <f aca="false">A473 +1000</f>
@@ -12136,7 +12229,7 @@
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E474" s="2" t="n">
         <f aca="false">A474 +1000</f>
@@ -12154,7 +12247,7 @@
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E475" s="2" t="n">
         <f aca="false">A475 +1000</f>
@@ -12172,7 +12265,7 @@
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E476" s="2" t="n">
         <f aca="false">A476 +1000</f>
@@ -12190,7 +12283,7 @@
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E477" s="2" t="n">
         <f aca="false">A477 +1000</f>
@@ -12208,7 +12301,7 @@
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E478" s="2" t="n">
         <f aca="false">A478 +1000</f>
@@ -12226,7 +12319,7 @@
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E479" s="2" t="n">
         <f aca="false">A479 +1000</f>
@@ -12244,7 +12337,7 @@
     </row>
     <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B480" s="3"/>
       <c r="E480" s="2" t="n">
@@ -12263,7 +12356,7 @@
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E481" s="2" t="n">
         <f aca="false">A481 +1000</f>
@@ -12281,7 +12374,7 @@
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E482" s="2" t="n">
         <f aca="false">A482 +1000</f>
@@ -12299,7 +12392,7 @@
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E483" s="2" t="n">
         <f aca="false">A483 +1000</f>
@@ -12317,7 +12410,7 @@
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E484" s="2" t="n">
         <f aca="false">A484 +1000</f>
@@ -12335,7 +12428,7 @@
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E485" s="2" t="n">
         <f aca="false">A485 +1000</f>
@@ -12353,7 +12446,7 @@
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E486" s="2" t="n">
         <f aca="false">A486 +1000</f>
@@ -12371,7 +12464,7 @@
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E487" s="2" t="n">
         <f aca="false">A487 +1000</f>
@@ -12389,7 +12482,7 @@
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E488" s="2" t="n">
         <f aca="false">A488 +1000</f>
@@ -12407,7 +12500,7 @@
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E489" s="2" t="n">
         <f aca="false">A489 +1000</f>
@@ -12425,7 +12518,7 @@
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E490" s="2" t="n">
         <f aca="false">A490 +1000</f>
@@ -12443,7 +12536,7 @@
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E491" s="2" t="n">
         <f aca="false">A491 +1000</f>
@@ -12461,7 +12554,7 @@
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E492" s="2" t="n">
         <f aca="false">A492 +1000</f>
@@ -12479,7 +12572,7 @@
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E493" s="2" t="n">
         <f aca="false">A493 +1000</f>
@@ -12497,7 +12590,7 @@
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E494" s="2" t="n">
         <f aca="false">A494 +1000</f>
@@ -12515,7 +12608,7 @@
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E495" s="2" t="n">
         <f aca="false">A495 +1000</f>
@@ -12533,7 +12626,7 @@
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E496" s="2" t="n">
         <f aca="false">A496 +1000</f>
@@ -12551,7 +12644,7 @@
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E497" s="2" t="n">
         <f aca="false">A497 +1000</f>
@@ -12569,7 +12662,7 @@
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E498" s="2" t="n">
         <f aca="false">A498 +1000</f>
@@ -12587,7 +12680,7 @@
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E499" s="2" t="n">
         <f aca="false">A499 +1000</f>
@@ -12605,7 +12698,7 @@
     </row>
     <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E500" s="2" t="n">
         <f aca="false">A500 +1000</f>
@@ -12629,7 +12722,7 @@
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E501" s="2" t="n">
         <f aca="false">A501 +1000</f>
@@ -12647,7 +12740,7 @@
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E502" s="2" t="n">
         <f aca="false">A502 +1000</f>
@@ -12665,7 +12758,7 @@
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E503" s="2" t="n">
         <f aca="false">A503 +1000</f>
@@ -12683,7 +12776,7 @@
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E504" s="2" t="n">
         <f aca="false">A504 +1000</f>
@@ -12701,7 +12794,7 @@
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E505" s="2" t="n">
         <f aca="false">A505 +1000</f>
@@ -12719,7 +12812,7 @@
     </row>
     <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>4</v>
@@ -12743,7 +12836,7 @@
     </row>
     <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E507" s="2" t="n">
         <f aca="false">A507 +1000</f>
@@ -12767,7 +12860,7 @@
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E508" s="2" t="n">
         <f aca="false">A508 +1000</f>
@@ -12785,7 +12878,7 @@
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E509" s="2" t="n">
         <f aca="false">A509 +1000</f>
@@ -12803,7 +12896,7 @@
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E510" s="2" t="n">
         <f aca="false">A510 +1000</f>
@@ -12821,7 +12914,7 @@
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E511" s="2" t="n">
         <f aca="false">A511 +1000</f>
@@ -12839,7 +12932,7 @@
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E512" s="2" t="n">
         <f aca="false">A512 +1000</f>
@@ -12857,7 +12950,7 @@
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E513" s="2" t="n">
         <f aca="false">A513 +1000</f>
@@ -12875,7 +12968,7 @@
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E514" s="2" t="n">
         <f aca="false">A514 +1000</f>
@@ -12893,7 +12986,7 @@
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E515" s="2" t="n">
         <f aca="false">A515 +1000</f>
@@ -12911,7 +13004,7 @@
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E516" s="2" t="n">
         <f aca="false">A516 +1000</f>
@@ -12929,7 +13022,7 @@
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E517" s="2" t="n">
         <f aca="false">A517 +1000</f>
@@ -12947,7 +13040,7 @@
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E518" s="2" t="n">
         <f aca="false">A518 +1000</f>
@@ -12965,7 +13058,7 @@
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E519" s="2" t="n">
         <f aca="false">A519 +1000</f>
@@ -12983,7 +13076,7 @@
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E520" s="2" t="n">
         <f aca="false">A520 +1000</f>
@@ -13001,7 +13094,7 @@
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E521" s="2" t="n">
         <f aca="false">A521 +1000</f>
@@ -13019,7 +13112,7 @@
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E522" s="2" t="n">
         <f aca="false">A522 +1000</f>
@@ -13037,7 +13130,7 @@
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E523" s="2" t="n">
         <f aca="false">A523 +1000</f>
@@ -13055,7 +13148,7 @@
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E524" s="2" t="n">
         <f aca="false">A524 +1000</f>
@@ -13073,7 +13166,7 @@
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E525" s="2" t="n">
         <f aca="false">A525 +1000</f>
@@ -13091,7 +13184,7 @@
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E526" s="2" t="n">
         <f aca="false">A526 +1000</f>
@@ -13109,7 +13202,7 @@
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E527" s="2" t="n">
         <f aca="false">A527 +1000</f>
@@ -13127,7 +13220,7 @@
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E528" s="2" t="n">
         <f aca="false">A528 +1000</f>
@@ -13145,7 +13238,7 @@
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E529" s="2" t="n">
         <f aca="false">A529 +1000</f>
@@ -13163,7 +13256,7 @@
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E530" s="2" t="n">
         <f aca="false">A530 +1000</f>
@@ -13181,7 +13274,7 @@
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E531" s="2" t="n">
         <f aca="false">A531 +1000</f>
@@ -13199,7 +13292,7 @@
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E532" s="2" t="n">
         <f aca="false">A532 +1000</f>
@@ -13217,7 +13310,7 @@
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E533" s="2" t="n">
         <f aca="false">A533 +1000</f>
@@ -13235,7 +13328,7 @@
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E534" s="2" t="n">
         <f aca="false">A534 +1000</f>
@@ -13253,7 +13346,7 @@
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E535" s="2" t="n">
         <f aca="false">A535 +1000</f>
@@ -13271,7 +13364,7 @@
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E536" s="2" t="n">
         <f aca="false">A536 +1000</f>
@@ -13289,7 +13382,7 @@
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E537" s="2" t="n">
         <f aca="false">A537 +1000</f>
@@ -13307,7 +13400,7 @@
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E538" s="2" t="n">
         <f aca="false">A538 +1000</f>
@@ -13325,7 +13418,7 @@
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E539" s="2" t="n">
         <f aca="false">A539 +1000</f>
@@ -13343,7 +13436,7 @@
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E540" s="2" t="n">
         <f aca="false">A540 +1000</f>
@@ -13361,7 +13454,7 @@
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E541" s="2" t="n">
         <f aca="false">A541 +1000</f>
@@ -13379,7 +13472,7 @@
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E542" s="2" t="n">
         <f aca="false">A542 +1000</f>
@@ -13397,7 +13490,7 @@
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E543" s="2" t="n">
         <f aca="false">A543 +1000</f>
@@ -13415,7 +13508,7 @@
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E544" s="2" t="n">
         <f aca="false">A544 +1000</f>
@@ -13433,7 +13526,7 @@
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E545" s="2" t="n">
         <f aca="false">A545 +1000</f>
@@ -13451,7 +13544,7 @@
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E546" s="2" t="n">
         <f aca="false">A546 +1000</f>
@@ -13469,7 +13562,7 @@
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E547" s="2" t="n">
         <f aca="false">A547 +1000</f>
@@ -13487,7 +13580,7 @@
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E548" s="2" t="n">
         <f aca="false">A548 +1000</f>
@@ -13505,7 +13598,7 @@
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E549" s="2" t="n">
         <f aca="false">A549 +1000</f>
@@ -13523,7 +13616,7 @@
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E550" s="2" t="n">
         <f aca="false">A550 +1000</f>
@@ -13541,7 +13634,7 @@
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E551" s="2" t="n">
         <f aca="false">A551 +1000</f>
@@ -13559,7 +13652,7 @@
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E552" s="2" t="n">
         <f aca="false">A552 +1000</f>
@@ -13577,7 +13670,7 @@
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E553" s="2" t="n">
         <f aca="false">A553 +1000</f>
@@ -13595,7 +13688,7 @@
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E554" s="2" t="n">
         <f aca="false">A554 +1000</f>
@@ -13613,7 +13706,7 @@
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E555" s="2" t="n">
         <f aca="false">A555 +1000</f>
@@ -13631,7 +13724,7 @@
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E556" s="2" t="n">
         <f aca="false">A556 +1000</f>
@@ -13649,7 +13742,7 @@
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E557" s="2" t="n">
         <f aca="false">A557 +1000</f>
@@ -13667,7 +13760,7 @@
     </row>
     <row r="558" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E558" s="2" t="n">
         <f aca="false">A558 +1000</f>
@@ -13691,7 +13784,7 @@
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E559" s="2" t="n">
         <f aca="false">A559 +1000</f>
@@ -13709,7 +13802,7 @@
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E560" s="2" t="n">
         <f aca="false">A560 +1000</f>
@@ -13727,7 +13820,7 @@
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E561" s="2" t="n">
         <f aca="false">A561 +1000</f>
@@ -13745,7 +13838,7 @@
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E562" s="2" t="n">
         <f aca="false">A562 +1000</f>
@@ -13763,7 +13856,7 @@
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E563" s="2" t="n">
         <f aca="false">A563 +1000</f>
@@ -13781,7 +13874,7 @@
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E564" s="2" t="n">
         <f aca="false">A564 +1000</f>
@@ -13799,7 +13892,7 @@
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E565" s="2" t="n">
         <f aca="false">A565 +1000</f>
@@ -13817,7 +13910,7 @@
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E566" s="2" t="n">
         <f aca="false">A566 +1000</f>
@@ -13835,7 +13928,7 @@
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E567" s="2" t="n">
         <f aca="false">A567 +1000</f>
@@ -13853,7 +13946,7 @@
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E568" s="2" t="n">
         <f aca="false">A568 +1000</f>
@@ -13871,7 +13964,7 @@
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E569" s="2" t="n">
         <f aca="false">A569 +1000</f>
@@ -13889,7 +13982,7 @@
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E570" s="2" t="n">
         <f aca="false">A570 +1000</f>
@@ -13907,7 +14000,7 @@
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E571" s="2" t="n">
         <f aca="false">A571 +1000</f>
@@ -13925,7 +14018,7 @@
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E572" s="2" t="n">
         <f aca="false">A572 +1000</f>
@@ -13943,7 +14036,7 @@
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E573" s="2" t="n">
         <f aca="false">A573 +1000</f>
@@ -13961,7 +14054,7 @@
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E574" s="2" t="n">
         <f aca="false">A574 +1000</f>
@@ -13979,7 +14072,7 @@
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E575" s="2" t="n">
         <f aca="false">A575 +1000</f>
@@ -13997,7 +14090,7 @@
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E576" s="2" t="n">
         <f aca="false">A576 +1000</f>
@@ -14015,7 +14108,7 @@
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E577" s="2" t="n">
         <f aca="false">A577 +1000</f>
@@ -14033,7 +14126,7 @@
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E578" s="2" t="n">
         <f aca="false">A578 +1000</f>
@@ -14051,7 +14144,7 @@
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E579" s="2" t="n">
         <f aca="false">A579 +1000</f>
@@ -14069,7 +14162,7 @@
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E580" s="2" t="n">
         <f aca="false">A580 +1000</f>
@@ -14087,7 +14180,7 @@
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E581" s="2" t="n">
         <f aca="false">A581 +1000</f>
@@ -14105,7 +14198,7 @@
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E582" s="2" t="n">
         <f aca="false">A582 +1000</f>
@@ -14123,7 +14216,7 @@
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E583" s="2" t="n">
         <f aca="false">A583 +1000</f>
@@ -14141,7 +14234,7 @@
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E584" s="2" t="n">
         <f aca="false">A584 +1000</f>
@@ -14159,7 +14252,7 @@
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E585" s="2" t="n">
         <f aca="false">A585 +1000</f>
@@ -14177,7 +14270,7 @@
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E586" s="2" t="n">
         <f aca="false">A586 +1000</f>
@@ -14195,7 +14288,7 @@
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E587" s="2" t="n">
         <f aca="false">A587 +1000</f>
@@ -14213,7 +14306,7 @@
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E588" s="2" t="n">
         <f aca="false">A588 +1000</f>
@@ -14231,7 +14324,7 @@
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E589" s="2" t="n">
         <f aca="false">A589 +1000</f>
@@ -14249,7 +14342,7 @@
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E590" s="2" t="n">
         <f aca="false">A590 +1000</f>
@@ -14267,7 +14360,7 @@
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E591" s="2" t="n">
         <f aca="false">A591 +1000</f>
@@ -14285,7 +14378,7 @@
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E592" s="2" t="n">
         <f aca="false">A592 +1000</f>
@@ -14303,7 +14396,7 @@
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E593" s="2" t="n">
         <f aca="false">A593 +1000</f>
@@ -14321,7 +14414,7 @@
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E594" s="2" t="n">
         <f aca="false">A594 +1000</f>
@@ -14339,7 +14432,7 @@
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E595" s="2" t="n">
         <f aca="false">A595 +1000</f>
@@ -14357,7 +14450,7 @@
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E596" s="2" t="n">
         <f aca="false">A596 +1000</f>
@@ -14375,7 +14468,7 @@
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E597" s="2" t="n">
         <f aca="false">A597 +1000</f>
@@ -14393,7 +14486,7 @@
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E598" s="2" t="n">
         <f aca="false">A598 +1000</f>
@@ -14411,7 +14504,7 @@
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E599" s="2" t="n">
         <f aca="false">A599 +1000</f>
@@ -14429,7 +14522,7 @@
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E600" s="2" t="n">
         <f aca="false">A600 +1000</f>
@@ -14447,7 +14540,7 @@
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E601" s="2" t="n">
         <f aca="false">A601 +1000</f>
@@ -14465,7 +14558,7 @@
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E602" s="2" t="n">
         <f aca="false">A602 +1000</f>
@@ -14483,7 +14576,7 @@
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E603" s="2" t="n">
         <f aca="false">A603 +1000</f>
@@ -14501,7 +14594,7 @@
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E604" s="2" t="n">
         <f aca="false">A604 +1000</f>
@@ -14519,7 +14612,7 @@
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E605" s="2" t="n">
         <f aca="false">A605 +1000</f>
@@ -14537,7 +14630,7 @@
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E606" s="2" t="n">
         <f aca="false">A606 +1000</f>
@@ -14555,7 +14648,7 @@
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E607" s="2" t="n">
         <f aca="false">A607 +1000</f>
@@ -14573,7 +14666,7 @@
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E608" s="2" t="n">
         <f aca="false">A608 +1000</f>
@@ -14591,7 +14684,7 @@
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E609" s="2" t="n">
         <f aca="false">A609 +1000</f>
@@ -14609,7 +14702,7 @@
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E610" s="2" t="n">
         <f aca="false">A610 +1000</f>
@@ -14627,7 +14720,7 @@
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E611" s="2" t="n">
         <f aca="false">A611 +1000</f>
@@ -14645,7 +14738,7 @@
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E612" s="2" t="n">
         <f aca="false">A612 +1000</f>
@@ -14663,7 +14756,7 @@
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E613" s="2" t="n">
         <f aca="false">A613 +1000</f>
@@ -14681,7 +14774,7 @@
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E614" s="2" t="n">
         <f aca="false">A614 +1000</f>
@@ -14699,12 +14792,21 @@
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E615" s="2" t="n">
         <f aca="false">A615 +1000</f>
         <v>1614</v>
       </c>
+      <c r="F615" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G615" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H615" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I615" s="2" t="n">
         <f aca="false">E615 +1000</f>
         <v>2614</v>
@@ -14717,7 +14819,7 @@
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E616" s="2" t="n">
         <f aca="false">A616 +1000</f>
@@ -14735,7 +14837,7 @@
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E617" s="2" t="n">
         <f aca="false">A617 +1000</f>
@@ -14753,7 +14855,7 @@
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E618" s="2" t="n">
         <f aca="false">A618 +1000</f>
@@ -14771,7 +14873,7 @@
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E619" s="2" t="n">
         <f aca="false">A619 +1000</f>
@@ -14789,7 +14891,7 @@
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E620" s="2" t="n">
         <f aca="false">A620 +1000</f>
@@ -14807,7 +14909,7 @@
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E621" s="2" t="n">
         <f aca="false">A621 +1000</f>
@@ -14825,7 +14927,7 @@
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>4</v>
@@ -14834,7 +14936,7 @@
         <v>4</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E622" s="2" t="n">
         <f aca="false">A622 +1000</f>
@@ -14852,7 +14954,7 @@
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E623" s="2" t="n">
         <f aca="false">A623 +1000</f>
@@ -14870,7 +14972,7 @@
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E624" s="2" t="n">
         <f aca="false">A624 +1000</f>
@@ -14888,7 +14990,7 @@
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E625" s="2" t="n">
         <f aca="false">A625 +1000</f>
@@ -14906,7 +15008,7 @@
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E626" s="2" t="n">
         <f aca="false">A626 +1000</f>
@@ -14924,7 +15026,7 @@
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E627" s="2" t="n">
         <f aca="false">A627 +1000</f>
@@ -14942,7 +15044,7 @@
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E628" s="2" t="n">
         <f aca="false">A628 +1000</f>
@@ -14960,7 +15062,7 @@
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E629" s="2" t="n">
         <f aca="false">A629 +1000</f>
@@ -14978,7 +15080,7 @@
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E630" s="2" t="n">
         <f aca="false">A630 +1000</f>
@@ -14996,7 +15098,7 @@
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E631" s="2" t="n">
         <f aca="false">A631 +1000</f>
@@ -15014,7 +15116,7 @@
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E632" s="2" t="n">
         <f aca="false">A632 +1000</f>
@@ -15032,7 +15134,7 @@
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E633" s="2" t="n">
         <f aca="false">A633 +1000</f>
@@ -15050,7 +15152,7 @@
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E634" s="2" t="n">
         <f aca="false">A634 +1000</f>
@@ -15068,7 +15170,7 @@
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E635" s="2" t="n">
         <f aca="false">A635 +1000</f>
@@ -15086,7 +15188,7 @@
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E636" s="2" t="n">
         <f aca="false">A636 +1000</f>
@@ -15104,7 +15206,7 @@
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E637" s="2" t="n">
         <f aca="false">A637 +1000</f>
@@ -15122,7 +15224,7 @@
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E638" s="2" t="n">
         <f aca="false">A638 +1000</f>
@@ -15140,7 +15242,7 @@
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E639" s="2" t="n">
         <f aca="false">A639 +1000</f>
@@ -15158,7 +15260,7 @@
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E640" s="2" t="n">
         <f aca="false">A640 +1000</f>
@@ -15176,7 +15278,7 @@
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E641" s="2" t="n">
         <f aca="false">A641 +1000</f>
@@ -15194,7 +15296,7 @@
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E642" s="2" t="n">
         <f aca="false">A642 +1000</f>
@@ -15212,7 +15314,7 @@
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E643" s="2" t="n">
         <f aca="false">A643 +1000</f>
@@ -15230,7 +15332,7 @@
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E644" s="2" t="n">
         <f aca="false">A644 +1000</f>
@@ -15248,7 +15350,7 @@
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E645" s="2" t="n">
         <f aca="false">A645 +1000</f>
@@ -15266,7 +15368,7 @@
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E646" s="2" t="n">
         <f aca="false">A646 +1000</f>
@@ -15284,7 +15386,7 @@
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E647" s="2" t="n">
         <f aca="false">A647 +1000</f>
@@ -15302,7 +15404,7 @@
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E648" s="2" t="n">
         <f aca="false">A648 +1000</f>
@@ -15320,7 +15422,7 @@
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E649" s="2" t="n">
         <f aca="false">A649 +1000</f>
@@ -15338,7 +15440,7 @@
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E650" s="2" t="n">
         <f aca="false">A650 +1000</f>
@@ -15356,7 +15458,7 @@
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E651" s="2" t="n">
         <f aca="false">A651 +1000</f>
@@ -15374,7 +15476,7 @@
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E652" s="2" t="n">
         <f aca="false">A652 +1000</f>
@@ -15392,7 +15494,7 @@
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E653" s="2" t="n">
         <f aca="false">A653 +1000</f>
@@ -15410,7 +15512,7 @@
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>4</v>
@@ -15419,7 +15521,7 @@
         <v>4</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E654" s="2" t="n">
         <f aca="false">A654 +1000</f>
@@ -15437,7 +15539,7 @@
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E655" s="2" t="n">
         <f aca="false">A655 +1000</f>
@@ -15455,7 +15557,7 @@
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E656" s="2" t="n">
         <f aca="false">A656 +1000</f>
@@ -15473,7 +15575,7 @@
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E657" s="2" t="n">
         <f aca="false">A657 +1000</f>
@@ -15491,7 +15593,7 @@
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E658" s="2" t="n">
         <f aca="false">A658 +1000</f>
@@ -15509,7 +15611,7 @@
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E659" s="2" t="n">
         <f aca="false">A659 +1000</f>
@@ -15527,7 +15629,7 @@
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E660" s="2" t="n">
         <f aca="false">A660 +1000</f>
@@ -15545,7 +15647,7 @@
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E661" s="2" t="n">
         <f aca="false">A661 +1000</f>
@@ -15563,7 +15665,7 @@
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E662" s="2" t="n">
         <f aca="false">A662 +1000</f>
@@ -15581,7 +15683,7 @@
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E663" s="2" t="n">
         <f aca="false">A663 +1000</f>
@@ -15599,7 +15701,7 @@
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E664" s="2" t="n">
         <f aca="false">A664 +1000</f>
@@ -15617,7 +15719,7 @@
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E665" s="2" t="n">
         <f aca="false">A665 +1000</f>
@@ -15635,7 +15737,7 @@
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="E666" s="2" t="n">
         <f aca="false">A666 +1000</f>
@@ -15653,7 +15755,7 @@
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E667" s="2" t="n">
         <f aca="false">A667 +1000</f>
@@ -15671,7 +15773,7 @@
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E668" s="2" t="n">
         <f aca="false">A668 +1000</f>
@@ -15689,7 +15791,7 @@
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E669" s="2" t="n">
         <f aca="false">A669 +1000</f>
@@ -15707,7 +15809,7 @@
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E670" s="2" t="n">
         <f aca="false">A670 +1000</f>
@@ -15725,7 +15827,7 @@
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E671" s="2" t="n">
         <f aca="false">A671 +1000</f>
@@ -15743,7 +15845,7 @@
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E672" s="2" t="n">
         <f aca="false">A672 +1000</f>
@@ -15761,7 +15863,7 @@
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E673" s="2" t="n">
         <f aca="false">A673 +1000</f>
@@ -15779,7 +15881,7 @@
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E674" s="2" t="n">
         <f aca="false">A674 +1000</f>
@@ -15797,7 +15899,7 @@
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E675" s="2" t="n">
         <f aca="false">A675 +1000</f>
@@ -15815,7 +15917,7 @@
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E676" s="2" t="n">
         <f aca="false">A676 +1000</f>
@@ -15833,7 +15935,7 @@
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E677" s="2" t="n">
         <f aca="false">A677 +1000</f>
@@ -15851,7 +15953,7 @@
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E678" s="2" t="n">
         <f aca="false">A678 +1000</f>
@@ -15869,7 +15971,7 @@
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E679" s="2" t="n">
         <f aca="false">A679 +1000</f>
@@ -15887,7 +15989,7 @@
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E680" s="2" t="n">
         <f aca="false">A680 +1000</f>
@@ -15905,7 +16007,7 @@
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E681" s="2" t="n">
         <f aca="false">A681 +1000</f>
@@ -15923,7 +16025,7 @@
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E682" s="2" t="n">
         <f aca="false">A682 +1000</f>
@@ -15941,7 +16043,7 @@
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E683" s="2" t="n">
         <f aca="false">A683 +1000</f>
@@ -15959,7 +16061,7 @@
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E684" s="2" t="n">
         <f aca="false">A684 +1000</f>
@@ -15977,7 +16079,7 @@
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E685" s="2" t="n">
         <f aca="false">A685 +1000</f>
@@ -15995,7 +16097,7 @@
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E686" s="2" t="n">
         <f aca="false">A686 +1000</f>
@@ -16013,7 +16115,7 @@
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E687" s="2" t="n">
         <f aca="false">A687 +1000</f>
@@ -16031,7 +16133,7 @@
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E688" s="2" t="n">
         <f aca="false">A688 +1000</f>
@@ -16049,7 +16151,7 @@
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E689" s="2" t="n">
         <f aca="false">A689 +1000</f>
@@ -16067,7 +16169,7 @@
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E690" s="2" t="n">
         <f aca="false">A690 +1000</f>
@@ -16085,7 +16187,7 @@
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E691" s="2" t="n">
         <f aca="false">A691 +1000</f>
@@ -16103,7 +16205,7 @@
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E692" s="2" t="n">
         <f aca="false">A692 +1000</f>
@@ -16121,7 +16223,7 @@
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E693" s="2" t="n">
         <f aca="false">A693 +1000</f>
@@ -16139,7 +16241,7 @@
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E694" s="2" t="n">
         <f aca="false">A694 +1000</f>
@@ -16157,7 +16259,7 @@
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E695" s="2" t="n">
         <f aca="false">A695 +1000</f>
@@ -16175,7 +16277,7 @@
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E696" s="2" t="n">
         <f aca="false">A696 +1000</f>
@@ -16193,7 +16295,7 @@
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E697" s="2" t="n">
         <f aca="false">A697 +1000</f>
@@ -16211,7 +16313,7 @@
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E698" s="2" t="n">
         <f aca="false">A698 +1000</f>
@@ -16229,7 +16331,7 @@
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E699" s="2" t="n">
         <f aca="false">A699 +1000</f>
@@ -16247,7 +16349,7 @@
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E700" s="2" t="n">
         <f aca="false">A700 +1000</f>
@@ -16265,7 +16367,7 @@
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>4</v>
@@ -16289,7 +16391,7 @@
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>4</v>
@@ -16313,7 +16415,7 @@
     </row>
     <row r="703" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>4</v>
@@ -16337,7 +16439,7 @@
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>4</v>
@@ -16361,7 +16463,7 @@
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E705" s="2" t="n">
         <f aca="false">A705 +1000</f>
@@ -16379,7 +16481,7 @@
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E706" s="2" t="n">
         <f aca="false">A706 +1000</f>
@@ -16397,7 +16499,7 @@
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E707" s="2" t="n">
         <f aca="false">A707 +1000</f>
@@ -16415,7 +16517,7 @@
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E708" s="2" t="n">
         <f aca="false">A708 +1000</f>
@@ -16428,7 +16530,7 @@
         <v>4</v>
       </c>
       <c r="H708" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I708" s="2" t="n">
         <f aca="false">E708 +1000</f>
@@ -16442,7 +16544,7 @@
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E709" s="2" t="n">
         <f aca="false">A709 +1000</f>
@@ -16463,7 +16565,7 @@
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E710" s="2" t="n">
         <f aca="false">A710 +1000</f>
@@ -16481,7 +16583,7 @@
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E711" s="2" t="n">
         <f aca="false">A711 +1000</f>
@@ -16499,7 +16601,7 @@
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E712" s="2" t="n">
         <f aca="false">A712 +1000</f>
@@ -16517,7 +16619,7 @@
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E713" s="2" t="n">
         <f aca="false">A713 +1000</f>
@@ -16535,7 +16637,7 @@
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E714" s="2" t="n">
         <f aca="false">A714 +1000</f>
@@ -16553,7 +16655,7 @@
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E715" s="2" t="n">
         <f aca="false">A715 +1000</f>
@@ -16571,7 +16673,7 @@
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E716" s="2" t="n">
         <f aca="false">A716 +1000</f>
@@ -16589,7 +16691,7 @@
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E717" s="2" t="n">
         <f aca="false">A717 +1000</f>
@@ -16607,7 +16709,7 @@
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E718" s="2" t="n">
         <f aca="false">A718 +1000</f>
@@ -16625,7 +16727,7 @@
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E719" s="2" t="n">
         <f aca="false">A719 +1000</f>
@@ -16643,7 +16745,7 @@
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E720" s="2" t="n">
         <f aca="false">A720 +1000</f>
@@ -16661,7 +16763,7 @@
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E721" s="2" t="n">
         <f aca="false">A721 +1000</f>
@@ -16679,7 +16781,7 @@
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E722" s="2" t="n">
         <f aca="false">A722 +1000</f>
@@ -16697,7 +16799,7 @@
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E723" s="2" t="n">
         <f aca="false">A723 +1000</f>
@@ -16715,7 +16817,7 @@
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E724" s="2" t="n">
         <f aca="false">A724 +1000</f>
@@ -16733,7 +16835,7 @@
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E725" s="2" t="n">
         <f aca="false">A725 +1000</f>
@@ -16751,7 +16853,7 @@
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E726" s="2" t="n">
         <f aca="false">A726 +1000</f>
@@ -16769,7 +16871,7 @@
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E727" s="2" t="n">
         <f aca="false">A727 +1000</f>
@@ -16787,7 +16889,7 @@
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E728" s="2" t="n">
         <f aca="false">A728 +1000</f>
@@ -16805,7 +16907,7 @@
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E729" s="2" t="n">
         <f aca="false">A729 +1000</f>
@@ -16823,7 +16925,7 @@
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E730" s="2" t="n">
         <f aca="false">A730 +1000</f>
@@ -16841,7 +16943,7 @@
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E731" s="2" t="n">
         <f aca="false">A731 +1000</f>
@@ -16859,7 +16961,7 @@
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E732" s="2" t="n">
         <f aca="false">A732 +1000</f>
@@ -16877,7 +16979,7 @@
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E733" s="2" t="n">
         <f aca="false">A733 +1000</f>
@@ -16895,7 +16997,7 @@
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E734" s="2" t="n">
         <f aca="false">A734 +1000</f>
@@ -16913,7 +17015,7 @@
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E735" s="2" t="n">
         <f aca="false">A735 +1000</f>
@@ -16931,7 +17033,7 @@
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E736" s="2" t="n">
         <f aca="false">A736 +1000</f>
@@ -16949,7 +17051,7 @@
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E737" s="2" t="n">
         <f aca="false">A737 +1000</f>
@@ -16967,7 +17069,7 @@
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E738" s="2" t="n">
         <f aca="false">A738 +1000</f>
@@ -16985,7 +17087,7 @@
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E739" s="2" t="n">
         <f aca="false">A739 +1000</f>
@@ -17003,7 +17105,7 @@
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E740" s="2" t="n">
         <f aca="false">A740 +1000</f>
@@ -17021,7 +17123,7 @@
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E741" s="2" t="n">
         <f aca="false">A741 +1000</f>
@@ -17039,7 +17141,7 @@
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E742" s="2" t="n">
         <f aca="false">A742 +1000</f>
@@ -17057,7 +17159,7 @@
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E743" s="2" t="n">
         <f aca="false">A743 +1000</f>
@@ -17075,7 +17177,7 @@
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E744" s="2" t="n">
         <f aca="false">A744 +1000</f>
@@ -17093,7 +17195,7 @@
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E745" s="2" t="n">
         <f aca="false">A745 +1000</f>
@@ -17111,7 +17213,7 @@
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E746" s="2" t="n">
         <f aca="false">A746 +1000</f>
@@ -17129,7 +17231,7 @@
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E747" s="2" t="n">
         <f aca="false">A747 +1000</f>
@@ -17147,7 +17249,7 @@
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E748" s="2" t="n">
         <f aca="false">A748 +1000</f>
@@ -17165,7 +17267,7 @@
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E749" s="2" t="n">
         <f aca="false">A749 +1000</f>
@@ -17183,7 +17285,7 @@
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E750" s="2" t="n">
         <f aca="false">A750 +1000</f>
@@ -17201,7 +17303,7 @@
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E751" s="2" t="n">
         <f aca="false">A751 +1000</f>
@@ -17219,7 +17321,7 @@
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E752" s="2" t="n">
         <f aca="false">A752 +1000</f>
@@ -17237,7 +17339,7 @@
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E753" s="2" t="n">
         <f aca="false">A753 +1000</f>
@@ -17255,7 +17357,7 @@
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E754" s="2" t="n">
         <f aca="false">A754 +1000</f>
@@ -17273,7 +17375,7 @@
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E755" s="2" t="n">
         <f aca="false">A755 +1000</f>
@@ -17291,7 +17393,7 @@
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E756" s="2" t="n">
         <f aca="false">A756 +1000</f>
@@ -17309,7 +17411,7 @@
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E757" s="2" t="n">
         <f aca="false">A757 +1000</f>
@@ -17327,7 +17429,7 @@
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E758" s="2" t="n">
         <f aca="false">A758 +1000</f>
@@ -17345,7 +17447,7 @@
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E759" s="2" t="n">
         <f aca="false">A759 +1000</f>
@@ -17363,7 +17465,7 @@
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E760" s="2" t="n">
         <f aca="false">A760 +1000</f>
@@ -17381,7 +17483,7 @@
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E761" s="2" t="n">
         <f aca="false">A761 +1000</f>
@@ -17399,7 +17501,7 @@
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E762" s="2" t="n">
         <f aca="false">A762 +1000</f>
@@ -17417,7 +17519,7 @@
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E763" s="2" t="n">
         <f aca="false">A763 +1000</f>
@@ -17435,7 +17537,7 @@
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E764" s="2" t="n">
         <f aca="false">A764 +1000</f>
@@ -17453,7 +17555,7 @@
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E765" s="2" t="n">
         <f aca="false">A765 +1000</f>
@@ -17471,7 +17573,7 @@
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E766" s="2" t="n">
         <f aca="false">A766 +1000</f>
@@ -17489,7 +17591,7 @@
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E767" s="2" t="n">
         <f aca="false">A767 +1000</f>
@@ -17507,7 +17609,7 @@
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E768" s="2" t="n">
         <f aca="false">A768 +1000</f>
@@ -17525,7 +17627,7 @@
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E769" s="2" t="n">
         <f aca="false">A769 +1000</f>
@@ -17543,7 +17645,7 @@
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E770" s="2" t="n">
         <f aca="false">A770 +1000</f>
@@ -17561,7 +17663,7 @@
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E771" s="2" t="n">
         <f aca="false">A771 +1000</f>
@@ -17579,7 +17681,7 @@
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E772" s="2" t="n">
         <f aca="false">A772 +1000</f>
@@ -17597,7 +17699,7 @@
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="E773" s="2" t="n">
         <f aca="false">A773 +1000</f>
@@ -17615,7 +17717,7 @@
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E774" s="2" t="n">
         <f aca="false">A774 +1000</f>
@@ -17633,7 +17735,7 @@
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E775" s="2" t="n">
         <f aca="false">A775 +1000</f>
@@ -17651,7 +17753,7 @@
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E776" s="2" t="n">
         <f aca="false">A776 +1000</f>
@@ -17669,7 +17771,7 @@
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E777" s="2" t="n">
         <f aca="false">A777 +1000</f>
@@ -17687,7 +17789,7 @@
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E778" s="2" t="n">
         <f aca="false">A778 +1000</f>
@@ -17705,7 +17807,7 @@
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E779" s="2" t="n">
         <f aca="false">A779 +1000</f>
@@ -17723,7 +17825,7 @@
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E780" s="2" t="n">
         <f aca="false">A780 +1000</f>
@@ -17741,7 +17843,7 @@
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="1" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E781" s="2" t="n">
         <f aca="false">A781 +1000</f>
@@ -17759,12 +17861,21 @@
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E782" s="2" t="n">
         <f aca="false">A782 +1000</f>
         <v>1781</v>
       </c>
+      <c r="F782" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H782" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I782" s="2" t="n">
         <f aca="false">E782 +1000</f>
         <v>2781</v>
@@ -17777,7 +17888,7 @@
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E783" s="2" t="n">
         <f aca="false">A783 +1000</f>
@@ -17795,7 +17906,7 @@
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E784" s="2" t="n">
         <f aca="false">A784 +1000</f>
@@ -17813,7 +17924,7 @@
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E785" s="2" t="n">
         <f aca="false">A785 +1000</f>
@@ -17831,7 +17942,7 @@
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E786" s="2" t="n">
         <f aca="false">A786 +1000</f>
@@ -17849,7 +17960,7 @@
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E787" s="2" t="n">
         <f aca="false">A787 +1000</f>
@@ -17867,7 +17978,7 @@
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E788" s="2" t="n">
         <f aca="false">A788 +1000</f>
@@ -17885,7 +17996,7 @@
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E789" s="2" t="n">
         <f aca="false">A789 +1000</f>
@@ -17903,7 +18014,7 @@
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E790" s="2" t="n">
         <f aca="false">A790 +1000</f>
@@ -17921,7 +18032,7 @@
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E791" s="2" t="n">
         <f aca="false">A791 +1000</f>
@@ -17939,7 +18050,7 @@
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E792" s="2" t="n">
         <f aca="false">A792 +1000</f>
@@ -17957,7 +18068,7 @@
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E793" s="2" t="n">
         <f aca="false">A793 +1000</f>
@@ -17975,7 +18086,7 @@
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E794" s="2" t="n">
         <f aca="false">A794 +1000</f>
@@ -17993,7 +18104,7 @@
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E795" s="2" t="n">
         <f aca="false">A795 +1000</f>
@@ -18011,7 +18122,7 @@
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E796" s="2" t="n">
         <f aca="false">A796 +1000</f>
@@ -18029,7 +18140,16 @@
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
+      </c>
+      <c r="B797" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C797" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D797" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E797" s="2" t="n">
         <f aca="false">A797 +1000</f>
@@ -18047,7 +18167,7 @@
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E798" s="2" t="n">
         <f aca="false">A798 +1000</f>
@@ -18065,7 +18185,7 @@
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E799" s="2" t="n">
         <f aca="false">A799 +1000</f>
@@ -18083,7 +18203,7 @@
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E800" s="2" t="n">
         <f aca="false">A800 +1000</f>
@@ -18101,7 +18221,7 @@
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E801" s="2" t="n">
         <f aca="false">A801 +1000</f>
@@ -18119,7 +18239,7 @@
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E802" s="2" t="n">
         <f aca="false">A802 +1000</f>
@@ -18137,7 +18257,7 @@
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E803" s="2" t="n">
         <f aca="false">A803 +1000</f>
@@ -18155,7 +18275,7 @@
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E804" s="2" t="n">
         <f aca="false">A804 +1000</f>
@@ -18173,7 +18293,7 @@
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E805" s="2" t="n">
         <f aca="false">A805 +1000</f>
@@ -18191,7 +18311,7 @@
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="E806" s="2" t="n">
         <f aca="false">A806 +1000</f>
@@ -18209,7 +18329,7 @@
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E807" s="2" t="n">
         <f aca="false">A807 +1000</f>
@@ -18227,7 +18347,7 @@
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E808" s="2" t="n">
         <f aca="false">A808 +1000</f>
@@ -18245,7 +18365,7 @@
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E809" s="2" t="n">
         <f aca="false">A809 +1000</f>
@@ -18263,7 +18383,7 @@
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E810" s="2" t="n">
         <f aca="false">A810 +1000</f>
@@ -18281,7 +18401,7 @@
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E811" s="2" t="n">
         <f aca="false">A811 +1000</f>
@@ -18299,7 +18419,7 @@
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E812" s="2" t="n">
         <f aca="false">A812 +1000</f>
@@ -18317,7 +18437,7 @@
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E813" s="2" t="n">
         <f aca="false">A813 +1000</f>
@@ -18335,7 +18455,7 @@
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E814" s="2" t="n">
         <f aca="false">A814 +1000</f>
@@ -18353,7 +18473,7 @@
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E815" s="2" t="n">
         <f aca="false">A815 +1000</f>
@@ -18371,7 +18491,7 @@
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E816" s="2" t="n">
         <f aca="false">A816 +1000</f>
@@ -18389,7 +18509,7 @@
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E817" s="2" t="n">
         <f aca="false">A817 +1000</f>
@@ -18407,7 +18527,7 @@
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E818" s="2" t="n">
         <f aca="false">A818 +1000</f>
@@ -18425,7 +18545,7 @@
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E819" s="2" t="n">
         <f aca="false">A819 +1000</f>
@@ -18443,7 +18563,7 @@
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="1" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E820" s="2" t="n">
         <f aca="false">A820 +1000</f>
@@ -18461,7 +18581,7 @@
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="1" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E821" s="2" t="n">
         <f aca="false">A821 +1000</f>
@@ -18479,7 +18599,7 @@
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="1" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E822" s="2" t="n">
         <f aca="false">A822 +1000</f>
@@ -18497,7 +18617,7 @@
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E823" s="2" t="n">
         <f aca="false">A823 +1000</f>
@@ -18515,7 +18635,7 @@
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="1" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E824" s="2" t="n">
         <f aca="false">A824 +1000</f>
@@ -18533,7 +18653,7 @@
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E825" s="2" t="n">
         <f aca="false">A825 +1000</f>
@@ -18551,7 +18671,7 @@
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E826" s="2" t="n">
         <f aca="false">A826 +1000</f>
@@ -18569,7 +18689,7 @@
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E827" s="2" t="n">
         <f aca="false">A827 +1000</f>
@@ -18587,7 +18707,7 @@
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E828" s="2" t="n">
         <f aca="false">A828 +1000</f>
@@ -18605,7 +18725,7 @@
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E829" s="2" t="n">
         <f aca="false">A829 +1000</f>
@@ -18623,7 +18743,7 @@
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E830" s="2" t="n">
         <f aca="false">A830 +1000</f>
@@ -18641,7 +18761,7 @@
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E831" s="2" t="n">
         <f aca="false">A831 +1000</f>
@@ -18659,7 +18779,7 @@
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="1" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E832" s="2" t="n">
         <f aca="false">A832 +1000</f>
@@ -18677,7 +18797,7 @@
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="1" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E833" s="2" t="n">
         <f aca="false">A833 +1000</f>
@@ -18695,7 +18815,7 @@
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E834" s="2" t="n">
         <f aca="false">A834 +1000</f>
@@ -18713,7 +18833,7 @@
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E835" s="2" t="n">
         <f aca="false">A835 +1000</f>
@@ -18731,7 +18851,7 @@
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E836" s="2" t="n">
         <f aca="false">A836 +1000</f>
@@ -18749,7 +18869,7 @@
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E837" s="2" t="n">
         <f aca="false">A837 +1000</f>
@@ -18767,7 +18887,7 @@
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E838" s="2" t="n">
         <f aca="false">A838 +1000</f>
@@ -18785,7 +18905,7 @@
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="1" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E839" s="2" t="n">
         <f aca="false">A839 +1000</f>
@@ -18803,7 +18923,7 @@
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E840" s="2" t="n">
         <f aca="false">A840 +1000</f>
@@ -18821,7 +18941,7 @@
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E841" s="2" t="n">
         <f aca="false">A841 +1000</f>
@@ -18839,7 +18959,7 @@
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E842" s="2" t="n">
         <f aca="false">A842 +1000</f>
@@ -18857,7 +18977,7 @@
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E843" s="2" t="n">
         <f aca="false">A843 +1000</f>
@@ -18875,7 +18995,7 @@
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E844" s="2" t="n">
         <f aca="false">A844 +1000</f>
@@ -18893,7 +19013,7 @@
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E845" s="2" t="n">
         <f aca="false">A845 +1000</f>
@@ -18911,7 +19031,7 @@
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E846" s="2" t="n">
         <f aca="false">A846 +1000</f>
@@ -18929,7 +19049,7 @@
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B847" s="3" t="s">
         <v>4</v>
@@ -18938,7 +19058,7 @@
         <v>4</v>
       </c>
       <c r="D847" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E847" s="2" t="n">
         <f aca="false">A847 +1000</f>
@@ -18956,7 +19076,7 @@
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E848" s="2" t="n">
         <f aca="false">A848 +1000</f>
@@ -18974,7 +19094,7 @@
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E849" s="2" t="n">
         <f aca="false">A849 +1000</f>
@@ -18992,7 +19112,7 @@
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="E850" s="2" t="n">
         <f aca="false">A850 +1000</f>
@@ -19010,7 +19130,7 @@
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E851" s="2" t="n">
         <f aca="false">A851 +1000</f>
@@ -19028,7 +19148,7 @@
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E852" s="2" t="n">
         <f aca="false">A852 +1000</f>
@@ -19046,7 +19166,7 @@
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="E853" s="2" t="n">
         <f aca="false">A853 +1000</f>
@@ -19064,7 +19184,7 @@
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E854" s="2" t="n">
         <f aca="false">A854 +1000</f>
@@ -19082,7 +19202,7 @@
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E855" s="2" t="n">
         <f aca="false">A855 +1000</f>
@@ -19100,7 +19220,7 @@
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="E856" s="2" t="n">
         <f aca="false">A856 +1000</f>
@@ -19118,7 +19238,7 @@
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E857" s="2" t="n">
         <f aca="false">A857 +1000</f>
@@ -19136,7 +19256,7 @@
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E858" s="2" t="n">
         <f aca="false">A858 +1000</f>
@@ -19154,7 +19274,7 @@
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E859" s="2" t="n">
         <f aca="false">A859 +1000</f>
@@ -19172,7 +19292,7 @@
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E860" s="2" t="n">
         <f aca="false">A860 +1000</f>
@@ -19190,7 +19310,7 @@
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E861" s="2" t="n">
         <f aca="false">A861 +1000</f>
@@ -19208,7 +19328,7 @@
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E862" s="2" t="n">
         <f aca="false">A862 +1000</f>
@@ -19226,7 +19346,7 @@
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E863" s="2" t="n">
         <f aca="false">A863 +1000</f>
@@ -19244,7 +19364,7 @@
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E864" s="2" t="n">
         <f aca="false">A864 +1000</f>
@@ -19262,7 +19382,7 @@
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E865" s="2" t="n">
         <f aca="false">A865 +1000</f>
@@ -19280,7 +19400,7 @@
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E866" s="2" t="n">
         <f aca="false">A866 +1000</f>
@@ -19298,7 +19418,7 @@
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E867" s="2" t="n">
         <f aca="false">A867 +1000</f>
@@ -19316,7 +19436,7 @@
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E868" s="2" t="n">
         <f aca="false">A868 +1000</f>
@@ -19334,7 +19454,7 @@
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E869" s="2" t="n">
         <f aca="false">A869 +1000</f>
@@ -19352,7 +19472,7 @@
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E870" s="2" t="n">
         <f aca="false">A870 +1000</f>
@@ -19370,7 +19490,7 @@
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E871" s="2" t="n">
         <f aca="false">A871 +1000</f>
@@ -19388,7 +19508,7 @@
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E872" s="2" t="n">
         <f aca="false">A872 +1000</f>
@@ -19406,7 +19526,7 @@
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E873" s="2" t="n">
         <f aca="false">A873 +1000</f>
@@ -19424,7 +19544,7 @@
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E874" s="2" t="n">
         <f aca="false">A874 +1000</f>
@@ -19442,7 +19562,7 @@
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E875" s="2" t="n">
         <f aca="false">A875 +1000</f>
@@ -19460,7 +19580,7 @@
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E876" s="2" t="n">
         <f aca="false">A876 +1000</f>
@@ -19478,7 +19598,7 @@
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E877" s="2" t="n">
         <f aca="false">A877 +1000</f>
@@ -19496,7 +19616,7 @@
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E878" s="2" t="n">
         <f aca="false">A878 +1000</f>
@@ -19514,7 +19634,7 @@
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E879" s="2" t="n">
         <f aca="false">A879 +1000</f>
@@ -19532,7 +19652,7 @@
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E880" s="2" t="n">
         <f aca="false">A880 +1000</f>
@@ -19550,7 +19670,7 @@
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E881" s="2" t="n">
         <f aca="false">A881 +1000</f>
@@ -19568,7 +19688,7 @@
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E882" s="2" t="n">
         <f aca="false">A882 +1000</f>
@@ -19586,7 +19706,7 @@
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E883" s="2" t="n">
         <f aca="false">A883 +1000</f>
@@ -19604,7 +19724,7 @@
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E884" s="2" t="n">
         <f aca="false">A884 +1000</f>
@@ -19622,7 +19742,7 @@
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E885" s="2" t="n">
         <f aca="false">A885 +1000</f>
@@ -19640,7 +19760,7 @@
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E886" s="2" t="n">
         <f aca="false">A886 +1000</f>
@@ -19658,7 +19778,7 @@
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E887" s="2" t="n">
         <f aca="false">A887 +1000</f>
@@ -19676,7 +19796,7 @@
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E888" s="2" t="n">
         <f aca="false">A888 +1000</f>
@@ -19694,7 +19814,7 @@
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E889" s="2" t="n">
         <f aca="false">A889 +1000</f>
@@ -19712,7 +19832,7 @@
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E890" s="2" t="n">
         <f aca="false">A890 +1000</f>
@@ -19730,7 +19850,7 @@
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E891" s="2" t="n">
         <f aca="false">A891 +1000</f>
@@ -19748,7 +19868,7 @@
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E892" s="2" t="n">
         <f aca="false">A892 +1000</f>
@@ -19766,7 +19886,7 @@
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E893" s="2" t="n">
         <f aca="false">A893 +1000</f>
@@ -19784,7 +19904,7 @@
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E894" s="2" t="n">
         <f aca="false">A894 +1000</f>
@@ -19802,7 +19922,7 @@
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E895" s="2" t="n">
         <f aca="false">A895 +1000</f>
@@ -19820,7 +19940,7 @@
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E896" s="2" t="n">
         <f aca="false">A896 +1000</f>
@@ -19838,7 +19958,7 @@
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E897" s="2" t="n">
         <f aca="false">A897 +1000</f>
@@ -19856,7 +19976,7 @@
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E898" s="2" t="n">
         <f aca="false">A898 +1000</f>
@@ -19874,7 +19994,7 @@
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E899" s="2" t="n">
         <f aca="false">A899 +1000</f>
@@ -19892,7 +20012,7 @@
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E900" s="2" t="n">
         <f aca="false">A900 +1000</f>
@@ -19910,7 +20030,7 @@
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E901" s="2" t="n">
         <f aca="false">A901 +1000</f>
@@ -19928,7 +20048,7 @@
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E902" s="2" t="n">
         <f aca="false">A902 +1000</f>
@@ -19946,7 +20066,7 @@
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E903" s="2" t="n">
         <f aca="false">A903 +1000</f>
@@ -19964,12 +20084,21 @@
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E904" s="2" t="n">
         <f aca="false">A904 +1000</f>
         <v>1903</v>
       </c>
+      <c r="F904" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G904" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H904" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I904" s="2" t="n">
         <f aca="false">E904 +1000</f>
         <v>2903</v>
@@ -19982,7 +20111,7 @@
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B905" s="3" t="s">
         <v>4</v>
@@ -20009,7 +20138,7 @@
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E906" s="2" t="n">
         <f aca="false">A906 +1000</f>
@@ -20027,7 +20156,7 @@
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E907" s="2" t="n">
         <f aca="false">A907 +1000</f>
@@ -20045,7 +20174,7 @@
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E908" s="2" t="n">
         <f aca="false">A908 +1000</f>
@@ -20063,7 +20192,7 @@
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E909" s="2" t="n">
         <f aca="false">A909 +1000</f>
@@ -20081,7 +20210,7 @@
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E910" s="2" t="n">
         <f aca="false">A910 +1000</f>
@@ -20099,7 +20228,7 @@
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E911" s="2" t="n">
         <f aca="false">A911 +1000</f>
@@ -20117,7 +20246,7 @@
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E912" s="2" t="n">
         <f aca="false">A912 +1000</f>
@@ -20135,7 +20264,7 @@
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E913" s="2" t="n">
         <f aca="false">A913 +1000</f>
@@ -20153,7 +20282,7 @@
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="1" t="s">
-       